--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,6 +60,11 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -132,48 +137,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -552,13 +556,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,7 +580,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Pièce</t>
@@ -592,6 +597,11 @@
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>URSSAF 12,4 %</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Marge</t>
         </is>
@@ -611,7 +621,11 @@
         <f>'Stock complet'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="7">
+        <f>'Stock complet'!L5</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
         <f>'Stock complet'!D5</f>
         <v/>
       </c>
@@ -630,83 +644,103 @@
         <f>'Stock complet'!C6</f>
         <v/>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="7">
+        <f>'Stock complet'!L6</f>
+        <v/>
+      </c>
+      <c r="E6" s="5">
         <f>'Stock complet'!D6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Bottes Forma Legacy Waterproof</t>
         </is>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="9">
         <f>'Stock complet'!B7</f>
         <v/>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="10">
         <f>'Stock complet'!C7</f>
         <v/>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="11">
+        <f>'Stock complet'!L7</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
         <f>'Stock complet'!D7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Robe Elisabetta Franchi ivoire, viscose</t>
         </is>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="9">
         <f>'Stock complet'!B8</f>
         <v/>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>'Stock complet'!C8</f>
         <v/>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="11">
+        <f>'Stock complet'!L8</f>
+        <v/>
+      </c>
+      <c r="E8" s="9">
         <f>'Stock complet'!D8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Ballerines Hogan 186 Zeppa Fashion</t>
         </is>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="9">
         <f>'Stock complet'!B9</f>
         <v/>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <f>'Stock complet'!C9</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
+        <f>'Stock complet'!L9</f>
+        <v/>
+      </c>
+      <c r="E9" s="9">
         <f>'Stock complet'!D9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Jupe Sonia Rykiel midi twill cerises</t>
         </is>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <f>'Stock complet'!B10</f>
         <v/>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <f>'Stock complet'!C10</f>
         <v/>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
+        <f>'Stock complet'!L10</f>
+        <v/>
+      </c>
+      <c r="E10" s="9">
         <f>'Stock complet'!D10</f>
         <v/>
       </c>
@@ -725,83 +759,103 @@
         <f>'Stock complet'!C11</f>
         <v/>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="7">
+        <f>'Stock complet'!L11</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
         <f>'Stock complet'!D11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>BMW Overall ProRain unisexe noir</t>
         </is>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="9">
         <f>'Stock complet'!B12</f>
         <v/>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="10">
         <f>'Stock complet'!C12</f>
         <v/>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="11">
+        <f>'Stock complet'!L12</f>
+        <v/>
+      </c>
+      <c r="E12" s="9">
         <f>'Stock complet'!D12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Baskets adidas by Stella McCartney UltraBoost 21</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <f>'Stock complet'!B13</f>
         <v/>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <f>'Stock complet'!C13</f>
         <v/>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
+        <f>'Stock complet'!L13</f>
+        <v/>
+      </c>
+      <c r="E13" s="9">
         <f>'Stock complet'!D13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Blazer Karl Lagerfeld punto noir</t>
         </is>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="9">
         <f>'Stock complet'!B14</f>
         <v/>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <f>'Stock complet'!C14</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="11">
+        <f>'Stock complet'!L14</f>
+        <v/>
+      </c>
+      <c r="E14" s="9">
         <f>'Stock complet'!D14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Salomon X Ultra 5 Mid GTX</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
         <f>'Stock complet'!B15</f>
         <v/>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <f>'Stock complet'!C15</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
+        <f>'Stock complet'!L15</f>
+        <v/>
+      </c>
+      <c r="E15" s="9">
         <f>'Stock complet'!D15</f>
         <v/>
       </c>
@@ -820,102 +874,126 @@
         <f>'Stock complet'!C16</f>
         <v/>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="7">
+        <f>'Stock complet'!L16</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
         <f>'Stock complet'!D16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Robe Sandro Noaim blanche</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="9">
         <f>'Stock complet'!B17</f>
         <v/>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="10">
         <f>'Stock complet'!C17</f>
         <v/>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="11">
+        <f>'Stock complet'!L17</f>
+        <v/>
+      </c>
+      <c r="E17" s="9">
         <f>'Stock complet'!D17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Ballerines Massimo Dutti cuir rouge</t>
         </is>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <f>'Stock complet'!B18</f>
         <v/>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="10">
         <f>'Stock complet'!C18</f>
         <v/>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="11">
+        <f>'Stock complet'!L18</f>
+        <v/>
+      </c>
+      <c r="E18" s="9">
         <f>'Stock complet'!D18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Robe bustier Chiara Ferragni noire</t>
         </is>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="9">
         <f>'Stock complet'!B19</f>
         <v/>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="10">
         <f>'Stock complet'!C19</f>
         <v/>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="11">
+        <f>'Stock complet'!L19</f>
+        <v/>
+      </c>
+      <c r="E19" s="9">
         <f>'Stock complet'!D19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Robe Pier Antonio Gaspari bleu marine</t>
         </is>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="9">
         <f>'Stock complet'!B20</f>
         <v/>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="10">
         <f>'Stock complet'!C20</f>
         <v/>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="11">
+        <f>'Stock complet'!L20</f>
+        <v/>
+      </c>
+      <c r="E20" s="9">
         <f>'Stock complet'!D20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Baskets Geox gris / argent</t>
         </is>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="9">
         <f>'Stock complet'!B21</f>
         <v/>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="10">
         <f>'Stock complet'!C21</f>
         <v/>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="11">
+        <f>'Stock complet'!L21</f>
+        <v/>
+      </c>
+      <c r="E21" s="9">
         <f>'Stock complet'!D21</f>
         <v/>
       </c>
@@ -934,180 +1012,227 @@
         <f>'Stock complet'!C22</f>
         <v/>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="7">
+        <f>'Stock complet'!L22</f>
+        <v/>
+      </c>
+      <c r="E22" s="5">
         <f>'Stock complet'!D22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Plein Sport montante blanc / violet</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="9">
         <f>'Stock complet'!B23</f>
         <v/>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="10">
         <f>'Stock complet'!C23</f>
         <v/>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="11">
+        <f>'Stock complet'!L23</f>
+        <v/>
+      </c>
+      <c r="E23" s="9">
         <f>'Stock complet'!D23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Short ba&amp;sh Fegor lightusedblue</t>
         </is>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="9">
         <f>'Stock complet'!B24</f>
         <v/>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="10">
         <f>'Stock complet'!C24</f>
         <v/>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="11">
+        <f>'Stock complet'!L24</f>
+        <v/>
+      </c>
+      <c r="E24" s="9">
         <f>'Stock complet'!D24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>New Balance GS 1906 Alkaline Green</t>
         </is>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="9">
         <f>'Stock complet'!B25</f>
         <v/>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="10">
         <f>'Stock complet'!C25</f>
         <v/>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="11">
+        <f>'Stock complet'!L25</f>
+        <v/>
+      </c>
+      <c r="E25" s="9">
         <f>'Stock complet'!D25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Baskets Emporio Armani bleu lavande</t>
         </is>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="9">
         <f>'Stock complet'!B26</f>
         <v/>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="10">
         <f>'Stock complet'!C26</f>
         <v/>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="11">
+        <f>'Stock complet'!L26</f>
+        <v/>
+      </c>
+      <c r="E26" s="9">
         <f>'Stock complet'!D26</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>New Balance BB80 blanc / marine</t>
         </is>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="9">
         <f>'Stock complet'!B27</f>
         <v/>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="10">
         <f>'Stock complet'!C27</f>
         <v/>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="11">
+        <f>'Stock complet'!L27</f>
+        <v/>
+      </c>
+      <c r="E27" s="9">
         <f>'Stock complet'!D27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Tommy Jeans baskets basses noir / blanc</t>
         </is>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="9">
         <f>'Stock complet'!B28</f>
         <v/>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="10">
         <f>'Stock complet'!C28</f>
         <v/>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="11">
+        <f>'Stock complet'!L28</f>
+        <v/>
+      </c>
+      <c r="E28" s="9">
         <f>'Stock complet'!D28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>New Balance 650 blanche montante</t>
         </is>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="9">
         <f>'Stock complet'!B29</f>
         <v/>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="10">
         <f>'Stock complet'!C29</f>
         <v/>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="11">
+        <f>'Stock complet'!L29</f>
+        <v/>
+      </c>
+      <c r="E29" s="9">
         <f>'Stock complet'!D29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Adidas Yeezy 700 V3 Mono Safflower</t>
         </is>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="9">
         <f>'Stock complet'!B30</f>
         <v/>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="10">
         <f>'Stock complet'!C30</f>
         <v/>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="11">
+        <f>'Stock complet'!L30</f>
+        <v/>
+      </c>
+      <c r="E30" s="9">
         <f>'Stock complet'!D30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="13">
         <f>SUM(B5:B30)</f>
         <v/>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="13">
         <f>SUM(C5:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="13">
         <f>SUM(D5:D30)</f>
         <v/>
+      </c>
+      <c r="E31" s="13">
+        <f>SUM(E5:E30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP sur le prix encaissé. À provisionner à chaque vente.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1162,107 +1287,107 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Pièce</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Coût total</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>PRIX DE VENTE</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Marge nette</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Rendement</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Nb</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Coût / article</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Prix / article</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Marge / article</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Prix marché</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Écart au marché</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>URSSAF + CFP</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Frais carte</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Taille</t>
         </is>
       </c>
-      <c r="P4" s="12" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>État</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Source du prix marché</t>
         </is>
       </c>
-      <c r="R4" s="12" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="S4" s="12" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>Mode de vente</t>
         </is>
       </c>
-      <c r="T4" s="12" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="U4" s="12" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
@@ -1274,7 +1399,7 @@
           <t>Adidas Predator Edge.1 TF ×2</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="14" t="n">
         <v>40</v>
       </c>
       <c r="C5" s="6" t="n">
@@ -1284,11 +1409,11 @@
         <f>IF($C5="","",$C5-$B5-$L5-$M5)</f>
         <v/>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="15">
         <f>IF($D5="","",$D5/$B5)</f>
         <v/>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="16" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="5">
@@ -1303,10 +1428,10 @@
         <f>IF($D5="","",$D5/$F5)</f>
         <v/>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>220</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="15">
         <f>IF(OR($J5="",$C5=""),"",$C5/$J5-1)</f>
         <v/>
       </c>
@@ -1333,7 +1458,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q5" s="16" t="inlineStr">
+      <c r="Q5" s="17" t="inlineStr">
         <is>
           <t>~110 € la paire</t>
         </is>
@@ -1365,7 +1490,7 @@
           <t>Lot 20 sandales et tongs (Relife, Tommy, Chattawak, Malabar)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <v>100.7</v>
       </c>
       <c r="C6" s="6" t="n">
@@ -1375,11 +1500,11 @@
         <f>IF($C6="","",$C6-$B6-$L6-$M6)</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="15">
         <f>IF($D6="","",$D6/$B6)</f>
         <v/>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="16" t="n">
         <v>20</v>
       </c>
       <c r="G6" s="5">
@@ -1394,10 +1519,10 @@
         <f>IF($D6="","",$D6/$F6)</f>
         <v/>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="14" t="n">
         <v>400</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="15">
         <f>IF(OR($J6="",$C6=""),"",$C6/$J6-1)</f>
         <v/>
       </c>
@@ -1424,7 +1549,7 @@
           <t>Neuves</t>
         </is>
       </c>
-      <c r="Q6" s="16" t="inlineStr">
+      <c r="Q6" s="17" t="inlineStr">
         <is>
           <t>~400 € valeur boutique du lot</t>
         </is>
@@ -1451,360 +1576,360 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Bottes Forma Legacy Waterproof</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>76</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <v>159</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="10">
         <f>IF($C7="","",$C7-$B7-$L7-$M7)</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>IF($D7="","",$D7/$B7)</f>
         <v/>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="9">
         <f>$B7/$F7</f>
         <v/>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="9">
         <f>IF($C7="","",$C7/$F7)</f>
         <v/>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="9">
         <f>IF($D7="","",$D7/$F7)</f>
         <v/>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="18" t="n">
         <v>172.49</v>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="19">
         <f>IF(OR($J7="",$C7=""),"",$C7/$J7-1)</f>
         <v/>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="9">
         <f>IF($C7="","",$C7*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="9">
         <f>IF($C7="","",$C7*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Neuves</t>
         </is>
       </c>
-      <c r="Q7" s="20" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>172,49 € Dafy Moto</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>Boutique + Vinted + Leboncoin</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T7" s="7" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>À recevoir</t>
         </is>
       </c>
-      <c r="U7" s="7" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Robe Elisabetta Franchi ivoire, viscose</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>26</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="10">
         <f>IF($C8="","",$C8-$B8-$L8-$M8)</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>IF($D8="","",$D8/$B8)</f>
         <v/>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="9">
         <f>$B8/$F8</f>
         <v/>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="9">
         <f>IF($C8="","",$C8/$F8)</f>
         <v/>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="9">
         <f>IF($D8="","",$D8/$F8)</f>
         <v/>
       </c>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="18">
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="19">
         <f>IF(OR($J8="",$C8=""),"",$C8/$J8-1)</f>
         <v/>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="9">
         <f>IF($C8="","",$C8*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="9">
         <f>IF($C8="","",$C8*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>46 IT / 42 FR</t>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="P8" s="8" t="inlineStr">
         <is>
           <t>Neuve avec étiquette</t>
         </is>
       </c>
-      <c r="Q8" s="20" t="inlineStr">
+      <c r="Q8" s="21" t="inlineStr">
         <is>
           <t>Outlet officiel −80 %</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="R8" s="8" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T8" s="7" t="inlineStr">
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>Reçue</t>
         </is>
       </c>
-      <c r="U8" s="7" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Ballerines Hogan 186 Zeppa Fashion</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="10">
         <f>IF($C9="","",$C9-$B9-$L9-$M9)</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>IF($D9="","",$D9/$B9)</f>
         <v/>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="9">
         <f>$B9/$F9</f>
         <v/>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="9">
         <f>IF($C9="","",$C9/$F9)</f>
         <v/>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="9">
         <f>IF($D9="","",$D9/$F9)</f>
         <v/>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <v>83</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="19">
         <f>IF(OR($J9="",$C9=""),"",$C9/$J9-1)</f>
         <v/>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="9">
         <f>IF($C9="","",$C9*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="9">
         <f>IF($C9="","",$C9*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="P9" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q9" s="20" t="inlineStr">
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>83 € Lyst</t>
         </is>
       </c>
-      <c r="R9" s="7" t="inlineStr">
+      <c r="R9" s="8" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T9" s="7" t="inlineStr">
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U9" s="7" t="inlineStr">
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Jupe Sonia Rykiel midi twill cerises</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>42.8</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="10">
         <f>IF($C10="","",$C10-$B10-$L10-$M10)</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>IF($D10="","",$D10/$B10)</f>
         <v/>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <f>$B10/$F10</f>
         <v/>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <f>IF($C10="","",$C10/$F10)</f>
         <v/>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="9">
         <f>IF($D10="","",$D10/$F10)</f>
         <v/>
       </c>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="18">
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="19">
         <f>IF(OR($J10="",$C10=""),"",$C10/$J10-1)</f>
         <v/>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="9">
         <f>IF($C10="","",$C10*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="9">
         <f>IF($C10="","",$C10*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="O10" s="8" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="P10" s="8" t="inlineStr">
         <is>
           <t>Neuve avec étiquette</t>
         </is>
       </c>
-      <c r="Q10" s="20" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>Jaiio −80 % · marque liquidée en 2019</t>
         </is>
       </c>
-      <c r="R10" s="7" t="inlineStr">
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T10" s="7" t="inlineStr">
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>Reçue</t>
         </is>
       </c>
-      <c r="U10" s="7" t="inlineStr">
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
@@ -1816,7 +1941,7 @@
           <t>Morgan — 6 vêtements femme</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="6" t="n">
@@ -1826,11 +1951,11 @@
         <f>IF($C11="","",$C11-$B11-$L11-$M11)</f>
         <v/>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="15">
         <f>IF($D11="","",$D11/$B11)</f>
         <v/>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="16" t="n">
         <v>6</v>
       </c>
       <c r="G11" s="5">
@@ -1845,8 +1970,8 @@
         <f>IF($D11="","",$D11/$F11)</f>
         <v/>
       </c>
-      <c r="J11" s="22" t="n"/>
-      <c r="K11" s="14">
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="15">
         <f>IF(OR($J11="",$C11=""),"",$C11/$J11-1)</f>
         <v/>
       </c>
@@ -1873,7 +1998,7 @@
           <t>Neufs avec étiquette</t>
         </is>
       </c>
-      <c r="Q11" s="16" t="inlineStr">
+      <c r="Q11" s="17" t="inlineStr">
         <is>
           <t>Modz −50 % · Once Again −80 %</t>
         </is>
@@ -1900,362 +2025,362 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>BMW Overall ProRain unisexe noir</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>82.61</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>139</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="10">
         <f>IF($C12="","",$C12-$B12-$L12-$M12)</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>IF($D12="","",$D12/$B12)</f>
         <v/>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="9">
         <f>$B12/$F12</f>
         <v/>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="9">
         <f>IF($C12="","",$C12/$F12)</f>
         <v/>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="9">
         <f>IF($D12="","",$D12/$F12)</f>
         <v/>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="18" t="n">
         <v>170</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="19">
         <f>IF(OR($J12="",$C12=""),"",$C12/$J12-1)</f>
         <v/>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="9">
         <f>IF($C12="","",$C12*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="9">
         <f>IF($C12="","",$C12*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>Neuf</t>
         </is>
       </c>
-      <c r="Q12" s="20" t="inlineStr">
+      <c r="Q12" s="21" t="inlineStr">
         <is>
           <t>170 € coloris noir</t>
         </is>
       </c>
-      <c r="R12" s="7" t="inlineStr">
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T12" s="7" t="inlineStr">
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>À recevoir</t>
         </is>
       </c>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Baskets adidas by Stella McCartney UltraBoost 21</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="10">
         <f>IF($C13="","",$C13-$B13-$L13-$M13)</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>IF($D13="","",$D13/$B13)</f>
         <v/>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="9">
         <f>$B13/$F13</f>
         <v/>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="9">
         <f>IF($C13="","",$C13/$F13)</f>
         <v/>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="9">
         <f>IF($D13="","",$D13/$F13)</f>
         <v/>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="18" t="n">
         <v>94</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="19">
         <f>IF(OR($J13="",$C13=""),"",$C13/$J13-1)</f>
         <v/>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="9">
         <f>IF($C13="","",$C13*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="9">
         <f>IF($C13="","",$C13*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q13" s="20" t="inlineStr">
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>94 € eBay.de</t>
         </is>
       </c>
-      <c r="R13" s="7" t="inlineStr">
+      <c r="R13" s="8" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T13" s="7" t="inlineStr">
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U13" s="7" t="inlineStr">
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Blazer Karl Lagerfeld punto noir</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>45</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="10">
         <f>IF($C14="","",$C14-$B14-$L14-$M14)</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>IF($D14="","",$D14/$B14)</f>
         <v/>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <f>$B14/$F14</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>IF($C14="","",$C14/$F14)</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f>IF($D14="","",$D14/$F14)</f>
         <v/>
       </c>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="18">
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="19">
         <f>IF(OR($J14="",$C14=""),"",$C14/$J14-1)</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="9">
         <f>IF($C14="","",$C14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="9">
         <f>IF($C14="","",$C14*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>36 FR / IT 40</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Neuf avec étiquette</t>
         </is>
       </c>
-      <c r="Q14" s="20" t="inlineStr">
+      <c r="Q14" s="21" t="inlineStr">
         <is>
           <t>Otrium outlet · Lyst dès 50 €</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr">
+      <c r="R14" s="8" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T14" s="7" t="inlineStr">
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>Reçu</t>
         </is>
       </c>
-      <c r="U14" s="7" t="inlineStr">
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Salomon X Ultra 5 Mid GTX</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="10">
         <f>IF($C15="","",$C15-$B15-$L15-$M15)</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>IF($D15="","",$D15/$B15)</f>
         <v/>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <f>$B15/$F15</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <f>IF($C15="","",$C15/$F15)</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <f>IF($D15="","",$D15/$F15)</f>
         <v/>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="18" t="n">
         <v>116</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="19">
         <f>IF(OR($J15="",$C15=""),"",$C15/$J15-1)</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="9">
         <f>IF($C15="","",$C15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="9">
         <f>IF($C15="","",$C15*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N15" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="P15" s="8" t="inlineStr">
         <is>
           <t>Neuves</t>
         </is>
       </c>
-      <c r="Q15" s="20" t="inlineStr">
+      <c r="Q15" s="21" t="inlineStr">
         <is>
           <t>116 €</t>
         </is>
       </c>
-      <c r="R15" s="7" t="inlineStr">
+      <c r="R15" s="8" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T15" s="7" t="inlineStr">
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U15" s="7" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
@@ -2267,7 +2392,7 @@
           <t>Mrs.Ertha — gilets de flottaison 3-6 ans</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>37.8</v>
       </c>
       <c r="C16" s="6" t="n">
@@ -2277,11 +2402,11 @@
         <f>IF($C16="","",$C16-$B16-$L16-$M16)</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="15">
         <f>IF($D16="","",$D16/$B16)</f>
         <v/>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="16" t="n">
         <v>4</v>
       </c>
       <c r="G16" s="5">
@@ -2296,10 +2421,10 @@
         <f>IF($D16="","",$D16/$F16)</f>
         <v/>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="15">
         <f>IF(OR($J16="",$C16=""),"",$C16/$J16-1)</f>
         <v/>
       </c>
@@ -2326,7 +2451,7 @@
           <t>Neufs</t>
         </is>
       </c>
-      <c r="Q16" s="16" t="inlineStr">
+      <c r="Q16" s="17" t="inlineStr">
         <is>
           <t>20 € Decathlon équivalent</t>
         </is>
@@ -2353,449 +2478,449 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Robe Sandro Noaim blanche</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>50.04</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="10">
         <f>IF($C17="","",$C17-$B17-$L17-$M17)</f>
         <v/>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="19">
         <f>IF($D17="","",$D17/$B17)</f>
         <v/>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="9">
         <f>$B17/$F17</f>
         <v/>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="9">
         <f>IF($C17="","",$C17/$F17)</f>
         <v/>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="9">
         <f>IF($D17="","",$D17/$F17)</f>
         <v/>
       </c>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="18">
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="19">
         <f>IF(OR($J17="",$C17=""),"",$C17/$J17-1)</f>
         <v/>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="9">
         <f>IF($C17="","",$C17*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="9">
         <f>IF($C17="","",$C17*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P17" s="7" t="inlineStr">
+      <c r="P17" s="8" t="inlineStr">
         <is>
           <t>Neuve avec étiquette</t>
         </is>
       </c>
-      <c r="Q17" s="20" t="inlineStr">
+      <c r="Q17" s="21" t="inlineStr">
         <is>
           <t>Once Again −90 % · Stylight −99 %</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr">
+      <c r="R17" s="8" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T17" s="7" t="inlineStr">
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>Reçue</t>
         </is>
       </c>
-      <c r="U17" s="7" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Ballerines Massimo Dutti cuir rouge</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="10">
         <f>IF($C18="","",$C18-$B18-$L18-$M18)</f>
         <v/>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="19">
         <f>IF($D18="","",$D18/$B18)</f>
         <v/>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="9">
         <f>$B18/$F18</f>
         <v/>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <f>IF($C18="","",$C18/$F18)</f>
         <v/>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="9">
         <f>IF($D18="","",$D18/$F18)</f>
         <v/>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="K18" s="18">
+      <c r="K18" s="19">
         <f>IF(OR($J18="",$C18=""),"",$C18/$J18-1)</f>
         <v/>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="9">
         <f>IF($C18="","",$C18*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="9">
         <f>IF($C18="","",$C18*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N18" s="7" t="inlineStr">
+      <c r="N18" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
         <is>
           <t>40 IT</t>
         </is>
       </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="P18" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q18" s="20" t="inlineStr">
+      <c r="Q18" s="21" t="inlineStr">
         <is>
           <t>70 €</t>
         </is>
       </c>
-      <c r="R18" s="7" t="inlineStr">
+      <c r="R18" s="8" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T18" s="7" t="inlineStr">
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U18" s="7" t="inlineStr">
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Robe bustier Chiara Ferragni noire</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="18" t="n">
         <v>38</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="10">
         <f>IF($C19="","",$C19-$B19-$L19-$M19)</f>
         <v/>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="19">
         <f>IF($D19="","",$D19/$B19)</f>
         <v/>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="9">
         <f>$B19/$F19</f>
         <v/>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="9">
         <f>IF($C19="","",$C19/$F19)</f>
         <v/>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="9">
         <f>IF($D19="","",$D19/$F19)</f>
         <v/>
       </c>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="18">
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="19">
         <f>IF(OR($J19="",$C19=""),"",$C19/$J19-1)</f>
         <v/>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="9">
         <f>IF($C19="","",$C19*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="9">
         <f>IF($C19="","",$C19*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="P19" s="7" t="inlineStr">
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t>Neuve avec étiquette</t>
         </is>
       </c>
-      <c r="Q19" s="20" t="inlineStr">
+      <c r="Q19" s="21" t="inlineStr">
         <is>
           <t>YOOX −85 % · marque en crise</t>
         </is>
       </c>
-      <c r="R19" s="7" t="inlineStr">
+      <c r="R19" s="8" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T19" s="7" t="inlineStr">
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>Reçue</t>
         </is>
       </c>
-      <c r="U19" s="7" t="inlineStr">
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Robe Pier Antonio Gaspari bleu marine</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="10">
         <f>IF($C20="","",$C20-$B20-$L20-$M20)</f>
         <v/>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="19">
         <f>IF($D20="","",$D20/$B20)</f>
         <v/>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="9">
         <f>$B20/$F20</f>
         <v/>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="9">
         <f>IF($C20="","",$C20/$F20)</f>
         <v/>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="9">
         <f>IF($D20="","",$D20/$F20)</f>
         <v/>
       </c>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="18">
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="19">
         <f>IF(OR($J20="",$C20=""),"",$C20/$J20-1)</f>
         <v/>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="9">
         <f>IF($C20="","",$C20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="9">
         <f>IF($C20="","",$C20*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="P20" s="8" t="inlineStr">
         <is>
           <t>Neuve</t>
         </is>
       </c>
-      <c r="Q20" s="20" t="inlineStr">
+      <c r="Q20" s="21" t="inlineStr">
         <is>
           <t>YOOX −69 % · Joli Closet −70 %</t>
         </is>
       </c>
-      <c r="R20" s="7" t="inlineStr">
+      <c r="R20" s="8" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T20" s="7" t="inlineStr">
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>Reçue</t>
         </is>
       </c>
-      <c r="U20" s="7" t="inlineStr">
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Baskets Geox gris / argent</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="10">
         <f>IF($C21="","",$C21-$B21-$L21-$M21)</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <f>IF($D21="","",$D21/$B21)</f>
         <v/>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="9">
         <f>$B21/$F21</f>
         <v/>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="9">
         <f>IF($C21="","",$C21/$F21)</f>
         <v/>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="9">
         <f>IF($D21="","",$D21/$F21)</f>
         <v/>
       </c>
-      <c r="J21" s="17" t="n">
+      <c r="J21" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="K21" s="18">
+      <c r="K21" s="19">
         <f>IF(OR($J21="",$C21=""),"",$C21/$J21-1)</f>
         <v/>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="9">
         <f>IF($C21="","",$C21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="9">
         <f>IF($C21="","",$C21*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="O21" s="8" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="P21" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q21" s="20" t="inlineStr">
+      <c r="Q21" s="21" t="inlineStr">
         <is>
           <t>55 €</t>
         </is>
       </c>
-      <c r="R21" s="7" t="inlineStr">
+      <c r="R21" s="8" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T21" s="7" t="inlineStr">
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U21" s="7" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
@@ -2807,7 +2932,7 @@
           <t>Havaianas Slim fuchsia 35/36 ×10</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
+      <c r="B22" s="14" t="n">
         <v>105</v>
       </c>
       <c r="C22" s="6" t="n">
@@ -2817,11 +2942,11 @@
         <f>IF($C22="","",$C22-$B22-$L22-$M22)</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="15">
         <f>IF($D22="","",$D22/$B22)</f>
         <v/>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F22" s="16" t="n">
         <v>10</v>
       </c>
       <c r="G22" s="5">
@@ -2836,10 +2961,10 @@
         <f>IF($D22="","",$D22/$F22)</f>
         <v/>
       </c>
-      <c r="J22" s="13" t="n">
+      <c r="J22" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="15">
         <f>IF(OR($J22="",$C22=""),"",$C22/$J22-1)</f>
         <v/>
       </c>
@@ -2866,7 +2991,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q22" s="16" t="inlineStr">
+      <c r="Q22" s="17" t="inlineStr">
         <is>
           <t>20 € la paire</t>
         </is>
@@ -2893,776 +3018,776 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Plein Sport montante blanc / violet</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="18" t="n">
         <v>62</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="10">
         <f>IF($C23="","",$C23-$B23-$L23-$M23)</f>
         <v/>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="19">
         <f>IF($D23="","",$D23/$B23)</f>
         <v/>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="9">
         <f>$B23/$F23</f>
         <v/>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="9">
         <f>IF($C23="","",$C23/$F23)</f>
         <v/>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="9">
         <f>IF($D23="","",$D23/$F23)</f>
         <v/>
       </c>
-      <c r="J23" s="17" t="n">
+      <c r="J23" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="19">
         <f>IF(OR($J23="",$C23=""),"",$C23/$J23-1)</f>
         <v/>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="9">
         <f>IF($C23="","",$C23*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="9">
         <f>IF($C23="","",$C23*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N23" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="O23" s="8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="P23" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q23" s="20" t="inlineStr">
+      <c r="Q23" s="21" t="inlineStr">
         <is>
           <t>~100 € Stylight −63 %</t>
         </is>
       </c>
-      <c r="R23" s="7" t="inlineStr">
+      <c r="R23" s="8" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="8" t="inlineStr">
         <is>
           <t>99 € puis 89 €</t>
         </is>
       </c>
-      <c r="T23" s="7" t="inlineStr">
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U23" s="7" t="inlineStr">
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Short ba&amp;sh Fegor lightusedblue</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="18" t="n">
         <v>55.4</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="10">
         <f>IF($C24="","",$C24-$B24-$L24-$M24)</f>
         <v/>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="19">
         <f>IF($D24="","",$D24/$B24)</f>
         <v/>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="9">
         <f>$B24/$F24</f>
         <v/>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="9">
         <f>IF($C24="","",$C24/$F24)</f>
         <v/>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="9">
         <f>IF($D24="","",$D24/$F24)</f>
         <v/>
       </c>
-      <c r="J24" s="17" t="n">
+      <c r="J24" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="19">
         <f>IF(OR($J24="",$C24=""),"",$C24/$J24-1)</f>
         <v/>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="9">
         <f>IF($C24="","",$C24*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M24" s="8">
+      <c r="M24" s="9">
         <f>IF($C24="","",$C24*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N24" s="7" t="inlineStr">
+      <c r="N24" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="O24" s="8" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="P24" s="8" t="inlineStr">
         <is>
           <t>Neuf avec étiquette</t>
         </is>
       </c>
-      <c r="Q24" s="20" t="inlineStr">
+      <c r="Q24" s="21" t="inlineStr">
         <is>
           <t>~75 € Modz −50 %</t>
         </is>
       </c>
-      <c r="R24" s="7" t="inlineStr">
+      <c r="R24" s="8" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T24" s="7" t="inlineStr">
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>Reçu</t>
         </is>
       </c>
-      <c r="U24" s="7" t="inlineStr">
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>URGENT — saisonnier</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>New Balance GS 1906 Alkaline Green</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="18" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="10">
         <f>IF($C25="","",$C25-$B25-$L25-$M25)</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="19">
         <f>IF($D25="","",$D25/$B25)</f>
         <v/>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="9">
         <f>$B25/$F25</f>
         <v/>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="9">
         <f>IF($C25="","",$C25/$F25)</f>
         <v/>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="9">
         <f>IF($D25="","",$D25/$F25)</f>
         <v/>
       </c>
-      <c r="J25" s="17" t="n">
+      <c r="J25" s="18" t="n">
         <v>87</v>
       </c>
-      <c r="K25" s="18">
+      <c r="K25" s="19">
         <f>IF(OR($J25="",$C25=""),"",$C25/$J25-1)</f>
         <v/>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="9">
         <f>IF($C25="","",$C25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="9">
         <f>IF($C25="","",$C25*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="N25" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
         <is>
           <t>38½</t>
         </is>
       </c>
-      <c r="P25" s="7" t="inlineStr">
+      <c r="P25" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q25" s="20" t="inlineStr">
+      <c r="Q25" s="21" t="inlineStr">
         <is>
           <t>87 € StockX</t>
         </is>
       </c>
-      <c r="R25" s="7" t="inlineStr">
+      <c r="R25" s="8" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T25" s="7" t="inlineStr">
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>À recevoir</t>
         </is>
       </c>
-      <c r="U25" s="7" t="inlineStr">
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Baskets Emporio Armani bleu lavande</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n">
+      <c r="B26" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="10">
         <f>IF($C26="","",$C26-$B26-$L26-$M26)</f>
         <v/>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="19">
         <f>IF($D26="","",$D26/$B26)</f>
         <v/>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="9">
         <f>$B26/$F26</f>
         <v/>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="9">
         <f>IF($C26="","",$C26/$F26)</f>
         <v/>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="9">
         <f>IF($D26="","",$D26/$F26)</f>
         <v/>
       </c>
-      <c r="J26" s="17" t="n">
+      <c r="J26" s="18" t="n">
         <v>62</v>
       </c>
-      <c r="K26" s="18">
+      <c r="K26" s="19">
         <f>IF(OR($J26="",$C26=""),"",$C26/$J26-1)</f>
         <v/>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="9">
         <f>IF($C26="","",$C26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="9">
         <f>IF($C26="","",$C26*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N26" s="7" t="inlineStr">
+      <c r="N26" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="P26" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q26" s="20" t="inlineStr">
+      <c r="Q26" s="21" t="inlineStr">
         <is>
           <t>62 € eBay</t>
         </is>
       </c>
-      <c r="R26" s="7" t="inlineStr">
+      <c r="R26" s="8" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T26" s="7" t="inlineStr">
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U26" s="7" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>New Balance BB80 blanc / marine</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="18" t="n">
         <v>45</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="10">
         <f>IF($C27="","",$C27-$B27-$L27-$M27)</f>
         <v/>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="19">
         <f>IF($D27="","",$D27/$B27)</f>
         <v/>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="9">
         <f>$B27/$F27</f>
         <v/>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="9">
         <f>IF($C27="","",$C27/$F27)</f>
         <v/>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="9">
         <f>IF($D27="","",$D27/$F27)</f>
         <v/>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J27" s="18" t="n">
         <v>54.99</v>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="19">
         <f>IF(OR($J27="",$C27=""),"",$C27/$J27-1)</f>
         <v/>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="9">
         <f>IF($C27="","",$C27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="9">
         <f>IF($C27="","",$C27*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="N27" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="O27" s="8" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="P27" s="7" t="inlineStr">
+      <c r="P27" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q27" s="20" t="inlineStr">
+      <c r="Q27" s="21" t="inlineStr">
         <is>
           <t>54,99 € idealo</t>
         </is>
       </c>
-      <c r="R27" s="7" t="inlineStr">
+      <c r="R27" s="8" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T27" s="7" t="inlineStr">
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U27" s="7" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Tommy Jeans baskets basses noir / blanc</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="10">
         <f>IF($C28="","",$C28-$B28-$L28-$M28)</f>
         <v/>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="19">
         <f>IF($D28="","",$D28/$B28)</f>
         <v/>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="9">
         <f>$B28/$F28</f>
         <v/>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="9">
         <f>IF($C28="","",$C28/$F28)</f>
         <v/>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="9">
         <f>IF($D28="","",$D28/$F28)</f>
         <v/>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="K28" s="18">
+      <c r="K28" s="19">
         <f>IF(OR($J28="",$C28=""),"",$C28/$J28-1)</f>
         <v/>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="9">
         <f>IF($C28="","",$C28*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M28" s="8">
+      <c r="M28" s="9">
         <f>IF($C28="","",$C28*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N28" s="7" t="inlineStr">
+      <c r="N28" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="O28" s="8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P28" s="7" t="inlineStr">
+      <c r="P28" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q28" s="20" t="inlineStr">
+      <c r="Q28" s="21" t="inlineStr">
         <is>
           <t>60 € Stylight · 41 € officiel</t>
         </is>
       </c>
-      <c r="R28" s="7" t="inlineStr">
+      <c r="R28" s="8" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T28" s="7" t="inlineStr">
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U28" s="7" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>New Balance 650 blanche montante</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="10">
         <f>IF($C29="","",$C29-$B29-$L29-$M29)</f>
         <v/>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="19">
         <f>IF($D29="","",$D29/$B29)</f>
         <v/>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="9">
         <f>$B29/$F29</f>
         <v/>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="9">
         <f>IF($C29="","",$C29/$F29)</f>
         <v/>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="9">
         <f>IF($D29="","",$D29/$F29)</f>
         <v/>
       </c>
-      <c r="J29" s="17" t="n">
+      <c r="J29" s="18" t="n">
         <v>61</v>
       </c>
-      <c r="K29" s="18">
+      <c r="K29" s="19">
         <f>IF(OR($J29="",$C29=""),"",$C29/$J29-1)</f>
         <v/>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="9">
         <f>IF($C29="","",$C29*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="9">
         <f>IF($C29="","",$C29*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="N29" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="O29" s="8" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="P29" s="7" t="inlineStr">
+      <c r="P29" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q29" s="20" t="inlineStr">
+      <c r="Q29" s="21" t="inlineStr">
         <is>
           <t>61 € idealo</t>
         </is>
       </c>
-      <c r="R29" s="7" t="inlineStr">
+      <c r="R29" s="8" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T29" s="7" t="inlineStr">
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U29" s="7" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Adidas Yeezy 700 V3 Mono Safflower</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="18" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="9">
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="10">
         <f>IF($C30="","",$C30-$B30-$L30-$M30)</f>
         <v/>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="19">
         <f>IF($D30="","",$D30/$B30)</f>
         <v/>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="9">
         <f>$B30/$F30</f>
         <v/>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="9">
         <f>IF($C30="","",$C30/$F30)</f>
         <v/>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="9">
         <f>IF($D30="","",$D30/$F30)</f>
         <v/>
       </c>
-      <c r="J30" s="21" t="n"/>
-      <c r="K30" s="18">
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="19">
         <f>IF(OR($J30="",$C30=""),"",$C30/$J30-1)</f>
         <v/>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="9">
         <f>IF($C30="","",$C30*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="9">
         <f>IF($C30="","",$C30*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="N30" s="7" t="inlineStr">
+      <c r="N30" s="8" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="O30" s="8" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="P30" s="7" t="inlineStr">
+      <c r="P30" s="8" t="inlineStr">
         <is>
           <t>Occasion, portée</t>
         </is>
       </c>
-      <c r="Q30" s="20" t="inlineStr">
+      <c r="Q30" s="21" t="inlineStr">
         <is>
           <t>À établir après authentification</t>
         </is>
       </c>
-      <c r="R30" s="7" t="inlineStr">
+      <c r="R30" s="8" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T30" s="7" t="inlineStr">
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>Authentification requise</t>
         </is>
       </c>
-      <c r="U30" s="7" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>TOTAL — 26 lignes</t>
         </is>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="13">
         <f>SUM(B5:B30)</f>
         <v/>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="13">
         <f>SUM(C5:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="13">
         <f>SUM(D5:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="24">
         <f>D31/B31</f>
         <v/>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="25">
         <f>SUM(F5:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="25" t="n"/>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
-      <c r="J31" s="25" t="n"/>
-      <c r="K31" s="25" t="n"/>
-      <c r="L31" s="11">
+      <c r="G31" s="26" t="n"/>
+      <c r="H31" s="26" t="n"/>
+      <c r="I31" s="26" t="n"/>
+      <c r="J31" s="26" t="n"/>
+      <c r="K31" s="26" t="n"/>
+      <c r="L31" s="13">
         <f>SUM(L5:L30)</f>
         <v/>
       </c>
-      <c r="M31" s="11">
+      <c r="M31" s="13">
         <f>SUM(M5:M30)</f>
         <v/>
       </c>
-      <c r="N31" s="25" t="n"/>
-      <c r="O31" s="25" t="n"/>
-      <c r="P31" s="25" t="n"/>
-      <c r="Q31" s="25" t="n"/>
-      <c r="R31" s="25" t="n"/>
-      <c r="S31" s="25" t="n"/>
-      <c r="T31" s="25" t="n"/>
-      <c r="U31" s="25" t="n"/>
+      <c r="N31" s="26" t="n"/>
+      <c r="O31" s="26" t="n"/>
+      <c r="P31" s="26" t="n"/>
+      <c r="Q31" s="26" t="n"/>
+      <c r="R31" s="26" t="n"/>
+      <c r="S31" s="26" t="n"/>
+      <c r="T31" s="26" t="n"/>
+      <c r="U31" s="26" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3716,147 +3841,147 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>VOLUME</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Lignes de stock</t>
         </is>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="29">
         <f>COUNTA('Stock complet'!A5:A30)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Articles physiques</t>
         </is>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <f>'Stock complet'!F31</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Annonces à publier</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="29">
         <f>Paramètres!B19</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>ARGENT</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Capital engagé</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="10">
         <f>'Stock complet'!B31</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Chiffre d'affaires attendu</t>
         </is>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="10">
         <f>'Stock complet'!C31</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>− URSSAF + CFP</t>
         </is>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="9">
         <f>-'Stock complet'!L31</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>− Commission carte</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
         <f>-'Stock complet'!M31</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29">
+      <c r="A14" s="30">
         <f> Marge brute</f>
         <v/>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="13">
         <f>'Stock complet'!D31</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>FRAIS DE VENTE</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>− Emballage</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="9">
         <f>-Paramètres!B18*Paramètres!B19</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>− Frais fixe par transaction</t>
         </is>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="9">
         <f>-Paramètres!B8*Paramètres!B19</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29">
+      <c r="A19" s="30">
         <f> Marge avant impôt</f>
         <v/>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="13">
         <f>B14+B17+B18</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>IMPÔT SUR LE REVENU</t>
         </is>
@@ -3870,23 +3995,23 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>Base imposable</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="9">
         <f>B11*(1-Paramètres!B14)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>− Impôt estimé</t>
         </is>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="9">
         <f>-B23*Paramètres!B15</f>
         <v/>
       </c>
@@ -3897,69 +4022,69 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29">
+      <c r="A25" s="30">
         <f> CE QUI RESTE</f>
         <v/>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <f>B19+B24</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>RENDEMENT</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>Marge nette / capital engagé</t>
         </is>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="33">
         <f>B25/B10</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Marge nette par annonce</t>
         </is>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="9">
         <f>B25/Paramètres!B19</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>Poids de l'URSSAF dans la marge nette</t>
         </is>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="33">
         <f>-B12/B25</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>CHARGES FIXES — hors calcul ci-dessus</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>Abonnement Shopify par mois</t>
         </is>
       </c>
-      <c r="B33" s="33" t="n">
+      <c r="B33" s="34" t="n">
         <v>36</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3969,23 +4094,23 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>Shopify sur douze mois</t>
         </is>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="35">
         <f>B33*12</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>CFE</t>
         </is>
       </c>
-      <c r="B35" s="33" t="n">
+      <c r="B35" s="34" t="n">
         <v>400</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4028,19 +4153,19 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>CHARGES SUR LE CHIFFRE D'AFFAIRES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Cotisations sociales URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="36" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4050,22 +4175,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>CFP — contribution formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="36" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4075,29 +4200,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n">
+      <c r="B8" s="34" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>ACHAT AUX ENCHÈRES</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Frais acheteur ADN Enchères</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="36" t="n">
         <v>0.26</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4107,19 +4232,19 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>IMPÔT SUR LE REVENU — MICRO-BIC</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="36" t="n">
         <v>0.71</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4129,12 +4254,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Tranche marginale d'imposition du foyer</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="36" t="n">
         <v>0.11</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4144,29 +4269,29 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>FRAIS DE VENTE</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Coût d'emballage par colis</t>
         </is>
       </c>
-      <c r="B18" s="33" t="n">
+      <c r="B18" s="34" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Nombre d'annonces / colis prévus</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
+      <c r="B19" s="37" t="n">
         <v>34</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4176,12 +4301,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>Coefficient net (1 − URSSAF − CFP − carte)</t>
         </is>
       </c>
-      <c r="B21" s="37">
+      <c r="B21" s="38">
         <f>1-B5-B6-B7</f>
         <v/>
       </c>
@@ -4212,287 +4337,287 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>LES FEUILLES</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Prix</t>
         </is>
       </c>
-      <c r="B3" s="38" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>Vue courte : pièce, coût, prix de vente, marge. Lisible sur téléphone.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Stock complet</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Tout le détail. Les 4 colonnes essentielles sont en tête, le reste suit.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>Synthèse</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Les totaux, les charges, l'impôt, le rendement.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Paramètres</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Les taux. Une seule cellule à changer répercute sur tout.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>COULEURS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Bleu</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>Valeur saisie à la main.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Jaune</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>Hypothèse à ajuster.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Noir</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>Formule, à ne pas écraser.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>Fond bleuté</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>Ligne de lot multiple.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Fond rouge</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>Marge sous 10 €, ou prix AU-DESSUS du marché.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>LES COLONNES QUI COMPTENT</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>Prix marché</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Le moins cher trouvé sur Internet. C'est le mur.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>Écart au marché</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Négatif = sous le marché, c'est ce qu'on veut. Positif = on perd la comparaison.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>Marge / article</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Sur un lot, le vrai indicateur : 15 € répartis sur dix ventes ne valent pas le travail.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>RÈGLES DE PRIX</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>Sous le moins cher du net</t>
         </is>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>20 à 30 % en dessous. La colonne Écart doit être négative.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>Aucun prix sans sa source</t>
         </is>
       </c>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Un prix sans référence vérifiée est une hypothèse, pas un prix.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>Port payé par l'acheteur</t>
         </is>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>Sans exception. Si la comparaison devient défavorable, on baisse le prix affiché.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>Frais acheteur ADN</t>
         </is>
       </c>
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>26 % sur l'adjudication, plus le transport, pour obtenir le coût réel.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>Palette</t>
         </is>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>Toujours demander une expédition en colis : 90 € → 44 € sur le lot de sandales.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>CE QUE LE CALCUL NE COUVRE PAS</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>Retours</t>
         </is>
       </c>
-      <c r="B28" s="38" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>14 jours de rétractation en vente à un particulier.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Garantie légale</t>
         </is>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>2 ans sur le neuf.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>Authentification</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>15 à 30 € par pièce sur les maisons très contrefaites.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>Temps</t>
         </is>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>Photos, rédaction, emballage, dépôt.</t>
         </is>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Légende" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock complet'!$A$4:$U$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock complet'!$A$4:$V$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,7 +83,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F4E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,32 +157,40 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -576,7 +589,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vue courte, lisible sur téléphone. Le détail complet est dans « Stock complet ».</t>
+          <t>Vue courte, lisible sur téléphone. Les lignes vertes sont déjà vendues.</t>
         </is>
       </c>
     </row>
@@ -838,24 +851,24 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Salomon X Ultra 5 Mid GTX</t>
         </is>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="13">
         <f>'Stock complet'!B15</f>
         <v/>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="14">
         <f>'Stock complet'!C15</f>
         <v/>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="15">
         <f>'Stock complet'!L15</f>
         <v/>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="13">
         <f>'Stock complet'!D15</f>
         <v/>
       </c>
@@ -1206,24 +1219,24 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="17">
         <f>SUM(B5:B30)</f>
         <v/>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="17">
         <f>SUM(C5:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="17">
         <f>SUM(D5:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="17">
         <f>SUM(E5:E30)</f>
         <v/>
       </c>
@@ -1246,7 +1259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1270,6 +1283,7 @@
     <col width="24" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1392,6 +1406,11 @@
           <t>Priorité</t>
         </is>
       </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Vendu le</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1399,7 +1418,7 @@
           <t>Adidas Predator Edge.1 TF ×2</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="18" t="n">
         <v>40</v>
       </c>
       <c r="C5" s="6" t="n">
@@ -1409,11 +1428,11 @@
         <f>IF($C5="","",$C5-$B5-$L5-$M5)</f>
         <v/>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="19">
         <f>IF($D5="","",$D5/$B5)</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="20" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="5">
@@ -1428,10 +1447,10 @@
         <f>IF($D5="","",$D5/$F5)</f>
         <v/>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="18" t="n">
         <v>220</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="19">
         <f>IF(OR($J5="",$C5=""),"",$C5/$J5-1)</f>
         <v/>
       </c>
@@ -1458,7 +1477,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q5" s="17" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>~110 € la paire</t>
         </is>
@@ -1483,6 +1502,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V5" s="22" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1490,7 +1510,7 @@
           <t>Lot 20 sandales et tongs (Relife, Tommy, Chattawak, Malabar)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="18" t="n">
         <v>100.7</v>
       </c>
       <c r="C6" s="6" t="n">
@@ -1500,11 +1520,11 @@
         <f>IF($C6="","",$C6-$B6-$L6-$M6)</f>
         <v/>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="19">
         <f>IF($D6="","",$D6/$B6)</f>
         <v/>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="20" t="n">
         <v>20</v>
       </c>
       <c r="G6" s="5">
@@ -1519,10 +1539,10 @@
         <f>IF($D6="","",$D6/$F6)</f>
         <v/>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="19">
         <f>IF(OR($J6="",$C6=""),"",$C6/$J6-1)</f>
         <v/>
       </c>
@@ -1549,7 +1569,7 @@
           <t>Neuves</t>
         </is>
       </c>
-      <c r="Q6" s="17" t="inlineStr">
+      <c r="Q6" s="21" t="inlineStr">
         <is>
           <t>~400 € valeur boutique du lot</t>
         </is>
@@ -1574,6 +1594,7 @@
           <t>Février-mars</t>
         </is>
       </c>
+      <c r="V6" s="22" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1581,7 +1602,7 @@
           <t>Bottes Forma Legacy Waterproof</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="23" t="n">
         <v>76</v>
       </c>
       <c r="C7" s="10" t="n">
@@ -1591,11 +1612,11 @@
         <f>IF($C7="","",$C7-$B7-$L7-$M7)</f>
         <v/>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="24">
         <f>IF($D7="","",$D7/$B7)</f>
         <v/>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="9">
@@ -1610,10 +1631,10 @@
         <f>IF($D7="","",$D7/$F7)</f>
         <v/>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="23" t="n">
         <v>172.49</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="24">
         <f>IF(OR($J7="",$C7=""),"",$C7/$J7-1)</f>
         <v/>
       </c>
@@ -1640,7 +1661,7 @@
           <t>Neuves</t>
         </is>
       </c>
-      <c r="Q7" s="21" t="inlineStr">
+      <c r="Q7" s="26" t="inlineStr">
         <is>
           <t>172,49 € Dafy Moto</t>
         </is>
@@ -1665,6 +1686,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1672,7 +1694,7 @@
           <t>Robe Elisabetta Franchi ivoire, viscose</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="23" t="n">
         <v>26</v>
       </c>
       <c r="C8" s="10" t="n">
@@ -1682,11 +1704,11 @@
         <f>IF($C8="","",$C8-$B8-$L8-$M8)</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="24">
         <f>IF($D8="","",$D8/$B8)</f>
         <v/>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="9">
@@ -1701,8 +1723,8 @@
         <f>IF($D8="","",$D8/$F8)</f>
         <v/>
       </c>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="19">
+      <c r="J8" s="27" t="n"/>
+      <c r="K8" s="24">
         <f>IF(OR($J8="",$C8=""),"",$C8/$J8-1)</f>
         <v/>
       </c>
@@ -1729,7 +1751,7 @@
           <t>Neuve avec étiquette</t>
         </is>
       </c>
-      <c r="Q8" s="21" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t>Outlet officiel −80 %</t>
         </is>
@@ -1754,6 +1776,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -1761,7 +1784,7 @@
           <t>Ballerines Hogan 186 Zeppa Fashion</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="23" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="10" t="n">
@@ -1771,11 +1794,11 @@
         <f>IF($C9="","",$C9-$B9-$L9-$M9)</f>
         <v/>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="24">
         <f>IF($D9="","",$D9/$B9)</f>
         <v/>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="9">
@@ -1790,10 +1813,10 @@
         <f>IF($D9="","",$D9/$F9)</f>
         <v/>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="23" t="n">
         <v>83</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="24">
         <f>IF(OR($J9="",$C9=""),"",$C9/$J9-1)</f>
         <v/>
       </c>
@@ -1820,7 +1843,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="Q9" s="26" t="inlineStr">
         <is>
           <t>83 € Lyst</t>
         </is>
@@ -1845,6 +1868,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1852,7 +1876,7 @@
           <t>Jupe Sonia Rykiel midi twill cerises</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="23" t="n">
         <v>42.8</v>
       </c>
       <c r="C10" s="10" t="n">
@@ -1862,11 +1886,11 @@
         <f>IF($C10="","",$C10-$B10-$L10-$M10)</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="24">
         <f>IF($D10="","",$D10/$B10)</f>
         <v/>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="9">
@@ -1881,8 +1905,8 @@
         <f>IF($D10="","",$D10/$F10)</f>
         <v/>
       </c>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="19">
+      <c r="J10" s="27" t="n"/>
+      <c r="K10" s="24">
         <f>IF(OR($J10="",$C10=""),"",$C10/$J10-1)</f>
         <v/>
       </c>
@@ -1909,7 +1933,7 @@
           <t>Neuve avec étiquette</t>
         </is>
       </c>
-      <c r="Q10" s="21" t="inlineStr">
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t>Jaiio −80 % · marque liquidée en 2019</t>
         </is>
@@ -1934,6 +1958,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1941,7 +1966,7 @@
           <t>Morgan — 6 vêtements femme</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="18" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="6" t="n">
@@ -1951,11 +1976,11 @@
         <f>IF($C11="","",$C11-$B11-$L11-$M11)</f>
         <v/>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="19">
         <f>IF($D11="","",$D11/$B11)</f>
         <v/>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="20" t="n">
         <v>6</v>
       </c>
       <c r="G11" s="5">
@@ -1970,8 +1995,8 @@
         <f>IF($D11="","",$D11/$F11)</f>
         <v/>
       </c>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="15">
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="19">
         <f>IF(OR($J11="",$C11=""),"",$C11/$J11-1)</f>
         <v/>
       </c>
@@ -1998,7 +2023,7 @@
           <t>Neufs avec étiquette</t>
         </is>
       </c>
-      <c r="Q11" s="17" t="inlineStr">
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>Modz −50 % · Once Again −80 %</t>
         </is>
@@ -2023,6 +2048,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V11" s="22" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -2030,7 +2056,7 @@
           <t>BMW Overall ProRain unisexe noir</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="23" t="n">
         <v>82.61</v>
       </c>
       <c r="C12" s="10" t="n">
@@ -2040,11 +2066,11 @@
         <f>IF($C12="","",$C12-$B12-$L12-$M12)</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="24">
         <f>IF($D12="","",$D12/$B12)</f>
         <v/>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="9">
@@ -2059,10 +2085,10 @@
         <f>IF($D12="","",$D12/$F12)</f>
         <v/>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="23" t="n">
         <v>170</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="24">
         <f>IF(OR($J12="",$C12=""),"",$C12/$J12-1)</f>
         <v/>
       </c>
@@ -2089,7 +2115,7 @@
           <t>Neuf</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="Q12" s="26" t="inlineStr">
         <is>
           <t>170 € coloris noir</t>
         </is>
@@ -2114,6 +2140,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -2121,7 +2148,7 @@
           <t>Baskets adidas by Stella McCartney UltraBoost 21</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="23" t="n">
         <v>35</v>
       </c>
       <c r="C13" s="10" t="n">
@@ -2131,11 +2158,11 @@
         <f>IF($C13="","",$C13-$B13-$L13-$M13)</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="24">
         <f>IF($D13="","",$D13/$B13)</f>
         <v/>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="9">
@@ -2150,10 +2177,10 @@
         <f>IF($D13="","",$D13/$F13)</f>
         <v/>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="23" t="n">
         <v>94</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="24">
         <f>IF(OR($J13="",$C13=""),"",$C13/$J13-1)</f>
         <v/>
       </c>
@@ -2180,7 +2207,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q13" s="21" t="inlineStr">
+      <c r="Q13" s="26" t="inlineStr">
         <is>
           <t>94 € eBay.de</t>
         </is>
@@ -2205,6 +2232,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V13" s="27" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -2212,7 +2240,7 @@
           <t>Blazer Karl Lagerfeld punto noir</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="23" t="n">
         <v>45</v>
       </c>
       <c r="C14" s="10" t="n">
@@ -2222,11 +2250,11 @@
         <f>IF($C14="","",$C14-$B14-$L14-$M14)</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="24">
         <f>IF($D14="","",$D14/$B14)</f>
         <v/>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G14" s="9">
@@ -2241,8 +2269,8 @@
         <f>IF($D14="","",$D14/$F14)</f>
         <v/>
       </c>
-      <c r="J14" s="22" t="n"/>
-      <c r="K14" s="19">
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="24">
         <f>IF(OR($J14="",$C14=""),"",$C14/$J14-1)</f>
         <v/>
       </c>
@@ -2269,7 +2297,7 @@
           <t>Neuf avec étiquette</t>
         </is>
       </c>
-      <c r="Q14" s="21" t="inlineStr">
+      <c r="Q14" s="26" t="inlineStr">
         <is>
           <t>Otrium outlet · Lyst dès 50 €</t>
         </is>
@@ -2294,95 +2322,100 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V14" s="27" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Salomon X Ultra 5 Mid GTX</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="28" t="n">
         <v>65</v>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>109</v>
-      </c>
-      <c r="D15" s="10">
+      <c r="C15" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" s="14">
         <f>IF($C15="","",$C15-$B15-$L15-$M15)</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="29">
         <f>IF($D15="","",$D15/$B15)</f>
         <v/>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="13">
         <f>$B15/$F15</f>
         <v/>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="13">
         <f>IF($C15="","",$C15/$F15)</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="13">
         <f>IF($D15="","",$D15/$F15)</f>
         <v/>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="28" t="n">
         <v>116</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="29">
         <f>IF(OR($J15="",$C15=""),"",$C15/$J15-1)</f>
         <v/>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="13">
         <f>IF($C15="","",$C15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M15" s="9">
-        <f>IF($C15="","",$C15*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="M15" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="12" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t>Neuves</t>
         </is>
       </c>
-      <c r="Q15" s="21" t="inlineStr">
+      <c r="Q15" s="31" t="inlineStr">
         <is>
           <t>116 €</t>
         </is>
       </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t>Pièce seule</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>Reçues</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>Normal</t>
+      <c r="R15" s="12" t="inlineStr">
+        <is>
+          <t>Vinted, acheteur en Italie</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>VENDUE le 12/08/2026</t>
+        </is>
+      </c>
+      <c r="T15" s="12" t="inlineStr">
+        <is>
+          <t>VENDUE</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>Vendu</t>
+        </is>
+      </c>
+      <c r="V15" s="12" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2425,7 @@
           <t>Mrs.Ertha — gilets de flottaison 3-6 ans</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="18" t="n">
         <v>37.8</v>
       </c>
       <c r="C16" s="6" t="n">
@@ -2402,11 +2435,11 @@
         <f>IF($C16="","",$C16-$B16-$L16-$M16)</f>
         <v/>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="19">
         <f>IF($D16="","",$D16/$B16)</f>
         <v/>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="20" t="n">
         <v>4</v>
       </c>
       <c r="G16" s="5">
@@ -2421,10 +2454,10 @@
         <f>IF($D16="","",$D16/$F16)</f>
         <v/>
       </c>
-      <c r="J16" s="14" t="n">
+      <c r="J16" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="19">
         <f>IF(OR($J16="",$C16=""),"",$C16/$J16-1)</f>
         <v/>
       </c>
@@ -2451,7 +2484,7 @@
           <t>Neufs</t>
         </is>
       </c>
-      <c r="Q16" s="17" t="inlineStr">
+      <c r="Q16" s="21" t="inlineStr">
         <is>
           <t>20 € Decathlon équivalent</t>
         </is>
@@ -2476,6 +2509,7 @@
           <t>URGENT — saisonnier</t>
         </is>
       </c>
+      <c r="V16" s="22" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -2483,7 +2517,7 @@
           <t>Robe Sandro Noaim blanche</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="23" t="n">
         <v>50.04</v>
       </c>
       <c r="C17" s="10" t="n">
@@ -2493,11 +2527,11 @@
         <f>IF($C17="","",$C17-$B17-$L17-$M17)</f>
         <v/>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="24">
         <f>IF($D17="","",$D17/$B17)</f>
         <v/>
       </c>
-      <c r="F17" s="20" t="n">
+      <c r="F17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="9">
@@ -2512,8 +2546,8 @@
         <f>IF($D17="","",$D17/$F17)</f>
         <v/>
       </c>
-      <c r="J17" s="22" t="n"/>
-      <c r="K17" s="19">
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="24">
         <f>IF(OR($J17="",$C17=""),"",$C17/$J17-1)</f>
         <v/>
       </c>
@@ -2540,7 +2574,7 @@
           <t>Neuve avec étiquette</t>
         </is>
       </c>
-      <c r="Q17" s="21" t="inlineStr">
+      <c r="Q17" s="26" t="inlineStr">
         <is>
           <t>Once Again −90 % · Stylight −99 %</t>
         </is>
@@ -2565,6 +2599,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V17" s="27" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -2572,7 +2607,7 @@
           <t>Ballerines Massimo Dutti cuir rouge</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="23" t="n">
         <v>25</v>
       </c>
       <c r="C18" s="10" t="n">
@@ -2582,11 +2617,11 @@
         <f>IF($C18="","",$C18-$B18-$L18-$M18)</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="24">
         <f>IF($D18="","",$D18/$B18)</f>
         <v/>
       </c>
-      <c r="F18" s="20" t="n">
+      <c r="F18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="9">
@@ -2601,10 +2636,10 @@
         <f>IF($D18="","",$D18/$F18)</f>
         <v/>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="23" t="n">
         <v>70</v>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="24">
         <f>IF(OR($J18="",$C18=""),"",$C18/$J18-1)</f>
         <v/>
       </c>
@@ -2631,7 +2666,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q18" s="21" t="inlineStr">
+      <c r="Q18" s="26" t="inlineStr">
         <is>
           <t>70 €</t>
         </is>
@@ -2656,6 +2691,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V18" s="27" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -2663,7 +2699,7 @@
           <t>Robe bustier Chiara Ferragni noire</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="23" t="n">
         <v>38</v>
       </c>
       <c r="C19" s="10" t="n">
@@ -2673,11 +2709,11 @@
         <f>IF($C19="","",$C19-$B19-$L19-$M19)</f>
         <v/>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="24">
         <f>IF($D19="","",$D19/$B19)</f>
         <v/>
       </c>
-      <c r="F19" s="20" t="n">
+      <c r="F19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="9">
@@ -2692,8 +2728,8 @@
         <f>IF($D19="","",$D19/$F19)</f>
         <v/>
       </c>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="19">
+      <c r="J19" s="27" t="n"/>
+      <c r="K19" s="24">
         <f>IF(OR($J19="",$C19=""),"",$C19/$J19-1)</f>
         <v/>
       </c>
@@ -2720,7 +2756,7 @@
           <t>Neuve avec étiquette</t>
         </is>
       </c>
-      <c r="Q19" s="21" t="inlineStr">
+      <c r="Q19" s="26" t="inlineStr">
         <is>
           <t>YOOX −85 % · marque en crise</t>
         </is>
@@ -2745,6 +2781,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V19" s="27" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -2752,7 +2789,7 @@
           <t>Robe Pier Antonio Gaspari bleu marine</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="23" t="n">
         <v>30</v>
       </c>
       <c r="C20" s="10" t="n">
@@ -2762,11 +2799,11 @@
         <f>IF($C20="","",$C20-$B20-$L20-$M20)</f>
         <v/>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="24">
         <f>IF($D20="","",$D20/$B20)</f>
         <v/>
       </c>
-      <c r="F20" s="20" t="n">
+      <c r="F20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="9">
@@ -2781,8 +2818,8 @@
         <f>IF($D20="","",$D20/$F20)</f>
         <v/>
       </c>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="19">
+      <c r="J20" s="27" t="n"/>
+      <c r="K20" s="24">
         <f>IF(OR($J20="",$C20=""),"",$C20/$J20-1)</f>
         <v/>
       </c>
@@ -2809,7 +2846,7 @@
           <t>Neuve</t>
         </is>
       </c>
-      <c r="Q20" s="21" t="inlineStr">
+      <c r="Q20" s="26" t="inlineStr">
         <is>
           <t>YOOX −69 % · Joli Closet −70 %</t>
         </is>
@@ -2834,6 +2871,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V20" s="27" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -2841,7 +2879,7 @@
           <t>Baskets Geox gris / argent</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="23" t="n">
         <v>25</v>
       </c>
       <c r="C21" s="10" t="n">
@@ -2851,11 +2889,11 @@
         <f>IF($C21="","",$C21-$B21-$L21-$M21)</f>
         <v/>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="24">
         <f>IF($D21="","",$D21/$B21)</f>
         <v/>
       </c>
-      <c r="F21" s="20" t="n">
+      <c r="F21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="9">
@@ -2870,10 +2908,10 @@
         <f>IF($D21="","",$D21/$F21)</f>
         <v/>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="23" t="n">
         <v>55</v>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="24">
         <f>IF(OR($J21="",$C21=""),"",$C21/$J21-1)</f>
         <v/>
       </c>
@@ -2900,7 +2938,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q21" s="21" t="inlineStr">
+      <c r="Q21" s="26" t="inlineStr">
         <is>
           <t>55 €</t>
         </is>
@@ -2925,6 +2963,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V21" s="27" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2932,7 +2971,7 @@
           <t>Havaianas Slim fuchsia 35/36 ×10</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="18" t="n">
         <v>105</v>
       </c>
       <c r="C22" s="6" t="n">
@@ -2942,11 +2981,11 @@
         <f>IF($C22="","",$C22-$B22-$L22-$M22)</f>
         <v/>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="19">
         <f>IF($D22="","",$D22/$B22)</f>
         <v/>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="20" t="n">
         <v>10</v>
       </c>
       <c r="G22" s="5">
@@ -2961,10 +3000,10 @@
         <f>IF($D22="","",$D22/$F22)</f>
         <v/>
       </c>
-      <c r="J22" s="14" t="n">
+      <c r="J22" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="19">
         <f>IF(OR($J22="",$C22=""),"",$C22/$J22-1)</f>
         <v/>
       </c>
@@ -2991,7 +3030,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q22" s="17" t="inlineStr">
+      <c r="Q22" s="21" t="inlineStr">
         <is>
           <t>20 € la paire</t>
         </is>
@@ -3016,6 +3055,7 @@
           <t>URGENT — saisonnier</t>
         </is>
       </c>
+      <c r="V22" s="22" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -3023,7 +3063,7 @@
           <t>Plein Sport montante blanc / violet</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="23" t="n">
         <v>62</v>
       </c>
       <c r="C23" s="10" t="n">
@@ -3033,11 +3073,11 @@
         <f>IF($C23="","",$C23-$B23-$L23-$M23)</f>
         <v/>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="24">
         <f>IF($D23="","",$D23/$B23)</f>
         <v/>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="9">
@@ -3052,10 +3092,10 @@
         <f>IF($D23="","",$D23/$F23)</f>
         <v/>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="24">
         <f>IF(OR($J23="",$C23=""),"",$C23/$J23-1)</f>
         <v/>
       </c>
@@ -3082,7 +3122,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q23" s="21" t="inlineStr">
+      <c r="Q23" s="26" t="inlineStr">
         <is>
           <t>~100 € Stylight −63 %</t>
         </is>
@@ -3107,6 +3147,7 @@
           <t>Normal</t>
         </is>
       </c>
+      <c r="V23" s="27" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -3114,7 +3155,7 @@
           <t>Short ba&amp;sh Fegor lightusedblue</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="23" t="n">
         <v>55.4</v>
       </c>
       <c r="C24" s="10" t="n">
@@ -3124,11 +3165,11 @@
         <f>IF($C24="","",$C24-$B24-$L24-$M24)</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="24">
         <f>IF($D24="","",$D24/$B24)</f>
         <v/>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="9">
@@ -3143,10 +3184,10 @@
         <f>IF($D24="","",$D24/$F24)</f>
         <v/>
       </c>
-      <c r="J24" s="18" t="n">
+      <c r="J24" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="24">
         <f>IF(OR($J24="",$C24=""),"",$C24/$J24-1)</f>
         <v/>
       </c>
@@ -3173,7 +3214,7 @@
           <t>Neuf avec étiquette</t>
         </is>
       </c>
-      <c r="Q24" s="21" t="inlineStr">
+      <c r="Q24" s="26" t="inlineStr">
         <is>
           <t>~75 € Modz −50 %</t>
         </is>
@@ -3198,6 +3239,7 @@
           <t>URGENT — saisonnier</t>
         </is>
       </c>
+      <c r="V24" s="27" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -3205,7 +3247,7 @@
           <t>New Balance GS 1906 Alkaline Green</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="23" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="C25" s="10" t="n">
@@ -3215,11 +3257,11 @@
         <f>IF($C25="","",$C25-$B25-$L25-$M25)</f>
         <v/>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="24">
         <f>IF($D25="","",$D25/$B25)</f>
         <v/>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="9">
@@ -3234,10 +3276,10 @@
         <f>IF($D25="","",$D25/$F25)</f>
         <v/>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="23" t="n">
         <v>87</v>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="24">
         <f>IF(OR($J25="",$C25=""),"",$C25/$J25-1)</f>
         <v/>
       </c>
@@ -3264,7 +3306,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q25" s="21" t="inlineStr">
+      <c r="Q25" s="26" t="inlineStr">
         <is>
           <t>87 € StockX</t>
         </is>
@@ -3289,6 +3331,7 @@
           <t>Liquider</t>
         </is>
       </c>
+      <c r="V25" s="27" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -3296,7 +3339,7 @@
           <t>Baskets Emporio Armani bleu lavande</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="23" t="n">
         <v>55</v>
       </c>
       <c r="C26" s="10" t="n">
@@ -3306,11 +3349,11 @@
         <f>IF($C26="","",$C26-$B26-$L26-$M26)</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="24">
         <f>IF($D26="","",$D26/$B26)</f>
         <v/>
       </c>
-      <c r="F26" s="20" t="n">
+      <c r="F26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="9">
@@ -3325,10 +3368,10 @@
         <f>IF($D26="","",$D26/$F26)</f>
         <v/>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="24">
         <f>IF(OR($J26="",$C26=""),"",$C26/$J26-1)</f>
         <v/>
       </c>
@@ -3355,7 +3398,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q26" s="21" t="inlineStr">
+      <c r="Q26" s="26" t="inlineStr">
         <is>
           <t>62 € eBay</t>
         </is>
@@ -3380,6 +3423,7 @@
           <t>Liquider</t>
         </is>
       </c>
+      <c r="V26" s="27" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -3387,7 +3431,7 @@
           <t>New Balance BB80 blanc / marine</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="23" t="n">
         <v>45</v>
       </c>
       <c r="C27" s="10" t="n">
@@ -3397,11 +3441,11 @@
         <f>IF($C27="","",$C27-$B27-$L27-$M27)</f>
         <v/>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="24">
         <f>IF($D27="","",$D27/$B27)</f>
         <v/>
       </c>
-      <c r="F27" s="20" t="n">
+      <c r="F27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="9">
@@ -3416,10 +3460,10 @@
         <f>IF($D27="","",$D27/$F27)</f>
         <v/>
       </c>
-      <c r="J27" s="18" t="n">
+      <c r="J27" s="23" t="n">
         <v>54.99</v>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="24">
         <f>IF(OR($J27="",$C27=""),"",$C27/$J27-1)</f>
         <v/>
       </c>
@@ -3446,7 +3490,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q27" s="21" t="inlineStr">
+      <c r="Q27" s="26" t="inlineStr">
         <is>
           <t>54,99 € idealo</t>
         </is>
@@ -3471,6 +3515,7 @@
           <t>Liquider</t>
         </is>
       </c>
+      <c r="V27" s="27" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -3478,7 +3523,7 @@
           <t>Tommy Jeans baskets basses noir / blanc</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="23" t="n">
         <v>55</v>
       </c>
       <c r="C28" s="10" t="n">
@@ -3488,11 +3533,11 @@
         <f>IF($C28="","",$C28-$B28-$L28-$M28)</f>
         <v/>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="24">
         <f>IF($D28="","",$D28/$B28)</f>
         <v/>
       </c>
-      <c r="F28" s="20" t="n">
+      <c r="F28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="9">
@@ -3507,10 +3552,10 @@
         <f>IF($D28="","",$D28/$F28)</f>
         <v/>
       </c>
-      <c r="J28" s="18" t="n">
+      <c r="J28" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="24">
         <f>IF(OR($J28="",$C28=""),"",$C28/$J28-1)</f>
         <v/>
       </c>
@@ -3537,7 +3582,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q28" s="21" t="inlineStr">
+      <c r="Q28" s="26" t="inlineStr">
         <is>
           <t>60 € Stylight · 41 € officiel</t>
         </is>
@@ -3562,6 +3607,7 @@
           <t>Liquider</t>
         </is>
       </c>
+      <c r="V28" s="27" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -3569,7 +3615,7 @@
           <t>New Balance 650 blanche montante</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="23" t="n">
         <v>55</v>
       </c>
       <c r="C29" s="10" t="n">
@@ -3579,11 +3625,11 @@
         <f>IF($C29="","",$C29-$B29-$L29-$M29)</f>
         <v/>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="24">
         <f>IF($D29="","",$D29/$B29)</f>
         <v/>
       </c>
-      <c r="F29" s="20" t="n">
+      <c r="F29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="9">
@@ -3598,10 +3644,10 @@
         <f>IF($D29="","",$D29/$F29)</f>
         <v/>
       </c>
-      <c r="J29" s="18" t="n">
+      <c r="J29" s="23" t="n">
         <v>61</v>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="24">
         <f>IF(OR($J29="",$C29=""),"",$C29/$J29-1)</f>
         <v/>
       </c>
@@ -3628,7 +3674,7 @@
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q29" s="21" t="inlineStr">
+      <c r="Q29" s="26" t="inlineStr">
         <is>
           <t>61 € idealo</t>
         </is>
@@ -3653,6 +3699,7 @@
           <t>Liquider</t>
         </is>
       </c>
+      <c r="V29" s="27" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -3660,19 +3707,19 @@
           <t>Adidas Yeezy 700 V3 Mono Safflower</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="23" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="C30" s="22" t="n"/>
+      <c r="C30" s="27" t="n"/>
       <c r="D30" s="10">
         <f>IF($C30="","",$C30-$B30-$L30-$M30)</f>
         <v/>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="24">
         <f>IF($D30="","",$D30/$B30)</f>
         <v/>
       </c>
-      <c r="F30" s="20" t="n">
+      <c r="F30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="9">
@@ -3687,8 +3734,8 @@
         <f>IF($D30="","",$D30/$F30)</f>
         <v/>
       </c>
-      <c r="J30" s="22" t="n"/>
-      <c r="K30" s="19">
+      <c r="J30" s="27" t="n"/>
+      <c r="K30" s="24">
         <f>IF(OR($J30="",$C30=""),"",$C30/$J30-1)</f>
         <v/>
       </c>
@@ -3715,7 +3762,7 @@
           <t>Occasion, portée</t>
         </is>
       </c>
-      <c r="Q30" s="21" t="inlineStr">
+      <c r="Q30" s="26" t="inlineStr">
         <is>
           <t>À établir après authentification</t>
         </is>
@@ -3740,54 +3787,56 @@
           <t>Bloqué</t>
         </is>
       </c>
+      <c r="V30" s="27" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>TOTAL — 26 lignes</t>
         </is>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="17">
         <f>SUM(B5:B30)</f>
         <v/>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="17">
         <f>SUM(C5:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="17">
         <f>SUM(D5:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="32">
         <f>D31/B31</f>
         <v/>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="33">
         <f>SUM(F5:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="26" t="n"/>
-      <c r="H31" s="26" t="n"/>
-      <c r="I31" s="26" t="n"/>
-      <c r="J31" s="26" t="n"/>
-      <c r="K31" s="26" t="n"/>
-      <c r="L31" s="13">
+      <c r="G31" s="34" t="n"/>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="34" t="n"/>
+      <c r="J31" s="34" t="n"/>
+      <c r="K31" s="34" t="n"/>
+      <c r="L31" s="17">
         <f>SUM(L5:L30)</f>
         <v/>
       </c>
-      <c r="M31" s="13">
+      <c r="M31" s="17">
         <f>SUM(M5:M30)</f>
         <v/>
       </c>
-      <c r="N31" s="26" t="n"/>
-      <c r="O31" s="26" t="n"/>
-      <c r="P31" s="26" t="n"/>
-      <c r="Q31" s="26" t="n"/>
-      <c r="R31" s="26" t="n"/>
-      <c r="S31" s="26" t="n"/>
-      <c r="T31" s="26" t="n"/>
-      <c r="U31" s="26" t="n"/>
+      <c r="N31" s="34" t="n"/>
+      <c r="O31" s="34" t="n"/>
+      <c r="P31" s="34" t="n"/>
+      <c r="Q31" s="34" t="n"/>
+      <c r="R31" s="34" t="n"/>
+      <c r="S31" s="34" t="n"/>
+      <c r="T31" s="34" t="n"/>
+      <c r="U31" s="34" t="n"/>
+      <c r="V31" s="34" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3797,7 +3846,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U30"/>
+  <autoFilter ref="A4:V30"/>
   <conditionalFormatting sqref="D5:D30">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>10</formula>
@@ -3818,7 +3867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3841,54 +3890,54 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>VOLUME</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Lignes de stock</t>
         </is>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="37">
         <f>COUNTA('Stock complet'!A5:A30)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Articles physiques</t>
         </is>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="39">
         <f>'Stock complet'!F31</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Annonces à publier</t>
         </is>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="37">
         <f>Paramètres!B19</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>ARGENT</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>Capital engagé</t>
         </is>
@@ -3899,7 +3948,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Chiffre d'affaires attendu</t>
         </is>
@@ -3910,7 +3959,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>− URSSAF + CFP</t>
         </is>
@@ -3921,7 +3970,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>− Commission carte</t>
         </is>
@@ -3932,188 +3981,250 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30">
+      <c r="A14" s="38">
         <f> Marge brute</f>
         <v/>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="17">
         <f>'Stock complet'!D31</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>OÙ EN EST LE STOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="38" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires déjà réalisé</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <f>SUMIF('Stock complet'!V5:V30,"&lt;&gt;",'Stock complet'!C5:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>Marge déjà réalisée</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>SUMIF('Stock complet'!V5:V30,"&lt;&gt;",'Stock complet'!D5:D30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires restant à faire</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>B11-B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>Marge restant à faire</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>B14-B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>Capital encore immobilisé</t>
+        </is>
+      </c>
+      <c r="B21" s="9">
+        <f>B10-SUMIF('Stock complet'!V5:V30,"&lt;&gt;",'Stock complet'!B5:B30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>FRAIS DE VENTE</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>− Emballage</t>
         </is>
       </c>
-      <c r="B17" s="9">
+      <c r="B24" s="9">
         <f>-Paramètres!B18*Paramètres!B19</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>− Frais fixe par transaction</t>
         </is>
       </c>
-      <c r="B18" s="9">
+      <c r="B25" s="9">
         <f>-Paramètres!B8*Paramètres!B19</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="30">
+    <row r="26">
+      <c r="A26" s="38">
         <f> Marge avant impôt</f>
         <v/>
       </c>
-      <c r="B19" s="13">
-        <f>B14+B17+B18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="B26" s="17">
+        <f>B14+B24+B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>IMPÔT SUR LE REVENU</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Versement libératoire non retenu : abattement de 71 %, le reste au barème du foyer.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>Base imposable</t>
         </is>
       </c>
-      <c r="B23" s="9">
+      <c r="B30" s="9">
         <f>B11*(1-Paramètres!B14)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>− Impôt estimé</t>
         </is>
       </c>
-      <c r="B24" s="9">
-        <f>-B23*Paramètres!B15</f>
-        <v/>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B31" s="9">
+        <f>-B30*Paramètres!B15</f>
+        <v/>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Dépend du foyer, pas de l'activité</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="30">
+    <row r="32">
+      <c r="A32" s="38">
         <f> CE QUI RESTE</f>
         <v/>
       </c>
-      <c r="B25" s="32">
-        <f>B19+B24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="B32" s="40">
+        <f>B26+B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>RENDEMENT</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>Marge nette / capital engagé</t>
         </is>
       </c>
-      <c r="B28" s="33">
-        <f>B25/B10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="B35" s="41">
+        <f>B32/B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>Marge nette par annonce</t>
         </is>
       </c>
-      <c r="B29" s="9">
-        <f>B25/Paramètres!B19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="B36" s="9">
+        <f>B32/Paramètres!B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>Poids de l'URSSAF dans la marge nette</t>
         </is>
       </c>
-      <c r="B30" s="33">
-        <f>-B12/B25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="B37" s="41">
+        <f>-B12/B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>CHARGES FIXES — hors calcul ci-dessus</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="28" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>Abonnement Shopify par mois</t>
         </is>
       </c>
-      <c r="B33" s="34" t="n">
+      <c r="B40" s="42" t="n">
         <v>36</v>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>À partir du 11/11/2026 — 1 €/mois jusque-là</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>Shopify sur douze mois</t>
         </is>
       </c>
-      <c r="B34" s="35">
-        <f>B33*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="28" t="inlineStr">
+      <c r="B41" s="43">
+        <f>B40*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>CFE</t>
         </is>
       </c>
-      <c r="B35" s="34" t="n">
+      <c r="B42" s="42" t="n">
         <v>400</v>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Exonérée la 1ʳᵉ année, puis 200 à 600 €/an — arrive en 2027</t>
         </is>
@@ -4153,19 +4264,19 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>CHARGES SUR LE CHIFFRE D'AFFAIRES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Cotisations sociales URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="44" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4175,22 +4286,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>CFP — contribution formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="44" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="44" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4200,29 +4311,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="42" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>ACHAT AUX ENCHÈRES</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Frais acheteur ADN Enchères</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="44" t="n">
         <v>0.26</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4232,19 +4343,19 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>IMPÔT SUR LE REVENU — MICRO-BIC</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="44" t="n">
         <v>0.71</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4254,12 +4365,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Tranche marginale d'imposition du foyer</t>
         </is>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="44" t="n">
         <v>0.11</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4269,29 +4380,29 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>FRAIS DE VENTE</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>Coût d'emballage par colis</t>
         </is>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="42" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Nombre d'annonces / colis prévus</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="45" t="n">
         <v>34</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4301,12 +4412,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>Coefficient net (1 − URSSAF − CFP − carte)</t>
         </is>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="46">
         <f>1-B5-B6-B7</f>
         <v/>
       </c>
@@ -4337,287 +4448,287 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>LES FEUILLES</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>Prix</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="47" t="inlineStr">
         <is>
           <t>Vue courte : pièce, coût, prix de vente, marge. Lisible sur téléphone.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Stock complet</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Tout le détail. Les 4 colonnes essentielles sont en tête, le reste suit.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Synthèse</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Les totaux, les charges, l'impôt, le rendement.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Paramètres</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>Les taux. Une seule cellule à changer répercute sur tout.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>COULEURS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Bleu</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>Valeur saisie à la main.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>Jaune</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>Hypothèse à ajuster.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Noir</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>Formule, à ne pas écraser.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Fond bleuté</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>Ligne de lot multiple.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>Fond rouge</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="47" t="inlineStr">
         <is>
           <t>Marge sous 10 €, ou prix AU-DESSUS du marché.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>LES COLONNES QUI COMPTENT</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>Prix marché</t>
         </is>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="47" t="inlineStr">
         <is>
           <t>Le moins cher trouvé sur Internet. C'est le mur.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>Écart au marché</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>Négatif = sous le marché, c'est ce qu'on veut. Positif = on perd la comparaison.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>Marge / article</t>
         </is>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="47" t="inlineStr">
         <is>
           <t>Sur un lot, le vrai indicateur : 15 € répartis sur dix ventes ne valent pas le travail.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>RÈGLES DE PRIX</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>Sous le moins cher du net</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>20 à 30 % en dessous. La colonne Écart doit être négative.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>Aucun prix sans sa source</t>
         </is>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>Un prix sans référence vérifiée est une hypothèse, pas un prix.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>Port payé par l'acheteur</t>
         </is>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" s="47" t="inlineStr">
         <is>
           <t>Sans exception. Si la comparaison devient défavorable, on baisse le prix affiché.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>Frais acheteur ADN</t>
         </is>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>26 % sur l'adjudication, plus le transport, pour obtenir le coût réel.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>Palette</t>
         </is>
       </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>Toujours demander une expédition en colis : 90 € → 44 € sur le lot de sandales.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>CE QUE LE CALCUL NE COUVRE PAS</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>Retours</t>
         </is>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
         <is>
           <t>14 jours de rétractation en vente à un particulier.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>Garantie légale</t>
         </is>
       </c>
-      <c r="B29" s="39" t="inlineStr">
+      <c r="B29" s="47" t="inlineStr">
         <is>
           <t>2 ans sur le neuf.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>Authentification</t>
         </is>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="47" t="inlineStr">
         <is>
           <t>15 à 30 € par pièce sur les maisons très contrefaites.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>Temps</t>
         </is>
       </c>
-      <c r="B31" s="39" t="inlineStr">
+      <c r="B31" s="47" t="inlineStr">
         <is>
           <t>Photos, rédaction, emballage, dépôt.</t>
         </is>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Légende" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock complet'!$A$4:$V$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stock complet'!$A$4:$V$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -897,24 +897,24 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Robe Sandro Noaim blanche</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Robby VP550W — pompes immergées 550 W ×2</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
         <f>'Stock complet'!B17</f>
         <v/>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="6">
         <f>'Stock complet'!C17</f>
         <v/>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="7">
         <f>'Stock complet'!L17</f>
         <v/>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="5">
         <f>'Stock complet'!D17</f>
         <v/>
       </c>
@@ -922,7 +922,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Ballerines Massimo Dutti cuir rouge</t>
+          <t>Robe Sandro Noaim blanche</t>
         </is>
       </c>
       <c r="B18" s="9">
@@ -945,7 +945,7 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Robe bustier Chiara Ferragni noire</t>
+          <t>Ballerines Massimo Dutti cuir rouge</t>
         </is>
       </c>
       <c r="B19" s="9">
@@ -968,7 +968,7 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Robe Pier Antonio Gaspari bleu marine</t>
+          <t>Robe bustier Chiara Ferragni noire</t>
         </is>
       </c>
       <c r="B20" s="9">
@@ -991,7 +991,7 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Baskets Geox gris / argent</t>
+          <t>Robe Pier Antonio Gaspari bleu marine</t>
         </is>
       </c>
       <c r="B21" s="9">
@@ -1012,47 +1012,47 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Baskets Geox gris / argent</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>'Stock complet'!B22</f>
+        <v/>
+      </c>
+      <c r="C22" s="10">
+        <f>'Stock complet'!C22</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>'Stock complet'!L22</f>
+        <v/>
+      </c>
+      <c r="E22" s="9">
+        <f>'Stock complet'!D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Havaianas Slim fuchsia 35/36 ×10</t>
         </is>
       </c>
-      <c r="B22" s="5">
-        <f>'Stock complet'!B22</f>
-        <v/>
-      </c>
-      <c r="C22" s="6">
-        <f>'Stock complet'!C22</f>
-        <v/>
-      </c>
-      <c r="D22" s="7">
-        <f>'Stock complet'!L22</f>
-        <v/>
-      </c>
-      <c r="E22" s="5">
-        <f>'Stock complet'!D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Plein Sport montante blanc / violet</t>
-        </is>
-      </c>
-      <c r="B23" s="9">
+      <c r="B23" s="5">
         <f>'Stock complet'!B23</f>
         <v/>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="6">
         <f>'Stock complet'!C23</f>
         <v/>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="7">
         <f>'Stock complet'!L23</f>
         <v/>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="5">
         <f>'Stock complet'!D23</f>
         <v/>
       </c>
@@ -1060,7 +1060,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Short ba&amp;sh Fegor lightusedblue</t>
+          <t>Plein Sport montante blanc / violet</t>
         </is>
       </c>
       <c r="B24" s="9">
@@ -1083,7 +1083,7 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>New Balance GS 1906 Alkaline Green</t>
+          <t>Short ba&amp;sh Fegor lightusedblue</t>
         </is>
       </c>
       <c r="B25" s="9">
@@ -1106,7 +1106,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Baskets Emporio Armani bleu lavande</t>
+          <t>New Balance GS 1906 Alkaline Green</t>
         </is>
       </c>
       <c r="B26" s="9">
@@ -1129,7 +1129,7 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>New Balance BB80 blanc / marine</t>
+          <t>Baskets Emporio Armani bleu lavande</t>
         </is>
       </c>
       <c r="B27" s="9">
@@ -1152,7 +1152,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Tommy Jeans baskets basses noir / blanc</t>
+          <t>New Balance BB80 blanc / marine</t>
         </is>
       </c>
       <c r="B28" s="9">
@@ -1175,7 +1175,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>New Balance 650 blanche montante</t>
+          <t>Tommy Jeans baskets basses noir / blanc</t>
         </is>
       </c>
       <c r="B29" s="9">
@@ -1198,7 +1198,7 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Adidas Yeezy 700 V3 Mono Safflower</t>
+          <t>New Balance 650 blanche montante</t>
         </is>
       </c>
       <c r="B30" s="9">
@@ -1219,30 +1219,53 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Adidas Yeezy 700 V3 Mono Safflower</t>
+        </is>
+      </c>
+      <c r="B31" s="9">
+        <f>'Stock complet'!B31</f>
+        <v/>
+      </c>
+      <c r="C31" s="10">
+        <f>'Stock complet'!C31</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>'Stock complet'!L31</f>
+        <v/>
+      </c>
+      <c r="E31" s="9">
+        <f>'Stock complet'!D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="17">
-        <f>SUM(B5:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="17">
-        <f>SUM(C5:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="17">
-        <f>SUM(D5:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="17">
-        <f>SUM(E5:E30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="B32" s="17">
+        <f>SUM(B5:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="17">
+        <f>SUM(C5:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>SUM(D5:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="17">
+        <f>SUM(E5:E31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>URSSAF = 12,3 % de cotisations + 0,1 % de CFP sur le prix encaissé. À provisionner à chaque vente.</t>
         </is>
@@ -1259,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1296,7 +1319,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26 lignes · 63 articles · trié par marge. Les 4 colonnes essentielles sont en tête. Lignes bleutées = lots.</t>
+          <t>27 lignes · 65 articles · trié par marge. Les 4 colonnes essentielles sont en tête. Lignes bleutées = lots.</t>
         </is>
       </c>
     </row>
@@ -2512,106 +2535,107 @@
       <c r="V16" s="22" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Robe Sandro Noaim blanche</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="n">
-        <v>50.04</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="D17" s="10">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Robby VP550W — pompes immergées 550 W ×2</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D17" s="6">
         <f>IF($C17="","",$C17-$B17-$L17-$M17)</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="19">
         <f>IF($D17="","",$D17/$B17)</f>
         <v/>
       </c>
-      <c r="F17" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9">
+      <c r="F17" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5">
         <f>$B17/$F17</f>
         <v/>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="5">
         <f>IF($C17="","",$C17/$F17)</f>
         <v/>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="5">
         <f>IF($D17="","",$D17/$F17)</f>
         <v/>
       </c>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="24">
+      <c r="J17" s="18" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="K17" s="19">
         <f>IF(OR($J17="",$C17=""),"",$C17/$J17-1)</f>
         <v/>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="5">
         <f>IF($C17="","",$C17*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="M17" s="9">
-        <f>IF($C17="","",$C17*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>Neuve avec étiquette</t>
-        </is>
-      </c>
-      <c r="Q17" s="26" t="inlineStr">
-        <is>
-          <t>Once Again −90 % · Stylight −99 %</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t>Pièce seule</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>Reçue</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="M17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Occasion, testées</t>
+        </is>
+      </c>
+      <c r="Q17" s="21" t="inlineStr">
+        <is>
+          <t>54,90 € neuve, idealo</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>À l'unité, 39 € pièce</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>Reçues</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V17" s="27" t="n"/>
+      <c r="V17" s="22" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Ballerines Massimo Dutti cuir rouge</t>
+          <t>Robe Sandro Noaim blanche</t>
         </is>
       </c>
       <c r="B18" s="23" t="n">
-        <v>25</v>
+        <v>50.04</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D18" s="10">
         <f>IF($C18="","",$C18-$B18-$L18-$M18)</f>
@@ -2636,9 +2660,7 @@
         <f>IF($D18="","",$D18/$F18)</f>
         <v/>
       </c>
-      <c r="J18" s="23" t="n">
-        <v>70</v>
-      </c>
+      <c r="J18" s="27" t="n"/>
       <c r="K18" s="24">
         <f>IF(OR($J18="",$C18=""),"",$C18/$J18-1)</f>
         <v/>
@@ -2658,22 +2680,22 @@
       </c>
       <c r="O18" s="8" t="inlineStr">
         <is>
-          <t>40 IT</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>Neuves avec boîte</t>
+          <t>Neuve avec étiquette</t>
         </is>
       </c>
       <c r="Q18" s="26" t="inlineStr">
         <is>
-          <t>70 €</t>
+          <t>Once Again −90 % · Stylight −99 %</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -2683,7 +2705,7 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>Reçues</t>
+          <t>Reçue</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -2696,14 +2718,14 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Robe bustier Chiara Ferragni noire</t>
+          <t>Ballerines Massimo Dutti cuir rouge</t>
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D19" s="10">
         <f>IF($C19="","",$C19-$B19-$L19-$M19)</f>
@@ -2728,7 +2750,9 @@
         <f>IF($D19="","",$D19/$F19)</f>
         <v/>
       </c>
-      <c r="J19" s="27" t="n"/>
+      <c r="J19" s="23" t="n">
+        <v>70</v>
+      </c>
       <c r="K19" s="24">
         <f>IF(OR($J19="",$C19=""),"",$C19/$J19-1)</f>
         <v/>
@@ -2748,22 +2772,22 @@
       </c>
       <c r="O19" s="8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>40 IT</t>
         </is>
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>Neuve avec étiquette</t>
+          <t>Neuves avec boîte</t>
         </is>
       </c>
       <c r="Q19" s="26" t="inlineStr">
         <is>
-          <t>YOOX −85 % · marque en crise</t>
+          <t>70 €</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
@@ -2773,7 +2797,7 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>Reçue</t>
+          <t>Reçues</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -2786,14 +2810,14 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Robe Pier Antonio Gaspari bleu marine</t>
+          <t>Robe bustier Chiara Ferragni noire</t>
         </is>
       </c>
       <c r="B20" s="23" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D20" s="10">
         <f>IF($C20="","",$C20-$B20-$L20-$M20)</f>
@@ -2838,17 +2862,17 @@
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>Neuve</t>
+          <t>Neuve avec étiquette</t>
         </is>
       </c>
       <c r="Q20" s="26" t="inlineStr">
         <is>
-          <t>YOOX −69 % · Joli Closet −70 %</t>
+          <t>YOOX −85 % · marque en crise</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
@@ -2876,14 +2900,14 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Baskets Geox gris / argent</t>
+          <t>Robe Pier Antonio Gaspari bleu marine</t>
         </is>
       </c>
       <c r="B21" s="23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D21" s="10">
         <f>IF($C21="","",$C21-$B21-$L21-$M21)</f>
@@ -2908,9 +2932,7 @@
         <f>IF($D21="","",$D21/$F21)</f>
         <v/>
       </c>
-      <c r="J21" s="23" t="n">
-        <v>55</v>
-      </c>
+      <c r="J21" s="27" t="n"/>
       <c r="K21" s="24">
         <f>IF(OR($J21="",$C21=""),"",$C21/$J21-1)</f>
         <v/>
@@ -2930,236 +2952,236 @@
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>Neuve</t>
+        </is>
+      </c>
+      <c r="Q21" s="26" t="inlineStr">
+        <is>
+          <t>YOOX −69 % · Joli Closet −70 %</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>Boutique + Leboncoin</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>Pièce seule</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>Reçue</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="V21" s="27" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Baskets Geox gris / argent</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="D22" s="10">
+        <f>IF($C22="","",$C22-$B22-$L22-$M22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>IF($D22="","",$D22/$B22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="9">
+        <f>$B22/$F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>IF($C22="","",$C22/$F22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="9">
+        <f>IF($D22="","",$D22/$F22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>55</v>
+      </c>
+      <c r="K22" s="24">
+        <f>IF(OR($J22="",$C22=""),"",$C22/$J22-1)</f>
+        <v/>
+      </c>
+      <c r="L22" s="9">
+        <f>IF($C22="","",$C22*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M22" s="9">
+        <f>IF($C22="","",$C22*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P21" s="8" t="inlineStr">
+      <c r="P22" s="8" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q21" s="26" t="inlineStr">
+      <c r="Q22" s="26" t="inlineStr">
         <is>
           <t>55 €</t>
         </is>
       </c>
-      <c r="R21" s="8" t="inlineStr">
+      <c r="R22" s="8" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr">
+      <c r="S22" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V21" s="27" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="V22" s="27" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Havaianas Slim fuchsia 35/36 ×10</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B23" s="18" t="n">
         <v>105</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C23" s="6" t="n">
         <v>139</v>
       </c>
-      <c r="D22" s="6">
-        <f>IF($C22="","",$C22-$B22-$L22-$M22)</f>
-        <v/>
-      </c>
-      <c r="E22" s="19">
-        <f>IF($D22="","",$D22/$B22)</f>
-        <v/>
-      </c>
-      <c r="F22" s="20" t="n">
+      <c r="D23" s="6">
+        <f>IF($C23="","",$C23-$B23-$L23-$M23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="19">
+        <f>IF($D23="","",$D23/$B23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="G22" s="5">
-        <f>$B22/$F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="5">
-        <f>IF($C22="","",$C22/$F22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="5">
-        <f>IF($D22="","",$D22/$F22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="18" t="n">
+      <c r="G23" s="5">
+        <f>$B23/$F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="5">
+        <f>IF($C23="","",$C23/$F23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="5">
+        <f>IF($D23="","",$D23/$F23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="K22" s="19">
-        <f>IF(OR($J22="",$C22=""),"",$C22/$J22-1)</f>
-        <v/>
-      </c>
-      <c r="L22" s="5">
-        <f>IF($C22="","",$C22*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M22" s="5">
-        <f>IF($C22="","",$C22*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="K23" s="19">
+        <f>IF(OR($J23="",$C23=""),"",$C23/$J23-1)</f>
+        <v/>
+      </c>
+      <c r="L23" s="5">
+        <f>IF($C23="","",$C23*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M23" s="5">
+        <f>IF($C23="","",$C23*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>Lot</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>35/36</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>Neuves avec boîte</t>
         </is>
       </c>
-      <c r="Q22" s="21" t="inlineStr">
+      <c r="Q23" s="21" t="inlineStr">
         <is>
           <t>20 € la paire</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr">
+      <c r="R23" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr">
+      <c r="S23" s="4" t="inlineStr">
         <is>
           <t>En lot</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr">
+      <c r="T23" s="4" t="inlineStr">
         <is>
           <t>Reçues</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr">
+      <c r="U23" s="4" t="inlineStr">
         <is>
           <t>URGENT — saisonnier</t>
         </is>
       </c>
-      <c r="V22" s="22" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Plein Sport montante blanc / violet</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="n">
-        <v>62</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="D23" s="10">
-        <f>IF($C23="","",$C23-$B23-$L23-$M23)</f>
-        <v/>
-      </c>
-      <c r="E23" s="24">
-        <f>IF($D23="","",$D23/$B23)</f>
-        <v/>
-      </c>
-      <c r="F23" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="9">
-        <f>$B23/$F23</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>IF($C23="","",$C23/$F23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="9">
-        <f>IF($D23="","",$D23/$F23)</f>
-        <v/>
-      </c>
-      <c r="J23" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="K23" s="24">
-        <f>IF(OR($J23="",$C23=""),"",$C23/$J23-1)</f>
-        <v/>
-      </c>
-      <c r="L23" s="9">
-        <f>IF($C23="","",$C23*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M23" s="9">
-        <f>IF($C23="","",$C23*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N23" s="8" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>Neuves avec boîte</t>
-        </is>
-      </c>
-      <c r="Q23" s="26" t="inlineStr">
-        <is>
-          <t>~100 € Stylight −63 %</t>
-        </is>
-      </c>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="S23" s="8" t="inlineStr">
-        <is>
-          <t>99 € puis 89 €</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>Reçues</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="V23" s="27" t="n"/>
+      <c r="V23" s="22" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Short ba&amp;sh Fegor lightusedblue</t>
+          <t>Plein Sport montante blanc / violet</t>
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>55.4</v>
+        <v>62</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D24" s="10">
         <f>IF($C24="","",$C24-$B24-$L24-$M24)</f>
@@ -3185,7 +3207,7 @@
         <v/>
       </c>
       <c r="J24" s="23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="K24" s="24">
         <f>IF(OR($J24="",$C24=""),"",$C24/$J24-1)</f>
@@ -3206,37 +3228,37 @@
       </c>
       <c r="O24" s="8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P24" s="8" t="inlineStr">
         <is>
-          <t>Neuf avec étiquette</t>
+          <t>Neuves avec boîte</t>
         </is>
       </c>
       <c r="Q24" s="26" t="inlineStr">
         <is>
-          <t>~75 € Modz −50 %</t>
+          <t>~100 € Stylight −63 %</t>
         </is>
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>Pièce seule</t>
+          <t>99 € puis 89 €</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>Reçu</t>
+          <t>Reçues</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="V24" s="27" t="n"/>
@@ -3244,14 +3266,14 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>New Balance GS 1906 Alkaline Green</t>
+          <t>Short ba&amp;sh Fegor lightusedblue</t>
         </is>
       </c>
       <c r="B25" s="23" t="n">
-        <v>80.59999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="D25" s="10">
         <f>IF($C25="","",$C25-$B25-$L25-$M25)</f>
@@ -3277,7 +3299,7 @@
         <v/>
       </c>
       <c r="J25" s="23" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K25" s="24">
         <f>IF(OR($J25="",$C25=""),"",$C25/$J25-1)</f>
@@ -3298,22 +3320,22 @@
       </c>
       <c r="O25" s="8" t="inlineStr">
         <is>
-          <t>38½</t>
+          <t>34</t>
         </is>
       </c>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>Neuves avec boîte</t>
+          <t>Neuf avec étiquette</t>
         </is>
       </c>
       <c r="Q25" s="26" t="inlineStr">
         <is>
-          <t>87 € StockX</t>
+          <t>~75 € Modz −50 %</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
@@ -3323,12 +3345,12 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>À recevoir</t>
+          <t>Reçu</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>Liquider</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="V25" s="27" t="n"/>
@@ -3336,14 +3358,14 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Baskets Emporio Armani bleu lavande</t>
+          <t>New Balance GS 1906 Alkaline Green</t>
         </is>
       </c>
       <c r="B26" s="23" t="n">
-        <v>55</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D26" s="10">
         <f>IF($C26="","",$C26-$B26-$L26-$M26)</f>
@@ -3369,7 +3391,7 @@
         <v/>
       </c>
       <c r="J26" s="23" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="K26" s="24">
         <f>IF(OR($J26="",$C26=""),"",$C26/$J26-1)</f>
@@ -3390,7 +3412,7 @@
       </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38½</t>
         </is>
       </c>
       <c r="P26" s="8" t="inlineStr">
@@ -3400,7 +3422,7 @@
       </c>
       <c r="Q26" s="26" t="inlineStr">
         <is>
-          <t>62 € eBay</t>
+          <t>87 € StockX</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
@@ -3415,7 +3437,7 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>Reçues</t>
+          <t>À recevoir</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -3428,14 +3450,14 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>New Balance BB80 blanc / marine</t>
+          <t>Baskets Emporio Armani bleu lavande</t>
         </is>
       </c>
       <c r="B27" s="23" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D27" s="10">
         <f>IF($C27="","",$C27-$B27-$L27-$M27)</f>
@@ -3461,7 +3483,7 @@
         <v/>
       </c>
       <c r="J27" s="23" t="n">
-        <v>54.99</v>
+        <v>62</v>
       </c>
       <c r="K27" s="24">
         <f>IF(OR($J27="",$C27=""),"",$C27/$J27-1)</f>
@@ -3482,7 +3504,7 @@
       </c>
       <c r="O27" s="8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="P27" s="8" t="inlineStr">
@@ -3492,7 +3514,7 @@
       </c>
       <c r="Q27" s="26" t="inlineStr">
         <is>
-          <t>54,99 € idealo</t>
+          <t>62 € eBay</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
@@ -3520,14 +3542,14 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Tommy Jeans baskets basses noir / blanc</t>
+          <t>New Balance BB80 blanc / marine</t>
         </is>
       </c>
       <c r="B28" s="23" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D28" s="10">
         <f>IF($C28="","",$C28-$B28-$L28-$M28)</f>
@@ -3553,7 +3575,7 @@
         <v/>
       </c>
       <c r="J28" s="23" t="n">
-        <v>60</v>
+        <v>54.99</v>
       </c>
       <c r="K28" s="24">
         <f>IF(OR($J28="",$C28=""),"",$C28/$J28-1)</f>
@@ -3574,7 +3596,7 @@
       </c>
       <c r="O28" s="8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="P28" s="8" t="inlineStr">
@@ -3584,12 +3606,12 @@
       </c>
       <c r="Q28" s="26" t="inlineStr">
         <is>
-          <t>60 € Stylight · 41 € officiel</t>
+          <t>54,99 € idealo</t>
         </is>
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -3612,7 +3634,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>New Balance 650 blanche montante</t>
+          <t>Tommy Jeans baskets basses noir / blanc</t>
         </is>
       </c>
       <c r="B29" s="23" t="n">
@@ -3645,7 +3667,7 @@
         <v/>
       </c>
       <c r="J29" s="23" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K29" s="24">
         <f>IF(OR($J29="",$C29=""),"",$C29/$J29-1)</f>
@@ -3666,7 +3688,7 @@
       </c>
       <c r="O29" s="8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P29" s="8" t="inlineStr">
@@ -3676,12 +3698,12 @@
       </c>
       <c r="Q29" s="26" t="inlineStr">
         <is>
-          <t>61 € idealo</t>
+          <t>60 € Stylight · 41 € officiel</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
@@ -3704,13 +3726,15 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Adidas Yeezy 700 V3 Mono Safflower</t>
+          <t>New Balance 650 blanche montante</t>
         </is>
       </c>
       <c r="B30" s="23" t="n">
-        <v>75.23999999999999</v>
-      </c>
-      <c r="C30" s="27" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>65</v>
+      </c>
       <c r="D30" s="10">
         <f>IF($C30="","",$C30-$B30-$L30-$M30)</f>
         <v/>
@@ -3734,7 +3758,9 @@
         <f>IF($D30="","",$D30/$F30)</f>
         <v/>
       </c>
-      <c r="J30" s="27" t="n"/>
+      <c r="J30" s="23" t="n">
+        <v>61</v>
+      </c>
       <c r="K30" s="24">
         <f>IF(OR($J30="",$C30=""),"",$C30/$J30-1)</f>
         <v/>
@@ -3754,105 +3780,193 @@
       </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>Neuves avec boîte</t>
+        </is>
+      </c>
+      <c r="Q30" s="26" t="inlineStr">
+        <is>
+          <t>61 € idealo</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>Pièce seule</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>Reçues</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="V30" s="27" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Adidas Yeezy 700 V3 Mono Safflower</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="10">
+        <f>IF($C31="","",$C31-$B31-$L31-$M31)</f>
+        <v/>
+      </c>
+      <c r="E31" s="24">
+        <f>IF($D31="","",$D31/$B31)</f>
+        <v/>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="9">
+        <f>$B31/$F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>IF($C31="","",$C31/$F31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="9">
+        <f>IF($D31="","",$D31/$F31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="27" t="n"/>
+      <c r="K31" s="24">
+        <f>IF(OR($J31="",$C31=""),"",$C31/$J31-1)</f>
+        <v/>
+      </c>
+      <c r="L31" s="9">
+        <f>IF($C31="","",$C31*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M31" s="9">
+        <f>IF($C31="","",$C31*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="P30" s="8" t="inlineStr">
+      <c r="P31" s="8" t="inlineStr">
         <is>
           <t>Occasion, portée</t>
         </is>
       </c>
-      <c r="Q30" s="26" t="inlineStr">
+      <c r="Q31" s="26" t="inlineStr">
         <is>
           <t>À établir après authentification</t>
         </is>
       </c>
-      <c r="R30" s="8" t="inlineStr">
+      <c r="R31" s="8" t="inlineStr">
         <is>
           <t>Vinted</t>
         </is>
       </c>
-      <c r="S30" s="8" t="inlineStr">
+      <c r="S31" s="8" t="inlineStr">
         <is>
           <t>Pièce seule</t>
         </is>
       </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>Authentification requise</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
       </c>
-      <c r="V30" s="27" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>TOTAL — 26 lignes</t>
-        </is>
-      </c>
-      <c r="B31" s="17">
-        <f>SUM(B5:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="17">
-        <f>SUM(C5:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="17">
-        <f>SUM(D5:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="32">
-        <f>D31/B31</f>
-        <v/>
-      </c>
-      <c r="F31" s="33">
-        <f>SUM(F5:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="34" t="n"/>
-      <c r="H31" s="34" t="n"/>
-      <c r="I31" s="34" t="n"/>
-      <c r="J31" s="34" t="n"/>
-      <c r="K31" s="34" t="n"/>
-      <c r="L31" s="17">
-        <f>SUM(L5:L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="17">
-        <f>SUM(M5:M30)</f>
-        <v/>
-      </c>
-      <c r="N31" s="34" t="n"/>
-      <c r="O31" s="34" t="n"/>
-      <c r="P31" s="34" t="n"/>
-      <c r="Q31" s="34" t="n"/>
-      <c r="R31" s="34" t="n"/>
-      <c r="S31" s="34" t="n"/>
-      <c r="T31" s="34" t="n"/>
-      <c r="U31" s="34" t="n"/>
-      <c r="V31" s="34" t="n"/>
+      <c r="V31" s="27" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL — 27 lignes</t>
+        </is>
+      </c>
+      <c r="B32" s="17">
+        <f>SUM(B5:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="17">
+        <f>SUM(C5:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>SUM(D5:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="32">
+        <f>D32/B32</f>
+        <v/>
+      </c>
+      <c r="F32" s="33">
+        <f>SUM(F5:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="34" t="n"/>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="34" t="n"/>
+      <c r="J32" s="34" t="n"/>
+      <c r="K32" s="34" t="n"/>
+      <c r="L32" s="17">
+        <f>SUM(L5:L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="17">
+        <f>SUM(M5:M31)</f>
+        <v/>
+      </c>
+      <c r="N32" s="34" t="n"/>
+      <c r="O32" s="34" t="n"/>
+      <c r="P32" s="34" t="n"/>
+      <c r="Q32" s="34" t="n"/>
+      <c r="R32" s="34" t="n"/>
+      <c r="S32" s="34" t="n"/>
+      <c r="T32" s="34" t="n"/>
+      <c r="U32" s="34" t="n"/>
+      <c r="V32" s="34" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Le coût total inclut la Yeezy (75,24 €) ; son prix de vente reste à établir.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V30"/>
-  <conditionalFormatting sqref="D5:D30">
+  <autoFilter ref="A4:V31"/>
+  <conditionalFormatting sqref="D5:D31">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K30">
+  <conditionalFormatting sqref="K5:K31">
     <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3903,7 +4017,7 @@
         </is>
       </c>
       <c r="B5" s="37">
-        <f>COUNTA('Stock complet'!A5:A30)</f>
+        <f>COUNTA('Stock complet'!A5:A31)</f>
         <v/>
       </c>
     </row>
@@ -3914,7 +4028,7 @@
         </is>
       </c>
       <c r="B6" s="39">
-        <f>'Stock complet'!F31</f>
+        <f>'Stock complet'!F32</f>
         <v/>
       </c>
     </row>
@@ -3943,7 +4057,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>'Stock complet'!B31</f>
+        <f>'Stock complet'!B32</f>
         <v/>
       </c>
     </row>
@@ -3954,7 +4068,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>'Stock complet'!C31</f>
+        <f>'Stock complet'!C32</f>
         <v/>
       </c>
     </row>
@@ -3965,7 +4079,7 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>-'Stock complet'!L31</f>
+        <f>-'Stock complet'!L32</f>
         <v/>
       </c>
     </row>
@@ -3976,7 +4090,7 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>-'Stock complet'!M31</f>
+        <f>-'Stock complet'!M32</f>
         <v/>
       </c>
     </row>
@@ -3986,7 +4100,7 @@
         <v/>
       </c>
       <c r="B14" s="17">
-        <f>'Stock complet'!D31</f>
+        <f>'Stock complet'!D32</f>
         <v/>
       </c>
     </row>
@@ -4004,7 +4118,7 @@
         </is>
       </c>
       <c r="B17" s="14">
-        <f>SUMIF('Stock complet'!V5:V30,"&lt;&gt;",'Stock complet'!C5:C30)</f>
+        <f>SUMIF('Stock complet'!V5:V31,"&lt;&gt;",'Stock complet'!C5:C31)</f>
         <v/>
       </c>
     </row>
@@ -4015,7 +4129,7 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>SUMIF('Stock complet'!V5:V30,"&lt;&gt;",'Stock complet'!D5:D30)</f>
+        <f>SUMIF('Stock complet'!V5:V31,"&lt;&gt;",'Stock complet'!D5:D31)</f>
         <v/>
       </c>
     </row>
@@ -4048,7 +4162,7 @@
         </is>
       </c>
       <c r="B21" s="9">
-        <f>B10-SUMIF('Stock complet'!V5:V30,"&lt;&gt;",'Stock complet'!B5:B30)</f>
+        <f>B10-SUMIF('Stock complet'!V5:V31,"&lt;&gt;",'Stock complet'!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -4403,11 +4517,11 @@
         </is>
       </c>
       <c r="B19" s="45" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20 uniques + 12 à l'unité + 2 lots</t>
+          <t>20 uniques + 14 à l'unité + 2 lots</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2544,7 +2544,7 @@
         <v>45</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D17" s="6">
         <f>IF($C17="","",$C17-$B17-$L17-$M17)</f>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>Occasion, testées</t>
+          <t>NEUVES</t>
         </is>
       </c>
       <c r="Q17" s="21" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>À l'unité, 39 € pièce</t>
+          <t>À l'unité, 49 € puis 44 €</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr">

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2544,7 +2544,7 @@
         <v>45</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D17" s="6">
         <f>IF($C17="","",$C17-$B17-$L17-$M17)</f>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>NEUVES</t>
+          <t>Très bon état, jamais utilisées</t>
         </is>
       </c>
       <c r="Q17" s="21" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>À l'unité, 49 € puis 44 €</t>
+          <t>À l'unité, 42 € pièce</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr">

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,7 +189,6 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -605,7 +604,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Le coût réel inclut l'adjudication, les frais acheteur et la livraison répartie au prorata.</t>
+          <t>Coût réel = adjudication + frais acheteur + frais plateforme + livraison répartie par article.</t>
         </is>
       </c>
     </row>
@@ -731,18 +730,18 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
+          <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>56.7</v>
+        <v>37.8</v>
       </c>
       <c r="C6" s="6">
-        <f>$B6*(1+Paramètres!$B$13)</f>
+        <f>$B6+$G6*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D6" s="7" t="n">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="E6" s="7">
         <f>IF($D6="","",$D6-$C6-$K6-$L6)</f>
@@ -753,7 +752,7 @@
         <v/>
       </c>
       <c r="G6" s="9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H6" s="6">
         <f>$C6/$G6</f>
@@ -775,40 +774,40 @@
         <v>0</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6354</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="R6" s="12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>357</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin B2B</t>
+          <t>eBay + Leboncoin</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>Février-mars</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr"/>
@@ -816,18 +815,18 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
+          <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>37.8</v>
+        <v>56.7</v>
       </c>
       <c r="C7" s="6">
-        <f>$B7*(1+Paramètres!$B$13)</f>
+        <f>$B7+$G7*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D7" s="7" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="E7" s="7">
         <f>IF($D7="","",$D7-$C7-$K7-$L7)</f>
@@ -838,7 +837,7 @@
         <v/>
       </c>
       <c r="G7" s="9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H7" s="6">
         <f>$C7/$G7</f>
@@ -860,40 +859,40 @@
         <v>0</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>7.8</v>
+        <v>11.7</v>
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-6354</t>
         </is>
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>eBay + Leboncoin</t>
+          <t>Leboncoin B2B</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr"/>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Février-mars</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
@@ -908,7 +907,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="6">
-        <f>$B8*(1+Paramètres!$B$13)</f>
+        <f>$B8+$G8*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D8" s="7" t="n">
@@ -994,7 +993,7 @@
         <v>20.45</v>
       </c>
       <c r="C9" s="6">
-        <f>$B9*(1+Paramètres!$B$13)</f>
+        <f>$B9+$G9*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D9" s="7" t="n">
@@ -1073,18 +1072,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Pokémon MEGA Munikis Zero M3 — boîte de 30 boosters</t>
+          <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>65</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="C10" s="6">
-        <f>$B10</f>
+        <f>$B10+$G10*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D10" s="7" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E10" s="7">
         <f>IF($D10="","",$D10-$C10-$K10-$L10)</f>
@@ -1095,7 +1094,7 @@
         <v/>
       </c>
       <c r="G10" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" s="6">
         <f>$C10/$G10</f>
@@ -1116,31 +1115,35 @@
       <c r="L10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
+      <c r="M10" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>8.57</v>
+      </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Vendeur au Japon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FB2026-46060</t>
         </is>
       </c>
       <c r="R10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>eBay + Leboncoin</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr"/>
@@ -1154,18 +1157,18 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Chaussures HOGAN P.36 — traces d'essayage</t>
+          <t>Pokémon MEGA Munikis Zero M3 — boîte de 30 boosters</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>12.6</v>
+        <v>65</v>
       </c>
       <c r="C11" s="6">
-        <f>$B11*(1+Paramètres!$B$13)</f>
+        <f>$B11</f>
         <v/>
       </c>
       <c r="D11" s="7" t="n">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="E11" s="7">
         <f>IF($D11="","",$D11-$C11-$K11-$L11)</f>
@@ -1176,7 +1179,7 @@
         <v/>
       </c>
       <c r="G11" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H11" s="6">
         <f>$C11/$G11</f>
@@ -1194,39 +1197,34 @@
         <f>IF($D11="","",$D11*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L11" s="6">
-        <f>IF($D11="","",$D11*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="L11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="13" t="n"/>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>Vendeur au Japon</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R11" s="12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>eBay + Leboncoin</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr"/>
@@ -1240,18 +1238,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
+          <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>68.56999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="C12" s="6">
-        <f>$B12*(1+Paramètres!$B$13)</f>
+        <f>$B12+$G12*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D12" s="7" t="n">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="E12" s="7">
         <f>IF($D12="","",$D12-$C12-$K12-$L12)</f>
@@ -1280,14 +1278,15 @@
         <f>IF($D12="","",$D12*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L12" s="6" t="n">
-        <v>0</v>
+      <c r="L12" s="6">
+        <f>IF($D12="","",$D12*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="M12" s="11" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>8.57</v>
+        <v>2.6</v>
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
@@ -1296,22 +1295,22 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46060</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="R12" s="12" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="T12" s="4" t="inlineStr"/>
@@ -1332,7 +1331,7 @@
         <v>37.8</v>
       </c>
       <c r="C13" s="6">
-        <f>$B13*(1+Paramètres!$B$13)</f>
+        <f>$B13+$G13*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D13" s="7" t="n">
@@ -1411,18 +1410,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
+          <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>37.8</v>
       </c>
       <c r="C14" s="6">
-        <f>$B14*(1+Paramètres!$B$13)</f>
+        <f>$B14+$G14*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D14" s="7" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E14" s="7">
         <f>IF($D14="","",$D14-$C14-$K14-$L14)</f>
@@ -1433,7 +1432,7 @@
         <v/>
       </c>
       <c r="G14" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6">
         <f>$C14/$G14</f>
@@ -1451,8 +1450,9 @@
         <f>IF($D14="","",$D14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L14" s="6" t="n">
-        <v>0</v>
+      <c r="L14" s="6">
+        <f>IF($D14="","",$D14*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="M14" s="11" t="n">
         <v>30</v>
@@ -1467,22 +1467,22 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46056</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="T14" s="4" t="inlineStr"/>
@@ -1496,18 +1496,18 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
+          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>100.8</v>
+        <v>37.8</v>
       </c>
       <c r="C15" s="6">
-        <f>$B15*(1+Paramètres!$B$13)</f>
+        <f>$B15+$G15*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D15" s="7" t="n">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="E15" s="7">
         <f>IF($D15="","",$D15-$C15-$K15-$L15)</f>
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="G15" s="9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H15" s="6">
         <f>$C15/$G15</f>
@@ -1540,40 +1540,40 @@
         <v>0</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>20.8</v>
+        <v>7.8</v>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5844</t>
+          <t>FB2026-46056</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>279</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, en lot</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr"/>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
@@ -1581,18 +1581,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Robe SANDRO T.40 — neuve</t>
+          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
         <v>37.8</v>
       </c>
       <c r="C16" s="6">
-        <f>$B16*(1+Paramètres!$B$13)</f>
+        <f>$B16+$G16*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D16" s="7" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E16" s="7">
         <f>IF($D16="","",$D16-$C16-$K16-$L16)</f>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="R16" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>434</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -1748,18 +1748,18 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
+          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>37.8</v>
+        <v>100.8</v>
       </c>
       <c r="C18" s="6">
-        <f>$B18*(1+Paramètres!$B$13)</f>
+        <f>$B18+$G18*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D18" s="7" t="n">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="E18" s="7">
         <f>IF($D18="","",$D18-$C18-$K18-$L18)</f>
@@ -1770,7 +1770,7 @@
         <v/>
       </c>
       <c r="G18" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H18" s="6">
         <f>$C18/$G18</f>
@@ -1788,19 +1788,18 @@
         <f>IF($D18="","",$D18*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L18" s="6">
-        <f>IF($D18="","",$D18*Paramètres!$B$7)</f>
-        <v/>
+      <c r="L18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>7.8</v>
+        <v>20.8</v>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
@@ -1810,23 +1809,23 @@
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-5844</t>
         </is>
       </c>
       <c r="R18" s="12" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>120</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin, en lot</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr"/>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr"/>
@@ -1834,18 +1833,18 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
+          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>37.8</v>
+        <v>50.4</v>
       </c>
       <c r="C19" s="6">
-        <f>$B19*(1+Paramètres!$B$13)</f>
+        <f>$B19+$G19*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D19" s="7" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E19" s="7">
         <f>IF($D19="","",$D19-$C19-$K19-$L19)</f>
@@ -1856,7 +1855,7 @@
         <v/>
       </c>
       <c r="G19" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" s="6">
         <f>$C19/$G19</f>
@@ -1874,14 +1873,15 @@
         <f>IF($D19="","",$D19*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
+      <c r="L19" s="6">
+        <f>IF($D19="","",$D19*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="M19" s="11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
@@ -1890,28 +1890,28 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43717</t>
+          <t>FB2026-44194</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr"/>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
@@ -1919,18 +1919,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
+          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>50.4</v>
+        <v>31.95</v>
       </c>
       <c r="C20" s="6">
-        <f>$B20*(1+Paramètres!$B$13)</f>
+        <f>$B20+$G20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E20" s="7">
         <f>IF($D20="","",$D20-$C20-$K20-$L20)</f>
@@ -1964,14 +1964,14 @@
         <v/>
       </c>
       <c r="M20" s="11" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N20" s="11" t="n">
-        <v>10.4</v>
+        <v>6.5</v>
       </c>
       <c r="O20" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="P20" s="12" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr"/>
@@ -2005,18 +2005,18 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
+          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>31.95</v>
+        <v>25.2</v>
       </c>
       <c r="C21" s="6">
-        <f>$B21*(1+Paramètres!$B$13)</f>
+        <f>$B21+$G21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E21" s="7">
         <f>IF($D21="","",$D21-$C21-$K21-$L21)</f>
@@ -2045,39 +2045,38 @@
         <f>IF($D21="","",$D21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L21" s="6">
-        <f>IF($D21="","",$D21*Paramètres!$B$7)</f>
-        <v/>
+      <c r="L21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N21" s="11" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="R21" s="12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>439</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr"/>
@@ -2091,14 +2090,14 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
+          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>25.2</v>
+        <v>25.56</v>
       </c>
       <c r="C22" s="6">
-        <f>$B22*(1+Paramètres!$B$13)</f>
+        <f>$B22+$G22*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D22" s="7" t="n">
@@ -2131,8 +2130,9 @@
         <f>IF($D22="","",$D22*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L22" s="6" t="n">
-        <v>0</v>
+      <c r="L22" s="6">
+        <f>IF($D22="","",$D22*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="M22" s="11" t="n">
         <v>20</v>
@@ -2142,27 +2142,27 @@
       </c>
       <c r="O22" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="R22" s="12" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>29</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="T22" s="4" t="inlineStr"/>
@@ -2176,18 +2176,18 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
+          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>25.56</v>
+        <v>37.8</v>
       </c>
       <c r="C23" s="6">
-        <f>$B23*(1+Paramètres!$B$13)</f>
+        <f>$B23+$G23*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D23" s="7" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E23" s="7">
         <f>IF($D23="","",$D23-$C23-$K23-$L23)</f>
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H23" s="6">
         <f>$C23/$G23</f>
@@ -2216,45 +2216,44 @@
         <f>IF($D23="","",$D23*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L23" s="6">
-        <f>IF($D23="","",$D23*Paramètres!$B$7)</f>
-        <v/>
+      <c r="L23" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-43717</t>
         </is>
       </c>
       <c r="R23" s="12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>303</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr"/>
       <c r="U23" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
@@ -2269,7 +2268,7 @@
         <v>57.51</v>
       </c>
       <c r="C24" s="6">
-        <f>$B24*(1+Paramètres!$B$13)</f>
+        <f>$B24+$G24*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D24" s="7" t="n">
@@ -2354,7 +2353,7 @@
         <v>21.73</v>
       </c>
       <c r="C25" s="6">
-        <f>$B25*(1+Paramètres!$B$13)</f>
+        <f>$B25+$G25*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D25" s="7" t="n">
@@ -2439,7 +2438,7 @@
         <v>50.4</v>
       </c>
       <c r="C26" s="6">
-        <f>$B26*(1+Paramètres!$B$13)</f>
+        <f>$B26+$G26*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D26" s="7" t="n">
@@ -2525,7 +2524,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="C27" s="6">
-        <f>$B27*(1+Paramètres!$B$13)</f>
+        <f>$B27+$G27*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D27" s="7" t="n">
@@ -2610,7 +2609,7 @@
         <v>76.68000000000001</v>
       </c>
       <c r="C28" s="16">
-        <f>$B28*(1+Paramètres!$B$13)</f>
+        <f>$B28+$G28*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D28" s="17" t="n">
@@ -2699,7 +2698,7 @@
         <v>51.12</v>
       </c>
       <c r="C29" s="6">
-        <f>$B29*(1+Paramètres!$B$13)</f>
+        <f>$B29+$G29*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D29" s="7" t="n">
@@ -2784,7 +2783,7 @@
         <v>38.34</v>
       </c>
       <c r="C30" s="6">
-        <f>$B30*(1+Paramètres!$B$13)</f>
+        <f>$B30+$G30*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D30" s="7" t="n">
@@ -2869,7 +2868,7 @@
         <v>51.12</v>
       </c>
       <c r="C31" s="6">
-        <f>$B31*(1+Paramètres!$B$13)</f>
+        <f>$B31+$G31*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D31" s="7" t="n">
@@ -2954,7 +2953,7 @@
         <v>52.4</v>
       </c>
       <c r="C32" s="6">
-        <f>$B32*(1+Paramètres!$B$13)</f>
+        <f>$B32+$G32*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D32" s="7" t="n">
@@ -3039,7 +3038,7 @@
         <v>19.17</v>
       </c>
       <c r="C33" s="25">
-        <f>$B33*(1+Paramètres!$B$13)</f>
+        <f>$B33+$G33*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D33" s="26" t="n"/>
@@ -3122,7 +3121,7 @@
         <v>25.2</v>
       </c>
       <c r="C34" s="25">
-        <f>$B34*(1+Paramètres!$B$13)</f>
+        <f>$B34+$G34*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D34" s="26" t="n"/>
@@ -3206,7 +3205,7 @@
         <v>38.34</v>
       </c>
       <c r="C35" s="25">
-        <f>$B35*(1+Paramètres!$B$13)</f>
+        <f>$B35+$G35*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D35" s="26" t="n"/>
@@ -3289,7 +3288,7 @@
         <v>50.4</v>
       </c>
       <c r="C36" s="25">
-        <f>$B36*(1+Paramètres!$B$13)</f>
+        <f>$B36+$G36*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D36" s="26" t="n"/>
@@ -3372,7 +3371,7 @@
         <v>50.4</v>
       </c>
       <c r="C37" s="25">
-        <f>$B37*(1+Paramètres!$B$13)</f>
+        <f>$B37+$G37*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D37" s="26" t="n"/>
@@ -3456,7 +3455,7 @@
         <v>57.51</v>
       </c>
       <c r="C38" s="25">
-        <f>$B38*(1+Paramètres!$B$13)</f>
+        <f>$B38+$G38*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D38" s="26" t="n"/>
@@ -3539,7 +3538,7 @@
         <v>63</v>
       </c>
       <c r="C39" s="25">
-        <f>$B39*(1+Paramètres!$B$13)</f>
+        <f>$B39+$G39*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D39" s="26" t="n"/>
@@ -3622,7 +3621,7 @@
         <v>63</v>
       </c>
       <c r="C40" s="6">
-        <f>$B40*(1+Paramètres!$B$13)</f>
+        <f>$B40+$G40*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D40" s="13" t="n"/>
@@ -3705,7 +3704,7 @@
         <v>113.4</v>
       </c>
       <c r="C41" s="25">
-        <f>$B41*(1+Paramètres!$B$13)</f>
+        <f>$B41+$G41*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D41" s="26" t="n"/>
@@ -3876,9 +3875,8 @@
           <t>Marchandise ADN</t>
         </is>
       </c>
-      <c r="B4" s="6">
-        <f>Paramètres!B12</f>
-        <v/>
+      <c r="B4" s="6" t="n">
+        <v>1637.35</v>
       </c>
     </row>
     <row r="5">
@@ -4204,31 +4202,31 @@
     <row r="12">
       <c r="A12" s="39" t="inlineStr">
         <is>
-          <t>Total marchandise ADN</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>1637.35</v>
+          <t>Nombre d'articles physiques reçus d'ADN</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>79</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34 lots</t>
+          <t>les lots comptent pour leur nombre de pièces</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="39" t="inlineStr">
         <is>
-          <t>Taux de livraison appliqué</t>
-        </is>
-      </c>
-      <c r="B13" s="46">
+          <t>Livraison par article</t>
+        </is>
+      </c>
+      <c r="B13" s="6">
         <f>B11/B12</f>
         <v/>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Réparti au prorata du prix d'achat</t>
+          <t>réparti au nombre d'articles, pas au prix</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4290,7 @@
           <t>Nombre d'annonces prévues</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
+      <c r="B21" s="46" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5920,32 +5918,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="48" t="inlineStr">
+      <c r="A42" s="47" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="B42" s="48" t="inlineStr">
+      <c r="B42" s="47" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C42" s="48" t="inlineStr">
+      <c r="C42" s="47" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="D42" s="48" t="inlineStr">
+      <c r="D42" s="47" t="inlineStr">
         <is>
           <t>Commande</t>
         </is>
       </c>
-      <c r="E42" s="48" t="inlineStr">
+      <c r="E42" s="47" t="inlineStr">
         <is>
           <t>Désignation</t>
         </is>
       </c>
-      <c r="F42" s="48" t="inlineStr">
+      <c r="F42" s="47" t="inlineStr">
         <is>
           <t>Total TTC</t>
         </is>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$V$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$W$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -592,6 +592,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -604,7 +605,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coût réel = adjudication + frais acheteur + frais plateforme + livraison répartie par article.</t>
+          <t>Coût réel = adjudication + frais acheteur + frais plateforme + livraison répartie par unité de vente.</t>
         </is>
       </c>
     </row>
@@ -726,22 +727,27 @@
           <t>Vendu le</t>
         </is>
       </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>Unités de vente</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
+          <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>37.8</v>
+        <v>56.7</v>
       </c>
       <c r="C6" s="6">
-        <f>$B6+$G6*Paramètres!$B$13</f>
+        <f>$B6+$W6*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D6" s="7" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="E6" s="7">
         <f>IF($D6="","",$D6-$C6-$K6-$L6)</f>
@@ -752,7 +758,7 @@
         <v/>
       </c>
       <c r="G6" s="9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H6" s="6">
         <f>$C6/$G6</f>
@@ -774,59 +780,62 @@
         <v>0</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>7.8</v>
+        <v>11.7</v>
       </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-6354</t>
         </is>
       </c>
       <c r="R6" s="12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>388</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>eBay + Leboncoin</t>
+          <t>Leboncoin B2B</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Février-mars</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
+          <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>56.7</v>
+        <v>37.8</v>
       </c>
       <c r="C7" s="6">
-        <f>$B7+$G7*Paramètres!$B$13</f>
+        <f>$B7+$W7*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D7" s="7" t="n">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="E7" s="7">
         <f>IF($D7="","",$D7-$C7-$K7-$L7)</f>
@@ -837,7 +846,7 @@
         <v/>
       </c>
       <c r="G7" s="9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H7" s="6">
         <f>$C7/$G7</f>
@@ -859,43 +868,46 @@
         <v>0</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6354</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>357</t>
         </is>
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin B2B</t>
+          <t>eBay + Leboncoin</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr"/>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>Février-mars</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -907,7 +919,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="6">
-        <f>$B8+$G8*Paramètres!$B$13</f>
+        <f>$B8+$W8*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D8" s="7" t="n">
@@ -982,6 +994,9 @@
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -993,7 +1008,7 @@
         <v>20.45</v>
       </c>
       <c r="C9" s="6">
-        <f>$B9+$G9*Paramètres!$B$13</f>
+        <f>$B9+$W9*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D9" s="7" t="n">
@@ -1068,6 +1083,9 @@
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1079,7 +1097,7 @@
         <v>68.56999999999999</v>
       </c>
       <c r="C10" s="6">
-        <f>$B10+$G10*Paramètres!$B$13</f>
+        <f>$B10+$W10*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D10" s="7" t="n">
@@ -1153,6 +1171,9 @@
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1234,6 +1255,9 @@
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1245,7 +1269,7 @@
         <v>12.6</v>
       </c>
       <c r="C12" s="6">
-        <f>$B12+$G12*Paramètres!$B$13</f>
+        <f>$B12+$W12*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D12" s="7" t="n">
@@ -1320,6 +1344,9 @@
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1331,7 +1358,7 @@
         <v>37.8</v>
       </c>
       <c r="C13" s="6">
-        <f>$B13+$G13*Paramètres!$B$13</f>
+        <f>$B13+$W13*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D13" s="7" t="n">
@@ -1406,22 +1433,25 @@
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Robe SANDRO T.40 — neuve</t>
+          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>37.8</v>
+        <v>100.8</v>
       </c>
       <c r="C14" s="6">
-        <f>$B14+$G14*Paramètres!$B$13</f>
+        <f>$B14+$W14*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D14" s="7" t="n">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="E14" s="7">
         <f>IF($D14="","",$D14-$C14-$K14-$L14)</f>
@@ -1432,7 +1462,7 @@
         <v/>
       </c>
       <c r="G14" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H14" s="6">
         <f>$C14/$G14</f>
@@ -1450,19 +1480,18 @@
         <f>IF($D14="","",$D14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L14" s="6">
-        <f>IF($D14="","",$D14*Paramètres!$B$7)</f>
-        <v/>
+      <c r="L14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>7.8</v>
+        <v>20.8</v>
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="P14" s="12" t="inlineStr">
@@ -1472,42 +1501,45 @@
       </c>
       <c r="Q14" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-5844</t>
         </is>
       </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>120</t>
         </is>
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin, en lot</t>
         </is>
       </c>
       <c r="T14" s="4" t="inlineStr"/>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
+          <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
         <v>37.8</v>
       </c>
       <c r="C15" s="6">
-        <f>$B15+$G15*Paramètres!$B$13</f>
+        <f>$B15+$W15*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D15" s="7" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E15" s="7">
         <f>IF($D15="","",$D15-$C15-$K15-$L15)</f>
@@ -1518,7 +1550,7 @@
         <v/>
       </c>
       <c r="G15" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6">
         <f>$C15/$G15</f>
@@ -1536,8 +1568,9 @@
         <f>IF($D15="","",$D15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
+      <c r="L15" s="6">
+        <f>IF($D15="","",$D15*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="M15" s="11" t="n">
         <v>30</v>
@@ -1552,22 +1585,22 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46056</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr"/>
@@ -1577,22 +1610,25 @@
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
+          <t>Lot de 2 pompes immergées ROBBY VP550W</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>37.8</v>
+        <v>45</v>
       </c>
       <c r="C16" s="6">
-        <f>$B16+$G16*Paramètres!$B$13</f>
+        <f>$B16</f>
         <v/>
       </c>
       <c r="D16" s="7" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E16" s="7">
         <f>IF($D16="","",$D16-$C16-$K16-$L16)</f>
@@ -1603,7 +1639,7 @@
         <v/>
       </c>
       <c r="G16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="6">
         <f>$C16/$G16</f>
@@ -1621,39 +1657,34 @@
         <f>IF($D16="","",$D16*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L16" s="6">
-        <f>IF($D16="","",$D16*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M16" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="N16" s="11" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="L16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN (facture à retrouver)</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R16" s="12" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>84</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin, main propre</t>
         </is>
       </c>
       <c r="T16" s="4" t="inlineStr"/>
@@ -1663,22 +1694,25 @@
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Lot de 2 pompes immergées ROBBY VP550W</t>
+          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>45</v>
+        <v>37.8</v>
       </c>
       <c r="C17" s="6">
-        <f>$B17</f>
+        <f>$B17+$W17*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D17" s="7" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E17" s="7">
         <f>IF($D17="","",$D17-$C17-$K17-$L17)</f>
@@ -1689,7 +1723,7 @@
         <v/>
       </c>
       <c r="G17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="6">
         <f>$C17/$G17</f>
@@ -1707,34 +1741,39 @@
         <f>IF($D17="","",$D17*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="L17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
+      <c r="L17" s="6">
+        <f>IF($D17="","",$D17*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>7.8</v>
+      </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>ADN (facture à retrouver)</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="R17" s="12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>434</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr"/>
@@ -1744,22 +1783,25 @@
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
+          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>100.8</v>
+        <v>37.8</v>
       </c>
       <c r="C18" s="6">
-        <f>$B18+$G18*Paramètres!$B$13</f>
+        <f>$B18+$W18*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D18" s="7" t="n">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="E18" s="7">
         <f>IF($D18="","",$D18-$C18-$K18-$L18)</f>
@@ -1770,7 +1812,7 @@
         <v/>
       </c>
       <c r="G18" s="9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H18" s="6">
         <f>$C18/$G18</f>
@@ -1792,43 +1834,46 @@
         <v>0</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>20.8</v>
+        <v>7.8</v>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5844</t>
+          <t>FB2026-46056</t>
         </is>
       </c>
       <c r="R18" s="12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>279</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, en lot</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr"/>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1840,7 +1885,7 @@
         <v>50.4</v>
       </c>
       <c r="C19" s="6">
-        <f>$B19+$G19*Paramètres!$B$13</f>
+        <f>$B19+$W19*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D19" s="7" t="n">
@@ -1915,6 +1960,9 @@
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1926,7 +1974,7 @@
         <v>31.95</v>
       </c>
       <c r="C20" s="6">
-        <f>$B20+$G20*Paramètres!$B$13</f>
+        <f>$B20+$W20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7" t="n">
@@ -2001,6 +2049,9 @@
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2012,7 +2063,7 @@
         <v>25.2</v>
       </c>
       <c r="C21" s="6">
-        <f>$B21+$G21*Paramètres!$B$13</f>
+        <f>$B21+$W21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7" t="n">
@@ -2086,6 +2137,9 @@
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2097,7 +2151,7 @@
         <v>25.56</v>
       </c>
       <c r="C22" s="6">
-        <f>$B22+$G22*Paramètres!$B$13</f>
+        <f>$B22+$W22*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D22" s="7" t="n">
@@ -2172,22 +2226,25 @@
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
+          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>37.8</v>
+        <v>57.51</v>
       </c>
       <c r="C23" s="6">
-        <f>$B23+$G23*Paramètres!$B$13</f>
+        <f>$B23+$W23*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D23" s="7" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E23" s="7">
         <f>IF($D23="","",$D23-$C23-$K23-$L23)</f>
@@ -2198,7 +2255,7 @@
         <v/>
       </c>
       <c r="G23" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" s="6">
         <f>$C23/$G23</f>
@@ -2220,59 +2277,62 @@
         <v>0</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>7.8</v>
+        <v>11.7</v>
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43717</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="R23" s="12" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>159</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr"/>
       <c r="U23" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
+          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>57.51</v>
+        <v>37.8</v>
       </c>
       <c r="C24" s="6">
-        <f>$B24+$G24*Paramètres!$B$13</f>
+        <f>$B24+$W24*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D24" s="7" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E24" s="7">
         <f>IF($D24="","",$D24-$C24-$K24-$L24)</f>
@@ -2283,7 +2343,7 @@
         <v/>
       </c>
       <c r="G24" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24" s="6">
         <f>$C24/$G24</f>
@@ -2305,43 +2365,46 @@
         <v>0</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N24" s="11" t="n">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="O24" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-43717</t>
         </is>
       </c>
       <c r="R24" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>303</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="T24" s="4" t="inlineStr"/>
       <c r="U24" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2353,7 +2416,7 @@
         <v>21.73</v>
       </c>
       <c r="C25" s="6">
-        <f>$B25+$G25*Paramètres!$B$13</f>
+        <f>$B25+$W25*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D25" s="7" t="n">
@@ -2427,6 +2490,9 @@
         </is>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
+      <c r="W25" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2438,7 +2504,7 @@
         <v>50.4</v>
       </c>
       <c r="C26" s="6">
-        <f>$B26+$G26*Paramètres!$B$13</f>
+        <f>$B26+$W26*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D26" s="7" t="n">
@@ -2513,6 +2579,9 @@
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2524,7 +2593,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="C27" s="6">
-        <f>$B27+$G27*Paramètres!$B$13</f>
+        <f>$B27+$W27*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D27" s="7" t="n">
@@ -2598,6 +2667,9 @@
         </is>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -2609,7 +2681,7 @@
         <v>76.68000000000001</v>
       </c>
       <c r="C28" s="16">
-        <f>$B28+$G28*Paramètres!$B$13</f>
+        <f>$B28+$W28*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D28" s="17" t="n">
@@ -2687,6 +2759,9 @@
           <t>12/08/2026</t>
         </is>
       </c>
+      <c r="W28" s="14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2698,7 +2773,7 @@
         <v>51.12</v>
       </c>
       <c r="C29" s="6">
-        <f>$B29+$G29*Paramètres!$B$13</f>
+        <f>$B29+$W29*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D29" s="7" t="n">
@@ -2772,6 +2847,9 @@
         </is>
       </c>
       <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2783,7 +2861,7 @@
         <v>38.34</v>
       </c>
       <c r="C30" s="6">
-        <f>$B30+$G30*Paramètres!$B$13</f>
+        <f>$B30+$W30*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D30" s="7" t="n">
@@ -2857,6 +2935,9 @@
         </is>
       </c>
       <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2868,7 +2949,7 @@
         <v>51.12</v>
       </c>
       <c r="C31" s="6">
-        <f>$B31+$G31*Paramètres!$B$13</f>
+        <f>$B31+$W31*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D31" s="7" t="n">
@@ -2942,6 +3023,9 @@
         </is>
       </c>
       <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2953,7 +3037,7 @@
         <v>52.4</v>
       </c>
       <c r="C32" s="6">
-        <f>$B32+$G32*Paramètres!$B$13</f>
+        <f>$B32+$W32*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D32" s="7" t="n">
@@ -3027,6 +3111,9 @@
         </is>
       </c>
       <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
@@ -3038,7 +3125,7 @@
         <v>19.17</v>
       </c>
       <c r="C33" s="25">
-        <f>$B33+$G33*Paramètres!$B$13</f>
+        <f>$B33+$W33*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D33" s="26" t="n"/>
@@ -3110,6 +3197,9 @@
         </is>
       </c>
       <c r="V33" s="23" t="inlineStr"/>
+      <c r="W33" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
@@ -3121,7 +3211,7 @@
         <v>25.2</v>
       </c>
       <c r="C34" s="25">
-        <f>$B34+$G34*Paramètres!$B$13</f>
+        <f>$B34+$W34*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D34" s="26" t="n"/>
@@ -3194,6 +3284,9 @@
         </is>
       </c>
       <c r="V34" s="23" t="inlineStr"/>
+      <c r="W34" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
@@ -3205,7 +3298,7 @@
         <v>38.34</v>
       </c>
       <c r="C35" s="25">
-        <f>$B35+$G35*Paramètres!$B$13</f>
+        <f>$B35+$W35*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D35" s="26" t="n"/>
@@ -3277,6 +3370,9 @@
         </is>
       </c>
       <c r="V35" s="23" t="inlineStr"/>
+      <c r="W35" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="23" t="inlineStr">
@@ -3288,7 +3384,7 @@
         <v>50.4</v>
       </c>
       <c r="C36" s="25">
-        <f>$B36+$G36*Paramètres!$B$13</f>
+        <f>$B36+$W36*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D36" s="26" t="n"/>
@@ -3360,6 +3456,9 @@
         </is>
       </c>
       <c r="V36" s="23" t="inlineStr"/>
+      <c r="W36" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
@@ -3371,7 +3470,7 @@
         <v>50.4</v>
       </c>
       <c r="C37" s="25">
-        <f>$B37+$G37*Paramètres!$B$13</f>
+        <f>$B37+$W37*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D37" s="26" t="n"/>
@@ -3444,6 +3543,9 @@
         </is>
       </c>
       <c r="V37" s="23" t="inlineStr"/>
+      <c r="W37" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="23" t="inlineStr">
@@ -3455,7 +3557,7 @@
         <v>57.51</v>
       </c>
       <c r="C38" s="25">
-        <f>$B38+$G38*Paramètres!$B$13</f>
+        <f>$B38+$W38*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D38" s="26" t="n"/>
@@ -3527,6 +3629,9 @@
         </is>
       </c>
       <c r="V38" s="23" t="inlineStr"/>
+      <c r="W38" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
@@ -3538,7 +3643,7 @@
         <v>63</v>
       </c>
       <c r="C39" s="25">
-        <f>$B39+$G39*Paramètres!$B$13</f>
+        <f>$B39+$W39*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D39" s="26" t="n"/>
@@ -3610,6 +3715,9 @@
         </is>
       </c>
       <c r="V39" s="23" t="inlineStr"/>
+      <c r="W39" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3621,7 +3729,7 @@
         <v>63</v>
       </c>
       <c r="C40" s="6">
-        <f>$B40+$G40*Paramètres!$B$13</f>
+        <f>$B40+$W40*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D40" s="13" t="n"/>
@@ -3693,6 +3801,9 @@
         </is>
       </c>
       <c r="V40" s="4" t="inlineStr"/>
+      <c r="W40" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
@@ -3704,7 +3815,7 @@
         <v>113.4</v>
       </c>
       <c r="C41" s="25">
-        <f>$B41+$G41*Paramètres!$B$13</f>
+        <f>$B41+$W41*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D41" s="26" t="n"/>
@@ -3777,6 +3888,9 @@
         </is>
       </c>
       <c r="V41" s="23" t="inlineStr"/>
+      <c r="W41" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
@@ -3829,9 +3943,10 @@
       <c r="T42" s="37" t="n"/>
       <c r="U42" s="37" t="n"/>
       <c r="V42" s="37" t="n"/>
+      <c r="W42" s="37" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:V41"/>
+  <autoFilter ref="A5:W41"/>
   <conditionalFormatting sqref="E6:E41">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>10</formula>
@@ -4202,22 +4317,22 @@
     <row r="12">
       <c r="A12" s="39" t="inlineStr">
         <is>
-          <t>Nombre d'articles physiques reçus d'ADN</t>
+          <t>Unités de vente reçues d'ADN</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>les lots comptent pour leur nombre de pièces</t>
+          <t>un lot vendu en bloc compte pour 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="39" t="inlineStr">
         <is>
-          <t>Livraison par article</t>
+          <t>Livraison par unité de vente</t>
         </is>
       </c>
       <c r="B13" s="6">
@@ -4226,7 +4341,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>réparti au nombre d'articles, pas au prix</t>
+          <t>réparti au nombre de colis à expédier</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$W$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$X$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,12 +67,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
+      <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00C0392B"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -151,9 +151,9 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,32 +161,33 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -567,32 +568,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="7" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,100 +636,105 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Seuil d'équilibre</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>PRIX DE VENTE</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Marge nette</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Rendement</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Nb</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Coût / art.</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Prix / art.</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Marge / art.</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>URSSAF</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Carte</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Adjugé</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Frais acheteur</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Lot</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Vendu le</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Unités de vente</t>
         </is>
@@ -743,81 +750,85 @@
         <v>56.7</v>
       </c>
       <c r="C6" s="6">
-        <f>$B6+$W6*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D6" s="7" t="n">
+        <f>$B6+$X6*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D6" s="7">
+        <f>$C6/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>199</v>
       </c>
-      <c r="E6" s="7">
-        <f>IF($D6="","",$D6-$C6-$K6-$L6)</f>
-        <v/>
-      </c>
       <c r="F6" s="8">
-        <f>IF($E6="","",$E6/$C6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="9" t="n">
+        <f>IF($E6="","",$E6-$C6-$L6-$M6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="9">
+        <f>IF($F6="","",$F6/$C6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="6">
-        <f>$C6/$G6</f>
-        <v/>
-      </c>
       <c r="I6" s="6">
-        <f>IF($D6="","",$D6/$G6)</f>
+        <f>$C6/$H6</f>
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF($E6="","",$E6/$G6)</f>
-        <v/>
-      </c>
-      <c r="K6" s="10">
-        <f>IF($D6="","",$D6*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L6" s="6" t="n">
+        <f>IF($E6="","",$E6/$H6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="6">
+        <f>IF($F6="","",$F6/$H6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="7">
+        <f>IF($E6="","",$E6*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="N6" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="O6" s="11" t="n">
         <v>11.7</v>
       </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P6" s="12" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr">
         <is>
           <t>FB2026-6354</t>
         </is>
       </c>
-      <c r="R6" s="12" t="inlineStr">
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>Leboncoin B2B</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>Février-mars</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="n">
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -831,81 +842,85 @@
         <v>37.8</v>
       </c>
       <c r="C7" s="6">
-        <f>$B7+$W7*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D7" s="7" t="n">
+        <f>$B7+$X7*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
+        <f>$C7/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>178</v>
       </c>
-      <c r="E7" s="7">
-        <f>IF($D7="","",$D7-$C7-$K7-$L7)</f>
-        <v/>
-      </c>
       <c r="F7" s="8">
-        <f>IF($E7="","",$E7/$C7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="9" t="n">
+        <f>IF($E7="","",$E7-$C7-$L7-$M7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>IF($F7="","",$F7/$C7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="6">
-        <f>$C7/$G7</f>
-        <v/>
-      </c>
       <c r="I7" s="6">
-        <f>IF($D7="","",$D7/$G7)</f>
+        <f>$C7/$H7</f>
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF($E7="","",$E7/$G7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="10">
-        <f>IF($D7="","",$D7*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L7" s="6" t="n">
+        <f>IF($E7="","",$E7/$H7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="6">
+        <f>IF($F7="","",$F7/$H7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="7">
+        <f>IF($E7="","",$E7*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="N7" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="O7" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P7" s="12" t="inlineStr">
+      <c r="Q7" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="R7" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R7" s="12" t="inlineStr">
+      <c r="S7" s="12" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="n">
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -919,82 +934,86 @@
         <v>63</v>
       </c>
       <c r="C8" s="6">
-        <f>$B8+$W8*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D8" s="7" t="n">
+        <f>$B8+$X8*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D8" s="7">
+        <f>$C8/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>159</v>
       </c>
-      <c r="E8" s="7">
-        <f>IF($D8="","",$D8-$C8-$K8-$L8)</f>
-        <v/>
-      </c>
       <c r="F8" s="8">
-        <f>IF($E8="","",$E8/$C8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="9" t="n">
+        <f>IF($E8="","",$E8-$C8-$L8-$M8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>IF($F8="","",$F8/$C8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="6">
-        <f>$C8/$G8</f>
-        <v/>
-      </c>
       <c r="I8" s="6">
-        <f>IF($D8="","",$D8/$G8)</f>
+        <f>$C8/$H8</f>
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF($E8="","",$E8/$G8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="10">
-        <f>IF($D8="","",$D8*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L8" s="6">
-        <f>IF($D8="","",$D8*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M8" s="11" t="n">
+        <f>IF($E8="","",$E8/$H8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="6">
+        <f>IF($F8="","",$F8/$H8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="7">
+        <f>IF($E8="","",$E8*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M8" s="6">
+        <f>IF($E8="","",$E8*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N8" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="O8" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P8" s="12" t="inlineStr">
+      <c r="Q8" s="12" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="Q8" s="12" t="inlineStr">
+      <c r="R8" s="12" t="inlineStr">
         <is>
           <t>FB2026-46058</t>
         </is>
       </c>
-      <c r="R8" s="12" t="inlineStr">
+      <c r="S8" s="12" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="n">
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1008,82 +1027,86 @@
         <v>20.45</v>
       </c>
       <c r="C9" s="6">
-        <f>$B9+$W9*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D9" s="7" t="n">
+        <f>$B9+$X9*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
+        <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="E9" s="7">
-        <f>IF($D9="","",$D9-$C9-$K9-$L9)</f>
-        <v/>
-      </c>
       <c r="F9" s="8">
-        <f>IF($E9="","",$E9/$C9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="9" t="n">
+        <f>IF($E9="","",$E9-$C9-$L9-$M9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>IF($F9="","",$F9/$C9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="6">
-        <f>$C9/$G9</f>
-        <v/>
-      </c>
       <c r="I9" s="6">
-        <f>IF($D9="","",$D9/$G9)</f>
+        <f>$C9/$H9</f>
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF($E9="","",$E9/$G9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="10">
-        <f>IF($D9="","",$D9*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L9" s="6">
-        <f>IF($D9="","",$D9*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M9" s="11" t="n">
+        <f>IF($E9="","",$E9/$H9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="6">
+        <f>IF($F9="","",$F9/$H9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="7">
+        <f>IF($E9="","",$E9*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M9" s="6">
+        <f>IF($E9="","",$E9*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N9" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="O9" s="11" t="n">
         <v>4.16</v>
       </c>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P9" s="12" t="inlineStr">
+      <c r="Q9" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q9" s="12" t="inlineStr">
+      <c r="R9" s="12" t="inlineStr">
         <is>
           <t>FB2026-5996</t>
         </is>
       </c>
-      <c r="R9" s="12" t="inlineStr">
+      <c r="S9" s="12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="n">
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1097,81 +1120,85 @@
         <v>68.56999999999999</v>
       </c>
       <c r="C10" s="6">
-        <f>$B10+$W10*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D10" s="7" t="n">
+        <f>$B10+$X10*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
+        <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E10" s="8" t="n">
         <v>139</v>
       </c>
-      <c r="E10" s="7">
-        <f>IF($D10="","",$D10-$C10-$K10-$L10)</f>
-        <v/>
-      </c>
       <c r="F10" s="8">
-        <f>IF($E10="","",$E10/$C10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="9" t="n">
+        <f>IF($E10="","",$E10-$C10-$L10-$M10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="9">
+        <f>IF($F10="","",$F10/$C10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="6">
-        <f>$C10/$G10</f>
-        <v/>
-      </c>
       <c r="I10" s="6">
-        <f>IF($D10="","",$D10/$G10)</f>
+        <f>$C10/$H10</f>
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF($E10="","",$E10/$G10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="10">
-        <f>IF($D10="","",$D10*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L10" s="6" t="n">
+        <f>IF($E10="","",$E10/$H10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="6">
+        <f>IF($F10="","",$F10/$H10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="7">
+        <f>IF($E10="","",$E10*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="N10" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="N10" s="11" t="n">
+      <c r="O10" s="11" t="n">
         <v>8.57</v>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="Q10" s="12" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="Q10" s="12" t="inlineStr">
+      <c r="R10" s="12" t="inlineStr">
         <is>
           <t>FB2026-46060</t>
         </is>
       </c>
-      <c r="R10" s="12" t="inlineStr">
+      <c r="S10" s="12" t="inlineStr">
         <is>
           <t>1350</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr">
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr">
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="n">
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1188,74 +1215,78 @@
         <f>$B11</f>
         <v/>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="7">
+        <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>132</v>
       </c>
-      <c r="E11" s="7">
-        <f>IF($D11="","",$D11-$C11-$K11-$L11)</f>
-        <v/>
-      </c>
       <c r="F11" s="8">
-        <f>IF($E11="","",$E11/$C11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="9" t="n">
+        <f>IF($E11="","",$E11-$C11-$L11-$M11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>IF($F11="","",$F11/$C11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="6">
-        <f>$C11/$G11</f>
-        <v/>
-      </c>
       <c r="I11" s="6">
-        <f>IF($D11="","",$D11/$G11)</f>
+        <f>$C11/$H11</f>
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF($E11="","",$E11/$G11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="10">
-        <f>IF($D11="","",$D11*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L11" s="6" t="n">
+        <f>IF($E11="","",$E11/$H11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="6">
+        <f>IF($F11="","",$F11/$H11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="7">
+        <f>IF($E11="","",$E11*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="13" t="n"/>
       <c r="N11" s="13" t="n"/>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="O11" s="13" t="n"/>
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>Vendeur au Japon</t>
         </is>
       </c>
-      <c r="P11" s="12" t="inlineStr">
+      <c r="Q11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q11" s="12" t="inlineStr">
+      <c r="R11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R11" s="12" t="inlineStr">
+      <c r="S11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="n">
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1269,82 +1300,86 @@
         <v>12.6</v>
       </c>
       <c r="C12" s="6">
-        <f>$B12+$W12*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D12" s="7" t="n">
+        <f>$B12+$X12*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
+        <f>$C12/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="E12" s="7">
-        <f>IF($D12="","",$D12-$C12-$K12-$L12)</f>
-        <v/>
-      </c>
       <c r="F12" s="8">
-        <f>IF($E12="","",$E12/$C12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="9" t="n">
+        <f>IF($E12="","",$E12-$C12-$L12-$M12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>IF($F12="","",$F12/$C12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="6">
-        <f>$C12/$G12</f>
-        <v/>
-      </c>
       <c r="I12" s="6">
-        <f>IF($D12="","",$D12/$G12)</f>
+        <f>$C12/$H12</f>
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF($E12="","",$E12/$G12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="10">
-        <f>IF($D12="","",$D12*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L12" s="6">
-        <f>IF($D12="","",$D12*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M12" s="11" t="n">
+        <f>IF($E12="","",$E12/$H12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="6">
+        <f>IF($F12="","",$F12/$H12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="7">
+        <f>IF($E12="","",$E12*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M12" s="6">
+        <f>IF($E12="","",$E12*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="N12" s="11" t="n">
+      <c r="O12" s="11" t="n">
         <v>2.6</v>
       </c>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="Q12" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q12" s="12" t="inlineStr">
+      <c r="R12" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R12" s="12" t="inlineStr">
+      <c r="S12" s="12" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="4" t="n">
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1358,260 +1393,272 @@
         <v>37.8</v>
       </c>
       <c r="C13" s="6">
-        <f>$B13+$W13*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D13" s="7" t="n">
+        <f>$B13+$X13*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>$C13/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="E13" s="7">
-        <f>IF($D13="","",$D13-$C13-$K13-$L13)</f>
-        <v/>
-      </c>
       <c r="F13" s="8">
-        <f>IF($E13="","",$E13/$C13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="9" t="n">
+        <f>IF($E13="","",$E13-$C13-$L13-$M13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>IF($F13="","",$F13/$C13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="6">
-        <f>$C13/$G13</f>
-        <v/>
-      </c>
       <c r="I13" s="6">
-        <f>IF($D13="","",$D13/$G13)</f>
+        <f>$C13/$H13</f>
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF($E13="","",$E13/$G13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="10">
-        <f>IF($D13="","",$D13*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L13" s="6">
-        <f>IF($D13="","",$D13*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M13" s="11" t="n">
+        <f>IF($E13="","",$E13/$H13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="6">
+        <f>IF($F13="","",$F13/$H13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="7">
+        <f>IF($E13="","",$E13*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M13" s="6">
+        <f>IF($E13="","",$E13*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N13" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N13" s="11" t="n">
+      <c r="O13" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="Q13" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q13" s="12" t="inlineStr">
+      <c r="R13" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R13" s="12" t="inlineStr">
+      <c r="S13" s="12" t="inlineStr">
         <is>
           <t>417</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr"/>
-      <c r="W13" s="4" t="n">
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
+          <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>100.8</v>
+        <v>37.8</v>
       </c>
       <c r="C14" s="6">
-        <f>$B14+$W14*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>159</v>
-      </c>
-      <c r="E14" s="7">
-        <f>IF($D14="","",$D14-$C14-$K14-$L14)</f>
-        <v/>
+        <f>$B14+$X14*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D14" s="7">
+        <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="F14" s="8">
-        <f>IF($E14="","",$E14/$C14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H14" s="6">
-        <f>$C14/$G14</f>
-        <v/>
+        <f>IF($E14="","",$E14-$C14-$L14-$M14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>IF($F14="","",$F14/$C14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="I14" s="6">
-        <f>IF($D14="","",$D14/$G14)</f>
+        <f>$C14/$H14</f>
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF($E14="","",$E14/$G14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="10">
-        <f>IF($D14="","",$D14*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="11" t="n">
-        <v>80</v>
+        <f>IF($E14="","",$E14/$H14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="6">
+        <f>IF($F14="","",$F14/$H14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="7">
+        <f>IF($E14="","",$E14*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M14" s="6">
+        <f>IF($E14="","",$E14*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="N14" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>7.8</v>
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="Q14" s="12" t="inlineStr">
+        <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q14" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-5844</t>
-        </is>
-      </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin, en lot</t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>URGENT — saisonnier</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="4" t="n">
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="S14" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>Boutique</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Robe SANDRO T.40 — neuve</t>
+          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
         <v>37.8</v>
       </c>
       <c r="C15" s="6">
-        <f>$B15+$W15*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="E15" s="7">
-        <f>IF($D15="","",$D15-$C15-$K15-$L15)</f>
-        <v/>
+        <f>$B15+$X15*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D15" s="7">
+        <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>92</v>
       </c>
       <c r="F15" s="8">
-        <f>IF($E15="","",$E15/$C15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="6">
-        <f>$C15/$G15</f>
-        <v/>
+        <f>IF($E15="","",$E15-$C15-$L15-$M15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="9">
+        <f>IF($F15="","",$F15/$C15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="I15" s="6">
-        <f>IF($D15="","",$D15/$G15)</f>
+        <f>$C15/$H15</f>
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF($E15="","",$E15/$G15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="10">
-        <f>IF($D15="","",$D15*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L15" s="6">
-        <f>IF($D15="","",$D15*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M15" s="11" t="n">
+        <f>IF($E15="","",$E15/$H15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="6">
+        <f>IF($F15="","",$F15/$H15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="7">
+        <f>IF($E15="","",$E15*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="O15" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="O15" s="12" t="inlineStr">
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P15" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr">
+          <t>FB2026-46056</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V15" s="4" t="inlineStr"/>
-      <c r="W15" s="4" t="n">
-        <v>1</v>
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1627,74 +1674,78 @@
         <f>$B16</f>
         <v/>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="7">
+        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E16" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="E16" s="7">
-        <f>IF($D16="","",$D16-$C16-$K16-$L16)</f>
-        <v/>
-      </c>
       <c r="F16" s="8">
-        <f>IF($E16="","",$E16/$C16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="9" t="n">
+        <f>IF($E16="","",$E16-$C16-$L16-$M16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="9">
+        <f>IF($F16="","",$F16/$C16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="6">
-        <f>$C16/$G16</f>
-        <v/>
-      </c>
       <c r="I16" s="6">
-        <f>IF($D16="","",$D16/$G16)</f>
+        <f>$C16/$H16</f>
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF($E16="","",$E16/$G16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="10">
-        <f>IF($D16="","",$D16*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L16" s="6" t="n">
+        <f>IF($E16="","",$E16/$H16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="6">
+        <f>IF($F16="","",$F16/$H16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="7">
+        <f>IF($E16="","",$E16*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
-      <c r="O16" s="12" t="inlineStr">
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="12" t="inlineStr">
         <is>
           <t>ADN (facture à retrouver)</t>
         </is>
       </c>
-      <c r="P16" s="12" t="inlineStr">
+      <c r="Q16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q16" s="12" t="inlineStr">
+      <c r="R16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R16" s="12" t="inlineStr">
+      <c r="S16" s="12" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr">
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="n">
+      <c r="W16" s="4" t="inlineStr"/>
+      <c r="X16" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1708,171 +1759,183 @@
         <v>37.8</v>
       </c>
       <c r="C17" s="6">
-        <f>$B17+$W17*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D17" s="7" t="n">
+        <f>$B17+$X17*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D17" s="7">
+        <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E17" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="E17" s="7">
-        <f>IF($D17="","",$D17-$C17-$K17-$L17)</f>
-        <v/>
-      </c>
       <c r="F17" s="8">
-        <f>IF($E17="","",$E17/$C17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="9" t="n">
+        <f>IF($E17="","",$E17-$C17-$L17-$M17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="9">
+        <f>IF($F17="","",$F17/$C17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="6">
-        <f>$C17/$G17</f>
-        <v/>
-      </c>
       <c r="I17" s="6">
-        <f>IF($D17="","",$D17/$G17)</f>
+        <f>$C17/$H17</f>
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF($E17="","",$E17/$G17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="10">
-        <f>IF($D17="","",$D17*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L17" s="6">
-        <f>IF($D17="","",$D17*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M17" s="11" t="n">
+        <f>IF($E17="","",$E17/$H17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="6">
+        <f>IF($F17="","",$F17/$H17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="7">
+        <f>IF($E17="","",$E17*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M17" s="6">
+        <f>IF($E17="","",$E17*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N17" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="O17" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="O17" s="12" t="inlineStr">
+      <c r="P17" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="Q17" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q17" s="12" t="inlineStr">
+      <c r="R17" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R17" s="12" t="inlineStr">
+      <c r="S17" s="12" t="inlineStr">
         <is>
           <t>434</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="inlineStr">
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" s="4" t="n">
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C18" s="6">
-        <f>$B18+$W18*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="E18" s="7">
-        <f>IF($D18="","",$D18-$C18-$K18-$L18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="8">
-        <f>IF($E18="","",$E18/$C18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" s="6">
-        <f>$C18/$G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="6">
-        <f>IF($D18="","",$D18/$G18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="6">
-        <f>IF($E18="","",$E18/$G18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="10">
-        <f>IF($D18="","",$D18*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L18" s="6" t="n">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="C18" s="16">
+        <f>$B18+$X18*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>168</v>
+      </c>
+      <c r="F18" s="18">
+        <f>IF($E18="","",$E18-$C18-$L18-$M18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>IF($F18="","",$F18/$C18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" s="16">
+        <f>$C18/$H18</f>
+        <v/>
+      </c>
+      <c r="J18" s="16">
+        <f>IF($E18="","",$E18/$H18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="16">
+        <f>IF($F18="","",$F18/$H18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="17">
+        <f>IF($E18="","",$E18*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="N18" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="P18" s="12" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="Q18" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-46056</t>
-        </is>
-      </c>
-      <c r="R18" s="12" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="4" t="n">
-        <v>6</v>
+      <c r="N18" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="O18" s="21" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="P18" s="22" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="Q18" s="22" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="R18" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-5844</t>
+        </is>
+      </c>
+      <c r="S18" s="22" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="T18" s="14" t="inlineStr">
+        <is>
+          <t>Leboncoin, à l'unité</t>
+        </is>
+      </c>
+      <c r="U18" s="14" t="inlineStr"/>
+      <c r="V18" s="14" t="inlineStr">
+        <is>
+          <t>URGENT — 2 sur 12 vendues</t>
+        </is>
+      </c>
+      <c r="W18" s="14" t="inlineStr">
+        <is>
+          <t>2 vendues</t>
+        </is>
+      </c>
+      <c r="X18" s="14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -1885,82 +1948,86 @@
         <v>50.4</v>
       </c>
       <c r="C19" s="6">
-        <f>$B19+$W19*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D19" s="7" t="n">
+        <f>$B19+$X19*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D19" s="7">
+        <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E19" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="E19" s="7">
-        <f>IF($D19="","",$D19-$C19-$K19-$L19)</f>
-        <v/>
-      </c>
       <c r="F19" s="8">
-        <f>IF($E19="","",$E19/$C19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="9" t="n">
+        <f>IF($E19="","",$E19-$C19-$L19-$M19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="9">
+        <f>IF($F19="","",$F19/$C19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="6">
-        <f>$C19/$G19</f>
-        <v/>
-      </c>
       <c r="I19" s="6">
-        <f>IF($D19="","",$D19/$G19)</f>
+        <f>$C19/$H19</f>
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF($E19="","",$E19/$G19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="10">
-        <f>IF($D19="","",$D19*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L19" s="6">
-        <f>IF($D19="","",$D19*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M19" s="11" t="n">
+        <f>IF($E19="","",$E19/$H19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="6">
+        <f>IF($F19="","",$F19/$H19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="7">
+        <f>IF($E19="","",$E19*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M19" s="6">
+        <f>IF($E19="","",$E19*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N19" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N19" s="11" t="n">
+      <c r="O19" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="P19" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P19" s="12" t="inlineStr">
+      <c r="Q19" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q19" s="12" t="inlineStr">
+      <c r="R19" s="12" t="inlineStr">
         <is>
           <t>FB2026-44194</t>
         </is>
       </c>
-      <c r="R19" s="12" t="inlineStr">
+      <c r="S19" s="12" t="inlineStr">
         <is>
           <t>229</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr">
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr">
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V19" s="4" t="inlineStr"/>
-      <c r="W19" s="4" t="n">
+      <c r="W19" s="4" t="inlineStr"/>
+      <c r="X19" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1974,82 +2041,86 @@
         <v>31.95</v>
       </c>
       <c r="C20" s="6">
-        <f>$B20+$W20*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D20" s="7" t="n">
+        <f>$B20+$X20*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D20" s="7">
+        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E20" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="E20" s="7">
-        <f>IF($D20="","",$D20-$C20-$K20-$L20)</f>
-        <v/>
-      </c>
       <c r="F20" s="8">
-        <f>IF($E20="","",$E20/$C20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="9" t="n">
+        <f>IF($E20="","",$E20-$C20-$L20-$M20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="9">
+        <f>IF($F20="","",$F20/$C20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="6">
-        <f>$C20/$G20</f>
-        <v/>
-      </c>
       <c r="I20" s="6">
-        <f>IF($D20="","",$D20/$G20)</f>
+        <f>$C20/$H20</f>
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF($E20="","",$E20/$G20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="10">
-        <f>IF($D20="","",$D20*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L20" s="6">
-        <f>IF($D20="","",$D20*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M20" s="11" t="n">
+        <f>IF($E20="","",$E20/$H20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="6">
+        <f>IF($F20="","",$F20/$H20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="7">
+        <f>IF($E20="","",$E20*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M20" s="6">
+        <f>IF($E20="","",$E20*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N20" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N20" s="11" t="n">
+      <c r="O20" s="11" t="n">
         <v>6.5</v>
       </c>
-      <c r="O20" s="12" t="inlineStr">
+      <c r="P20" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P20" s="12" t="inlineStr">
+      <c r="Q20" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q20" s="12" t="inlineStr">
+      <c r="R20" s="12" t="inlineStr">
         <is>
           <t>FB2026-5996</t>
         </is>
       </c>
-      <c r="R20" s="12" t="inlineStr">
+      <c r="S20" s="12" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="S20" s="4" t="inlineStr">
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="inlineStr">
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr"/>
-      <c r="W20" s="4" t="n">
+      <c r="W20" s="4" t="inlineStr"/>
+      <c r="X20" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2063,81 +2134,85 @@
         <v>25.2</v>
       </c>
       <c r="C21" s="6">
-        <f>$B21+$W21*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D21" s="7" t="n">
+        <f>$B21+$X21*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D21" s="7">
+        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E21" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="E21" s="7">
-        <f>IF($D21="","",$D21-$C21-$K21-$L21)</f>
-        <v/>
-      </c>
       <c r="F21" s="8">
-        <f>IF($E21="","",$E21/$C21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="9" t="n">
+        <f>IF($E21="","",$E21-$C21-$L21-$M21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="9">
+        <f>IF($F21="","",$F21/$C21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="6">
-        <f>$C21/$G21</f>
-        <v/>
-      </c>
       <c r="I21" s="6">
-        <f>IF($D21="","",$D21/$G21)</f>
+        <f>$C21/$H21</f>
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF($E21="","",$E21/$G21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="10">
-        <f>IF($D21="","",$D21*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L21" s="6" t="n">
+        <f>IF($E21="","",$E21/$H21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="6">
+        <f>IF($F21="","",$F21/$H21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="7">
+        <f>IF($E21="","",$E21*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="N21" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="N21" s="11" t="n">
+      <c r="O21" s="11" t="n">
         <v>5.2</v>
       </c>
-      <c r="O21" s="12" t="inlineStr">
+      <c r="P21" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P21" s="12" t="inlineStr">
+      <c r="Q21" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q21" s="12" t="inlineStr">
+      <c r="R21" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R21" s="12" t="inlineStr">
+      <c r="S21" s="12" t="inlineStr">
         <is>
           <t>439</t>
         </is>
       </c>
-      <c r="S21" s="4" t="inlineStr">
+      <c r="T21" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V21" s="4" t="inlineStr"/>
-      <c r="W21" s="4" t="n">
+      <c r="W21" s="4" t="inlineStr"/>
+      <c r="X21" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2151,82 +2226,86 @@
         <v>25.56</v>
       </c>
       <c r="C22" s="6">
-        <f>$B22+$W22*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D22" s="7" t="n">
+        <f>$B22+$X22*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D22" s="7">
+        <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E22" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="E22" s="7">
-        <f>IF($D22="","",$D22-$C22-$K22-$L22)</f>
-        <v/>
-      </c>
       <c r="F22" s="8">
-        <f>IF($E22="","",$E22/$C22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="9" t="n">
+        <f>IF($E22="","",$E22-$C22-$L22-$M22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="9">
+        <f>IF($F22="","",$F22/$C22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="6">
-        <f>$C22/$G22</f>
-        <v/>
-      </c>
       <c r="I22" s="6">
-        <f>IF($D22="","",$D22/$G22)</f>
+        <f>$C22/$H22</f>
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF($E22="","",$E22/$G22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="10">
-        <f>IF($D22="","",$D22*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L22" s="6">
-        <f>IF($D22="","",$D22*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M22" s="11" t="n">
+        <f>IF($E22="","",$E22/$H22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="6">
+        <f>IF($F22="","",$F22/$H22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="7">
+        <f>IF($E22="","",$E22*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M22" s="6">
+        <f>IF($E22="","",$E22*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N22" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="N22" s="11" t="n">
+      <c r="O22" s="11" t="n">
         <v>5.2</v>
       </c>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="P22" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="Q22" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q22" s="12" t="inlineStr">
+      <c r="R22" s="12" t="inlineStr">
         <is>
           <t>FB2026-5996</t>
         </is>
       </c>
-      <c r="R22" s="12" t="inlineStr">
+      <c r="S22" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr">
+      <c r="T22" s="4" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="inlineStr">
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr"/>
-      <c r="W22" s="4" t="n">
+      <c r="W22" s="4" t="inlineStr"/>
+      <c r="X22" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2240,81 +2319,85 @@
         <v>57.51</v>
       </c>
       <c r="C23" s="6">
-        <f>$B23+$W23*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D23" s="7" t="n">
+        <f>$B23+$X23*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D23" s="7">
+        <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E23" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="E23" s="7">
-        <f>IF($D23="","",$D23-$C23-$K23-$L23)</f>
-        <v/>
-      </c>
       <c r="F23" s="8">
-        <f>IF($E23="","",$E23/$C23)</f>
-        <v/>
-      </c>
-      <c r="G23" s="9" t="n">
+        <f>IF($E23="","",$E23-$C23-$L23-$M23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="9">
+        <f>IF($F23="","",$F23/$C23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="6">
-        <f>$C23/$G23</f>
-        <v/>
-      </c>
       <c r="I23" s="6">
-        <f>IF($D23="","",$D23/$G23)</f>
+        <f>$C23/$H23</f>
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF($E23="","",$E23/$G23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="10">
-        <f>IF($D23="","",$D23*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L23" s="6" t="n">
+        <f>IF($E23="","",$E23/$H23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="6">
+        <f>IF($F23="","",$F23/$H23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="7">
+        <f>IF($E23="","",$E23*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="11" t="n">
+      <c r="N23" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="N23" s="11" t="n">
+      <c r="O23" s="11" t="n">
         <v>11.7</v>
       </c>
-      <c r="O23" s="12" t="inlineStr">
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="Q23" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q23" s="12" t="inlineStr">
+      <c r="R23" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="R23" s="12" t="inlineStr">
+      <c r="S23" s="12" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="S23" s="4" t="inlineStr">
+      <c r="T23" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="inlineStr">
+      <c r="U23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V23" s="4" t="inlineStr"/>
-      <c r="W23" s="4" t="n">
+      <c r="W23" s="4" t="inlineStr"/>
+      <c r="X23" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2328,81 +2411,85 @@
         <v>37.8</v>
       </c>
       <c r="C24" s="6">
-        <f>$B24+$W24*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D24" s="7" t="n">
+        <f>$B24+$X24*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D24" s="7">
+        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E24" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="E24" s="7">
-        <f>IF($D24="","",$D24-$C24-$K24-$L24)</f>
-        <v/>
-      </c>
       <c r="F24" s="8">
-        <f>IF($E24="","",$E24/$C24)</f>
-        <v/>
-      </c>
-      <c r="G24" s="9" t="n">
+        <f>IF($E24="","",$E24-$C24-$L24-$M24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="9">
+        <f>IF($F24="","",$F24/$C24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="6">
-        <f>$C24/$G24</f>
-        <v/>
-      </c>
       <c r="I24" s="6">
-        <f>IF($D24="","",$D24/$G24)</f>
+        <f>$C24/$H24</f>
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF($E24="","",$E24/$G24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="10">
-        <f>IF($D24="","",$D24*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L24" s="6" t="n">
+        <f>IF($E24="","",$E24/$H24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="6">
+        <f>IF($F24="","",$F24/$H24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="7">
+        <f>IF($E24="","",$E24*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="N24" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N24" s="11" t="n">
+      <c r="O24" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="O24" s="12" t="inlineStr">
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="Q24" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q24" s="12" t="inlineStr">
+      <c r="R24" s="12" t="inlineStr">
         <is>
           <t>FB2026-43717</t>
         </is>
       </c>
-      <c r="R24" s="12" t="inlineStr">
+      <c r="S24" s="12" t="inlineStr">
         <is>
           <t>303</t>
         </is>
       </c>
-      <c r="S24" s="4" t="inlineStr">
+      <c r="T24" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="inlineStr">
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>URGENT — saisonnier</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="4" t="n">
+      <c r="W24" s="4" t="inlineStr"/>
+      <c r="X24" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2416,81 +2503,85 @@
         <v>21.73</v>
       </c>
       <c r="C25" s="6">
-        <f>$B25+$W25*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D25" s="7" t="n">
+        <f>$B25+$X25*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D25" s="7">
+        <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E25" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="E25" s="7">
-        <f>IF($D25="","",$D25-$C25-$K25-$L25)</f>
-        <v/>
-      </c>
       <c r="F25" s="8">
-        <f>IF($E25="","",$E25/$C25)</f>
-        <v/>
-      </c>
-      <c r="G25" s="9" t="n">
+        <f>IF($E25="","",$E25-$C25-$L25-$M25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="9">
+        <f>IF($F25="","",$F25/$C25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="6">
-        <f>$C25/$G25</f>
-        <v/>
-      </c>
       <c r="I25" s="6">
-        <f>IF($D25="","",$D25/$G25)</f>
+        <f>$C25/$H25</f>
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF($E25="","",$E25/$G25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="10">
-        <f>IF($D25="","",$D25*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L25" s="6" t="n">
+        <f>IF($E25="","",$E25/$H25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="6">
+        <f>IF($F25="","",$F25/$H25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="7">
+        <f>IF($E25="","",$E25*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="11" t="n">
+      <c r="N25" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="N25" s="11" t="n">
+      <c r="O25" s="11" t="n">
         <v>4.42</v>
       </c>
-      <c r="O25" s="12" t="inlineStr">
+      <c r="P25" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P25" s="12" t="inlineStr">
+      <c r="Q25" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q25" s="12" t="inlineStr">
+      <c r="R25" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="R25" s="12" t="inlineStr">
+      <c r="S25" s="12" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="S25" s="4" t="inlineStr">
+      <c r="T25" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="inlineStr">
+      <c r="U25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="V25" s="4" t="inlineStr"/>
-      <c r="W25" s="4" t="n">
+      <c r="W25" s="4" t="inlineStr"/>
+      <c r="X25" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2504,82 +2595,86 @@
         <v>50.4</v>
       </c>
       <c r="C26" s="6">
-        <f>$B26+$W26*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D26" s="7" t="n">
+        <f>$B26+$X26*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D26" s="7">
+        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="E26" s="7">
-        <f>IF($D26="","",$D26-$C26-$K26-$L26)</f>
-        <v/>
-      </c>
       <c r="F26" s="8">
-        <f>IF($E26="","",$E26/$C26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="9" t="n">
+        <f>IF($E26="","",$E26-$C26-$L26-$M26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="9">
+        <f>IF($F26="","",$F26/$C26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="6">
-        <f>$C26/$G26</f>
-        <v/>
-      </c>
       <c r="I26" s="6">
-        <f>IF($D26="","",$D26/$G26)</f>
+        <f>$C26/$H26</f>
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF($E26="","",$E26/$G26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="10">
-        <f>IF($D26="","",$D26*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L26" s="6">
-        <f>IF($D26="","",$D26*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M26" s="11" t="n">
+        <f>IF($E26="","",$E26/$H26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="6">
+        <f>IF($F26="","",$F26/$H26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="7">
+        <f>IF($E26="","",$E26*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M26" s="6">
+        <f>IF($E26="","",$E26*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="N26" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N26" s="11" t="n">
+      <c r="O26" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="P26" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="Q26" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q26" s="12" t="inlineStr">
+      <c r="R26" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R26" s="12" t="inlineStr">
+      <c r="S26" s="12" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr">
+      <c r="T26" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="inlineStr">
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="inlineStr">
         <is>
           <t>URGENT — saisonnier</t>
         </is>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="4" t="n">
+      <c r="W26" s="4" t="inlineStr"/>
+      <c r="X26" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2593,81 +2688,85 @@
         <v>75.59999999999999</v>
       </c>
       <c r="C27" s="6">
-        <f>$B27+$W27*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D27" s="7" t="n">
+        <f>$B27+$X27*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D27" s="7">
+        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="E27" s="7">
-        <f>IF($D27="","",$D27-$C27-$K27-$L27)</f>
-        <v/>
-      </c>
       <c r="F27" s="8">
-        <f>IF($E27="","",$E27/$C27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="9" t="n">
+        <f>IF($E27="","",$E27-$C27-$L27-$M27)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9">
+        <f>IF($F27="","",$F27/$C27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="6">
-        <f>$C27/$G27</f>
-        <v/>
-      </c>
       <c r="I27" s="6">
-        <f>IF($D27="","",$D27/$G27)</f>
+        <f>$C27/$H27</f>
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF($E27="","",$E27/$G27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="10">
-        <f>IF($D27="","",$D27*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L27" s="6" t="n">
+        <f>IF($E27="","",$E27/$H27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="6">
+        <f>IF($F27="","",$F27/$H27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="7">
+        <f>IF($E27="","",$E27*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="11" t="n">
+      <c r="N27" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="N27" s="11" t="n">
+      <c r="O27" s="11" t="n">
         <v>15.6</v>
       </c>
-      <c r="O27" s="12" t="inlineStr">
+      <c r="P27" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P27" s="12" t="inlineStr">
+      <c r="Q27" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q27" s="12" t="inlineStr">
+      <c r="R27" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R27" s="12" t="inlineStr">
+      <c r="S27" s="12" t="inlineStr">
         <is>
           <t>199</t>
         </is>
       </c>
-      <c r="S27" s="4" t="inlineStr">
+      <c r="T27" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="inlineStr">
+      <c r="U27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="V27" s="4" t="inlineStr"/>
-      <c r="W27" s="4" t="n">
+      <c r="W27" s="4" t="inlineStr"/>
+      <c r="X27" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2681,85 +2780,89 @@
         <v>76.68000000000001</v>
       </c>
       <c r="C28" s="16">
-        <f>$B28+$W28*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D28" s="17" t="n">
+        <f>$B28+$X28*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D28" s="17">
+        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E28" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="E28" s="17">
-        <f>IF($D28="","",$D28-$C28-$K28-$L28)</f>
-        <v/>
-      </c>
       <c r="F28" s="18">
-        <f>IF($E28="","",$E28/$C28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="19" t="n">
+        <f>IF($E28="","",$E28-$C28-$L28-$M28)</f>
+        <v/>
+      </c>
+      <c r="G28" s="19">
+        <f>IF($F28="","",$F28/$C28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="16">
-        <f>$C28/$G28</f>
-        <v/>
-      </c>
       <c r="I28" s="16">
-        <f>IF($D28="","",$D28/$G28)</f>
+        <f>$C28/$H28</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>IF($E28="","",$E28/$G28)</f>
-        <v/>
-      </c>
-      <c r="K28" s="20">
-        <f>IF($D28="","",$D28*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L28" s="16" t="n">
+        <f>IF($E28="","",$E28/$H28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
+        <f>IF($F28="","",$F28/$H28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="17">
+        <f>IF($E28="","",$E28*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="21" t="n">
+      <c r="N28" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="N28" s="21" t="n">
+      <c r="O28" s="21" t="n">
         <v>15.6</v>
       </c>
-      <c r="O28" s="22" t="inlineStr">
+      <c r="P28" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P28" s="22" t="inlineStr">
+      <c r="Q28" s="22" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q28" s="22" t="inlineStr">
+      <c r="R28" s="22" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="R28" s="22" t="inlineStr">
+      <c r="S28" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S28" s="14" t="inlineStr">
+      <c r="T28" s="14" t="inlineStr">
         <is>
           <t>Vinted, acheteur en Italie</t>
         </is>
       </c>
-      <c r="T28" s="14" t="inlineStr"/>
-      <c r="U28" s="14" t="inlineStr">
+      <c r="U28" s="14" t="inlineStr"/>
+      <c r="V28" s="14" t="inlineStr">
         <is>
           <t>VENDUE</t>
         </is>
       </c>
-      <c r="V28" s="14" t="inlineStr">
+      <c r="W28" s="14" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="W28" s="14" t="n">
+      <c r="X28" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2773,81 +2876,85 @@
         <v>51.12</v>
       </c>
       <c r="C29" s="6">
-        <f>$B29+$W29*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D29" s="7" t="n">
+        <f>$B29+$X29*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D29" s="7">
+        <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E29" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="E29" s="7">
-        <f>IF($D29="","",$D29-$C29-$K29-$L29)</f>
-        <v/>
-      </c>
       <c r="F29" s="8">
-        <f>IF($E29="","",$E29/$C29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="9" t="n">
+        <f>IF($E29="","",$E29-$C29-$L29-$M29)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9">
+        <f>IF($F29="","",$F29/$C29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="6">
-        <f>$C29/$G29</f>
-        <v/>
-      </c>
       <c r="I29" s="6">
-        <f>IF($D29="","",$D29/$G29)</f>
+        <f>$C29/$H29</f>
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF($E29="","",$E29/$G29)</f>
-        <v/>
-      </c>
-      <c r="K29" s="10">
-        <f>IF($D29="","",$D29*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L29" s="6" t="n">
+        <f>IF($E29="","",$E29/$H29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="6">
+        <f>IF($F29="","",$F29/$H29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="7">
+        <f>IF($E29="","",$E29*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="11" t="n">
+      <c r="N29" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N29" s="11" t="n">
+      <c r="O29" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="O29" s="12" t="inlineStr">
+      <c r="P29" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P29" s="12" t="inlineStr">
+      <c r="Q29" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q29" s="12" t="inlineStr">
+      <c r="R29" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="R29" s="12" t="inlineStr">
+      <c r="S29" s="12" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="S29" s="4" t="inlineStr">
+      <c r="T29" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="inlineStr">
+      <c r="U29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="V29" s="4" t="inlineStr"/>
-      <c r="W29" s="4" t="n">
+      <c r="W29" s="4" t="inlineStr"/>
+      <c r="X29" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2861,81 +2968,85 @@
         <v>38.34</v>
       </c>
       <c r="C30" s="6">
-        <f>$B30+$W30*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D30" s="7" t="n">
+        <f>$B30+$X30*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D30" s="7">
+        <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="E30" s="7">
-        <f>IF($D30="","",$D30-$C30-$K30-$L30)</f>
-        <v/>
-      </c>
       <c r="F30" s="8">
-        <f>IF($E30="","",$E30/$C30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="9" t="n">
+        <f>IF($E30="","",$E30-$C30-$L30-$M30)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9">
+        <f>IF($F30="","",$F30/$C30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="6">
-        <f>$C30/$G30</f>
-        <v/>
-      </c>
       <c r="I30" s="6">
-        <f>IF($D30="","",$D30/$G30)</f>
+        <f>$C30/$H30</f>
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF($E30="","",$E30/$G30)</f>
-        <v/>
-      </c>
-      <c r="K30" s="10">
-        <f>IF($D30="","",$D30*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L30" s="6" t="n">
+        <f>IF($E30="","",$E30/$H30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="6">
+        <f>IF($F30="","",$F30/$H30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="7">
+        <f>IF($E30="","",$E30*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="11" t="n">
+      <c r="N30" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="N30" s="11" t="n">
+      <c r="O30" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="O30" s="12" t="inlineStr">
+      <c r="P30" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P30" s="12" t="inlineStr">
+      <c r="Q30" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q30" s="12" t="inlineStr">
+      <c r="R30" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="R30" s="12" t="inlineStr">
+      <c r="S30" s="12" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="S30" s="4" t="inlineStr">
+      <c r="T30" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr">
+      <c r="U30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="4" t="n">
+      <c r="W30" s="4" t="inlineStr"/>
+      <c r="X30" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2949,81 +3060,85 @@
         <v>51.12</v>
       </c>
       <c r="C31" s="6">
-        <f>$B31+$W31*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D31" s="7" t="n">
+        <f>$B31+$X31*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D31" s="7">
+        <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="E31" s="7">
-        <f>IF($D31="","",$D31-$C31-$K31-$L31)</f>
-        <v/>
-      </c>
       <c r="F31" s="8">
-        <f>IF($E31="","",$E31/$C31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="9" t="n">
+        <f>IF($E31="","",$E31-$C31-$L31-$M31)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9">
+        <f>IF($F31="","",$F31/$C31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="6">
-        <f>$C31/$G31</f>
-        <v/>
-      </c>
       <c r="I31" s="6">
-        <f>IF($D31="","",$D31/$G31)</f>
+        <f>$C31/$H31</f>
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF($E31="","",$E31/$G31)</f>
-        <v/>
-      </c>
-      <c r="K31" s="10">
-        <f>IF($D31="","",$D31*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L31" s="6" t="n">
+        <f>IF($E31="","",$E31/$H31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="6">
+        <f>IF($F31="","",$F31/$H31)</f>
+        <v/>
+      </c>
+      <c r="L31" s="7">
+        <f>IF($E31="","",$E31*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="11" t="n">
+      <c r="N31" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N31" s="11" t="n">
+      <c r="O31" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="O31" s="12" t="inlineStr">
+      <c r="P31" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P31" s="12" t="inlineStr">
+      <c r="Q31" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q31" s="12" t="inlineStr">
+      <c r="R31" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="R31" s="12" t="inlineStr">
+      <c r="S31" s="12" t="inlineStr">
         <is>
           <t>156</t>
         </is>
       </c>
-      <c r="S31" s="4" t="inlineStr">
+      <c r="T31" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr">
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="V31" s="4" t="inlineStr"/>
-      <c r="W31" s="4" t="n">
+      <c r="W31" s="4" t="inlineStr"/>
+      <c r="X31" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3037,858 +3152,931 @@
         <v>52.4</v>
       </c>
       <c r="C32" s="6">
-        <f>$B32+$W32*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D32" s="7" t="n">
+        <f>$B32+$X32*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D32" s="7">
+        <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="E32" s="7">
-        <f>IF($D32="","",$D32-$C32-$K32-$L32)</f>
-        <v/>
-      </c>
       <c r="F32" s="8">
-        <f>IF($E32="","",$E32/$C32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="9" t="n">
+        <f>IF($E32="","",$E32-$C32-$L32-$M32)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9">
+        <f>IF($F32="","",$F32/$C32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="6">
-        <f>$C32/$G32</f>
-        <v/>
-      </c>
       <c r="I32" s="6">
-        <f>IF($D32="","",$D32/$G32)</f>
+        <f>$C32/$H32</f>
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF($E32="","",$E32/$G32)</f>
-        <v/>
-      </c>
-      <c r="K32" s="10">
-        <f>IF($D32="","",$D32*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L32" s="6" t="n">
+        <f>IF($E32="","",$E32/$H32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="6">
+        <f>IF($F32="","",$F32/$H32)</f>
+        <v/>
+      </c>
+      <c r="L32" s="7">
+        <f>IF($E32="","",$E32*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="11" t="n">
+      <c r="N32" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="N32" s="11" t="n">
+      <c r="O32" s="11" t="n">
         <v>10.66</v>
       </c>
-      <c r="O32" s="12" t="inlineStr">
+      <c r="P32" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="P32" s="12" t="inlineStr">
+      <c r="Q32" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q32" s="12" t="inlineStr">
+      <c r="R32" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="R32" s="12" t="inlineStr">
+      <c r="S32" s="12" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="S32" s="4" t="inlineStr">
+      <c r="T32" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="inlineStr">
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="4" t="n">
+      <c r="W32" s="4" t="inlineStr"/>
+      <c r="X32" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="C33" s="25">
-        <f>$B33+$W33*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="27">
-        <f>IF($D33="","",$D33-$C33-$K33-$L33)</f>
-        <v/>
-      </c>
-      <c r="F33" s="28">
-        <f>IF($E33="","",$E33/$C33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" s="25">
-        <f>$C33/$G33</f>
-        <v/>
-      </c>
-      <c r="I33" s="25">
-        <f>IF($D33="","",$D33/$G33)</f>
-        <v/>
-      </c>
-      <c r="J33" s="25">
-        <f>IF($E33="","",$E33/$G33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="30">
-        <f>IF($D33="","",$D33*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L33" s="25" t="n">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>LACOSTE sneakers P.42 — neuves</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="C33" s="16">
+        <f>$B33+$X33*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="F33" s="18">
+        <f>IF($E33="","",$E33-$C33-$L33-$M33)</f>
+        <v/>
+      </c>
+      <c r="G33" s="19">
+        <f>IF($F33="","",$F33/$C33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="16">
+        <f>$C33/$H33</f>
+        <v/>
+      </c>
+      <c r="J33" s="16">
+        <f>IF($E33="","",$E33/$H33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="16">
+        <f>IF($F33="","",$F33/$H33)</f>
+        <v/>
+      </c>
+      <c r="L33" s="17">
+        <f>IF($E33="","",$E33*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="N33" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O33" s="32" t="inlineStr">
+      <c r="N33" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="O33" s="21" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="P33" s="22" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="Q33" s="22" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="R33" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="S33" s="22" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="T33" s="14" t="inlineStr">
+        <is>
+          <t>date à compléter</t>
+        </is>
+      </c>
+      <c r="U33" s="14" t="inlineStr"/>
+      <c r="V33" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="W33" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X33" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="C34" s="16">
+        <f>$B34+$X34*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>125</v>
+      </c>
+      <c r="F34" s="18">
+        <f>IF($E34="","",$E34-$C34-$L34-$M34)</f>
+        <v/>
+      </c>
+      <c r="G34" s="19">
+        <f>IF($F34="","",$F34/$C34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="16">
+        <f>$C34/$H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="16">
+        <f>IF($E34="","",$E34/$H34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="16">
+        <f>IF($F34="","",$F34/$H34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="17">
+        <f>IF($E34="","",$E34*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="O34" s="21" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="P34" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P33" s="32" t="inlineStr">
+      <c r="Q34" s="22" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="Q33" s="32" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="R33" s="32" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="S33" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="T33" s="23" t="inlineStr"/>
-      <c r="U33" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="V33" s="23" t="inlineStr"/>
-      <c r="W33" s="23" t="n">
+      <c r="R34" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-44194</t>
+        </is>
+      </c>
+      <c r="S34" s="22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T34" s="14" t="inlineStr">
+        <is>
+          <t>date à compléter</t>
+        </is>
+      </c>
+      <c r="U34" s="14" t="inlineStr"/>
+      <c r="V34" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="W34" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X34" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="B34" s="24" t="n">
+      <c r="B35" s="15" t="n">
         <v>25.2</v>
       </c>
-      <c r="C34" s="25">
-        <f>$B34+$W34*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="27">
-        <f>IF($D34="","",$D34-$C34-$K34-$L34)</f>
-        <v/>
-      </c>
-      <c r="F34" s="28">
-        <f>IF($E34="","",$E34/$C34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="29" t="n">
+      <c r="C35" s="16">
+        <f>$B35+$X35*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="F35" s="18">
+        <f>IF($E35="","",$E35-$C35-$L35-$M35)</f>
+        <v/>
+      </c>
+      <c r="G35" s="19">
+        <f>IF($F35="","",$F35/$C35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="25">
-        <f>$C34/$G34</f>
-        <v/>
-      </c>
-      <c r="I34" s="25">
-        <f>IF($D34="","",$D34/$G34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="25">
-        <f>IF($E34="","",$E34/$G34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="30">
-        <f>IF($D34="","",$D34*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L34" s="25">
-        <f>IF($D34="","",$D34*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M34" s="31" t="n">
+      <c r="I35" s="16">
+        <f>$C35/$H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="16">
+        <f>IF($E35="","",$E35/$H35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="16">
+        <f>IF($F35="","",$F35/$H35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="17">
+        <f>IF($E35="","",$E35*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="N34" s="31" t="n">
+      <c r="O35" s="21" t="n">
         <v>5.2</v>
       </c>
-      <c r="O34" s="32" t="inlineStr">
+      <c r="P35" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P34" s="32" t="inlineStr">
+      <c r="Q35" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q34" s="32" t="inlineStr">
+      <c r="R35" s="22" t="inlineStr">
         <is>
           <t>FB2026-43717</t>
         </is>
       </c>
-      <c r="R34" s="32" t="inlineStr">
+      <c r="S35" s="22" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="S34" s="23" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="T34" s="23" t="inlineStr"/>
-      <c r="U34" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="V34" s="23" t="inlineStr"/>
-      <c r="W34" s="23" t="n">
+      <c r="T35" s="14" t="inlineStr">
+        <is>
+          <t>date à compléter</t>
+        </is>
+      </c>
+      <c r="U35" s="14" t="inlineStr"/>
+      <c r="V35" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="W35" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X35" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C35" s="25">
-        <f>$B35+$W35*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="27">
-        <f>IF($D35="","",$D35-$C35-$K35-$L35)</f>
-        <v/>
-      </c>
-      <c r="F35" s="28">
-        <f>IF($E35="","",$E35/$C35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" s="25">
-        <f>$C35/$G35</f>
-        <v/>
-      </c>
-      <c r="I35" s="25">
-        <f>IF($D35="","",$D35/$G35)</f>
-        <v/>
-      </c>
-      <c r="J35" s="25">
-        <f>IF($E35="","",$E35/$G35)</f>
-        <v/>
-      </c>
-      <c r="K35" s="30">
-        <f>IF($D35="","",$D35*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L35" s="25" t="n">
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C36" s="16">
+        <f>$B36+$X36*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="F36" s="18">
+        <f>IF($E36="","",$E36-$C36-$L36-$M36)</f>
+        <v/>
+      </c>
+      <c r="G36" s="19">
+        <f>IF($F36="","",$F36/$C36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="16">
+        <f>$C36/$H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="16">
+        <f>IF($E36="","",$E36/$H36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="16">
+        <f>IF($F36="","",$F36/$H36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="17">
+        <f>IF($E36="","",$E36*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="31" t="n">
-        <v>30</v>
-      </c>
-      <c r="N35" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O35" s="32" t="inlineStr">
+      <c r="N36" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="O36" s="21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P36" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P35" s="32" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="Q35" s="32" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="R35" s="32" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="S35" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="T35" s="23" t="inlineStr"/>
-      <c r="U35" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="V35" s="23" t="inlineStr"/>
-      <c r="W35" s="23" t="n">
+      <c r="Q36" s="22" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="R36" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="S36" s="22" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="T36" s="14" t="inlineStr">
+        <is>
+          <t>date à compléter</t>
+        </is>
+      </c>
+      <c r="U36" s="14" t="inlineStr"/>
+      <c r="V36" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="W36" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X36" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="n">
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
         <v>50.4</v>
       </c>
-      <c r="C36" s="25">
-        <f>$B36+$W36*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="27">
-        <f>IF($D36="","",$D36-$C36-$K36-$L36)</f>
-        <v/>
-      </c>
-      <c r="F36" s="28">
-        <f>IF($E36="","",$E36/$C36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="29" t="n">
+      <c r="C37" s="16">
+        <f>$B37+$X37*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="18">
+        <f>IF($E37="","",$E37-$C37-$L37-$M37)</f>
+        <v/>
+      </c>
+      <c r="G37" s="19">
+        <f>IF($F37="","",$F37/$C37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="25">
-        <f>$C36/$G36</f>
-        <v/>
-      </c>
-      <c r="I36" s="25">
-        <f>IF($D36="","",$D36/$G36)</f>
-        <v/>
-      </c>
-      <c r="J36" s="25">
-        <f>IF($E36="","",$E36/$G36)</f>
-        <v/>
-      </c>
-      <c r="K36" s="30">
-        <f>IF($D36="","",$D36*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L36" s="25" t="n">
+      <c r="I37" s="16">
+        <f>$C37/$H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="16">
+        <f>IF($E37="","",$E37/$H37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="16">
+        <f>IF($F37="","",$F37/$H37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="17">
+        <f>IF($E37="","",$E37*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="31" t="n">
+      <c r="N37" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="N36" s="31" t="n">
+      <c r="O37" s="21" t="n">
         <v>10.4</v>
       </c>
-      <c r="O36" s="32" t="inlineStr">
+      <c r="P37" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P36" s="32" t="inlineStr">
+      <c r="Q37" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q36" s="32" t="inlineStr">
+      <c r="R37" s="22" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R36" s="32" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="S36" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="T36" s="23" t="inlineStr"/>
-      <c r="U36" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="V36" s="23" t="inlineStr"/>
-      <c r="W36" s="23" t="n">
+      <c r="S37" s="22" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="T37" s="14" t="inlineStr">
+        <is>
+          <t>date à compléter</t>
+        </is>
+      </c>
+      <c r="U37" s="14" t="inlineStr"/>
+      <c r="V37" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="W37" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X37" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C37" s="25">
-        <f>$B37+$W37*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D37" s="26" t="n"/>
-      <c r="E37" s="27">
-        <f>IF($D37="","",$D37-$C37-$K37-$L37)</f>
-        <v/>
-      </c>
-      <c r="F37" s="28">
-        <f>IF($E37="","",$E37/$C37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="29" t="n">
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Baskets HOKA P.37 1/3 — neuves</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="C38" s="16">
+        <f>$B38+$X38*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="F38" s="18">
+        <f>IF($E38="","",$E38-$C38-$L38-$M38)</f>
+        <v/>
+      </c>
+      <c r="G38" s="19">
+        <f>IF($F38="","",$F38/$C38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="25">
-        <f>$C37/$G37</f>
-        <v/>
-      </c>
-      <c r="I37" s="25">
-        <f>IF($D37="","",$D37/$G37)</f>
-        <v/>
-      </c>
-      <c r="J37" s="25">
-        <f>IF($E37="","",$E37/$G37)</f>
-        <v/>
-      </c>
-      <c r="K37" s="30">
-        <f>IF($D37="","",$D37*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L37" s="25">
-        <f>IF($D37="","",$D37*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M37" s="31" t="n">
-        <v>40</v>
-      </c>
-      <c r="N37" s="31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="O37" s="32" t="inlineStr">
+      <c r="I38" s="16">
+        <f>$C38/$H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="16">
+        <f>IF($E38="","",$E38/$H38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="16">
+        <f>IF($F38="","",$F38/$H38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="17">
+        <f>IF($E38="","",$E38*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="O38" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="P38" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P37" s="32" t="inlineStr">
+      <c r="Q38" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="Q37" s="32" t="inlineStr">
+      <c r="R38" s="22" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="R37" s="32" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="S37" s="23" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="T37" s="23" t="inlineStr"/>
-      <c r="U37" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="V37" s="23" t="inlineStr"/>
-      <c r="W37" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>LACOSTE sneakers P.42 — neuves</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="n">
-        <v>57.51</v>
-      </c>
-      <c r="C38" s="25">
-        <f>$B38+$W38*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="27">
-        <f>IF($D38="","",$D38-$C38-$K38-$L38)</f>
-        <v/>
-      </c>
-      <c r="F38" s="28">
-        <f>IF($E38="","",$E38/$C38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="25">
-        <f>$C38/$G38</f>
-        <v/>
-      </c>
-      <c r="I38" s="25">
-        <f>IF($D38="","",$D38/$G38)</f>
-        <v/>
-      </c>
-      <c r="J38" s="25">
-        <f>IF($E38="","",$E38/$G38)</f>
-        <v/>
-      </c>
-      <c r="K38" s="30">
-        <f>IF($D38="","",$D38*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L38" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="31" t="n">
-        <v>45</v>
-      </c>
-      <c r="N38" s="31" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="O38" s="32" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="P38" s="32" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="Q38" s="32" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="R38" s="32" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="S38" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="T38" s="23" t="inlineStr"/>
-      <c r="U38" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="V38" s="23" t="inlineStr"/>
-      <c r="W38" s="23" t="n">
+      <c r="S38" s="22" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="T38" s="14" t="inlineStr">
+        <is>
+          <t>date à compléter</t>
+        </is>
+      </c>
+      <c r="U38" s="14" t="inlineStr"/>
+      <c r="V38" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="W38" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X38" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>Baskets HOKA P.37 1/3 — neuves</t>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
       <c r="B39" s="24" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="C39" s="25">
+        <f>$B39+$X39*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D39" s="26">
+        <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="28">
+        <f>IF($E39="","",$E39-$C39-$L39-$M39)</f>
+        <v/>
+      </c>
+      <c r="G39" s="29">
+        <f>IF($F39="","",$F39/$C39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="25">
+        <f>$C39/$H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="25">
+        <f>IF($E39="","",$E39/$H39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="25">
+        <f>IF($F39="","",$F39/$H39)</f>
+        <v/>
+      </c>
+      <c r="L39" s="26">
+        <f>IF($E39="","",$E39*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="O39" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P39" s="32" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="Q39" s="32" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="R39" s="32" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="S39" s="32" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="T39" s="23" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="U39" s="23" t="inlineStr"/>
+      <c r="V39" s="23" t="inlineStr">
+        <is>
+          <t>PRIX À ÉTABLIR</t>
+        </is>
+      </c>
+      <c r="W39" s="23" t="inlineStr"/>
+      <c r="X39" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C40" s="25">
+        <f>$B40+$X40*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="28">
+        <f>IF($E40="","",$E40-$C40-$L40-$M40)</f>
+        <v/>
+      </c>
+      <c r="G40" s="29">
+        <f>IF($F40="","",$F40/$C40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" s="25">
+        <f>$C40/$H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="25">
+        <f>IF($E40="","",$E40/$H40)</f>
+        <v/>
+      </c>
+      <c r="K40" s="25">
+        <f>IF($F40="","",$F40/$H40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="26">
+        <f>IF($E40="","",$E40*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="31" t="n">
+        <v>30</v>
+      </c>
+      <c r="O40" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P40" s="32" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="Q40" s="32" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="R40" s="32" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="S40" s="32" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="T40" s="23" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="U40" s="23" t="inlineStr"/>
+      <c r="V40" s="23" t="inlineStr">
+        <is>
+          <t>PRIX À ÉTABLIR</t>
+        </is>
+      </c>
+      <c r="W40" s="23" t="inlineStr"/>
+      <c r="X40" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="C39" s="25">
-        <f>$B39+$W39*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="27">
-        <f>IF($D39="","",$D39-$C39-$K39-$L39)</f>
-        <v/>
-      </c>
-      <c r="F39" s="28">
-        <f>IF($E39="","",$E39/$C39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="29" t="n">
+      <c r="C41" s="6">
+        <f>$B41+$X41*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D41" s="7">
+        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="8">
+        <f>IF($E41="","",$E41-$C41-$L41-$M41)</f>
+        <v/>
+      </c>
+      <c r="G41" s="9">
+        <f>IF($F41="","",$F41/$C41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="25">
-        <f>$C39/$G39</f>
-        <v/>
-      </c>
-      <c r="I39" s="25">
-        <f>IF($D39="","",$D39/$G39)</f>
-        <v/>
-      </c>
-      <c r="J39" s="25">
-        <f>IF($E39="","",$E39/$G39)</f>
-        <v/>
-      </c>
-      <c r="K39" s="30">
-        <f>IF($D39="","",$D39*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L39" s="25" t="n">
+      <c r="I41" s="6">
+        <f>$C41/$H41</f>
+        <v/>
+      </c>
+      <c r="J41" s="6">
+        <f>IF($E41="","",$E41/$H41)</f>
+        <v/>
+      </c>
+      <c r="K41" s="6">
+        <f>IF($F41="","",$F41/$H41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="7">
+        <f>IF($E41="","",$E41*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="M41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="31" t="n">
+      <c r="N41" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="N39" s="31" t="n">
+      <c r="O41" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="O39" s="32" t="inlineStr">
+      <c r="P41" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="P39" s="32" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="Q39" s="32" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="R39" s="32" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="S39" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="T39" s="23" t="inlineStr"/>
-      <c r="U39" s="23" t="inlineStr">
+      <c r="Q41" s="12" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="R41" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-46056</t>
+        </is>
+      </c>
+      <c r="S41" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>Vinted, authentification</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr"/>
+      <c r="V41" s="4" t="inlineStr">
         <is>
           <t>PRIX À ÉTABLIR</t>
         </is>
       </c>
-      <c r="V39" s="23" t="inlineStr"/>
-      <c r="W39" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="C40" s="6">
-        <f>$B40+$W40*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="7">
-        <f>IF($D40="","",$D40-$C40-$K40-$L40)</f>
-        <v/>
-      </c>
-      <c r="F40" s="8">
-        <f>IF($E40="","",$E40/$C40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="6">
-        <f>$C40/$G40</f>
-        <v/>
-      </c>
-      <c r="I40" s="6">
-        <f>IF($D40="","",$D40/$G40)</f>
-        <v/>
-      </c>
-      <c r="J40" s="6">
-        <f>IF($E40="","",$E40/$G40)</f>
-        <v/>
-      </c>
-      <c r="K40" s="10">
-        <f>IF($D40="","",$D40*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="N40" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="O40" s="12" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="P40" s="12" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="Q40" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-46056</t>
-        </is>
-      </c>
-      <c r="R40" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S40" s="4" t="inlineStr">
-        <is>
-          <t>Vinted, authentification</t>
-        </is>
-      </c>
-      <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="V40" s="4" t="inlineStr"/>
-      <c r="W40" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="C41" s="25">
-        <f>$B41+$W41*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D41" s="26" t="n"/>
-      <c r="E41" s="27">
-        <f>IF($D41="","",$D41-$C41-$K41-$L41)</f>
-        <v/>
-      </c>
-      <c r="F41" s="28">
-        <f>IF($E41="","",$E41/$C41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="25">
-        <f>$C41/$G41</f>
-        <v/>
-      </c>
-      <c r="I41" s="25">
-        <f>IF($D41="","",$D41/$G41)</f>
-        <v/>
-      </c>
-      <c r="J41" s="25">
-        <f>IF($E41="","",$E41/$G41)</f>
-        <v/>
-      </c>
-      <c r="K41" s="30">
-        <f>IF($D41="","",$D41*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="L41" s="25">
-        <f>IF($D41="","",$D41*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="M41" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="N41" s="31" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="O41" s="32" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="P41" s="32" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="Q41" s="32" t="inlineStr">
-        <is>
-          <t>FB2026-44194</t>
-        </is>
-      </c>
-      <c r="R41" s="32" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S41" s="23" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="T41" s="23" t="inlineStr"/>
-      <c r="U41" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="V41" s="23" t="inlineStr"/>
-      <c r="W41" s="23" t="n">
+      <c r="W41" s="4" t="inlineStr"/>
+      <c r="X41" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3906,48 +4094,49 @@
         <f>SUM(C6:C41)</f>
         <v/>
       </c>
-      <c r="D42" s="34">
-        <f>SUM(D6:D41)</f>
-        <v/>
-      </c>
+      <c r="D42" s="35" t="n"/>
       <c r="E42" s="34">
         <f>SUM(E6:E41)</f>
         <v/>
       </c>
-      <c r="F42" s="35">
-        <f>E42/C42</f>
+      <c r="F42" s="34">
+        <f>SUM(F6:F41)</f>
         <v/>
       </c>
       <c r="G42" s="36">
-        <f>SUM(G6:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="37" t="n"/>
-      <c r="I42" s="37" t="n"/>
-      <c r="J42" s="37" t="n"/>
-      <c r="K42" s="34">
-        <f>SUM(K6:K41)</f>
-        <v/>
-      </c>
+        <f>F42/C42</f>
+        <v/>
+      </c>
+      <c r="H42" s="37">
+        <f>SUM(H6:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="35" t="n"/>
+      <c r="J42" s="35" t="n"/>
+      <c r="K42" s="35" t="n"/>
       <c r="L42" s="34">
         <f>SUM(L6:L41)</f>
         <v/>
       </c>
-      <c r="M42" s="37" t="n"/>
-      <c r="N42" s="37" t="n"/>
-      <c r="O42" s="37" t="n"/>
-      <c r="P42" s="37" t="n"/>
-      <c r="Q42" s="37" t="n"/>
-      <c r="R42" s="37" t="n"/>
-      <c r="S42" s="37" t="n"/>
-      <c r="T42" s="37" t="n"/>
-      <c r="U42" s="37" t="n"/>
-      <c r="V42" s="37" t="n"/>
-      <c r="W42" s="37" t="n"/>
+      <c r="M42" s="34">
+        <f>SUM(M6:M41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="35" t="n"/>
+      <c r="O42" s="35" t="n"/>
+      <c r="P42" s="35" t="n"/>
+      <c r="Q42" s="35" t="n"/>
+      <c r="R42" s="35" t="n"/>
+      <c r="S42" s="35" t="n"/>
+      <c r="T42" s="35" t="n"/>
+      <c r="U42" s="35" t="n"/>
+      <c r="V42" s="35" t="n"/>
+      <c r="W42" s="35" t="n"/>
+      <c r="X42" s="35" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:W41"/>
-  <conditionalFormatting sqref="E6:E41">
+  <autoFilter ref="A5:X41"/>
+  <conditionalFormatting sqref="F6:F41">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -3962,7 +4151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4039,8 +4228,8 @@
           <t>Chiffre d'affaires attendu</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>'Stock complet'!D42</f>
+      <c r="B10" s="8">
+        <f>'Stock complet'!E42</f>
         <v/>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4055,8 +4244,8 @@
           <t>− URSSAF + CFP</t>
         </is>
       </c>
-      <c r="B11" s="10">
-        <f>-'Stock complet'!K42</f>
+      <c r="B11" s="7">
+        <f>-'Stock complet'!L42</f>
         <v/>
       </c>
     </row>
@@ -4067,7 +4256,7 @@
         </is>
       </c>
       <c r="B12" s="6">
-        <f>-'Stock complet'!L42</f>
+        <f>-'Stock complet'!M42</f>
         <v/>
       </c>
     </row>
@@ -4077,7 +4266,7 @@
         <v/>
       </c>
       <c r="B13" s="34">
-        <f>'Stock complet'!E42</f>
+        <f>'Stock complet'!F42</f>
         <v/>
       </c>
     </row>
@@ -4170,7 +4359,7 @@
         </is>
       </c>
       <c r="B23" s="43">
-        <f>'Stock complet'!G42</f>
+        <f>'Stock complet'!H42</f>
         <v/>
       </c>
     </row>
@@ -4184,14 +4373,14 @@
     <row r="26">
       <c r="A26" s="39" t="inlineStr">
         <is>
-          <t>8 lots sans prix de vente (lignes jaunes) : Balenciaga, sac Karl Lagerfeld, Hoka, Nike Air Max,</t>
+          <t>3 lots sans prix : Yeezy 700 V3 et les deux lots de toupies Beyblade.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="39" t="inlineStr">
         <is>
-          <t>Lacoste, veste Armani Exchange, 2 lots Beyblade. Prix marché à vérifier avant de les chiffrer.</t>
+          <t>Dates de vente à compléter sur les 6 ventes récentes.</t>
         </is>
       </c>
     </row>
@@ -4199,6 +4388,13 @@
       <c r="A28" s="39" t="inlineStr">
         <is>
           <t>Facture manquante : lot n°84, les 2 pompes Robby.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>COLONNE SEUIL D'ÉQUILIBRE : ne jamais vendre en dessous. En dessous, la vente coûte de l'argent.</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4444,7 @@
           <t>Cotisations URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="45" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4263,7 +4459,7 @@
           <t>CFP — formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="45" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -4273,7 +4469,7 @@
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="45" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4288,7 +4484,7 @@
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="46" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4320,8 +4516,8 @@
           <t>Unités de vente reçues d'ADN</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>43</v>
+      <c r="B12" s="10" t="n">
+        <v>54</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -4358,7 +4554,7 @@
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B16" s="44" t="n">
+      <c r="B16" s="45" t="n">
         <v>0.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4373,7 +4569,7 @@
           <t>Tranche marginale du foyer</t>
         </is>
       </c>
-      <c r="B17" s="44" t="n">
+      <c r="B17" s="45" t="n">
         <v>0.11</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -4395,7 +4591,7 @@
           <t>Emballage par colis</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n">
+      <c r="B20" s="46" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4405,7 +4601,7 @@
           <t>Nombre d'annonces prévues</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n">
+      <c r="B21" s="47" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5998,11 +6194,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="n"/>
-      <c r="B39" s="37" t="n"/>
-      <c r="C39" s="37" t="n"/>
-      <c r="D39" s="37" t="n"/>
-      <c r="E39" s="37" t="n"/>
+      <c r="A39" s="35" t="n"/>
+      <c r="B39" s="35" t="n"/>
+      <c r="C39" s="35" t="n"/>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
       <c r="F39" s="33" t="inlineStr">
         <is>
           <t>TOTAL MARCHANDISE</t>
@@ -6033,32 +6229,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="47" t="inlineStr">
+      <c r="A42" s="48" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="B42" s="47" t="inlineStr">
+      <c r="B42" s="48" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C42" s="47" t="inlineStr">
+      <c r="C42" s="48" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="D42" s="47" t="inlineStr">
+      <c r="D42" s="48" t="inlineStr">
         <is>
           <t>Commande</t>
         </is>
       </c>
-      <c r="E42" s="47" t="inlineStr">
+      <c r="E42" s="48" t="inlineStr">
         <is>
           <t>Désignation</t>
         </is>
       </c>
-      <c r="F42" s="47" t="inlineStr">
+      <c r="F42" s="48" t="inlineStr">
         <is>
           <t>Total TTC</t>
         </is>
@@ -6215,10 +6411,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="37" t="n"/>
-      <c r="B48" s="37" t="n"/>
-      <c r="C48" s="37" t="n"/>
-      <c r="D48" s="37" t="n"/>
+      <c r="A48" s="35" t="n"/>
+      <c r="B48" s="35" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="35" t="n"/>
       <c r="E48" s="33" t="inlineStr">
         <is>
           <t>TOTAL LIVRAISON</t>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$X$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$Y$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -191,6 +191,7 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -568,33 +569,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="7" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,100 +643,105 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Prix plancher</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>PRIX DE VENTE</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Marge nette</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Rendement</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Nb</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Coût / art.</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Prix / art.</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Marge / art.</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>URSSAF</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Carte</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Adjugé</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Frais acheteur</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Lot</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>Vendu le</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Unités de vente</t>
         </is>
@@ -750,85 +757,89 @@
         <v>56.7</v>
       </c>
       <c r="C6" s="6">
-        <f>$B6+$X6*Paramètres!$B$13</f>
+        <f>$B6+$Y6*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D6" s="7">
         <f>$C6/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="6">
+        <f>CEILING($D6*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>199</v>
       </c>
-      <c r="F6" s="8">
-        <f>IF($E6="","",$E6-$C6-$L6-$M6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="9">
-        <f>IF($F6="","",$F6/$C6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="10" t="n">
+      <c r="G6" s="8">
+        <f>IF($F6="","",$F6-$C6-$M6-$N6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>IF($G6="","",$G6/$C6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="6">
-        <f>$C6/$H6</f>
-        <v/>
-      </c>
       <c r="J6" s="6">
-        <f>IF($E6="","",$E6/$H6)</f>
+        <f>$C6/$I6</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF($F6="","",$F6/$H6)</f>
-        <v/>
-      </c>
-      <c r="L6" s="7">
-        <f>IF($E6="","",$E6*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M6" s="6" t="n">
+        <f>IF($F6="","",$F6/$I6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="6">
+        <f>IF($G6="","",$G6/$I6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="7">
+        <f>IF($F6="","",$F6*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="O6" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="P6" s="11" t="n">
         <v>11.7</v>
       </c>
-      <c r="P6" s="12" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="R6" s="12" t="inlineStr">
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>FB2026-6354</t>
         </is>
       </c>
-      <c r="S6" s="12" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
         <is>
           <t>Leboncoin B2B</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>Février-mars</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="n">
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -842,85 +853,89 @@
         <v>37.8</v>
       </c>
       <c r="C7" s="6">
-        <f>$B7+$X7*Paramètres!$B$13</f>
+        <f>$B7+$Y7*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D7" s="7">
         <f>$C7/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="6">
+        <f>CEILING($D7*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>178</v>
       </c>
-      <c r="F7" s="8">
-        <f>IF($E7="","",$E7-$C7-$L7-$M7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="9">
-        <f>IF($F7="","",$F7/$C7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="10" t="n">
+      <c r="G7" s="8">
+        <f>IF($F7="","",$F7-$C7-$M7-$N7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>IF($G7="","",$G7/$C7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="6">
-        <f>$C7/$H7</f>
-        <v/>
-      </c>
       <c r="J7" s="6">
-        <f>IF($E7="","",$E7/$H7)</f>
+        <f>$C7/$I7</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF($F7="","",$F7/$H7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="7">
-        <f>IF($E7="","",$E7*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M7" s="6" t="n">
+        <f>IF($F7="","",$F7/$I7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="6">
+        <f>IF($G7="","",$G7/$I7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="7">
+        <f>IF($F7="","",$F7*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="O7" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="P7" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="P7" s="12" t="inlineStr">
+      <c r="Q7" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="R7" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R7" s="12" t="inlineStr">
+      <c r="S7" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S7" s="12" t="inlineStr">
+      <c r="T7" s="12" t="inlineStr">
         <is>
           <t>357</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="n">
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -934,86 +949,90 @@
         <v>63</v>
       </c>
       <c r="C8" s="6">
-        <f>$B8+$X8*Paramètres!$B$13</f>
+        <f>$B8+$Y8*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D8" s="7">
         <f>$C8/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="6">
+        <f>CEILING($D8*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>159</v>
       </c>
-      <c r="F8" s="8">
-        <f>IF($E8="","",$E8-$C8-$L8-$M8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="9">
-        <f>IF($F8="","",$F8/$C8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="10" t="n">
+      <c r="G8" s="8">
+        <f>IF($F8="","",$F8-$C8-$M8-$N8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>IF($G8="","",$G8/$C8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="6">
-        <f>$C8/$H8</f>
-        <v/>
-      </c>
       <c r="J8" s="6">
-        <f>IF($E8="","",$E8/$H8)</f>
+        <f>$C8/$I8</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF($F8="","",$F8/$H8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="7">
-        <f>IF($E8="","",$E8*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M8" s="6">
-        <f>IF($E8="","",$E8*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N8" s="11" t="n">
+        <f>IF($F8="","",$F8/$I8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="6">
+        <f>IF($G8="","",$G8/$I8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="7">
+        <f>IF($F8="","",$F8*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N8" s="6">
+        <f>IF($F8="","",$F8*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O8" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="P8" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="P8" s="12" t="inlineStr">
+      <c r="Q8" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q8" s="12" t="inlineStr">
+      <c r="R8" s="12" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="R8" s="12" t="inlineStr">
+      <c r="S8" s="12" t="inlineStr">
         <is>
           <t>FB2026-46058</t>
         </is>
       </c>
-      <c r="S8" s="12" t="inlineStr">
+      <c r="T8" s="12" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr"/>
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="n">
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1027,86 +1046,90 @@
         <v>20.45</v>
       </c>
       <c r="C9" s="6">
-        <f>$B9+$X9*Paramètres!$B$13</f>
+        <f>$B9+$Y9*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D9" s="7">
         <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="6">
+        <f>CEILING($D9*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F9" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="F9" s="8">
-        <f>IF($E9="","",$E9-$C9-$L9-$M9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="9">
-        <f>IF($F9="","",$F9/$C9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="10" t="n">
+      <c r="G9" s="8">
+        <f>IF($F9="","",$F9-$C9-$M9-$N9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>IF($G9="","",$G9/$C9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="6">
-        <f>$C9/$H9</f>
-        <v/>
-      </c>
       <c r="J9" s="6">
-        <f>IF($E9="","",$E9/$H9)</f>
+        <f>$C9/$I9</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF($F9="","",$F9/$H9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="7">
-        <f>IF($E9="","",$E9*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M9" s="6">
-        <f>IF($E9="","",$E9*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N9" s="11" t="n">
+        <f>IF($F9="","",$F9/$I9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="6">
+        <f>IF($G9="","",$G9/$I9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="7">
+        <f>IF($F9="","",$F9*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N9" s="6">
+        <f>IF($F9="","",$F9*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O9" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="P9" s="11" t="n">
         <v>4.16</v>
       </c>
-      <c r="P9" s="12" t="inlineStr">
+      <c r="Q9" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q9" s="12" t="inlineStr">
+      <c r="R9" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R9" s="12" t="inlineStr">
+      <c r="S9" s="12" t="inlineStr">
         <is>
           <t>FB2026-5996</t>
         </is>
       </c>
-      <c r="S9" s="12" t="inlineStr">
+      <c r="T9" s="12" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="n">
+      <c r="X9" s="4" t="inlineStr"/>
+      <c r="Y9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1120,85 +1143,89 @@
         <v>68.56999999999999</v>
       </c>
       <c r="C10" s="6">
-        <f>$B10+$X10*Paramètres!$B$13</f>
+        <f>$B10+$Y10*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D10" s="7">
         <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="6">
+        <f>CEILING($D10*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>139</v>
       </c>
-      <c r="F10" s="8">
-        <f>IF($E10="","",$E10-$C10-$L10-$M10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="9">
-        <f>IF($F10="","",$F10/$C10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="10" t="n">
+      <c r="G10" s="8">
+        <f>IF($F10="","",$F10-$C10-$M10-$N10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>IF($G10="","",$G10/$C10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="6">
-        <f>$C10/$H10</f>
-        <v/>
-      </c>
       <c r="J10" s="6">
-        <f>IF($E10="","",$E10/$H10)</f>
+        <f>$C10/$I10</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF($F10="","",$F10/$H10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="7">
-        <f>IF($E10="","",$E10*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M10" s="6" t="n">
+        <f>IF($F10="","",$F10/$I10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="6">
+        <f>IF($G10="","",$G10/$I10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="7">
+        <f>IF($F10="","",$F10*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="11" t="n">
+      <c r="O10" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="O10" s="11" t="n">
+      <c r="P10" s="11" t="n">
         <v>8.57</v>
       </c>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="Q10" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q10" s="12" t="inlineStr">
+      <c r="R10" s="12" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="R10" s="12" t="inlineStr">
+      <c r="S10" s="12" t="inlineStr">
         <is>
           <t>FB2026-46060</t>
         </is>
       </c>
-      <c r="S10" s="12" t="inlineStr">
+      <c r="T10" s="12" t="inlineStr">
         <is>
           <t>1350</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="U10" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr"/>
+      <c r="W10" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="n">
+      <c r="X10" s="4" t="inlineStr"/>
+      <c r="Y10" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1219,74 +1246,78 @@
         <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="6">
+        <f>CEILING($D11*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>132</v>
       </c>
-      <c r="F11" s="8">
-        <f>IF($E11="","",$E11-$C11-$L11-$M11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="9">
-        <f>IF($F11="","",$F11/$C11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="10" t="n">
+      <c r="G11" s="8">
+        <f>IF($F11="","",$F11-$C11-$M11-$N11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>IF($G11="","",$G11/$C11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I11" s="6">
-        <f>$C11/$H11</f>
-        <v/>
-      </c>
       <c r="J11" s="6">
-        <f>IF($E11="","",$E11/$H11)</f>
+        <f>$C11/$I11</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF($F11="","",$F11/$H11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="7">
-        <f>IF($E11="","",$E11*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M11" s="6" t="n">
+        <f>IF($F11="","",$F11/$I11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="6">
+        <f>IF($G11="","",$G11/$I11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="7">
+        <f>IF($F11="","",$F11*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="13" t="n"/>
       <c r="O11" s="13" t="n"/>
-      <c r="P11" s="12" t="inlineStr">
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="12" t="inlineStr">
         <is>
           <t>Vendeur au Japon</t>
         </is>
       </c>
-      <c r="Q11" s="12" t="inlineStr">
+      <c r="R11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R11" s="12" t="inlineStr">
+      <c r="S11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S11" s="12" t="inlineStr">
+      <c r="T11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>eBay + Leboncoin</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="n">
+      <c r="X11" s="4" t="inlineStr"/>
+      <c r="Y11" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1300,86 +1331,90 @@
         <v>12.6</v>
       </c>
       <c r="C12" s="6">
-        <f>$B12+$X12*Paramètres!$B$13</f>
+        <f>$B12+$Y12*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D12" s="7">
         <f>$C12/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="6">
+        <f>CEILING($D12*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="F12" s="8">
-        <f>IF($E12="","",$E12-$C12-$L12-$M12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="9">
-        <f>IF($F12="","",$F12/$C12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="10" t="n">
+      <c r="G12" s="8">
+        <f>IF($F12="","",$F12-$C12-$M12-$N12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>IF($G12="","",$G12/$C12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="6">
-        <f>$C12/$H12</f>
-        <v/>
-      </c>
       <c r="J12" s="6">
-        <f>IF($E12="","",$E12/$H12)</f>
+        <f>$C12/$I12</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF($F12="","",$F12/$H12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="7">
-        <f>IF($E12="","",$E12*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M12" s="6">
-        <f>IF($E12="","",$E12*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N12" s="11" t="n">
+        <f>IF($F12="","",$F12/$I12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="6">
+        <f>IF($G12="","",$G12/$I12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="7">
+        <f>IF($F12="","",$F12*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N12" s="6">
+        <f>IF($F12="","",$F12*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="O12" s="11" t="n">
+      <c r="P12" s="11" t="n">
         <v>2.6</v>
       </c>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="Q12" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q12" s="12" t="inlineStr">
+      <c r="R12" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R12" s="12" t="inlineStr">
+      <c r="S12" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S12" s="12" t="inlineStr">
+      <c r="T12" s="12" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr"/>
+      <c r="W12" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="n">
+      <c r="X12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1393,86 +1428,90 @@
         <v>37.8</v>
       </c>
       <c r="C13" s="6">
-        <f>$B13+$X13*Paramètres!$B$13</f>
+        <f>$B13+$Y13*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D13" s="7">
         <f>$C13/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="6">
+        <f>CEILING($D13*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="F13" s="8">
-        <f>IF($E13="","",$E13-$C13-$L13-$M13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="9">
-        <f>IF($F13="","",$F13/$C13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="10" t="n">
+      <c r="G13" s="8">
+        <f>IF($F13="","",$F13-$C13-$M13-$N13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>IF($G13="","",$G13/$C13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="6">
-        <f>$C13/$H13</f>
-        <v/>
-      </c>
       <c r="J13" s="6">
-        <f>IF($E13="","",$E13/$H13)</f>
+        <f>$C13/$I13</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF($F13="","",$F13/$H13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="7">
-        <f>IF($E13="","",$E13*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M13" s="6">
-        <f>IF($E13="","",$E13*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N13" s="11" t="n">
+        <f>IF($F13="","",$F13/$I13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="6">
+        <f>IF($G13="","",$G13/$I13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="7">
+        <f>IF($F13="","",$F13*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N13" s="6">
+        <f>IF($F13="","",$F13*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O13" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="O13" s="11" t="n">
+      <c r="P13" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="Q13" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q13" s="12" t="inlineStr">
+      <c r="R13" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R13" s="12" t="inlineStr">
+      <c r="S13" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S13" s="12" t="inlineStr">
+      <c r="T13" s="12" t="inlineStr">
         <is>
           <t>417</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="n">
+      <c r="X13" s="4" t="inlineStr"/>
+      <c r="Y13" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1486,86 +1525,90 @@
         <v>37.8</v>
       </c>
       <c r="C14" s="6">
-        <f>$B14+$X14*Paramètres!$B$13</f>
+        <f>$B14+$Y14*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D14" s="7">
         <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="6">
+        <f>CEILING($D14*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="F14" s="8">
-        <f>IF($E14="","",$E14-$C14-$L14-$M14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="9">
-        <f>IF($F14="","",$F14/$C14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="10" t="n">
+      <c r="G14" s="8">
+        <f>IF($F14="","",$F14-$C14-$M14-$N14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>IF($G14="","",$G14/$C14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="6">
-        <f>$C14/$H14</f>
-        <v/>
-      </c>
       <c r="J14" s="6">
-        <f>IF($E14="","",$E14/$H14)</f>
+        <f>$C14/$I14</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF($F14="","",$F14/$H14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="7">
-        <f>IF($E14="","",$E14*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M14" s="6">
-        <f>IF($E14="","",$E14*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N14" s="11" t="n">
+        <f>IF($F14="","",$F14/$I14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="6">
+        <f>IF($G14="","",$G14/$I14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="7">
+        <f>IF($F14="","",$F14*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N14" s="6">
+        <f>IF($F14="","",$F14*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O14" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="O14" s="11" t="n">
+      <c r="P14" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="Q14" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q14" s="12" t="inlineStr">
+      <c r="R14" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R14" s="12" t="inlineStr">
+      <c r="S14" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S14" s="12" t="inlineStr">
+      <c r="T14" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr">
+      <c r="U14" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr"/>
+      <c r="W14" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="n">
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1579,85 +1622,89 @@
         <v>37.8</v>
       </c>
       <c r="C15" s="6">
-        <f>$B15+$X15*Paramètres!$B$13</f>
+        <f>$B15+$Y15*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D15" s="7">
         <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="6">
+        <f>CEILING($D15*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>92</v>
       </c>
-      <c r="F15" s="8">
-        <f>IF($E15="","",$E15-$C15-$L15-$M15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="9">
-        <f>IF($F15="","",$F15/$C15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="10" t="n">
+      <c r="G15" s="8">
+        <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="9">
+        <f>IF($G15="","",$G15/$C15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I15" s="6">
-        <f>$C15/$H15</f>
-        <v/>
-      </c>
       <c r="J15" s="6">
-        <f>IF($E15="","",$E15/$H15)</f>
+        <f>$C15/$I15</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF($F15="","",$F15/$H15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="7">
-        <f>IF($E15="","",$E15*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M15" s="6" t="n">
+        <f>IF($F15="","",$F15/$I15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="6">
+        <f>IF($G15="","",$G15/$I15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="7">
+        <f>IF($F15="","",$F15*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="O15" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="P15" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="P15" s="12" t="inlineStr">
+      <c r="Q15" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q15" s="12" t="inlineStr">
+      <c r="R15" s="12" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="R15" s="12" t="inlineStr">
+      <c r="S15" s="12" t="inlineStr">
         <is>
           <t>FB2026-46056</t>
         </is>
       </c>
-      <c r="S15" s="12" t="inlineStr">
+      <c r="T15" s="12" t="inlineStr">
         <is>
           <t>279</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr">
+      <c r="U15" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="n">
+      <c r="X15" s="4" t="inlineStr"/>
+      <c r="Y15" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1678,74 +1725,78 @@
         <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="6">
+        <f>CEILING($D16*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F16" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="F16" s="8">
-        <f>IF($E16="","",$E16-$C16-$L16-$M16)</f>
-        <v/>
-      </c>
-      <c r="G16" s="9">
-        <f>IF($F16="","",$F16/$C16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="10" t="n">
+      <c r="G16" s="8">
+        <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>IF($G16="","",$G16/$C16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="6">
-        <f>$C16/$H16</f>
-        <v/>
-      </c>
       <c r="J16" s="6">
-        <f>IF($E16="","",$E16/$H16)</f>
+        <f>$C16/$I16</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF($F16="","",$F16/$H16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="7">
-        <f>IF($E16="","",$E16*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M16" s="6" t="n">
+        <f>IF($F16="","",$F16/$I16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="6">
+        <f>IF($G16="","",$G16/$I16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="7">
+        <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="13" t="n"/>
       <c r="O16" s="13" t="n"/>
-      <c r="P16" s="12" t="inlineStr">
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="12" t="inlineStr">
         <is>
           <t>ADN (facture à retrouver)</t>
         </is>
       </c>
-      <c r="Q16" s="12" t="inlineStr">
+      <c r="R16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R16" s="12" t="inlineStr">
+      <c r="S16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S16" s="12" t="inlineStr">
+      <c r="T16" s="12" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr">
+      <c r="U16" s="4" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="inlineStr">
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="n">
+      <c r="X16" s="4" t="inlineStr"/>
+      <c r="Y16" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1759,86 +1810,90 @@
         <v>37.8</v>
       </c>
       <c r="C17" s="6">
-        <f>$B17+$X17*Paramètres!$B$13</f>
+        <f>$B17+$Y17*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D17" s="7">
         <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="6">
+        <f>CEILING($D17*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F17" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="F17" s="8">
-        <f>IF($E17="","",$E17-$C17-$L17-$M17)</f>
-        <v/>
-      </c>
-      <c r="G17" s="9">
-        <f>IF($F17="","",$F17/$C17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="10" t="n">
+      <c r="G17" s="8">
+        <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>IF($G17="","",$G17/$C17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="6">
-        <f>$C17/$H17</f>
-        <v/>
-      </c>
       <c r="J17" s="6">
-        <f>IF($E17="","",$E17/$H17)</f>
+        <f>$C17/$I17</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF($F17="","",$F17/$H17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="7">
-        <f>IF($E17="","",$E17*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M17" s="6">
-        <f>IF($E17="","",$E17*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N17" s="11" t="n">
+        <f>IF($F17="","",$F17/$I17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="6">
+        <f>IF($G17="","",$G17/$I17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="7">
+        <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N17" s="6">
+        <f>IF($F17="","",$F17*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O17" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="P17" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="Q17" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q17" s="12" t="inlineStr">
+      <c r="R17" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R17" s="12" t="inlineStr">
+      <c r="S17" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S17" s="12" t="inlineStr">
+      <c r="T17" s="12" t="inlineStr">
         <is>
           <t>434</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
+      <c r="U17" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="n">
+      <c r="X17" s="4" t="inlineStr"/>
+      <c r="Y17" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1852,89 +1907,93 @@
         <v>100.8</v>
       </c>
       <c r="C18" s="16">
-        <f>$B18+$X18*Paramètres!$B$13</f>
+        <f>$B18+$Y18*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D18" s="17">
         <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="16">
+        <f>CEILING($D18*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F18" s="18" t="n">
         <v>168</v>
       </c>
-      <c r="F18" s="18">
-        <f>IF($E18="","",$E18-$C18-$L18-$M18)</f>
-        <v/>
-      </c>
-      <c r="G18" s="19">
-        <f>IF($F18="","",$F18/$C18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="20" t="n">
+      <c r="G18" s="18">
+        <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="19">
+        <f>IF($G18="","",$G18/$C18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="I18" s="16">
-        <f>$C18/$H18</f>
-        <v/>
-      </c>
       <c r="J18" s="16">
-        <f>IF($E18="","",$E18/$H18)</f>
+        <f>$C18/$I18</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>IF($F18="","",$F18/$H18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="17">
-        <f>IF($E18="","",$E18*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M18" s="16" t="n">
+        <f>IF($F18="","",$F18/$I18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="16">
+        <f>IF($G18="","",$G18/$I18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="17">
+        <f>IF($F18="","",$F18*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="21" t="n">
+      <c r="O18" s="21" t="n">
         <v>80</v>
       </c>
-      <c r="O18" s="21" t="n">
+      <c r="P18" s="21" t="n">
         <v>20.8</v>
       </c>
-      <c r="P18" s="22" t="inlineStr">
+      <c r="Q18" s="22" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q18" s="22" t="inlineStr">
+      <c r="R18" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R18" s="22" t="inlineStr">
+      <c r="S18" s="22" t="inlineStr">
         <is>
           <t>FB2026-5844</t>
         </is>
       </c>
-      <c r="S18" s="22" t="inlineStr">
+      <c r="T18" s="22" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="T18" s="14" t="inlineStr">
+      <c r="U18" s="14" t="inlineStr">
         <is>
           <t>Leboncoin, à l'unité</t>
         </is>
       </c>
-      <c r="U18" s="14" t="inlineStr"/>
-      <c r="V18" s="14" t="inlineStr">
+      <c r="V18" s="14" t="inlineStr"/>
+      <c r="W18" s="14" t="inlineStr">
         <is>
           <t>URGENT — 2 sur 12 vendues</t>
         </is>
       </c>
-      <c r="W18" s="14" t="inlineStr">
+      <c r="X18" s="14" t="inlineStr">
         <is>
           <t>2 vendues</t>
         </is>
       </c>
-      <c r="X18" s="14" t="n">
+      <c r="Y18" s="14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1948,86 +2007,90 @@
         <v>50.4</v>
       </c>
       <c r="C19" s="6">
-        <f>$B19+$X19*Paramètres!$B$13</f>
+        <f>$B19+$Y19*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D19" s="7">
         <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="6">
+        <f>CEILING($D19*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="F19" s="8">
-        <f>IF($E19="","",$E19-$C19-$L19-$M19)</f>
-        <v/>
-      </c>
-      <c r="G19" s="9">
-        <f>IF($F19="","",$F19/$C19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="10" t="n">
+      <c r="G19" s="8">
+        <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="9">
+        <f>IF($G19="","",$G19/$C19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="6">
-        <f>$C19/$H19</f>
-        <v/>
-      </c>
       <c r="J19" s="6">
-        <f>IF($E19="","",$E19/$H19)</f>
+        <f>$C19/$I19</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF($F19="","",$F19/$H19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="7">
-        <f>IF($E19="","",$E19*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M19" s="6">
-        <f>IF($E19="","",$E19*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N19" s="11" t="n">
+        <f>IF($F19="","",$F19/$I19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="6">
+        <f>IF($G19="","",$G19/$I19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="7">
+        <f>IF($F19="","",$F19*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N19" s="6">
+        <f>IF($F19="","",$F19*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O19" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="P19" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="P19" s="12" t="inlineStr">
+      <c r="Q19" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q19" s="12" t="inlineStr">
+      <c r="R19" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R19" s="12" t="inlineStr">
+      <c r="S19" s="12" t="inlineStr">
         <is>
           <t>FB2026-44194</t>
         </is>
       </c>
-      <c r="S19" s="12" t="inlineStr">
+      <c r="T19" s="12" t="inlineStr">
         <is>
           <t>229</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="U19" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="n">
+      <c r="X19" s="4" t="inlineStr"/>
+      <c r="Y19" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2041,86 +2104,90 @@
         <v>31.95</v>
       </c>
       <c r="C20" s="6">
-        <f>$B20+$X20*Paramètres!$B$13</f>
+        <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7">
         <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="6">
+        <f>CEILING($D20*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="F20" s="8">
-        <f>IF($E20="","",$E20-$C20-$L20-$M20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="9">
-        <f>IF($F20="","",$F20/$C20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="10" t="n">
+      <c r="G20" s="8">
+        <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>IF($G20="","",$G20/$C20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="6">
-        <f>$C20/$H20</f>
-        <v/>
-      </c>
       <c r="J20" s="6">
-        <f>IF($E20="","",$E20/$H20)</f>
+        <f>$C20/$I20</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF($F20="","",$F20/$H20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="7">
-        <f>IF($E20="","",$E20*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M20" s="6">
-        <f>IF($E20="","",$E20*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N20" s="11" t="n">
+        <f>IF($F20="","",$F20/$I20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="6">
+        <f>IF($G20="","",$G20/$I20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="7">
+        <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N20" s="6">
+        <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O20" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="P20" s="11" t="n">
         <v>6.5</v>
       </c>
-      <c r="P20" s="12" t="inlineStr">
+      <c r="Q20" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q20" s="12" t="inlineStr">
+      <c r="R20" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R20" s="12" t="inlineStr">
+      <c r="S20" s="12" t="inlineStr">
         <is>
           <t>FB2026-5996</t>
         </is>
       </c>
-      <c r="S20" s="12" t="inlineStr">
+      <c r="T20" s="12" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="T20" s="4" t="inlineStr">
+      <c r="U20" s="4" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="inlineStr">
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="n">
+      <c r="X20" s="4" t="inlineStr"/>
+      <c r="Y20" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2134,85 +2201,89 @@
         <v>25.2</v>
       </c>
       <c r="C21" s="6">
-        <f>$B21+$X21*Paramètres!$B$13</f>
+        <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7">
         <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="6">
+        <f>CEILING($D21*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="F21" s="8">
-        <f>IF($E21="","",$E21-$C21-$L21-$M21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="9">
-        <f>IF($F21="","",$F21/$C21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="10" t="n">
+      <c r="G21" s="8">
+        <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>IF($G21="","",$G21/$C21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="6">
-        <f>$C21/$H21</f>
-        <v/>
-      </c>
       <c r="J21" s="6">
-        <f>IF($E21="","",$E21/$H21)</f>
+        <f>$C21/$I21</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF($F21="","",$F21/$H21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="7">
-        <f>IF($E21="","",$E21*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M21" s="6" t="n">
+        <f>IF($F21="","",$F21/$I21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="6">
+        <f>IF($G21="","",$G21/$I21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="7">
+        <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="11" t="n">
+      <c r="O21" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="P21" s="11" t="n">
         <v>5.2</v>
       </c>
-      <c r="P21" s="12" t="inlineStr">
+      <c r="Q21" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q21" s="12" t="inlineStr">
+      <c r="R21" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R21" s="12" t="inlineStr">
+      <c r="S21" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S21" s="12" t="inlineStr">
+      <c r="T21" s="12" t="inlineStr">
         <is>
           <t>439</t>
         </is>
       </c>
-      <c r="T21" s="4" t="inlineStr">
+      <c r="U21" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="inlineStr">
+      <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="n">
+      <c r="X21" s="4" t="inlineStr"/>
+      <c r="Y21" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2226,86 +2297,90 @@
         <v>25.56</v>
       </c>
       <c r="C22" s="6">
-        <f>$B22+$X22*Paramètres!$B$13</f>
+        <f>$B22+$Y22*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D22" s="7">
         <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="6">
+        <f>CEILING($D22*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F22" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="F22" s="8">
-        <f>IF($E22="","",$E22-$C22-$L22-$M22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="9">
-        <f>IF($F22="","",$F22/$C22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="10" t="n">
+      <c r="G22" s="8">
+        <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>IF($G22="","",$G22/$C22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="6">
-        <f>$C22/$H22</f>
-        <v/>
-      </c>
       <c r="J22" s="6">
-        <f>IF($E22="","",$E22/$H22)</f>
+        <f>$C22/$I22</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF($F22="","",$F22/$H22)</f>
-        <v/>
-      </c>
-      <c r="L22" s="7">
-        <f>IF($E22="","",$E22*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M22" s="6">
-        <f>IF($E22="","",$E22*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N22" s="11" t="n">
+        <f>IF($F22="","",$F22/$I22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="6">
+        <f>IF($G22="","",$G22/$I22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="7">
+        <f>IF($F22="","",$F22*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N22" s="6">
+        <f>IF($F22="","",$F22*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O22" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="P22" s="11" t="n">
         <v>5.2</v>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="Q22" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q22" s="12" t="inlineStr">
+      <c r="R22" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R22" s="12" t="inlineStr">
+      <c r="S22" s="12" t="inlineStr">
         <is>
           <t>FB2026-5996</t>
         </is>
       </c>
-      <c r="S22" s="12" t="inlineStr">
+      <c r="T22" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr">
+      <c r="U22" s="4" t="inlineStr">
         <is>
           <t>Boutique + Leboncoin</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="inlineStr">
+      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="n">
+      <c r="X22" s="4" t="inlineStr"/>
+      <c r="Y22" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2319,85 +2394,89 @@
         <v>57.51</v>
       </c>
       <c r="C23" s="6">
-        <f>$B23+$X23*Paramètres!$B$13</f>
+        <f>$B23+$Y23*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D23" s="7">
         <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="6">
+        <f>CEILING($D23*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="F23" s="8">
-        <f>IF($E23="","",$E23-$C23-$L23-$M23)</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
-        <f>IF($F23="","",$F23/$C23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="10" t="n">
+      <c r="G23" s="8">
+        <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>IF($G23="","",$G23/$C23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="6">
-        <f>$C23/$H23</f>
-        <v/>
-      </c>
       <c r="J23" s="6">
-        <f>IF($E23="","",$E23/$H23)</f>
+        <f>$C23/$I23</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF($F23="","",$F23/$H23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="7">
-        <f>IF($E23="","",$E23*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M23" s="6" t="n">
+        <f>IF($F23="","",$F23/$I23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="6">
+        <f>IF($G23="","",$G23/$I23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="7">
+        <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="11" t="n">
+      <c r="O23" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="O23" s="11" t="n">
+      <c r="P23" s="11" t="n">
         <v>11.7</v>
       </c>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="Q23" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q23" s="12" t="inlineStr">
+      <c r="R23" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R23" s="12" t="inlineStr">
+      <c r="S23" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="S23" s="12" t="inlineStr">
+      <c r="T23" s="12" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr">
+      <c r="U23" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="inlineStr">
+      <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W23" s="4" t="inlineStr"/>
-      <c r="X23" s="4" t="n">
+      <c r="X23" s="4" t="inlineStr"/>
+      <c r="Y23" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2411,85 +2490,89 @@
         <v>37.8</v>
       </c>
       <c r="C24" s="6">
-        <f>$B24+$X24*Paramètres!$B$13</f>
+        <f>$B24+$Y24*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D24" s="7">
         <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="6">
+        <f>CEILING($D24*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="F24" s="8">
-        <f>IF($E24="","",$E24-$C24-$L24-$M24)</f>
-        <v/>
-      </c>
-      <c r="G24" s="9">
-        <f>IF($F24="","",$F24/$C24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="10" t="n">
+      <c r="G24" s="8">
+        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>IF($G24="","",$G24/$C24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I24" s="6">
-        <f>$C24/$H24</f>
-        <v/>
-      </c>
       <c r="J24" s="6">
-        <f>IF($E24="","",$E24/$H24)</f>
+        <f>$C24/$I24</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF($F24="","",$F24/$H24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="7">
-        <f>IF($E24="","",$E24*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M24" s="6" t="n">
+        <f>IF($F24="","",$F24/$I24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="6">
+        <f>IF($G24="","",$G24/$I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="7">
+        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="11" t="n">
+      <c r="O24" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="O24" s="11" t="n">
+      <c r="P24" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="Q24" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q24" s="12" t="inlineStr">
+      <c r="R24" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R24" s="12" t="inlineStr">
+      <c r="S24" s="12" t="inlineStr">
         <is>
           <t>FB2026-43717</t>
         </is>
       </c>
-      <c r="S24" s="12" t="inlineStr">
+      <c r="T24" s="12" t="inlineStr">
         <is>
           <t>303</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr">
+      <c r="U24" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + Vinted</t>
         </is>
       </c>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="inlineStr">
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="inlineStr">
         <is>
           <t>URGENT — saisonnier</t>
         </is>
       </c>
-      <c r="W24" s="4" t="inlineStr"/>
-      <c r="X24" s="4" t="n">
+      <c r="X24" s="4" t="inlineStr"/>
+      <c r="Y24" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2503,85 +2586,89 @@
         <v>21.73</v>
       </c>
       <c r="C25" s="6">
-        <f>$B25+$X25*Paramètres!$B$13</f>
+        <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D25" s="7">
         <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="6">
+        <f>CEILING($D25*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="F25" s="8">
-        <f>IF($E25="","",$E25-$C25-$L25-$M25)</f>
-        <v/>
-      </c>
-      <c r="G25" s="9">
-        <f>IF($F25="","",$F25/$C25)</f>
-        <v/>
-      </c>
-      <c r="H25" s="10" t="n">
+      <c r="G25" s="8">
+        <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>IF($G25="","",$G25/$C25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="6">
-        <f>$C25/$H25</f>
-        <v/>
-      </c>
       <c r="J25" s="6">
-        <f>IF($E25="","",$E25/$H25)</f>
+        <f>$C25/$I25</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF($F25="","",$F25/$H25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="7">
-        <f>IF($E25="","",$E25*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M25" s="6" t="n">
+        <f>IF($F25="","",$F25/$I25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="6">
+        <f>IF($G25="","",$G25/$I25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="7">
+        <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="11" t="n">
+      <c r="O25" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="O25" s="11" t="n">
+      <c r="P25" s="11" t="n">
         <v>4.42</v>
       </c>
-      <c r="P25" s="12" t="inlineStr">
+      <c r="Q25" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q25" s="12" t="inlineStr">
+      <c r="R25" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R25" s="12" t="inlineStr">
+      <c r="S25" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="S25" s="12" t="inlineStr">
+      <c r="T25" s="12" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr">
+      <c r="U25" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="inlineStr">
+      <c r="V25" s="4" t="inlineStr"/>
+      <c r="W25" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="W25" s="4" t="inlineStr"/>
-      <c r="X25" s="4" t="n">
+      <c r="X25" s="4" t="inlineStr"/>
+      <c r="Y25" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2595,86 +2682,90 @@
         <v>50.4</v>
       </c>
       <c r="C26" s="6">
-        <f>$B26+$X26*Paramètres!$B$13</f>
+        <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D26" s="7">
         <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="6">
+        <f>CEILING($D26*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="F26" s="8">
-        <f>IF($E26="","",$E26-$C26-$L26-$M26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="9">
-        <f>IF($F26="","",$F26/$C26)</f>
-        <v/>
-      </c>
-      <c r="H26" s="10" t="n">
+      <c r="G26" s="8">
+        <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="9">
+        <f>IF($G26="","",$G26/$C26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="6">
-        <f>$C26/$H26</f>
-        <v/>
-      </c>
       <c r="J26" s="6">
-        <f>IF($E26="","",$E26/$H26)</f>
+        <f>$C26/$I26</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF($F26="","",$F26/$H26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="7">
-        <f>IF($E26="","",$E26*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M26" s="6">
-        <f>IF($E26="","",$E26*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="N26" s="11" t="n">
+        <f>IF($F26="","",$F26/$I26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="6">
+        <f>IF($G26="","",$G26/$I26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="7">
+        <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N26" s="6">
+        <f>IF($F26="","",$F26*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O26" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="O26" s="11" t="n">
+      <c r="P26" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="Q26" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q26" s="12" t="inlineStr">
+      <c r="R26" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R26" s="12" t="inlineStr">
+      <c r="S26" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S26" s="12" t="inlineStr">
+      <c r="T26" s="12" t="inlineStr">
         <is>
           <t>408</t>
         </is>
       </c>
-      <c r="T26" s="4" t="inlineStr">
+      <c r="U26" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="inlineStr">
+      <c r="V26" s="4" t="inlineStr"/>
+      <c r="W26" s="4" t="inlineStr">
         <is>
           <t>URGENT — saisonnier</t>
         </is>
       </c>
-      <c r="W26" s="4" t="inlineStr"/>
-      <c r="X26" s="4" t="n">
+      <c r="X26" s="4" t="inlineStr"/>
+      <c r="Y26" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2688,85 +2779,89 @@
         <v>75.59999999999999</v>
       </c>
       <c r="C27" s="6">
-        <f>$B27+$X27*Paramètres!$B$13</f>
+        <f>$B27+$Y27*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D27" s="7">
         <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="6">
+        <f>CEILING($D27*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="F27" s="8">
-        <f>IF($E27="","",$E27-$C27-$L27-$M27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="9">
-        <f>IF($F27="","",$F27/$C27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="10" t="n">
+      <c r="G27" s="8">
+        <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>IF($G27="","",$G27/$C27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="6">
-        <f>$C27/$H27</f>
-        <v/>
-      </c>
       <c r="J27" s="6">
-        <f>IF($E27="","",$E27/$H27)</f>
+        <f>$C27/$I27</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF($F27="","",$F27/$H27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="7">
-        <f>IF($E27="","",$E27*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M27" s="6" t="n">
+        <f>IF($F27="","",$F27/$I27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="6">
+        <f>IF($G27="","",$G27/$I27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="7">
+        <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="11" t="n">
+      <c r="O27" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="O27" s="11" t="n">
+      <c r="P27" s="11" t="n">
         <v>15.6</v>
       </c>
-      <c r="P27" s="12" t="inlineStr">
+      <c r="Q27" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q27" s="12" t="inlineStr">
+      <c r="R27" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R27" s="12" t="inlineStr">
+      <c r="S27" s="12" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S27" s="12" t="inlineStr">
+      <c r="T27" s="12" t="inlineStr">
         <is>
           <t>199</t>
         </is>
       </c>
-      <c r="T27" s="4" t="inlineStr">
+      <c r="U27" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="inlineStr">
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="W27" s="4" t="inlineStr"/>
-      <c r="X27" s="4" t="n">
+      <c r="X27" s="4" t="inlineStr"/>
+      <c r="Y27" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2780,89 +2875,93 @@
         <v>76.68000000000001</v>
       </c>
       <c r="C28" s="16">
-        <f>$B28+$X28*Paramètres!$B$13</f>
+        <f>$B28+$Y28*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D28" s="17">
         <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="16">
+        <f>CEILING($D28*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F28" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="F28" s="18">
-        <f>IF($E28="","",$E28-$C28-$L28-$M28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="19">
-        <f>IF($F28="","",$F28/$C28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="20" t="n">
+      <c r="G28" s="18">
+        <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
+        <f>IF($G28="","",$G28/$C28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="16">
-        <f>$C28/$H28</f>
-        <v/>
-      </c>
       <c r="J28" s="16">
-        <f>IF($E28="","",$E28/$H28)</f>
+        <f>$C28/$I28</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>IF($F28="","",$F28/$H28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="17">
-        <f>IF($E28="","",$E28*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M28" s="16" t="n">
+        <f>IF($F28="","",$F28/$I28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="16">
+        <f>IF($G28="","",$G28/$I28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="17">
+        <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="21" t="n">
+      <c r="O28" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="O28" s="21" t="n">
+      <c r="P28" s="21" t="n">
         <v>15.6</v>
       </c>
-      <c r="P28" s="22" t="inlineStr">
+      <c r="Q28" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q28" s="22" t="inlineStr">
+      <c r="R28" s="22" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R28" s="22" t="inlineStr">
+      <c r="S28" s="22" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="S28" s="22" t="inlineStr">
+      <c r="T28" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T28" s="14" t="inlineStr">
+      <c r="U28" s="14" t="inlineStr">
         <is>
           <t>Vinted, acheteur en Italie</t>
         </is>
       </c>
-      <c r="U28" s="14" t="inlineStr"/>
-      <c r="V28" s="14" t="inlineStr">
+      <c r="V28" s="14" t="inlineStr"/>
+      <c r="W28" s="14" t="inlineStr">
         <is>
           <t>VENDUE</t>
         </is>
       </c>
-      <c r="W28" s="14" t="inlineStr">
+      <c r="X28" s="14" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="X28" s="14" t="n">
+      <c r="Y28" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2876,85 +2975,89 @@
         <v>51.12</v>
       </c>
       <c r="C29" s="6">
-        <f>$B29+$X29*Paramètres!$B$13</f>
+        <f>$B29+$Y29*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D29" s="7">
         <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="6">
+        <f>CEILING($D29*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="F29" s="8">
-        <f>IF($E29="","",$E29-$C29-$L29-$M29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="9">
-        <f>IF($F29="","",$F29/$C29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="10" t="n">
+      <c r="G29" s="8">
+        <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>IF($G29="","",$G29/$C29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="6">
-        <f>$C29/$H29</f>
-        <v/>
-      </c>
       <c r="J29" s="6">
-        <f>IF($E29="","",$E29/$H29)</f>
+        <f>$C29/$I29</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF($F29="","",$F29/$H29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="7">
-        <f>IF($E29="","",$E29*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M29" s="6" t="n">
+        <f>IF($F29="","",$F29/$I29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="6">
+        <f>IF($G29="","",$G29/$I29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="7">
+        <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="11" t="n">
+      <c r="O29" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="O29" s="11" t="n">
+      <c r="P29" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="P29" s="12" t="inlineStr">
+      <c r="Q29" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q29" s="12" t="inlineStr">
+      <c r="R29" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R29" s="12" t="inlineStr">
+      <c r="S29" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="S29" s="12" t="inlineStr">
+      <c r="T29" s="12" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T29" s="4" t="inlineStr">
+      <c r="U29" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="inlineStr">
+      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="W29" s="4" t="inlineStr"/>
-      <c r="X29" s="4" t="n">
+      <c r="X29" s="4" t="inlineStr"/>
+      <c r="Y29" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2968,85 +3071,89 @@
         <v>38.34</v>
       </c>
       <c r="C30" s="6">
-        <f>$B30+$X30*Paramètres!$B$13</f>
+        <f>$B30+$Y30*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D30" s="7">
         <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="6">
+        <f>CEILING($D30*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F30" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="F30" s="8">
-        <f>IF($E30="","",$E30-$C30-$L30-$M30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="9">
-        <f>IF($F30="","",$F30/$C30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="10" t="n">
+      <c r="G30" s="8">
+        <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="9">
+        <f>IF($G30="","",$G30/$C30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="6">
-        <f>$C30/$H30</f>
-        <v/>
-      </c>
       <c r="J30" s="6">
-        <f>IF($E30="","",$E30/$H30)</f>
+        <f>$C30/$I30</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF($F30="","",$F30/$H30)</f>
-        <v/>
-      </c>
-      <c r="L30" s="7">
-        <f>IF($E30="","",$E30*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M30" s="6" t="n">
+        <f>IF($F30="","",$F30/$I30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="6">
+        <f>IF($G30="","",$G30/$I30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="7">
+        <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="11" t="n">
+      <c r="O30" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="P30" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="P30" s="12" t="inlineStr">
+      <c r="Q30" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q30" s="12" t="inlineStr">
+      <c r="R30" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R30" s="12" t="inlineStr">
+      <c r="S30" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="S30" s="12" t="inlineStr">
+      <c r="T30" s="12" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="T30" s="4" t="inlineStr">
+      <c r="U30" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="inlineStr">
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="W30" s="4" t="inlineStr"/>
-      <c r="X30" s="4" t="n">
+      <c r="X30" s="4" t="inlineStr"/>
+      <c r="Y30" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3060,85 +3167,89 @@
         <v>51.12</v>
       </c>
       <c r="C31" s="6">
-        <f>$B31+$X31*Paramètres!$B$13</f>
+        <f>$B31+$Y31*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D31" s="7">
         <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="6">
+        <f>CEILING($D31*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F31" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="F31" s="8">
-        <f>IF($E31="","",$E31-$C31-$L31-$M31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="9">
-        <f>IF($F31="","",$F31/$C31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="10" t="n">
+      <c r="G31" s="8">
+        <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>IF($G31="","",$G31/$C31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="6">
-        <f>$C31/$H31</f>
-        <v/>
-      </c>
       <c r="J31" s="6">
-        <f>IF($E31="","",$E31/$H31)</f>
+        <f>$C31/$I31</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF($F31="","",$F31/$H31)</f>
-        <v/>
-      </c>
-      <c r="L31" s="7">
-        <f>IF($E31="","",$E31*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M31" s="6" t="n">
+        <f>IF($F31="","",$F31/$I31)</f>
+        <v/>
+      </c>
+      <c r="L31" s="6">
+        <f>IF($G31="","",$G31/$I31)</f>
+        <v/>
+      </c>
+      <c r="M31" s="7">
+        <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="11" t="n">
+      <c r="O31" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="O31" s="11" t="n">
+      <c r="P31" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="P31" s="12" t="inlineStr">
+      <c r="Q31" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q31" s="12" t="inlineStr">
+      <c r="R31" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R31" s="12" t="inlineStr">
+      <c r="S31" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="S31" s="12" t="inlineStr">
+      <c r="T31" s="12" t="inlineStr">
         <is>
           <t>156</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr">
+      <c r="U31" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="inlineStr">
+      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="W31" s="4" t="inlineStr"/>
-      <c r="X31" s="4" t="n">
+      <c r="X31" s="4" t="inlineStr"/>
+      <c r="Y31" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3152,85 +3263,89 @@
         <v>52.4</v>
       </c>
       <c r="C32" s="6">
-        <f>$B32+$X32*Paramètres!$B$13</f>
+        <f>$B32+$Y32*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D32" s="7">
         <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="6">
+        <f>CEILING($D32*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F32" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="F32" s="8">
-        <f>IF($E32="","",$E32-$C32-$L32-$M32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="9">
-        <f>IF($F32="","",$F32/$C32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="10" t="n">
+      <c r="G32" s="8">
+        <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="9">
+        <f>IF($G32="","",$G32/$C32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="6">
-        <f>$C32/$H32</f>
-        <v/>
-      </c>
       <c r="J32" s="6">
-        <f>IF($E32="","",$E32/$H32)</f>
+        <f>$C32/$I32</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF($F32="","",$F32/$H32)</f>
-        <v/>
-      </c>
-      <c r="L32" s="7">
-        <f>IF($E32="","",$E32*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M32" s="6" t="n">
+        <f>IF($F32="","",$F32/$I32)</f>
+        <v/>
+      </c>
+      <c r="L32" s="6">
+        <f>IF($G32="","",$G32/$I32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="7">
+        <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="11" t="n">
+      <c r="O32" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="O32" s="11" t="n">
+      <c r="P32" s="11" t="n">
         <v>10.66</v>
       </c>
-      <c r="P32" s="12" t="inlineStr">
+      <c r="Q32" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q32" s="12" t="inlineStr">
+      <c r="R32" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R32" s="12" t="inlineStr">
+      <c r="S32" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="S32" s="12" t="inlineStr">
+      <c r="T32" s="12" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
+      <c r="U32" s="4" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="inlineStr">
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="W32" s="4" t="inlineStr"/>
-      <c r="X32" s="4" t="n">
+      <c r="X32" s="4" t="inlineStr"/>
+      <c r="Y32" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3244,89 +3359,93 @@
         <v>57.51</v>
       </c>
       <c r="C33" s="16">
-        <f>$B33+$X33*Paramètres!$B$13</f>
+        <f>$B33+$Y33*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D33" s="17">
         <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="16">
+        <f>CEILING($D33*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F33" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="F33" s="18">
-        <f>IF($E33="","",$E33-$C33-$L33-$M33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="19">
-        <f>IF($F33="","",$F33/$C33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="20" t="n">
+      <c r="G33" s="18">
+        <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="19">
+        <f>IF($G33="","",$G33/$C33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="16">
-        <f>$C33/$H33</f>
-        <v/>
-      </c>
       <c r="J33" s="16">
-        <f>IF($E33="","",$E33/$H33)</f>
+        <f>$C33/$I33</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>IF($F33="","",$F33/$H33)</f>
-        <v/>
-      </c>
-      <c r="L33" s="17">
-        <f>IF($E33="","",$E33*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M33" s="16" t="n">
+        <f>IF($F33="","",$F33/$I33)</f>
+        <v/>
+      </c>
+      <c r="L33" s="16">
+        <f>IF($G33="","",$G33/$I33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="17">
+        <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N33" s="21" t="n">
+      <c r="O33" s="21" t="n">
         <v>45</v>
       </c>
-      <c r="O33" s="21" t="n">
+      <c r="P33" s="21" t="n">
         <v>11.7</v>
       </c>
-      <c r="P33" s="22" t="inlineStr">
+      <c r="Q33" s="22" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="Q33" s="22" t="inlineStr">
+      <c r="R33" s="22" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R33" s="22" t="inlineStr">
+      <c r="S33" s="22" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="S33" s="22" t="inlineStr">
+      <c r="T33" s="22" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="T33" s="14" t="inlineStr">
+      <c r="U33" s="14" t="inlineStr">
         <is>
           <t>date à compléter</t>
         </is>
       </c>
-      <c r="U33" s="14" t="inlineStr"/>
-      <c r="V33" s="14" t="inlineStr">
+      <c r="V33" s="14" t="inlineStr"/>
+      <c r="W33" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="W33" s="14" t="inlineStr">
+      <c r="X33" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X33" s="14" t="n">
+      <c r="Y33" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3340,89 +3459,93 @@
         <v>113.4</v>
       </c>
       <c r="C34" s="16">
-        <f>$B34+$X34*Paramètres!$B$13</f>
+        <f>$B34+$Y34*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D34" s="17">
         <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="16">
+        <f>CEILING($D34*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="18" t="n">
         <v>125</v>
       </c>
-      <c r="F34" s="18">
-        <f>IF($E34="","",$E34-$C34-$L34-$M34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="19">
-        <f>IF($F34="","",$F34/$C34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="20" t="n">
+      <c r="G34" s="18">
+        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="19">
+        <f>IF($G34="","",$G34/$C34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="16">
-        <f>$C34/$H34</f>
-        <v/>
-      </c>
       <c r="J34" s="16">
-        <f>IF($E34="","",$E34/$H34)</f>
+        <f>$C34/$I34</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>IF($F34="","",$F34/$H34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="17">
-        <f>IF($E34="","",$E34*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M34" s="16" t="n">
+        <f>IF($F34="","",$F34/$I34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="16">
+        <f>IF($G34="","",$G34/$I34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="17">
+        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N34" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="21" t="n">
+      <c r="O34" s="21" t="n">
         <v>90</v>
       </c>
-      <c r="O34" s="21" t="n">
+      <c r="P34" s="21" t="n">
         <v>23.4</v>
       </c>
-      <c r="P34" s="22" t="inlineStr">
+      <c r="Q34" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q34" s="22" t="inlineStr">
+      <c r="R34" s="22" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R34" s="22" t="inlineStr">
+      <c r="S34" s="22" t="inlineStr">
         <is>
           <t>FB2026-44194</t>
         </is>
       </c>
-      <c r="S34" s="22" t="inlineStr">
+      <c r="T34" s="22" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T34" s="14" t="inlineStr">
+      <c r="U34" s="14" t="inlineStr">
         <is>
           <t>date à compléter</t>
         </is>
       </c>
-      <c r="U34" s="14" t="inlineStr"/>
-      <c r="V34" s="14" t="inlineStr">
+      <c r="V34" s="14" t="inlineStr"/>
+      <c r="W34" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="W34" s="14" t="inlineStr">
+      <c r="X34" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X34" s="14" t="n">
+      <c r="Y34" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3436,89 +3559,93 @@
         <v>25.2</v>
       </c>
       <c r="C35" s="16">
-        <f>$B35+$X35*Paramètres!$B$13</f>
+        <f>$B35+$Y35*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D35" s="17">
         <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="16">
+        <f>CEILING($D35*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="F35" s="18">
-        <f>IF($E35="","",$E35-$C35-$L35-$M35)</f>
-        <v/>
-      </c>
-      <c r="G35" s="19">
-        <f>IF($F35="","",$F35/$C35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="20" t="n">
+      <c r="G35" s="18">
+        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="19">
+        <f>IF($G35="","",$G35/$C35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="16">
-        <f>$C35/$H35</f>
-        <v/>
-      </c>
       <c r="J35" s="16">
-        <f>IF($E35="","",$E35/$H35)</f>
+        <f>$C35/$I35</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>IF($F35="","",$F35/$H35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="17">
-        <f>IF($E35="","",$E35*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M35" s="16" t="n">
+        <f>IF($F35="","",$F35/$I35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="16">
+        <f>IF($G35="","",$G35/$I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="17">
+        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="21" t="n">
+      <c r="O35" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="O35" s="21" t="n">
+      <c r="P35" s="21" t="n">
         <v>5.2</v>
       </c>
-      <c r="P35" s="22" t="inlineStr">
+      <c r="Q35" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q35" s="22" t="inlineStr">
+      <c r="R35" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R35" s="22" t="inlineStr">
+      <c r="S35" s="22" t="inlineStr">
         <is>
           <t>FB2026-43717</t>
         </is>
       </c>
-      <c r="S35" s="22" t="inlineStr">
+      <c r="T35" s="22" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="T35" s="14" t="inlineStr">
+      <c r="U35" s="14" t="inlineStr">
         <is>
           <t>date à compléter</t>
         </is>
       </c>
-      <c r="U35" s="14" t="inlineStr"/>
-      <c r="V35" s="14" t="inlineStr">
+      <c r="V35" s="14" t="inlineStr"/>
+      <c r="W35" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="W35" s="14" t="inlineStr">
+      <c r="X35" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X35" s="14" t="n">
+      <c r="Y35" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3532,89 +3659,93 @@
         <v>50.4</v>
       </c>
       <c r="C36" s="16">
-        <f>$B36+$X36*Paramètres!$B$13</f>
+        <f>$B36+$Y36*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D36" s="17">
         <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="16">
+        <f>CEILING($D36*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="F36" s="18">
-        <f>IF($E36="","",$E36-$C36-$L36-$M36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="19">
-        <f>IF($F36="","",$F36/$C36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="20" t="n">
+      <c r="G36" s="18">
+        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="19">
+        <f>IF($G36="","",$G36/$C36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="16">
-        <f>$C36/$H36</f>
-        <v/>
-      </c>
       <c r="J36" s="16">
-        <f>IF($E36="","",$E36/$H36)</f>
+        <f>$C36/$I36</f>
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>IF($F36="","",$F36/$H36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="17">
-        <f>IF($E36="","",$E36*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M36" s="16" t="n">
+        <f>IF($F36="","",$F36/$I36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="16">
+        <f>IF($G36="","",$G36/$I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="17">
+        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="21" t="n">
+      <c r="O36" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="O36" s="21" t="n">
+      <c r="P36" s="21" t="n">
         <v>10.4</v>
       </c>
-      <c r="P36" s="22" t="inlineStr">
+      <c r="Q36" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q36" s="22" t="inlineStr">
+      <c r="R36" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R36" s="22" t="inlineStr">
+      <c r="S36" s="22" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S36" s="22" t="inlineStr">
+      <c r="T36" s="22" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="T36" s="14" t="inlineStr">
+      <c r="U36" s="14" t="inlineStr">
         <is>
           <t>date à compléter</t>
         </is>
       </c>
-      <c r="U36" s="14" t="inlineStr"/>
-      <c r="V36" s="14" t="inlineStr">
+      <c r="V36" s="14" t="inlineStr"/>
+      <c r="W36" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="W36" s="14" t="inlineStr">
+      <c r="X36" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X36" s="14" t="n">
+      <c r="Y36" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3628,89 +3759,93 @@
         <v>50.4</v>
       </c>
       <c r="C37" s="16">
-        <f>$B37+$X37*Paramètres!$B$13</f>
+        <f>$B37+$Y37*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D37" s="17">
         <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="16">
+        <f>CEILING($D37*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="F37" s="18">
-        <f>IF($E37="","",$E37-$C37-$L37-$M37)</f>
-        <v/>
-      </c>
-      <c r="G37" s="19">
-        <f>IF($F37="","",$F37/$C37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="20" t="n">
+      <c r="G37" s="18">
+        <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="19">
+        <f>IF($G37="","",$G37/$C37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="16">
-        <f>$C37/$H37</f>
-        <v/>
-      </c>
       <c r="J37" s="16">
-        <f>IF($E37="","",$E37/$H37)</f>
+        <f>$C37/$I37</f>
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>IF($F37="","",$F37/$H37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="17">
-        <f>IF($E37="","",$E37*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M37" s="16" t="n">
+        <f>IF($F37="","",$F37/$I37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="16">
+        <f>IF($G37="","",$G37/$I37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="17">
+        <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="21" t="n">
+      <c r="O37" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="O37" s="21" t="n">
+      <c r="P37" s="21" t="n">
         <v>10.4</v>
       </c>
-      <c r="P37" s="22" t="inlineStr">
+      <c r="Q37" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q37" s="22" t="inlineStr">
+      <c r="R37" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R37" s="22" t="inlineStr">
+      <c r="S37" s="22" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S37" s="22" t="inlineStr">
+      <c r="T37" s="22" t="inlineStr">
         <is>
           <t>431</t>
         </is>
       </c>
-      <c r="T37" s="14" t="inlineStr">
+      <c r="U37" s="14" t="inlineStr">
         <is>
           <t>date à compléter</t>
         </is>
       </c>
-      <c r="U37" s="14" t="inlineStr"/>
-      <c r="V37" s="14" t="inlineStr">
+      <c r="V37" s="14" t="inlineStr"/>
+      <c r="W37" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="W37" s="14" t="inlineStr">
+      <c r="X37" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X37" s="14" t="n">
+      <c r="Y37" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3724,89 +3859,93 @@
         <v>63</v>
       </c>
       <c r="C38" s="16">
-        <f>$B38+$X38*Paramètres!$B$13</f>
+        <f>$B38+$Y38*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D38" s="17">
         <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="18" t="n">
+      <c r="E38" s="16">
+        <f>CEILING($D38*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="F38" s="18">
-        <f>IF($E38="","",$E38-$C38-$L38-$M38)</f>
-        <v/>
-      </c>
-      <c r="G38" s="19">
-        <f>IF($F38="","",$F38/$C38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="20" t="n">
+      <c r="G38" s="18">
+        <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="19">
+        <f>IF($G38="","",$G38/$C38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="16">
-        <f>$C38/$H38</f>
-        <v/>
-      </c>
       <c r="J38" s="16">
-        <f>IF($E38="","",$E38/$H38)</f>
+        <f>$C38/$I38</f>
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>IF($F38="","",$F38/$H38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="17">
-        <f>IF($E38="","",$E38*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M38" s="16" t="n">
+        <f>IF($F38="","",$F38/$I38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="16">
+        <f>IF($G38="","",$G38/$I38)</f>
+        <v/>
+      </c>
+      <c r="M38" s="17">
+        <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="21" t="n">
+      <c r="O38" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="O38" s="21" t="n">
+      <c r="P38" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="22" t="inlineStr">
+      <c r="Q38" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q38" s="22" t="inlineStr">
+      <c r="R38" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="R38" s="22" t="inlineStr">
+      <c r="S38" s="22" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="S38" s="22" t="inlineStr">
+      <c r="T38" s="22" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="T38" s="14" t="inlineStr">
+      <c r="U38" s="14" t="inlineStr">
         <is>
           <t>date à compléter</t>
         </is>
       </c>
-      <c r="U38" s="14" t="inlineStr"/>
-      <c r="V38" s="14" t="inlineStr">
+      <c r="V38" s="14" t="inlineStr"/>
+      <c r="W38" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="W38" s="14" t="inlineStr">
+      <c r="X38" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X38" s="14" t="n">
+      <c r="Y38" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3820,83 +3959,87 @@
         <v>19.17</v>
       </c>
       <c r="C39" s="25">
-        <f>$B39+$X39*Paramètres!$B$13</f>
+        <f>$B39+$Y39*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D39" s="26">
         <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="28">
-        <f>IF($E39="","",$E39-$C39-$L39-$M39)</f>
-        <v/>
-      </c>
-      <c r="G39" s="29">
-        <f>IF($F39="","",$F39/$C39)</f>
-        <v/>
-      </c>
-      <c r="H39" s="30" t="n">
+      <c r="E39" s="25">
+        <f>CEILING($D39*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="28">
+        <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="29">
+        <f>IF($G39="","",$G39/$C39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="I39" s="25">
-        <f>$C39/$H39</f>
-        <v/>
-      </c>
       <c r="J39" s="25">
-        <f>IF($E39="","",$E39/$H39)</f>
+        <f>$C39/$I39</f>
         <v/>
       </c>
       <c r="K39" s="25">
-        <f>IF($F39="","",$F39/$H39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="26">
-        <f>IF($E39="","",$E39*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M39" s="25" t="n">
+        <f>IF($F39="","",$F39/$I39)</f>
+        <v/>
+      </c>
+      <c r="L39" s="25">
+        <f>IF($G39="","",$G39/$I39)</f>
+        <v/>
+      </c>
+      <c r="M39" s="26">
+        <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N39" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="N39" s="31" t="n">
+      <c r="O39" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="O39" s="31" t="n">
+      <c r="P39" s="31" t="n">
         <v>3.9</v>
       </c>
-      <c r="P39" s="32" t="inlineStr">
+      <c r="Q39" s="32" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q39" s="32" t="inlineStr">
+      <c r="R39" s="32" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R39" s="32" t="inlineStr">
+      <c r="S39" s="32" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="S39" s="32" t="inlineStr">
+      <c r="T39" s="32" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="T39" s="23" t="inlineStr">
+      <c r="U39" s="23" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="U39" s="23" t="inlineStr"/>
-      <c r="V39" s="23" t="inlineStr">
+      <c r="V39" s="23" t="inlineStr"/>
+      <c r="W39" s="23" t="inlineStr">
         <is>
           <t>PRIX À ÉTABLIR</t>
         </is>
       </c>
-      <c r="W39" s="23" t="inlineStr"/>
-      <c r="X39" s="23" t="n">
+      <c r="X39" s="23" t="inlineStr"/>
+      <c r="Y39" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3910,83 +4053,87 @@
         <v>38.34</v>
       </c>
       <c r="C40" s="25">
-        <f>$B40+$X40*Paramètres!$B$13</f>
+        <f>$B40+$Y40*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D40" s="26">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="28">
-        <f>IF($E40="","",$E40-$C40-$L40-$M40)</f>
-        <v/>
-      </c>
-      <c r="G40" s="29">
-        <f>IF($F40="","",$F40/$C40)</f>
-        <v/>
-      </c>
-      <c r="H40" s="30" t="n">
+      <c r="E40" s="25">
+        <f>CEILING($D40*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="28">
+        <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="29">
+        <f>IF($G40="","",$G40/$C40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="I40" s="25">
-        <f>$C40/$H40</f>
-        <v/>
-      </c>
       <c r="J40" s="25">
-        <f>IF($E40="","",$E40/$H40)</f>
+        <f>$C40/$I40</f>
         <v/>
       </c>
       <c r="K40" s="25">
-        <f>IF($F40="","",$F40/$H40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="26">
-        <f>IF($E40="","",$E40*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M40" s="25" t="n">
+        <f>IF($F40="","",$F40/$I40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="25">
+        <f>IF($G40="","",$G40/$I40)</f>
+        <v/>
+      </c>
+      <c r="M40" s="26">
+        <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N40" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="31" t="n">
+      <c r="O40" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="O40" s="31" t="n">
+      <c r="P40" s="31" t="n">
         <v>7.8</v>
       </c>
-      <c r="P40" s="32" t="inlineStr">
+      <c r="Q40" s="32" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q40" s="32" t="inlineStr">
+      <c r="R40" s="32" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="R40" s="32" t="inlineStr">
+      <c r="S40" s="32" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="S40" s="32" t="inlineStr">
+      <c r="T40" s="32" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="T40" s="23" t="inlineStr">
+      <c r="U40" s="23" t="inlineStr">
         <is>
           <t>Leboncoin + eBay</t>
         </is>
       </c>
-      <c r="U40" s="23" t="inlineStr"/>
-      <c r="V40" s="23" t="inlineStr">
+      <c r="V40" s="23" t="inlineStr"/>
+      <c r="W40" s="23" t="inlineStr">
         <is>
           <t>PRIX À ÉTABLIR</t>
         </is>
       </c>
-      <c r="W40" s="23" t="inlineStr"/>
-      <c r="X40" s="23" t="n">
+      <c r="X40" s="23" t="inlineStr"/>
+      <c r="Y40" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4000,83 +4147,87 @@
         <v>63</v>
       </c>
       <c r="C41" s="6">
-        <f>$B41+$X41*Paramètres!$B$13</f>
+        <f>$B41+$Y41*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D41" s="7">
         <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E41" s="13" t="n"/>
-      <c r="F41" s="8">
-        <f>IF($E41="","",$E41-$C41-$L41-$M41)</f>
-        <v/>
-      </c>
-      <c r="G41" s="9">
-        <f>IF($F41="","",$F41/$C41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="10" t="n">
+      <c r="E41" s="6">
+        <f>CEILING($D41*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="8">
+        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="9">
+        <f>IF($G41="","",$G41/$C41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="6">
-        <f>$C41/$H41</f>
-        <v/>
-      </c>
       <c r="J41" s="6">
-        <f>IF($E41="","",$E41/$H41)</f>
+        <f>$C41/$I41</f>
         <v/>
       </c>
       <c r="K41" s="6">
-        <f>IF($F41="","",$F41/$H41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="7">
-        <f>IF($E41="","",$E41*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="M41" s="6" t="n">
+        <f>IF($F41="","",$F41/$I41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="6">
+        <f>IF($G41="","",$G41/$I41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="7">
+        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="11" t="n">
+      <c r="O41" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="O41" s="11" t="n">
+      <c r="P41" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="P41" s="12" t="inlineStr">
+      <c r="Q41" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="Q41" s="12" t="inlineStr">
+      <c r="R41" s="12" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="R41" s="12" t="inlineStr">
+      <c r="S41" s="12" t="inlineStr">
         <is>
           <t>FB2026-46056</t>
         </is>
       </c>
-      <c r="S41" s="12" t="inlineStr">
+      <c r="T41" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T41" s="4" t="inlineStr">
+      <c r="U41" s="4" t="inlineStr">
         <is>
           <t>Vinted, authentification</t>
         </is>
       </c>
-      <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="4" t="inlineStr">
+      <c r="V41" s="4" t="inlineStr"/>
+      <c r="W41" s="4" t="inlineStr">
         <is>
           <t>PRIX À ÉTABLIR</t>
         </is>
       </c>
-      <c r="W41" s="4" t="inlineStr"/>
-      <c r="X41" s="4" t="n">
+      <c r="X41" s="4" t="inlineStr"/>
+      <c r="Y41" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4095,34 +4246,34 @@
         <v/>
       </c>
       <c r="D42" s="35" t="n"/>
-      <c r="E42" s="34">
-        <f>SUM(E6:E41)</f>
-        <v/>
-      </c>
+      <c r="E42" s="35" t="n"/>
       <c r="F42" s="34">
         <f>SUM(F6:F41)</f>
         <v/>
       </c>
-      <c r="G42" s="36">
-        <f>F42/C42</f>
-        <v/>
-      </c>
-      <c r="H42" s="37">
-        <f>SUM(H6:H41)</f>
-        <v/>
-      </c>
-      <c r="I42" s="35" t="n"/>
+      <c r="G42" s="34">
+        <f>SUM(G6:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="36">
+        <f>G42/C42</f>
+        <v/>
+      </c>
+      <c r="I42" s="37">
+        <f>SUM(I6:I41)</f>
+        <v/>
+      </c>
       <c r="J42" s="35" t="n"/>
       <c r="K42" s="35" t="n"/>
-      <c r="L42" s="34">
-        <f>SUM(L6:L41)</f>
-        <v/>
-      </c>
+      <c r="L42" s="35" t="n"/>
       <c r="M42" s="34">
         <f>SUM(M6:M41)</f>
         <v/>
       </c>
-      <c r="N42" s="35" t="n"/>
+      <c r="N42" s="34">
+        <f>SUM(N6:N41)</f>
+        <v/>
+      </c>
       <c r="O42" s="35" t="n"/>
       <c r="P42" s="35" t="n"/>
       <c r="Q42" s="35" t="n"/>
@@ -4133,10 +4284,11 @@
       <c r="V42" s="35" t="n"/>
       <c r="W42" s="35" t="n"/>
       <c r="X42" s="35" t="n"/>
+      <c r="Y42" s="35" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:X41"/>
-  <conditionalFormatting sqref="F6:F41">
+  <autoFilter ref="A5:Y41"/>
+  <conditionalFormatting sqref="G6:G41">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -4151,7 +4303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4229,7 +4381,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>'Stock complet'!E42</f>
+        <f>'Stock complet'!F42</f>
         <v/>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4245,7 +4397,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>-'Stock complet'!L42</f>
+        <f>-'Stock complet'!M42</f>
         <v/>
       </c>
     </row>
@@ -4256,7 +4408,7 @@
         </is>
       </c>
       <c r="B12" s="6">
-        <f>-'Stock complet'!M42</f>
+        <f>-'Stock complet'!N42</f>
         <v/>
       </c>
     </row>
@@ -4266,7 +4418,7 @@
         <v/>
       </c>
       <c r="B13" s="34">
-        <f>'Stock complet'!F42</f>
+        <f>'Stock complet'!G42</f>
         <v/>
       </c>
     </row>
@@ -4359,7 +4511,7 @@
         </is>
       </c>
       <c r="B23" s="43">
-        <f>'Stock complet'!H42</f>
+        <f>'Stock complet'!I42</f>
         <v/>
       </c>
     </row>
@@ -4394,7 +4546,14 @@
     <row r="29">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>COLONNE SEUIL D'ÉQUILIBRE : ne jamais vendre en dessous. En dessous, la vente coûte de l'argent.</t>
+          <t>SEUIL D'ÉQUILIBRE : ne jamais vendre en dessous, la vente coûterait de l'argent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>PRIX PLANCHER : le plus bas acceptable, y compris pour la famille. 15 % au-dessus du seuil.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4603,6 +4762,28 @@
       </c>
       <c r="B21" s="47" t="n">
         <v>40</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>PLANCHER DE NÉGOCIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>Coefficient appliqué au seuil d'équilibre</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>prix plancher = seuil × ce coefficient</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6229,32 +6410,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="48" t="inlineStr">
+      <c r="A42" s="49" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="B42" s="48" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C42" s="48" t="inlineStr">
+      <c r="C42" s="49" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="D42" s="48" t="inlineStr">
+      <c r="D42" s="49" t="inlineStr">
         <is>
           <t>Commande</t>
         </is>
       </c>
-      <c r="E42" s="48" t="inlineStr">
+      <c r="E42" s="49" t="inlineStr">
         <is>
           <t>Désignation</t>
         </is>
       </c>
-      <c r="F42" s="48" t="inlineStr">
+      <c r="F42" s="49" t="inlineStr">
         <is>
           <t>Total TTC</t>
         </is>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -4303,7 +4303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4553,7 +4553,14 @@
     <row r="30">
       <c r="A30" s="39" t="inlineStr">
         <is>
-          <t>PRIX PLANCHER : le plus bas acceptable, y compris pour la famille. 15 % au-dessus du seuil.</t>
+          <t>PRIX PLANCHER : 30 % au-dessus du seuil. Le plus bas acceptable, famille comprise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Ne pas confondre avec le seuil de sourcing de 25 € : celui-là sert à decider d'ACHETER, pas de vendre.</t>
         </is>
       </c>
     </row>
@@ -4774,15 +4781,15 @@
     <row r="24">
       <c r="A24" s="39" t="inlineStr">
         <is>
-          <t>Coefficient appliqué au seuil d'équilibre</t>
+          <t>Coefficient sur le seuil d'équilibre</t>
         </is>
       </c>
       <c r="B24" s="48" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>prix plancher = seuil × ce coefficient</t>
+          <t>plancher = seuil × ce coefficient</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,7 +170,6 @@
     <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2577,116 +2576,116 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>GEOX baskets P.35 — neuves</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>21.73</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="C25" s="25">
         <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="26">
         <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="25">
         <f>CEILING($D25*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="27">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
         <v/>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="28">
         <f>IF($G25="","",$G25/$C25)</f>
         <v/>
       </c>
-      <c r="I25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="6">
+      <c r="I25" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="25">
         <f>$C25/$I25</f>
         <v/>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="25">
         <f>IF($F25="","",$F25/$I25)</f>
         <v/>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="25">
         <f>IF($G25="","",$G25/$I25)</f>
         <v/>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="26">
         <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="P25" s="11" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="Q25" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R25" s="12" t="inlineStr">
+      <c r="O25" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="P25" s="30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q25" s="31" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R25" s="31" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S25" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T25" s="12" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr"/>
-      <c r="W25" s="4" t="inlineStr">
+      <c r="S25" s="31" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T25" s="31" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="U25" s="23" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V25" s="23" t="inlineStr"/>
+      <c r="W25" s="23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X25" s="4" t="inlineStr"/>
-      <c r="Y25" s="4" t="n">
+      <c r="X25" s="23" t="inlineStr"/>
+      <c r="Y25" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
+          <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>50.4</v>
+        <v>21.73</v>
       </c>
       <c r="C26" s="6">
         <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E26" s="6">
@@ -2694,7 +2693,7 @@
         <v/>
       </c>
       <c r="F26" s="8" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G26" s="8">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
@@ -2723,45 +2722,44 @@
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6">
-        <f>IF($F26="","",$F26*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N26" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O26" s="11" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="P26" s="11" t="n">
-        <v>10.4</v>
+        <v>4.42</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R26" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T26" s="12" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X26" s="4" t="inlineStr"/>
@@ -2772,18 +2770,18 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>75.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="C27" s="6">
         <f>$B27+$Y27*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E27" s="6">
@@ -2791,7 +2789,7 @@
         <v/>
       </c>
       <c r="F27" s="8" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G27" s="8">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
@@ -2820,14 +2818,15 @@
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="n">
-        <v>0</v>
+      <c r="N27" s="6">
+        <f>IF($F27="","",$F27*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O27" s="11" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P27" s="11" t="n">
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
@@ -2846,18 +2845,18 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>408</t>
         </is>
       </c>
       <c r="U27" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>Liquider</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X27" s="4" t="inlineStr"/>
@@ -2866,209 +2865,209 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="C28" s="6">
+        <f>$B28+$Y28*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D28" s="7">
+        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E28" s="6">
+        <f>CEILING($D28*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="G28" s="8">
+        <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>IF($G28="","",$G28/$C28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="6">
+        <f>$C28/$I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="6">
+        <f>IF($F28="","",$F28/$I28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="6">
+        <f>IF($G28="","",$G28/$I28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="7">
+        <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="P28" s="11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="Q28" s="12" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R28" s="12" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S28" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T28" s="12" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X28" s="4" t="inlineStr"/>
+      <c r="Y28" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B29" s="15" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="C28" s="16">
-        <f>$B28+$Y28*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D28" s="17">
-        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E28" s="16">
-        <f>CEILING($D28*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F28" s="18" t="n">
+      <c r="C29" s="16">
+        <f>$B29+$Y29*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D29" s="17">
+        <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E29" s="16">
+        <f>CEILING($D29*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F29" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="G28" s="18">
-        <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="19">
-        <f>IF($G28="","",$G28/$C28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="20" t="n">
+      <c r="G29" s="18">
+        <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="19">
+        <f>IF($G29="","",$G29/$C29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="16">
-        <f>$C28/$I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="16">
-        <f>IF($F28="","",$F28/$I28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="16">
-        <f>IF($G28="","",$G28/$I28)</f>
-        <v/>
-      </c>
-      <c r="M28" s="17">
-        <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N28" s="16" t="n">
+      <c r="J29" s="16">
+        <f>$C29/$I29</f>
+        <v/>
+      </c>
+      <c r="K29" s="16">
+        <f>IF($F29="","",$F29/$I29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="16">
+        <f>IF($G29="","",$G29/$I29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="17">
+        <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="21" t="n">
+      <c r="O29" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="P28" s="21" t="n">
+      <c r="P29" s="21" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q28" s="22" t="inlineStr">
+      <c r="Q29" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R28" s="22" t="inlineStr">
+      <c r="R29" s="22" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S28" s="22" t="inlineStr">
+      <c r="S29" s="22" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="T28" s="22" t="inlineStr">
+      <c r="T29" s="22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="U28" s="14" t="inlineStr">
+      <c r="U29" s="14" t="inlineStr">
         <is>
           <t>Vinted, acheteur en Italie</t>
         </is>
       </c>
-      <c r="V28" s="14" t="inlineStr"/>
-      <c r="W28" s="14" t="inlineStr">
+      <c r="V29" s="14" t="inlineStr"/>
+      <c r="W29" s="14" t="inlineStr">
         <is>
           <t>VENDUE</t>
         </is>
       </c>
-      <c r="X28" s="14" t="inlineStr">
+      <c r="X29" s="14" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="Y28" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="C29" s="6">
-        <f>$B29+$Y29*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D29" s="7">
-        <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E29" s="6">
-        <f>CEILING($D29*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="G29" s="8">
-        <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="9">
-        <f>IF($G29="","",$G29/$C29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="6">
-        <f>$C29/$I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="6">
-        <f>IF($F29="","",$F29/$I29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="6">
-        <f>IF($G29="","",$G29/$I29)</f>
-        <v/>
-      </c>
-      <c r="M29" s="7">
-        <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="P29" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q29" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R29" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S29" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T29" s="12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="U29" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="inlineStr"/>
-      <c r="W29" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X29" s="4" t="inlineStr"/>
-      <c r="Y29" s="4" t="n">
+      <c r="Y29" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE sneakers P.38 — neuves</t>
+          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>38.34</v>
+        <v>51.12</v>
       </c>
       <c r="C30" s="6">
         <f>$B30+$Y30*Paramètres!$B$13</f>
@@ -3083,7 +3082,7 @@
         <v/>
       </c>
       <c r="F30" s="8" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G30" s="8">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
@@ -3116,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="O30" s="11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P30" s="11" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="Q30" s="12" t="inlineStr">
         <is>
@@ -3138,7 +3137,7 @@
       </c>
       <c r="T30" s="12" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr">
@@ -3160,11 +3159,11 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
+          <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>51.12</v>
+        <v>38.34</v>
       </c>
       <c r="C31" s="6">
         <f>$B31+$Y31*Paramètres!$B$13</f>
@@ -3179,7 +3178,7 @@
         <v/>
       </c>
       <c r="F31" s="8" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G31" s="8">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
@@ -3212,10 +3211,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="11" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P31" s="11" t="n">
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q31" s="12" t="inlineStr">
         <is>
@@ -3234,7 +3233,7 @@
       </c>
       <c r="T31" s="12" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>114</t>
         </is>
       </c>
       <c r="U31" s="4" t="inlineStr">
@@ -3256,11 +3255,11 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
+          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>52.4</v>
+        <v>51.12</v>
       </c>
       <c r="C32" s="6">
         <f>$B32+$Y32*Paramètres!$B$13</f>
@@ -3308,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P32" s="11" t="n">
-        <v>10.66</v>
+        <v>10.4</v>
       </c>
       <c r="Q32" s="12" t="inlineStr">
         <is>
@@ -3330,12 +3329,12 @@
       </c>
       <c r="T32" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>156</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="V32" s="4" t="inlineStr"/>
@@ -3350,113 +3349,109 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>LACOSTE sneakers P.42 — neuves</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n">
-        <v>57.51</v>
-      </c>
-      <c r="C33" s="16">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="C33" s="6">
         <f>$B33+$Y33*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="7">
         <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="6">
         <f>CEILING($D33*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F33" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="G33" s="18">
+      <c r="F33" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G33" s="8">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
         <v/>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="9">
         <f>IF($G33="","",$G33/$C33)</f>
         <v/>
       </c>
-      <c r="I33" s="20" t="n">
+      <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="6">
         <f>$C33/$I33</f>
         <v/>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="6">
         <f>IF($F33="","",$F33/$I33)</f>
         <v/>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="6">
         <f>IF($G33="","",$G33/$I33)</f>
         <v/>
       </c>
-      <c r="M33" s="17">
+      <c r="M33" s="7">
         <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N33" s="16" t="n">
+      <c r="N33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="21" t="n">
-        <v>45</v>
-      </c>
-      <c r="P33" s="21" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Q33" s="22" t="inlineStr">
+      <c r="O33" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="P33" s="11" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="Q33" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R33" s="22" t="inlineStr">
+      <c r="R33" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S33" s="22" t="inlineStr">
+      <c r="S33" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T33" s="22" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="U33" s="14" t="inlineStr">
-        <is>
-          <t>date à compléter</t>
-        </is>
-      </c>
-      <c r="V33" s="14" t="inlineStr"/>
-      <c r="W33" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X33" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y33" s="14" t="n">
+      <c r="T33" s="12" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr"/>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X33" s="4" t="inlineStr"/>
+      <c r="Y33" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+          <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
       <c r="B34" s="15" t="n">
-        <v>113.4</v>
+        <v>57.51</v>
       </c>
       <c r="C34" s="16">
         <f>$B34+$Y34*Paramètres!$B$13</f>
@@ -3471,7 +3466,7 @@
         <v/>
       </c>
       <c r="F34" s="18" t="n">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="G34" s="18">
         <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
@@ -3504,14 +3499,14 @@
         <v>0</v>
       </c>
       <c r="O34" s="21" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>23.4</v>
+        <v>11.7</v>
       </c>
       <c r="Q34" s="22" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R34" s="22" t="inlineStr">
@@ -3521,12 +3516,12 @@
       </c>
       <c r="S34" s="22" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T34" s="22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>141</t>
         </is>
       </c>
       <c r="U34" s="14" t="inlineStr">
@@ -3552,11 +3547,11 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
       <c r="B35" s="15" t="n">
-        <v>25.2</v>
+        <v>113.4</v>
       </c>
       <c r="C35" s="16">
         <f>$B35+$Y35*Paramètres!$B$13</f>
@@ -3571,7 +3566,7 @@
         <v/>
       </c>
       <c r="F35" s="18" t="n">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="G35" s="18">
         <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
@@ -3604,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="O35" s="21" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="P35" s="21" t="n">
-        <v>5.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q35" s="22" t="inlineStr">
         <is>
@@ -3616,17 +3611,17 @@
       </c>
       <c r="R35" s="22" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S35" s="22" t="inlineStr">
         <is>
-          <t>FB2026-43717</t>
+          <t>FB2026-44194</t>
         </is>
       </c>
       <c r="T35" s="22" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U35" s="14" t="inlineStr">
@@ -3650,113 +3645,109 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C36" s="16">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C36" s="25">
         <f>$B36+$Y36*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="26">
         <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="25">
         <f>CEILING($D36*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F36" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="G36" s="18">
+      <c r="F36" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="G36" s="27">
         <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
         <v/>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="28">
         <f>IF($G36="","",$G36/$C36)</f>
         <v/>
       </c>
-      <c r="I36" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="16">
+      <c r="I36" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="25">
         <f>$C36/$I36</f>
         <v/>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="25">
         <f>IF($F36="","",$F36/$I36)</f>
         <v/>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="25">
         <f>IF($G36="","",$G36/$I36)</f>
         <v/>
       </c>
-      <c r="M36" s="17">
+      <c r="M36" s="26">
         <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N36" s="16" t="n">
+      <c r="N36" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="P36" s="21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q36" s="22" t="inlineStr">
+      <c r="O36" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="P36" s="30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q36" s="31" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R36" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S36" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T36" s="22" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="U36" s="14" t="inlineStr">
-        <is>
-          <t>date à compléter</t>
-        </is>
-      </c>
-      <c r="V36" s="14" t="inlineStr"/>
-      <c r="W36" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X36" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y36" s="14" t="n">
+      <c r="R36" s="31" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S36" s="31" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T36" s="31" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="U36" s="23" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V36" s="23" t="inlineStr"/>
+      <c r="W36" s="23" t="inlineStr">
+        <is>
+          <t>Marge faible</t>
+        </is>
+      </c>
+      <c r="X36" s="23" t="inlineStr"/>
+      <c r="Y36" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
       <c r="B37" s="15" t="n">
-        <v>50.4</v>
+        <v>25.2</v>
       </c>
       <c r="C37" s="16">
         <f>$B37+$Y37*Paramètres!$B$13</f>
@@ -3771,7 +3762,7 @@
         <v/>
       </c>
       <c r="F37" s="18" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G37" s="18">
         <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
@@ -3804,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="O37" s="21" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="P37" s="21" t="n">
-        <v>10.4</v>
+        <v>5.2</v>
       </c>
       <c r="Q37" s="22" t="inlineStr">
         <is>
@@ -3821,12 +3812,12 @@
       </c>
       <c r="S37" s="22" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-43717</t>
         </is>
       </c>
       <c r="T37" s="22" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>168</t>
         </is>
       </c>
       <c r="U37" s="14" t="inlineStr">
@@ -3852,11 +3843,11 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Baskets HOKA P.37 1/3 — neuves</t>
+          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
       <c r="B38" s="15" t="n">
-        <v>63</v>
+        <v>50.4</v>
       </c>
       <c r="C38" s="16">
         <f>$B38+$Y38*Paramètres!$B$13</f>
@@ -3871,7 +3862,7 @@
         <v/>
       </c>
       <c r="F38" s="18" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G38" s="18">
         <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
@@ -3904,10 +3895,10 @@
         <v>0</v>
       </c>
       <c r="O38" s="21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P38" s="21" t="n">
-        <v>13</v>
+        <v>10.4</v>
       </c>
       <c r="Q38" s="22" t="inlineStr">
         <is>
@@ -3926,7 +3917,7 @@
       </c>
       <c r="T38" s="22" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>170</t>
         </is>
       </c>
       <c r="U38" s="14" t="inlineStr">
@@ -3950,190 +3941,202 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="C39" s="25">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C39" s="16">
         <f>$B39+$Y39*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="17">
         <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="16">
         <f>CEILING($D39*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="28">
+      <c r="F39" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="G39" s="18">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
         <v/>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="19">
         <f>IF($G39="","",$G39/$C39)</f>
         <v/>
       </c>
-      <c r="I39" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" s="25">
+      <c r="I39" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="16">
         <f>$C39/$I39</f>
         <v/>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="16">
         <f>IF($F39="","",$F39/$I39)</f>
         <v/>
       </c>
-      <c r="L39" s="25">
+      <c r="L39" s="16">
         <f>IF($G39="","",$G39/$I39)</f>
         <v/>
       </c>
-      <c r="M39" s="26">
+      <c r="M39" s="17">
         <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N39" s="25" t="n">
+      <c r="N39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="P39" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q39" s="32" t="inlineStr">
+      <c r="O39" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="P39" s="21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q39" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R39" s="32" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S39" s="32" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T39" s="32" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="U39" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V39" s="23" t="inlineStr"/>
-      <c r="W39" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="X39" s="23" t="inlineStr"/>
-      <c r="Y39" s="23" t="n">
+      <c r="R39" s="22" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S39" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T39" s="22" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="U39" s="14" t="inlineStr">
+        <is>
+          <t>date à compléter</t>
+        </is>
+      </c>
+      <c r="V39" s="14" t="inlineStr"/>
+      <c r="W39" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X39" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y39" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C40" s="25">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Baskets HOKA P.37 1/3 — neuves</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="C40" s="16">
         <f>$B40+$Y40*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="17">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="16">
         <f>CEILING($D40*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="28">
+      <c r="F40" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="G40" s="18">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
         <v/>
       </c>
-      <c r="H40" s="29">
+      <c r="H40" s="19">
         <f>IF($G40="","",$G40/$C40)</f>
         <v/>
       </c>
-      <c r="I40" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="25">
+      <c r="I40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="16">
         <f>$C40/$I40</f>
         <v/>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="16">
         <f>IF($F40="","",$F40/$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="25">
+      <c r="L40" s="16">
         <f>IF($G40="","",$G40/$I40)</f>
         <v/>
       </c>
-      <c r="M40" s="26">
+      <c r="M40" s="17">
         <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N40" s="25" t="n">
+      <c r="N40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="31" t="n">
-        <v>30</v>
-      </c>
-      <c r="P40" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q40" s="32" t="inlineStr">
+      <c r="O40" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="P40" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q40" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R40" s="32" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S40" s="32" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T40" s="32" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="U40" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V40" s="23" t="inlineStr"/>
-      <c r="W40" s="23" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="X40" s="23" t="inlineStr"/>
-      <c r="Y40" s="23" t="n">
+      <c r="R40" s="22" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S40" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T40" s="22" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="U40" s="14" t="inlineStr">
+        <is>
+          <t>date à compléter</t>
+        </is>
+      </c>
+      <c r="V40" s="14" t="inlineStr"/>
+      <c r="W40" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X40" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y40" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4232,59 +4235,59 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="33" t="inlineStr">
+      <c r="A42" s="32" t="inlineStr">
         <is>
           <t>TOTAL — 36 lots</t>
         </is>
       </c>
-      <c r="B42" s="34">
+      <c r="B42" s="33">
         <f>SUM(B6:B41)</f>
         <v/>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="33">
         <f>SUM(C6:C41)</f>
         <v/>
       </c>
-      <c r="D42" s="35" t="n"/>
-      <c r="E42" s="35" t="n"/>
-      <c r="F42" s="34">
+      <c r="D42" s="34" t="n"/>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="33">
         <f>SUM(F6:F41)</f>
         <v/>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="33">
         <f>SUM(G6:G41)</f>
         <v/>
       </c>
-      <c r="H42" s="36">
+      <c r="H42" s="35">
         <f>G42/C42</f>
         <v/>
       </c>
-      <c r="I42" s="37">
+      <c r="I42" s="36">
         <f>SUM(I6:I41)</f>
         <v/>
       </c>
-      <c r="J42" s="35" t="n"/>
-      <c r="K42" s="35" t="n"/>
-      <c r="L42" s="35" t="n"/>
-      <c r="M42" s="34">
+      <c r="J42" s="34" t="n"/>
+      <c r="K42" s="34" t="n"/>
+      <c r="L42" s="34" t="n"/>
+      <c r="M42" s="33">
         <f>SUM(M6:M41)</f>
         <v/>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="33">
         <f>SUM(N6:N41)</f>
         <v/>
       </c>
-      <c r="O42" s="35" t="n"/>
-      <c r="P42" s="35" t="n"/>
-      <c r="Q42" s="35" t="n"/>
-      <c r="R42" s="35" t="n"/>
-      <c r="S42" s="35" t="n"/>
-      <c r="T42" s="35" t="n"/>
-      <c r="U42" s="35" t="n"/>
-      <c r="V42" s="35" t="n"/>
-      <c r="W42" s="35" t="n"/>
-      <c r="X42" s="35" t="n"/>
-      <c r="Y42" s="35" t="n"/>
+      <c r="O42" s="34" t="n"/>
+      <c r="P42" s="34" t="n"/>
+      <c r="Q42" s="34" t="n"/>
+      <c r="R42" s="34" t="n"/>
+      <c r="S42" s="34" t="n"/>
+      <c r="T42" s="34" t="n"/>
+      <c r="U42" s="34" t="n"/>
+      <c r="V42" s="34" t="n"/>
+      <c r="W42" s="34" t="n"/>
+      <c r="X42" s="34" t="n"/>
+      <c r="Y42" s="34" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:Y41"/>
@@ -4319,14 +4322,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>CAPITAL ENGAGÉ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Marchandise ADN</t>
         </is>
@@ -4336,7 +4339,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Livraison ADN</t>
         </is>
@@ -4347,7 +4350,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Achats hors ADN (pompes, Pokémon)</t>
         </is>
@@ -4357,25 +4360,25 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>TOTAL ENGAGÉ</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="33">
         <f>'Stock complet'!C42</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>CHIFFRE D'AFFAIRES ET MARGE</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Chiffre d'affaires attendu</t>
         </is>
@@ -4391,7 +4394,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>− URSSAF + CFP</t>
         </is>
@@ -4402,7 +4405,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>− Commission carte</t>
         </is>
@@ -4413,17 +4416,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40">
+      <c r="A13" s="39">
         <f> Marge brute</f>
         <v/>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="33">
         <f>'Stock complet'!G42</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>− Emballage</t>
         </is>
@@ -4434,7 +4437,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>− Frais fixe carte</t>
         </is>
@@ -4445,17 +4448,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="40">
+      <c r="A16" s="39">
         <f> Marge avant impôt</f>
         <v/>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="33">
         <f>B13+B14+B15</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>Base imposable</t>
         </is>
@@ -4466,7 +4469,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>− Impôt estimé</t>
         </is>
@@ -4477,81 +4480,81 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="40">
+      <c r="A19" s="39">
         <f> CE QUI RESTE</f>
         <v/>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="40">
         <f>B16+B18</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>RENDEMENT</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>Marge nette / capital engagé</t>
         </is>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="41">
         <f>B19/B7</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>Articles physiques</t>
         </is>
       </c>
-      <c r="B23" s="43">
+      <c r="B23" s="42">
         <f>'Stock complet'!I42</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>À FAIRE</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
-        <is>
-          <t>3 lots sans prix : Yeezy 700 V3 et les deux lots de toupies Beyblade.</t>
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>1 lot sans prix : Yeezy 700 V3, en attente d'authentification.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>Dates de vente à compléter sur les 6 ventes récentes.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>Facture manquante : lot n°84, les 2 pompes Robby.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="44" t="inlineStr">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>SEUIL D'ÉQUILIBRE : ne jamais vendre en dessous, la vente coûterait de l'argent.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>PRIX PLANCHER : 30 % au-dessus du seuil. Le plus bas acceptable, famille comprise.</t>
         </is>
@@ -4598,19 +4601,19 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>CHARGES SUR LE CHIFFRE D'AFFAIRES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Cotisations URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="44" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4620,22 +4623,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>CFP — formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="44" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="44" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4645,24 +4648,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="45" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>LIVRAISON DES LOTS</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Total des factures de livraison ADN</t>
         </is>
@@ -4677,7 +4680,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Unités de vente reçues d'ADN</t>
         </is>
@@ -4692,7 +4695,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>Livraison par unité de vente</t>
         </is>
@@ -4708,19 +4711,19 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>IMPÔT SUR LE REVENU — MICRO-BIC</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B16" s="45" t="n">
+      <c r="B16" s="44" t="n">
         <v>0.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4730,12 +4733,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>Tranche marginale du foyer</t>
         </is>
       </c>
-      <c r="B17" s="45" t="n">
+      <c r="B17" s="44" t="n">
         <v>0.11</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -4745,46 +4748,46 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>FRAIS DE VENTE</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>Emballage par colis</t>
         </is>
       </c>
-      <c r="B20" s="46" t="n">
+      <c r="B20" s="45" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>Nombre d'annonces prévues</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
+      <c r="B21" s="46" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>PLANCHER DE NÉGOCIATION</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>Coefficient sur le seuil d'équilibre</t>
         </is>
       </c>
-      <c r="B24" s="48" t="n">
+      <c r="B24" s="47" t="n">
         <v>1.3</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -6382,67 +6385,67 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="n"/>
-      <c r="B39" s="35" t="n"/>
-      <c r="C39" s="35" t="n"/>
-      <c r="D39" s="35" t="n"/>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="33" t="inlineStr">
+      <c r="A39" s="34" t="n"/>
+      <c r="B39" s="34" t="n"/>
+      <c r="C39" s="34" t="n"/>
+      <c r="D39" s="34" t="n"/>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>TOTAL MARCHANDISE</t>
         </is>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="33">
         <f>SUM(G5:G38)</f>
         <v/>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="33">
         <f>SUM(H5:H38)</f>
         <v/>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="33">
         <f>SUM(I5:I38)</f>
         <v/>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="33">
         <f>SUM(J5:J38)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="38" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>FACTURES DE LIVRAISON</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="49" t="inlineStr">
+      <c r="A42" s="48" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="B42" s="49" t="inlineStr">
+      <c r="B42" s="48" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C42" s="49" t="inlineStr">
+      <c r="C42" s="48" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="D42" s="49" t="inlineStr">
+      <c r="D42" s="48" t="inlineStr">
         <is>
           <t>Commande</t>
         </is>
       </c>
-      <c r="E42" s="49" t="inlineStr">
+      <c r="E42" s="48" t="inlineStr">
         <is>
           <t>Désignation</t>
         </is>
       </c>
-      <c r="F42" s="49" t="inlineStr">
+      <c r="F42" s="48" t="inlineStr">
         <is>
           <t>Total TTC</t>
         </is>
@@ -6599,16 +6602,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="33" t="inlineStr">
+      <c r="A48" s="34" t="n"/>
+      <c r="B48" s="34" t="n"/>
+      <c r="C48" s="34" t="n"/>
+      <c r="D48" s="34" t="n"/>
+      <c r="E48" s="32" t="inlineStr">
         <is>
           <t>TOTAL LIVRAISON</t>
         </is>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="33">
         <f>SUM(F43:F47)</f>
         <v/>
       </c>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -3042,13 +3042,13 @@
       </c>
       <c r="U29" s="14" t="inlineStr">
         <is>
-          <t>Vinted, acheteur en Italie</t>
+          <t>Vinted, Italie — non encaissé</t>
         </is>
       </c>
       <c r="V29" s="14" t="inlineStr"/>
       <c r="W29" s="14" t="inlineStr">
         <is>
-          <t>VENDUE</t>
+          <t>VENDUE, en attente</t>
         </is>
       </c>
       <c r="X29" s="14" t="inlineStr">
@@ -3061,301 +3061,313 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="C30" s="16">
         <f>$B30+$Y30*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="17">
         <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="16">
         <f>CEILING($D30*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F30" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="G30" s="8">
+      <c r="F30" s="18" t="n">
+        <v>135</v>
+      </c>
+      <c r="G30" s="18">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
         <v/>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="19">
         <f>IF($G30="","",$G30/$C30)</f>
         <v/>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="I30" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="16">
         <f>$C30/$I30</f>
         <v/>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="16">
         <f>IF($F30="","",$F30/$I30)</f>
         <v/>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="16">
         <f>IF($G30="","",$G30/$I30)</f>
         <v/>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="17">
         <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="O30" s="21" t="n">
+        <v>90</v>
+      </c>
+      <c r="P30" s="21" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q30" s="22" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R30" s="22" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S30" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-44194</t>
+        </is>
+      </c>
+      <c r="T30" s="22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U30" s="14" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V30" s="14" t="inlineStr"/>
+      <c r="W30" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X30" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y30" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C31" s="16">
+        <f>$B31+$Y31*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>CEILING($D31*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="G31" s="18">
+        <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="19">
+        <f>IF($G31="","",$G31/$C31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="16">
+        <f>$C31/$I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="16">
+        <f>IF($F31="","",$F31/$I31)</f>
+        <v/>
+      </c>
+      <c r="L31" s="16">
+        <f>IF($G31="","",$G31/$I31)</f>
+        <v/>
+      </c>
+      <c r="M31" s="17">
+        <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="P30" s="11" t="n">
+      <c r="P31" s="21" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q30" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R30" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S30" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T30" s="12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X30" s="4" t="inlineStr"/>
-      <c r="Y30" s="4" t="n">
+      <c r="Q31" s="22" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R31" s="22" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S31" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T31" s="22" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="U31" s="14" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V31" s="14" t="inlineStr"/>
+      <c r="W31" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X31" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y31" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>NEW BALANCE sneakers P.38 — neuves</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C31" s="6">
-        <f>$B31+$Y31*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D31" s="7">
-        <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E31" s="6">
-        <f>CEILING($D31*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="G31" s="8">
-        <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="9">
-        <f>IF($G31="","",$G31/$C31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="10" t="n">
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C32" s="16">
+        <f>$B32+$Y32*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E32" s="16">
+        <f>CEILING($D32*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="G32" s="18">
+        <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="19">
+        <f>IF($G32="","",$G32/$C32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="6">
-        <f>$C31/$I31</f>
-        <v/>
-      </c>
-      <c r="K31" s="6">
-        <f>IF($F31="","",$F31/$I31)</f>
-        <v/>
-      </c>
-      <c r="L31" s="6">
-        <f>IF($G31="","",$G31/$I31)</f>
-        <v/>
-      </c>
-      <c r="M31" s="7">
-        <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N31" s="6" t="n">
+      <c r="J32" s="16">
+        <f>$C32/$I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="16">
+        <f>IF($F32="","",$F32/$I32)</f>
+        <v/>
+      </c>
+      <c r="L32" s="16">
+        <f>IF($G32="","",$G32/$I32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="17">
+        <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P31" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q31" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R31" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S31" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T31" s="12" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="inlineStr"/>
-      <c r="W31" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X31" s="4" t="inlineStr"/>
-      <c r="Y31" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="C32" s="6">
-        <f>$B32+$Y32*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D32" s="7">
-        <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E32" s="6">
-        <f>CEILING($D32*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G32" s="8">
-        <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="9">
-        <f>IF($G32="","",$G32/$C32)</f>
-        <v/>
-      </c>
-      <c r="I32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="6">
-        <f>$C32/$I32</f>
-        <v/>
-      </c>
-      <c r="K32" s="6">
-        <f>IF($F32="","",$F32/$I32)</f>
-        <v/>
-      </c>
-      <c r="L32" s="6">
-        <f>IF($G32="","",$G32/$I32)</f>
-        <v/>
-      </c>
-      <c r="M32" s="7">
-        <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="11" t="n">
+      <c r="O32" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="P32" s="11" t="n">
+      <c r="P32" s="21" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q32" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R32" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S32" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T32" s="12" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X32" s="4" t="inlineStr"/>
-      <c r="Y32" s="4" t="n">
+      <c r="Q32" s="22" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R32" s="22" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S32" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T32" s="22" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="U32" s="14" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V32" s="14" t="inlineStr"/>
+      <c r="W32" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X32" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y32" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
+          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>52.4</v>
+        <v>51.12</v>
       </c>
       <c r="C33" s="6">
         <f>$B33+$Y33*Paramètres!$B$13</f>
@@ -3370,7 +3382,7 @@
         <v/>
       </c>
       <c r="F33" s="8" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G33" s="8">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
@@ -3403,10 +3415,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P33" s="11" t="n">
-        <v>10.66</v>
+        <v>10.4</v>
       </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
@@ -3425,12 +3437,12 @@
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U33" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="V33" s="4" t="inlineStr"/>
@@ -3447,11 +3459,11 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>LACOSTE sneakers P.42 — neuves</t>
+          <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
       <c r="B34" s="15" t="n">
-        <v>57.51</v>
+        <v>63</v>
       </c>
       <c r="C34" s="16">
         <f>$B34+$Y34*Paramètres!$B$13</f>
@@ -3466,7 +3478,7 @@
         <v/>
       </c>
       <c r="F34" s="18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G34" s="18">
         <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
@@ -3499,34 +3511,34 @@
         <v>0</v>
       </c>
       <c r="O34" s="21" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P34" s="21" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
       <c r="Q34" s="22" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R34" s="22" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S34" s="22" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T34" s="22" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>103</t>
         </is>
       </c>
       <c r="U34" s="14" t="inlineStr">
         <is>
-          <t>date à compléter</t>
+          <t>vendu</t>
         </is>
       </c>
       <c r="V34" s="14" t="inlineStr"/>
@@ -3545,409 +3557,401 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="C35" s="16">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE sneakers P.38 — neuves</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C35" s="6">
         <f>$B35+$Y35*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="7">
         <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="6">
         <f>CEILING($D35*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F35" s="18" t="n">
-        <v>125</v>
-      </c>
-      <c r="G35" s="18">
+      <c r="F35" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="G35" s="8">
         <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
         <v/>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="9">
         <f>IF($G35="","",$G35/$C35)</f>
         <v/>
       </c>
-      <c r="I35" s="20" t="n">
+      <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="16">
+      <c r="J35" s="6">
         <f>$C35/$I35</f>
         <v/>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="6">
         <f>IF($F35="","",$F35/$I35)</f>
         <v/>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="6">
         <f>IF($G35="","",$G35/$I35)</f>
         <v/>
       </c>
-      <c r="M35" s="17">
+      <c r="M35" s="7">
         <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N35" s="16" t="n">
+      <c r="N35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="P35" s="21" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Q35" s="22" t="inlineStr">
+      <c r="O35" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q35" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S35" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T35" s="12" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X35" s="4" t="inlineStr"/>
+      <c r="Y35" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C36" s="16">
+        <f>$B36+$Y36*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E36" s="16">
+        <f>CEILING($D36*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="G36" s="18">
+        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="19">
+        <f>IF($G36="","",$G36/$C36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="16">
+        <f>$C36/$I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="16">
+        <f>IF($F36="","",$F36/$I36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="16">
+        <f>IF($G36="","",$G36/$I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="17">
+        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P36" s="21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q36" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R35" s="22" t="inlineStr">
+      <c r="R36" s="22" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S36" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-43717</t>
+        </is>
+      </c>
+      <c r="T36" s="22" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="U36" s="14" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V36" s="14" t="inlineStr"/>
+      <c r="W36" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X36" s="14" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y36" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="C37" s="6">
+        <f>$B37+$Y37*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D37" s="7">
+        <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E37" s="6">
+        <f>CEILING($D37*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G37" s="8">
+        <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="9">
+        <f>IF($G37="","",$G37/$C37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="6">
+        <f>$C37/$I37</f>
+        <v/>
+      </c>
+      <c r="K37" s="6">
+        <f>IF($F37="","",$F37/$I37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="6">
+        <f>IF($G37="","",$G37/$I37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="7">
+        <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P37" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q37" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R37" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S35" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-44194</t>
-        </is>
-      </c>
-      <c r="T35" s="22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U35" s="14" t="inlineStr">
-        <is>
-          <t>date à compléter</t>
-        </is>
-      </c>
-      <c r="V35" s="14" t="inlineStr"/>
-      <c r="W35" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X35" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y35" s="14" t="n">
+      <c r="S37" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T37" s="12" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="inlineStr"/>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X37" s="4" t="inlineStr"/>
+      <c r="Y37" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C36" s="25">
-        <f>$B36+$Y36*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D36" s="26">
-        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E36" s="25">
-        <f>CEILING($D36*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="G36" s="27">
-        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="28">
-        <f>IF($G36="","",$G36/$C36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" s="25">
-        <f>$C36/$I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="25">
-        <f>IF($F36="","",$F36/$I36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="25">
-        <f>IF($G36="","",$G36/$I36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="26">
-        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N36" s="25" t="n">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="C38" s="6">
+        <f>$B38+$Y38*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D38" s="7">
+        <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E38" s="6">
+        <f>CEILING($D38*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G38" s="8">
+        <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="9">
+        <f>IF($G38="","",$G38/$C38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="6">
+        <f>$C38/$I38</f>
+        <v/>
+      </c>
+      <c r="K38" s="6">
+        <f>IF($F38="","",$F38/$I38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>IF($G38="","",$G38/$I38)</f>
+        <v/>
+      </c>
+      <c r="M38" s="7">
+        <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="P36" s="30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q36" s="31" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R36" s="31" t="inlineStr">
+      <c r="O38" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="P38" s="11" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="Q38" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R38" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S36" s="31" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T36" s="31" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="U36" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay, en lot</t>
-        </is>
-      </c>
-      <c r="V36" s="23" t="inlineStr"/>
-      <c r="W36" s="23" t="inlineStr">
-        <is>
-          <t>Marge faible</t>
-        </is>
-      </c>
-      <c r="X36" s="23" t="inlineStr"/>
-      <c r="Y36" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="C37" s="16">
-        <f>$B37+$Y37*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D37" s="17">
-        <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>CEILING($D37*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="G37" s="18">
-        <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="19">
-        <f>IF($G37="","",$G37/$C37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="16">
-        <f>$C37/$I37</f>
-        <v/>
-      </c>
-      <c r="K37" s="16">
-        <f>IF($F37="","",$F37/$I37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="16">
-        <f>IF($G37="","",$G37/$I37)</f>
-        <v/>
-      </c>
-      <c r="M37" s="17">
-        <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N37" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="P37" s="21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q37" s="22" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R37" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S37" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T37" s="22" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="U37" s="14" t="inlineStr">
-        <is>
-          <t>date à compléter</t>
-        </is>
-      </c>
-      <c r="V37" s="14" t="inlineStr"/>
-      <c r="W37" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X37" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y37" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C38" s="16">
-        <f>$B38+$Y38*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D38" s="17">
-        <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E38" s="16">
-        <f>CEILING($D38*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="G38" s="18">
-        <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="19">
-        <f>IF($G38="","",$G38/$C38)</f>
-        <v/>
-      </c>
-      <c r="I38" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="16">
-        <f>$C38/$I38</f>
-        <v/>
-      </c>
-      <c r="K38" s="16">
-        <f>IF($F38="","",$F38/$I38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="16">
-        <f>IF($G38="","",$G38/$I38)</f>
-        <v/>
-      </c>
-      <c r="M38" s="17">
-        <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="P38" s="21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q38" s="22" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R38" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S38" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T38" s="22" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="U38" s="14" t="inlineStr">
-        <is>
-          <t>date à compléter</t>
-        </is>
-      </c>
-      <c r="V38" s="14" t="inlineStr"/>
-      <c r="W38" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X38" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y38" s="14" t="n">
+      <c r="S38" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T38" s="12" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr"/>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="inlineStr"/>
+      <c r="Y38" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+          <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
       <c r="B39" s="15" t="n">
-        <v>50.4</v>
+        <v>57.51</v>
       </c>
       <c r="C39" s="16">
         <f>$B39+$Y39*Paramètres!$B$13</f>
@@ -3962,7 +3966,7 @@
         <v/>
       </c>
       <c r="F39" s="18" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G39" s="18">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
@@ -3995,34 +3999,34 @@
         <v>0</v>
       </c>
       <c r="O39" s="21" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P39" s="21" t="n">
-        <v>10.4</v>
+        <v>11.7</v>
       </c>
       <c r="Q39" s="22" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R39" s="22" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S39" s="22" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T39" s="22" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>141</t>
         </is>
       </c>
       <c r="U39" s="14" t="inlineStr">
         <is>
-          <t>date à compléter</t>
+          <t>vendu</t>
         </is>
       </c>
       <c r="V39" s="14" t="inlineStr"/>
@@ -4041,102 +4045,98 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>Baskets HOKA P.37 1/3 — neuves</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n">
-        <v>63</v>
-      </c>
-      <c r="C40" s="16">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C40" s="25">
         <f>$B40+$Y40*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="26">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="25">
         <f>CEILING($D40*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F40" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="G40" s="18">
+      <c r="F40" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="G40" s="27">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
         <v/>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="28">
         <f>IF($G40="","",$G40/$C40)</f>
         <v/>
       </c>
-      <c r="I40" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="16">
+      <c r="I40" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" s="25">
         <f>$C40/$I40</f>
         <v/>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="25">
         <f>IF($F40="","",$F40/$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="25">
         <f>IF($G40="","",$G40/$I40)</f>
         <v/>
       </c>
-      <c r="M40" s="17">
+      <c r="M40" s="26">
         <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N40" s="16" t="n">
+      <c r="N40" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="21" t="n">
-        <v>50</v>
-      </c>
-      <c r="P40" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q40" s="22" t="inlineStr">
+      <c r="O40" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="P40" s="30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q40" s="31" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R40" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S40" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T40" s="22" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="U40" s="14" t="inlineStr">
-        <is>
-          <t>date à compléter</t>
-        </is>
-      </c>
-      <c r="V40" s="14" t="inlineStr"/>
-      <c r="W40" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X40" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y40" s="14" t="n">
+      <c r="R40" s="31" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S40" s="31" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T40" s="31" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="U40" s="23" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V40" s="23" t="inlineStr"/>
+      <c r="W40" s="23" t="inlineStr">
+        <is>
+          <t>Marge faible</t>
+        </is>
+      </c>
+      <c r="X40" s="23" t="inlineStr"/>
+      <c r="Y40" s="23" t="n">
         <v>1</v>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -1710,7 +1710,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Lot de 2 pompes immergées ROBBY VP550W</t>
+          <t>Lot de 3 pompes immergées ROBBY VP550W — 1 prélevée usage personnel, 2 à vendre</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -4535,14 +4535,14 @@
     <row r="27">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>Dates de vente à compléter sur les 6 ventes récentes.</t>
+          <t>Ventes du 09/08 et du 10/08/2026 : espèces, main propre. Nom de l'acheteur à noter.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t>Facture manquante : lot n°84, les 2 pompes Robby.</t>
+          <t>Factures annoncées : lot n°84 (3 pompes Robby) et boîte de 30 boosters Pokémon.</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$Y$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$Y$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1231,18 +1231,18 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pokémon MEGA Munikis Zero M3 — boîte de 30 boosters</t>
+          <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>65</v>
+        <v>12.6</v>
       </c>
       <c r="C11" s="6">
-        <f>$B11</f>
+        <f>$B11+$Y11*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E11" s="6">
@@ -1250,7 +1250,7 @@
         <v/>
       </c>
       <c r="F11" s="8" t="n">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="G11" s="8">
         <f>IF($F11="","",$F11-$C11-$M11-$N11)</f>
@@ -1261,7 +1261,7 @@
         <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J11" s="6">
         <f>$C11/$I11</f>
@@ -1279,34 +1279,39 @@
         <f>IF($F11="","",$F11*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="13" t="n"/>
-      <c r="P11" s="13" t="n"/>
+      <c r="N11" s="6">
+        <f>IF($F11="","",$F11*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>2.6</v>
+      </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>Vendeur au Japon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T11" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>eBay + Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
@@ -1317,17 +1322,17 @@
       </c>
       <c r="X11" s="4" t="inlineStr"/>
       <c r="Y11" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Chaussures HOGAN P.36 — traces d'essayage</t>
+          <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12.6</v>
+        <v>37.8</v>
       </c>
       <c r="C12" s="6">
         <f>$B12+$Y12*Paramètres!$B$13</f>
@@ -1342,7 +1347,7 @@
         <v/>
       </c>
       <c r="F12" s="8" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="G12" s="8">
         <f>IF($F12="","",$F12-$C12-$M12-$N12)</f>
@@ -1376,10 +1381,10 @@
         <v/>
       </c>
       <c r="O12" s="11" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
@@ -1398,7 +1403,7 @@
       </c>
       <c r="T12" s="12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>417</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
@@ -1420,7 +1425,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
+          <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -1439,7 +1444,7 @@
         <v/>
       </c>
       <c r="F13" s="8" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G13" s="8">
         <f>IF($F13="","",$F13-$C13-$M13-$N13)</f>
@@ -1495,7 +1500,7 @@
       </c>
       <c r="T13" s="12" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
@@ -1517,7 +1522,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Robe SANDRO T.40 — neuve</t>
+          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -1528,7 +1533,7 @@
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E14" s="6">
@@ -1536,7 +1541,7 @@
         <v/>
       </c>
       <c r="F14" s="8" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G14" s="8">
         <f>IF($F14="","",$F14-$C14-$M14-$N14)</f>
@@ -1547,7 +1552,7 @@
         <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J14" s="6">
         <f>$C14/$I14</f>
@@ -1565,9 +1570,8 @@
         <f>IF($F14="","",$F14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N14" s="6">
-        <f>IF($F14="","",$F14*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O14" s="11" t="n">
         <v>30</v>
@@ -1582,22 +1586,22 @@
       </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-46056</t>
         </is>
       </c>
       <c r="T14" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>279</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr"/>
@@ -1608,20 +1612,20 @@
       </c>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
+          <t>Lot de 3 pompes immergées ROBBY VP550W — 1 prélevée usage personnel, 2 à vendre</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>37.8</v>
+        <v>45</v>
       </c>
       <c r="C15" s="6">
-        <f>$B15+$Y15*Paramètres!$B$13</f>
+        <f>$B15</f>
         <v/>
       </c>
       <c r="D15" s="7">
@@ -1633,7 +1637,7 @@
         <v/>
       </c>
       <c r="F15" s="8" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G15" s="8">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
@@ -1644,7 +1648,7 @@
         <v/>
       </c>
       <c r="I15" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J15" s="6">
         <f>$C15/$I15</f>
@@ -1665,35 +1669,31 @@
       <c r="N15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P15" s="11" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="O15" s="13" t="n"/>
+      <c r="P15" s="13" t="n"/>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN (facture à retrouver)</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin, main propre</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
@@ -1704,24 +1704,24 @@
       </c>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Lot de 3 pompes immergées ROBBY VP550W — 1 prélevée usage personnel, 2 à vendre</t>
+          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>45</v>
+        <v>37.8</v>
       </c>
       <c r="C16" s="6">
-        <f>$B16</f>
+        <f>$B16+$Y16*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E16" s="6">
@@ -1729,7 +1729,7 @@
         <v/>
       </c>
       <c r="F16" s="8" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G16" s="8">
         <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
@@ -1740,7 +1740,7 @@
         <v/>
       </c>
       <c r="I16" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="6">
         <f>$C16/$I16</f>
@@ -1758,34 +1758,39 @@
         <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="13" t="n"/>
+      <c r="N16" s="6">
+        <f>IF($F16="","",$F16*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>7.8</v>
+      </c>
       <c r="Q16" s="12" t="inlineStr">
         <is>
-          <t>ADN (facture à retrouver)</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R16" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T16" s="12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>434</t>
         </is>
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr"/>
@@ -1796,214 +1801,214 @@
       </c>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="C17" s="16">
         <f>$B17+$Y17*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D17" s="7">
-        <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="E17" s="6">
+      <c r="D17" s="17">
+        <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
         <f>CEILING($D17*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="G17" s="8">
+      <c r="F17" s="18" t="n">
+        <v>168</v>
+      </c>
+      <c r="G17" s="18">
         <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
         <v/>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="19">
         <f>IF($G17="","",$G17/$C17)</f>
         <v/>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I17" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" s="16">
+        <f>$C17/$I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="16">
+        <f>IF($F17="","",$F17/$I17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="16">
+        <f>IF($G17="","",$G17/$I17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="17">
+        <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="P17" s="21" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q17" s="22" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R17" s="22" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S17" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-5844</t>
+        </is>
+      </c>
+      <c r="T17" s="22" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="U17" s="14" t="inlineStr">
+        <is>
+          <t>Leboncoin, à l'unité</t>
+        </is>
+      </c>
+      <c r="V17" s="14" t="inlineStr"/>
+      <c r="W17" s="14" t="inlineStr">
+        <is>
+          <t>URGENT — 2 sur 12 vendues</t>
+        </is>
+      </c>
+      <c r="X17" s="14" t="inlineStr">
+        <is>
+          <t>2 vendues</t>
+        </is>
+      </c>
+      <c r="Y17" s="14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C18" s="6">
+        <f>$B18+$Y18*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D18" s="7">
+        <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E18" s="6">
+        <f>CEILING($D18*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="G18" s="8">
+        <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="9">
+        <f>IF($G18="","",$G18/$C18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="6">
-        <f>$C17/$I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="6">
-        <f>IF($F17="","",$F17/$I17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="6">
-        <f>IF($G17="","",$G17/$I17)</f>
-        <v/>
-      </c>
-      <c r="M17" s="7">
-        <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N17" s="6">
-        <f>IF($F17="","",$F17*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O17" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P17" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q17" s="12" t="inlineStr">
+      <c r="J18" s="6">
+        <f>$C18/$I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="6">
+        <f>IF($F18="","",$F18/$I18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="6">
+        <f>IF($G18="","",$G18/$I18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="7">
+        <f>IF($F18="","",$F18*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N18" s="6">
+        <f>IF($F18="","",$F18*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q18" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R17" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S17" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T17" s="12" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
+      <c r="R18" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-44194</t>
+        </is>
+      </c>
+      <c r="T18" s="12" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" s="4" t="inlineStr">
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="n">
+      <c r="X18" s="4" t="inlineStr"/>
+      <c r="Y18" s="4" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="C18" s="16">
-        <f>$B18+$Y18*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D18" s="17">
-        <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E18" s="16">
-        <f>CEILING($D18*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>168</v>
-      </c>
-      <c r="G18" s="18">
-        <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="19">
-        <f>IF($G18="","",$G18/$C18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" s="16">
-        <f>$C18/$I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="16">
-        <f>IF($F18="","",$F18/$I18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="16">
-        <f>IF($G18="","",$G18/$I18)</f>
-        <v/>
-      </c>
-      <c r="M18" s="17">
-        <f>IF($F18="","",$F18*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="P18" s="21" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q18" s="22" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R18" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S18" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-5844</t>
-        </is>
-      </c>
-      <c r="T18" s="22" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="U18" s="14" t="inlineStr">
-        <is>
-          <t>Leboncoin, à l'unité</t>
-        </is>
-      </c>
-      <c r="V18" s="14" t="inlineStr"/>
-      <c r="W18" s="14" t="inlineStr">
-        <is>
-          <t>URGENT — 2 sur 12 vendues</t>
-        </is>
-      </c>
-      <c r="X18" s="14" t="inlineStr">
-        <is>
-          <t>2 vendues</t>
-        </is>
-      </c>
-      <c r="Y18" s="14" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
+          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>50.4</v>
+        <v>31.95</v>
       </c>
       <c r="C19" s="6">
         <f>$B19+$Y19*Paramètres!$B$13</f>
@@ -2018,7 +2023,7 @@
         <v/>
       </c>
       <c r="F19" s="8" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G19" s="8">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
@@ -2052,14 +2057,14 @@
         <v/>
       </c>
       <c r="O19" s="11" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="P19" s="11" t="n">
-        <v>10.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
@@ -2069,17 +2074,17 @@
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
@@ -2096,18 +2101,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
+          <t>Booster Box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters — 6 lots de 5 à 17 €</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>31.95</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="C20" s="6">
-        <f>$B20+$Y20*Paramètres!$B$13</f>
+        <f>$B20</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E20" s="6">
@@ -2115,7 +2120,7 @@
         <v/>
       </c>
       <c r="F20" s="8" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="G20" s="8">
         <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
@@ -2126,7 +2131,7 @@
         <v/>
       </c>
       <c r="I20" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J20" s="6">
         <f>$C20/$I20</f>
@@ -2144,19 +2149,14 @@
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6">
-        <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O20" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="P20" s="11" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="N20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="13" t="n"/>
+      <c r="P20" s="13" t="n"/>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>4521329432274</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin, lots de 5</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -4143,14 +4143,14 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
+          <t>Boosters Pokémon MEGA Storm Emeralda M6 ×2 — 5 cartes chacun — prix à confirmer avant publication</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>63</v>
+        <v>12.74</v>
       </c>
       <c r="C41" s="6">
-        <f>$B41+$Y41*Paramètres!$B$13</f>
+        <f>$B41</f>
         <v/>
       </c>
       <c r="D41" s="7">
@@ -4161,7 +4161,9 @@
         <f>CEILING($D41*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F41" s="13" t="n"/>
+      <c r="F41" s="8" t="n">
+        <v>19</v>
+      </c>
       <c r="G41" s="8">
         <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
         <v/>
@@ -4192,41 +4194,37 @@
       <c r="N41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="P41" s="11" t="n">
-        <v>13</v>
-      </c>
+      <c r="O41" s="13" t="n"/>
+      <c r="P41" s="13" t="n"/>
       <c r="Q41" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R41" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S41" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46056</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T41" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4521329462226</t>
         </is>
       </c>
       <c r="U41" s="4" t="inlineStr">
         <is>
-          <t>Vinted, authentification</t>
+          <t>Leboncoin, lot de 2</t>
         </is>
       </c>
       <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>PRIX À ÉTABLIR</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X41" s="4" t="inlineStr"/>
@@ -4235,63 +4233,249 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="inlineStr">
-        <is>
-          <t>TOTAL — 36 lots</t>
-        </is>
-      </c>
-      <c r="B42" s="33">
-        <f>SUM(B6:B41)</f>
-        <v/>
-      </c>
-      <c r="C42" s="33">
-        <f>SUM(C6:C41)</f>
-        <v/>
-      </c>
-      <c r="D42" s="34" t="n"/>
-      <c r="E42" s="34" t="n"/>
-      <c r="F42" s="33">
-        <f>SUM(F6:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="33">
-        <f>SUM(G6:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="35">
-        <f>G42/C42</f>
-        <v/>
-      </c>
-      <c r="I42" s="36">
-        <f>SUM(I6:I41)</f>
-        <v/>
-      </c>
-      <c r="J42" s="34" t="n"/>
-      <c r="K42" s="34" t="n"/>
-      <c r="L42" s="34" t="n"/>
-      <c r="M42" s="33">
-        <f>SUM(M6:M41)</f>
-        <v/>
-      </c>
-      <c r="N42" s="33">
-        <f>SUM(N6:N41)</f>
-        <v/>
-      </c>
-      <c r="O42" s="34" t="n"/>
-      <c r="P42" s="34" t="n"/>
-      <c r="Q42" s="34" t="n"/>
-      <c r="R42" s="34" t="n"/>
-      <c r="S42" s="34" t="n"/>
-      <c r="T42" s="34" t="n"/>
-      <c r="U42" s="34" t="n"/>
-      <c r="V42" s="34" t="n"/>
-      <c r="W42" s="34" t="n"/>
-      <c r="X42" s="34" t="n"/>
-      <c r="Y42" s="34" t="n"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes — prix à confirmer avant publication</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="C42" s="6">
+        <f>$B42</f>
+        <v/>
+      </c>
+      <c r="D42" s="7">
+        <f>$C42/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E42" s="6">
+        <f>CEILING($D42*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G42" s="8">
+        <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
+        <v/>
+      </c>
+      <c r="H42" s="9">
+        <f>IF($G42="","",$G42/$C42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="6">
+        <f>$C42/$I42</f>
+        <v/>
+      </c>
+      <c r="K42" s="6">
+        <f>IF($F42="","",$F42/$I42)</f>
+        <v/>
+      </c>
+      <c r="L42" s="6">
+        <f>IF($G42="","",$G42/$I42)</f>
+        <v/>
+      </c>
+      <c r="M42" s="7">
+        <f>IF($F42="","",$F42*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="13" t="n"/>
+      <c r="P42" s="13" t="n"/>
+      <c r="Q42" s="12" t="inlineStr">
+        <is>
+          <t>Meccha Japan</t>
+        </is>
+      </c>
+      <c r="R42" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S42" s="12" t="inlineStr">
+        <is>
+          <t>#FA429713</t>
+        </is>
+      </c>
+      <c r="T42" s="12" t="inlineStr">
+        <is>
+          <t>4521329431925</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin, à l'unité</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr"/>
+      <c r="W42" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X42" s="4" t="inlineStr"/>
+      <c r="Y42" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C43" s="6">
+        <f>$B43+$Y43*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D43" s="7">
+        <f>$C43/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E43" s="6">
+        <f>CEILING($D43*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F43" s="13" t="n"/>
+      <c r="G43" s="8">
+        <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
+        <v/>
+      </c>
+      <c r="H43" s="9">
+        <f>IF($G43="","",$G43/$C43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="6">
+        <f>$C43/$I43</f>
+        <v/>
+      </c>
+      <c r="K43" s="6">
+        <f>IF($F43="","",$F43/$I43)</f>
+        <v/>
+      </c>
+      <c r="L43" s="6">
+        <f>IF($G43="","",$G43/$I43)</f>
+        <v/>
+      </c>
+      <c r="M43" s="7">
+        <f>IF($F43="","",$F43*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q43" s="12" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R43" s="12" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="S43" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-46056</t>
+        </is>
+      </c>
+      <c r="T43" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>Vinted, authentification</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr"/>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>PRIX À ÉTABLIR</t>
+        </is>
+      </c>
+      <c r="X43" s="4" t="inlineStr"/>
+      <c r="Y43" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL — 38 lots</t>
+        </is>
+      </c>
+      <c r="B44" s="33">
+        <f>SUM(B6:B43)</f>
+        <v/>
+      </c>
+      <c r="C44" s="33">
+        <f>SUM(C6:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="34" t="n"/>
+      <c r="E44" s="34" t="n"/>
+      <c r="F44" s="33">
+        <f>SUM(F6:F43)</f>
+        <v/>
+      </c>
+      <c r="G44" s="33">
+        <f>SUM(G6:G43)</f>
+        <v/>
+      </c>
+      <c r="H44" s="35">
+        <f>G44/C44</f>
+        <v/>
+      </c>
+      <c r="I44" s="36">
+        <f>SUM(I6:I43)</f>
+        <v/>
+      </c>
+      <c r="J44" s="34" t="n"/>
+      <c r="K44" s="34" t="n"/>
+      <c r="L44" s="34" t="n"/>
+      <c r="M44" s="33">
+        <f>SUM(M6:M43)</f>
+        <v/>
+      </c>
+      <c r="N44" s="33">
+        <f>SUM(N6:N43)</f>
+        <v/>
+      </c>
+      <c r="O44" s="34" t="n"/>
+      <c r="P44" s="34" t="n"/>
+      <c r="Q44" s="34" t="n"/>
+      <c r="R44" s="34" t="n"/>
+      <c r="S44" s="34" t="n"/>
+      <c r="T44" s="34" t="n"/>
+      <c r="U44" s="34" t="n"/>
+      <c r="V44" s="34" t="n"/>
+      <c r="W44" s="34" t="n"/>
+      <c r="X44" s="34" t="n"/>
+      <c r="Y44" s="34" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Y41"/>
-  <conditionalFormatting sqref="G6:G41">
+  <autoFilter ref="A5:Y43"/>
+  <conditionalFormatting sqref="G6:G43">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -4356,7 +4540,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>110</v>
+        <v>139.93</v>
       </c>
     </row>
     <row r="7">
@@ -4366,7 +4550,7 @@
         </is>
       </c>
       <c r="B7" s="33">
-        <f>'Stock complet'!C42</f>
+        <f>'Stock complet'!C44</f>
         <v/>
       </c>
     </row>
@@ -4384,7 +4568,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>'Stock complet'!F42</f>
+        <f>'Stock complet'!F44</f>
         <v/>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4400,7 +4584,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>-'Stock complet'!M42</f>
+        <f>-'Stock complet'!M44</f>
         <v/>
       </c>
     </row>
@@ -4411,7 +4595,7 @@
         </is>
       </c>
       <c r="B12" s="6">
-        <f>-'Stock complet'!N42</f>
+        <f>-'Stock complet'!N44</f>
         <v/>
       </c>
     </row>
@@ -4421,7 +4605,7 @@
         <v/>
       </c>
       <c r="B13" s="33">
-        <f>'Stock complet'!G42</f>
+        <f>'Stock complet'!G44</f>
         <v/>
       </c>
     </row>
@@ -4514,7 +4698,7 @@
         </is>
       </c>
       <c r="B23" s="42">
-        <f>'Stock complet'!I42</f>
+        <f>'Stock complet'!I44</f>
         <v/>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2101,14 +2101,14 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Booster Box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters — 6 lots de 5 à 17 €</t>
+          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>25.2</v>
       </c>
       <c r="C20" s="6">
-        <f>$B20</f>
+        <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7">
@@ -2120,7 +2120,7 @@
         <v/>
       </c>
       <c r="F20" s="8" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="G20" s="8">
         <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
@@ -2131,7 +2131,7 @@
         <v/>
       </c>
       <c r="I20" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J20" s="6">
         <f>$C20/$I20</f>
@@ -2152,31 +2152,35 @@
       <c r="N20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="13" t="n"/>
+      <c r="O20" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>5.2</v>
+      </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>4521329432274</t>
+          <t>439</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lots de 5</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
@@ -2187,24 +2191,24 @@
       </c>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
+          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>25.2</v>
+        <v>25.56</v>
       </c>
       <c r="C21" s="6">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E21" s="6">
@@ -2241,8 +2245,9 @@
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
+      <c r="N21" s="6">
+        <f>IF($F21="","",$F21*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O21" s="11" t="n">
         <v>20</v>
@@ -2252,27 +2257,27 @@
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R21" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
@@ -2289,18 +2294,18 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
+          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>25.56</v>
+        <v>57.51</v>
       </c>
       <c r="C22" s="6">
         <f>$B22+$Y22*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E22" s="6">
@@ -2308,7 +2313,7 @@
         <v/>
       </c>
       <c r="F22" s="8" t="n">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G22" s="8">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
@@ -2337,15 +2342,14 @@
         <f>IF($F22="","",$F22*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N22" s="6">
-        <f>IF($F22="","",$F22*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N22" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>5.2</v>
+        <v>11.7</v>
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
@@ -2359,17 +2363,17 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T22" s="12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>159</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
@@ -2386,11 +2390,11 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
+          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>57.51</v>
+        <v>37.8</v>
       </c>
       <c r="C23" s="6">
         <f>$B23+$Y23*Paramètres!$B$13</f>
@@ -2405,7 +2409,7 @@
         <v/>
       </c>
       <c r="F23" s="8" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G23" s="8">
         <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
@@ -2416,7 +2420,7 @@
         <v/>
       </c>
       <c r="I23" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J23" s="6">
         <f>$C23/$I23</f>
@@ -2438,254 +2442,254 @@
         <v>0</v>
       </c>
       <c r="O23" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="P23" s="11" t="n">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R23" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S23" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-43717</t>
         </is>
       </c>
       <c r="T23" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U23" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="C24" s="25">
+        <f>$B24+$Y24*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D24" s="26">
+        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E24" s="25">
+        <f>CEILING($D24*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="G24" s="27">
+        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="28">
+        <f>IF($G24="","",$G24/$C24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="25">
+        <f>$C24/$I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="25">
+        <f>IF($F24="","",$F24/$I24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="25">
+        <f>IF($G24="","",$G24/$I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="26">
+        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="P24" s="30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q24" s="31" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R24" s="31" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S24" s="31" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T24" s="31" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="U24" s="23" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V24" s="23" t="inlineStr"/>
+      <c r="W24" s="23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X24" s="23" t="inlineStr"/>
+      <c r="Y24" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C24" s="6">
-        <f>$B24+$Y24*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D24" s="7">
-        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E24" s="6">
-        <f>CEILING($D24*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="G24" s="8">
-        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="9">
-        <f>IF($G24="","",$G24/$C24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="6">
-        <f>$C24/$I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="6">
-        <f>IF($F24="","",$F24/$I24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="6">
-        <f>IF($G24="","",$G24/$I24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="7">
-        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N24" s="6" t="n">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>GEOX baskets P.35 — neuves</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="C25" s="6">
+        <f>$B25+$Y25*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D25" s="7">
+        <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E25" s="6">
+        <f>CEILING($D25*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="G25" s="8">
+        <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="9">
+        <f>IF($G25="","",$G25/$C25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="6">
+        <f>$C25/$I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="6">
+        <f>IF($F25="","",$F25/$I25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="6">
+        <f>IF($G25="","",$G25/$I25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="7">
+        <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P24" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q24" s="12" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R24" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S24" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T24" s="12" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="4" t="inlineStr">
-        <is>
-          <t>URGENT — saisonnier</t>
-        </is>
-      </c>
-      <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="C25" s="25">
-        <f>$B25+$Y25*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D25" s="26">
-        <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E25" s="25">
-        <f>CEILING($D25*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="G25" s="27">
-        <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
-        <v/>
-      </c>
-      <c r="H25" s="28">
-        <f>IF($G25="","",$G25/$C25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="25">
-        <f>$C25/$I25</f>
-        <v/>
-      </c>
-      <c r="K25" s="25">
-        <f>IF($F25="","",$F25/$I25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="25">
-        <f>IF($G25="","",$G25/$I25)</f>
-        <v/>
-      </c>
-      <c r="M25" s="26">
-        <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N25" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="P25" s="30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q25" s="31" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R25" s="31" t="inlineStr">
+      <c r="O25" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="Q25" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R25" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S25" s="31" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T25" s="31" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="U25" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay, en lot</t>
-        </is>
-      </c>
-      <c r="V25" s="23" t="inlineStr"/>
-      <c r="W25" s="23" t="inlineStr">
+      <c r="S25" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T25" s="12" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr"/>
+      <c r="W25" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X25" s="23" t="inlineStr"/>
-      <c r="Y25" s="23" t="n">
+      <c r="X25" s="4" t="inlineStr"/>
+      <c r="Y25" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>GEOX baskets P.35 — neuves</t>
+          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>21.73</v>
+        <v>50.4</v>
       </c>
       <c r="C26" s="6">
         <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E26" s="6">
@@ -2693,7 +2697,7 @@
         <v/>
       </c>
       <c r="F26" s="8" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="G26" s="8">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
@@ -2722,44 +2726,45 @@
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="n">
-        <v>0</v>
+      <c r="N26" s="6">
+        <f>IF($F26="","",$F26*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O26" s="11" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="P26" s="11" t="n">
-        <v>4.42</v>
+        <v>10.4</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R26" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T26" s="12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>408</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X26" s="4" t="inlineStr"/>
@@ -2770,18 +2775,18 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
+          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>50.4</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="C27" s="6">
         <f>$B27+$Y27*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E27" s="6">
@@ -2789,7 +2794,7 @@
         <v/>
       </c>
       <c r="F27" s="8" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="G27" s="8">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
@@ -2818,15 +2823,14 @@
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6">
-        <f>IF($F27="","",$F27*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N27" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O27" s="11" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P27" s="11" t="n">
-        <v>10.4</v>
+        <v>15.6</v>
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
@@ -2845,18 +2849,18 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>199</t>
         </is>
       </c>
       <c r="U27" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Liquider</t>
         </is>
       </c>
       <c r="X27" s="4" t="inlineStr"/>
@@ -2865,109 +2869,113 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="C28" s="6">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="C28" s="16">
         <f>$B28+$Y28*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="17">
         <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="16">
         <f>CEILING($D28*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="G28" s="8">
+      <c r="F28" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" s="18">
         <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
         <v/>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="19">
         <f>IF($G28="","",$G28/$C28)</f>
         <v/>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="16">
         <f>$C28/$I28</f>
         <v/>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="16">
         <f>IF($F28="","",$F28/$I28)</f>
         <v/>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="16">
         <f>IF($G28="","",$G28/$I28)</f>
         <v/>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="17">
         <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="11" t="n">
+      <c r="O28" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="P28" s="11" t="n">
+      <c r="P28" s="21" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q28" s="12" t="inlineStr">
+      <c r="Q28" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R28" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S28" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T28" s="12" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr"/>
-      <c r="W28" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X28" s="4" t="inlineStr"/>
-      <c r="Y28" s="4" t="n">
+      <c r="R28" s="22" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S28" s="22" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T28" s="22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U28" s="14" t="inlineStr">
+        <is>
+          <t>Vinted, Italie — non encaissé</t>
+        </is>
+      </c>
+      <c r="V28" s="14" t="inlineStr"/>
+      <c r="W28" s="14" t="inlineStr">
+        <is>
+          <t>VENDUE, en attente</t>
+        </is>
+      </c>
+      <c r="X28" s="14" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="Y28" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>76.68000000000001</v>
+        <v>113.4</v>
       </c>
       <c r="C29" s="16">
         <f>$B29+$Y29*Paramètres!$B$13</f>
@@ -2982,7 +2990,7 @@
         <v/>
       </c>
       <c r="F29" s="18" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="G29" s="18">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
@@ -3015,10 +3023,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="21" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>15.6</v>
+        <v>23.4</v>
       </c>
       <c r="Q29" s="22" t="inlineStr">
         <is>
@@ -3032,28 +3040,28 @@
       </c>
       <c r="S29" s="22" t="inlineStr">
         <is>
-          <t>FB2026-44192</t>
+          <t>FB2026-44194</t>
         </is>
       </c>
       <c r="T29" s="22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
         <is>
-          <t>Vinted, Italie — non encaissé</t>
+          <t>vendu</t>
         </is>
       </c>
       <c r="V29" s="14" t="inlineStr"/>
       <c r="W29" s="14" t="inlineStr">
         <is>
-          <t>VENDUE, en attente</t>
+          <t>VENDU</t>
         </is>
       </c>
       <c r="X29" s="14" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>VENDU</t>
         </is>
       </c>
       <c r="Y29" s="14" t="n">
@@ -3063,11 +3071,11 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>113.4</v>
+        <v>50.4</v>
       </c>
       <c r="C30" s="16">
         <f>$B30+$Y30*Paramètres!$B$13</f>
@@ -3082,7 +3090,7 @@
         <v/>
       </c>
       <c r="F30" s="18" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="G30" s="18">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
@@ -3115,10 +3123,10 @@
         <v>0</v>
       </c>
       <c r="O30" s="21" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="P30" s="21" t="n">
-        <v>23.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q30" s="22" t="inlineStr">
         <is>
@@ -3127,17 +3135,17 @@
       </c>
       <c r="R30" s="22" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S30" s="22" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T30" s="22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>170</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
@@ -3163,7 +3171,7 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
       <c r="B31" s="15" t="n">
@@ -3237,7 +3245,7 @@
       </c>
       <c r="T31" s="22" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>431</t>
         </is>
       </c>
       <c r="U31" s="14" t="inlineStr">
@@ -3261,116 +3269,108 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C32" s="16">
-        <f>$B32+$Y32*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D32" s="17">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes — invendable seul : bundle avec 5 Nihil Zero à 30 €</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="C32" s="6">
+        <f>$B32</f>
+        <v/>
+      </c>
+      <c r="D32" s="7">
         <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="6">
         <f>CEILING($D32*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F32" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="G32" s="18">
+      <c r="F32" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G32" s="8">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
         <v/>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="9">
         <f>IF($G32="","",$G32/$C32)</f>
         <v/>
       </c>
-      <c r="I32" s="20" t="n">
+      <c r="I32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="6">
         <f>$C32/$I32</f>
         <v/>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="6">
         <f>IF($F32="","",$F32/$I32)</f>
         <v/>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="6">
         <f>IF($G32="","",$G32/$I32)</f>
         <v/>
       </c>
-      <c r="M32" s="17">
+      <c r="M32" s="7">
         <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N32" s="16" t="n">
+      <c r="N32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="P32" s="21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q32" s="22" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R32" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S32" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T32" s="22" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="U32" s="14" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V32" s="14" t="inlineStr"/>
-      <c r="W32" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X32" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y32" s="14" t="n">
+      <c r="O32" s="13" t="n"/>
+      <c r="P32" s="13" t="n"/>
+      <c r="Q32" s="12" t="inlineStr">
+        <is>
+          <t>Meccha Japan</t>
+        </is>
+      </c>
+      <c r="R32" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S32" s="12" t="inlineStr">
+        <is>
+          <t>#FA429713</t>
+        </is>
+      </c>
+      <c r="T32" s="12" t="inlineStr">
+        <is>
+          <t>4521329431925</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin, bundle</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X32" s="4" t="inlineStr"/>
+      <c r="Y32" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
+          <t>Booster Box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters — 5 lots de 5 à 17 €, le 6e part en bundle</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>51.12</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="C33" s="6">
-        <f>$B33+$Y33*Paramètres!$B$13</f>
+        <f>$B33</f>
         <v/>
       </c>
       <c r="D33" s="7">
@@ -3382,7 +3382,7 @@
         <v/>
       </c>
       <c r="F33" s="8" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="G33" s="8">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="I33" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J33" s="6">
         <f>$C33/$I33</f>
@@ -3414,15 +3414,11 @@
       <c r="N33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="P33" s="11" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="O33" s="13" t="n"/>
+      <c r="P33" s="13" t="n"/>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R33" s="12" t="inlineStr">
@@ -3432,430 +3428,430 @@
       </c>
       <c r="S33" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4521329432274</t>
         </is>
       </c>
       <c r="U33" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Leboncoin, lots de 5</t>
         </is>
       </c>
       <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>Liquider</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="C34" s="6">
+        <f>$B34+$Y34*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D34" s="7">
+        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E34" s="6">
+        <f>CEILING($D34*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="G34" s="8">
+        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="9">
+        <f>IF($G34="","",$G34/$C34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="10" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="J34" s="6">
+        <f>$C34/$I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="6">
+        <f>IF($F34="","",$F34/$I34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="6">
+        <f>IF($G34="","",$G34/$I34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="7">
+        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P34" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q34" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S34" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T34" s="12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X34" s="4" t="inlineStr"/>
+      <c r="Y34" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
+      <c r="B35" s="15" t="n">
         <v>63</v>
       </c>
-      <c r="C34" s="16">
-        <f>$B34+$Y34*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D34" s="17">
-        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E34" s="16">
-        <f>CEILING($D34*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F34" s="18" t="n">
+      <c r="C35" s="16">
+        <f>$B35+$Y35*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>CEILING($D35*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="G34" s="18">
-        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="19">
-        <f>IF($G34="","",$G34/$C34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="20" t="n">
+      <c r="G35" s="18">
+        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="19">
+        <f>IF($G35="","",$G35/$C35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="16">
-        <f>$C34/$I34</f>
-        <v/>
-      </c>
-      <c r="K34" s="16">
-        <f>IF($F34="","",$F34/$I34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="16">
-        <f>IF($G34="","",$G34/$I34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="17">
-        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N34" s="16" t="n">
+      <c r="J35" s="16">
+        <f>$C35/$I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="16">
+        <f>IF($F35="","",$F35/$I35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="16">
+        <f>IF($G35="","",$G35/$I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="17">
+        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="21" t="n">
+      <c r="O35" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="P34" s="21" t="n">
+      <c r="P35" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="Q34" s="22" t="inlineStr">
+      <c r="Q35" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R34" s="22" t="inlineStr">
+      <c r="R35" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S34" s="22" t="inlineStr">
+      <c r="S35" s="22" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="T34" s="22" t="inlineStr">
+      <c r="T35" s="22" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="U34" s="14" t="inlineStr">
+      <c r="U35" s="14" t="inlineStr">
         <is>
           <t>vendu</t>
         </is>
       </c>
-      <c r="V34" s="14" t="inlineStr"/>
-      <c r="W34" s="14" t="inlineStr">
+      <c r="V35" s="14" t="inlineStr"/>
+      <c r="W35" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X34" s="14" t="inlineStr">
+      <c r="X35" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="Y34" s="14" t="n">
+      <c r="Y35" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B36" s="5" t="n">
         <v>38.34</v>
       </c>
-      <c r="C35" s="6">
-        <f>$B35+$Y35*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D35" s="7">
-        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E35" s="6">
-        <f>CEILING($D35*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F35" s="8" t="n">
+      <c r="C36" s="6">
+        <f>$B36+$Y36*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D36" s="7">
+        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E36" s="6">
+        <f>CEILING($D36*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="G35" s="8">
-        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="9">
-        <f>IF($G35="","",$G35/$C35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="10" t="n">
+      <c r="G36" s="8">
+        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="9">
+        <f>IF($G36="","",$G36/$C36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="6">
-        <f>$C35/$I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="6">
-        <f>IF($F35="","",$F35/$I35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="6">
-        <f>IF($G35="","",$G35/$I35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="7">
-        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N35" s="6" t="n">
+      <c r="J36" s="6">
+        <f>$C36/$I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="6">
+        <f>IF($F36="","",$F36/$I36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="6">
+        <f>IF($G36="","",$G36/$I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="7">
+        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="11" t="n">
+      <c r="O36" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="P35" s="11" t="n">
+      <c r="P36" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="Q35" s="12" t="inlineStr">
+      <c r="Q36" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R35" s="12" t="inlineStr">
+      <c r="R36" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S35" s="12" t="inlineStr">
+      <c r="S36" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T35" s="12" t="inlineStr">
+      <c r="T36" s="12" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="U35" s="4" t="inlineStr">
+      <c r="U36" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="V35" s="4" t="inlineStr"/>
-      <c r="W35" s="4" t="inlineStr">
+      <c r="V36" s="4" t="inlineStr"/>
+      <c r="W36" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="X35" s="4" t="inlineStr"/>
-      <c r="Y35" s="4" t="n">
+      <c r="X36" s="4" t="inlineStr"/>
+      <c r="Y36" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
+      <c r="B37" s="15" t="n">
         <v>25.2</v>
       </c>
-      <c r="C36" s="16">
-        <f>$B36+$Y36*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D36" s="17">
-        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E36" s="16">
-        <f>CEILING($D36*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F36" s="18" t="n">
+      <c r="C37" s="16">
+        <f>$B37+$Y37*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E37" s="16">
+        <f>CEILING($D37*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="G36" s="18">
-        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="19">
-        <f>IF($G36="","",$G36/$C36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="20" t="n">
+      <c r="G37" s="18">
+        <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="19">
+        <f>IF($G37="","",$G37/$C37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="16">
-        <f>$C36/$I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="16">
-        <f>IF($F36="","",$F36/$I36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="16">
-        <f>IF($G36="","",$G36/$I36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="17">
-        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N36" s="16" t="n">
+      <c r="J37" s="16">
+        <f>$C37/$I37</f>
+        <v/>
+      </c>
+      <c r="K37" s="16">
+        <f>IF($F37="","",$F37/$I37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="16">
+        <f>IF($G37="","",$G37/$I37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="17">
+        <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="21" t="n">
+      <c r="O37" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="P36" s="21" t="n">
+      <c r="P37" s="21" t="n">
         <v>5.2</v>
       </c>
-      <c r="Q36" s="22" t="inlineStr">
+      <c r="Q37" s="22" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R36" s="22" t="inlineStr">
+      <c r="R37" s="22" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S36" s="22" t="inlineStr">
+      <c r="S37" s="22" t="inlineStr">
         <is>
           <t>FB2026-43717</t>
         </is>
       </c>
-      <c r="T36" s="22" t="inlineStr">
+      <c r="T37" s="22" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="U36" s="14" t="inlineStr">
+      <c r="U37" s="14" t="inlineStr">
         <is>
           <t>vendu</t>
         </is>
       </c>
-      <c r="V36" s="14" t="inlineStr"/>
-      <c r="W36" s="14" t="inlineStr">
+      <c r="V37" s="14" t="inlineStr"/>
+      <c r="W37" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X36" s="14" t="inlineStr">
+      <c r="X37" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="Y36" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="C37" s="6">
-        <f>$B37+$Y37*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D37" s="7">
-        <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E37" s="6">
-        <f>CEILING($D37*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G37" s="8">
-        <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="9">
-        <f>IF($G37="","",$G37/$C37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="6">
-        <f>$C37/$I37</f>
-        <v/>
-      </c>
-      <c r="K37" s="6">
-        <f>IF($F37="","",$F37/$I37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="6">
-        <f>IF($G37="","",$G37/$I37)</f>
-        <v/>
-      </c>
-      <c r="M37" s="7">
-        <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="P37" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q37" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R37" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S37" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T37" s="12" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="U37" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V37" s="4" t="inlineStr"/>
-      <c r="W37" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X37" s="4" t="inlineStr"/>
-      <c r="Y37" s="4" t="n">
+      <c r="Y37" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
+          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>52.4</v>
+        <v>51.12</v>
       </c>
       <c r="C38" s="6">
         <f>$B38+$Y38*Paramètres!$B$13</f>
@@ -3903,10 +3899,10 @@
         <v>0</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P38" s="11" t="n">
-        <v>10.66</v>
+        <v>10.4</v>
       </c>
       <c r="Q38" s="12" t="inlineStr">
         <is>
@@ -3925,12 +3921,12 @@
       </c>
       <c r="T38" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>156</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="V38" s="4" t="inlineStr"/>
@@ -3945,301 +3941,305 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="C39" s="6">
+        <f>$B39+$Y39*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D39" s="7">
+        <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E39" s="6">
+        <f>CEILING($D39*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G39" s="8">
+        <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="9">
+        <f>IF($G39="","",$G39/$C39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="6">
+        <f>$C39/$I39</f>
+        <v/>
+      </c>
+      <c r="K39" s="6">
+        <f>IF($F39="","",$F39/$I39)</f>
+        <v/>
+      </c>
+      <c r="L39" s="6">
+        <f>IF($G39="","",$G39/$I39)</f>
+        <v/>
+      </c>
+      <c r="M39" s="7">
+        <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="Q39" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R39" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S39" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T39" s="12" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr"/>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X39" s="4" t="inlineStr"/>
+      <c r="Y39" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
+      <c r="B40" s="15" t="n">
         <v>57.51</v>
       </c>
-      <c r="C39" s="16">
-        <f>$B39+$Y39*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D39" s="17">
-        <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E39" s="16">
-        <f>CEILING($D39*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F39" s="18" t="n">
+      <c r="C40" s="16">
+        <f>$B40+$Y40*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D40" s="17">
+        <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E40" s="16">
+        <f>CEILING($D40*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F40" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="G39" s="18">
-        <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
-        <v/>
-      </c>
-      <c r="H39" s="19">
-        <f>IF($G39="","",$G39/$C39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="20" t="n">
+      <c r="G40" s="18">
+        <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="19">
+        <f>IF($G40="","",$G40/$C40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="16">
-        <f>$C39/$I39</f>
-        <v/>
-      </c>
-      <c r="K39" s="16">
-        <f>IF($F39="","",$F39/$I39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="16">
-        <f>IF($G39="","",$G39/$I39)</f>
-        <v/>
-      </c>
-      <c r="M39" s="17">
-        <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N39" s="16" t="n">
+      <c r="J40" s="16">
+        <f>$C40/$I40</f>
+        <v/>
+      </c>
+      <c r="K40" s="16">
+        <f>IF($F40="","",$F40/$I40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="16">
+        <f>IF($G40="","",$G40/$I40)</f>
+        <v/>
+      </c>
+      <c r="M40" s="17">
+        <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="21" t="n">
+      <c r="O40" s="21" t="n">
         <v>45</v>
       </c>
-      <c r="P39" s="21" t="n">
+      <c r="P40" s="21" t="n">
         <v>11.7</v>
       </c>
-      <c r="Q39" s="22" t="inlineStr">
+      <c r="Q40" s="22" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R39" s="22" t="inlineStr">
+      <c r="R40" s="22" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S39" s="22" t="inlineStr">
+      <c r="S40" s="22" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T39" s="22" t="inlineStr">
+      <c r="T40" s="22" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="U39" s="14" t="inlineStr">
+      <c r="U40" s="14" t="inlineStr">
         <is>
           <t>vendu</t>
         </is>
       </c>
-      <c r="V39" s="14" t="inlineStr"/>
-      <c r="W39" s="14" t="inlineStr">
+      <c r="V40" s="14" t="inlineStr"/>
+      <c r="W40" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X39" s="14" t="inlineStr">
+      <c r="X40" s="14" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="Y39" s="14" t="n">
+      <c r="Y40" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B40" s="24" t="n">
+      <c r="B41" s="24" t="n">
         <v>38.34</v>
       </c>
-      <c r="C40" s="25">
-        <f>$B40+$Y40*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D40" s="26">
-        <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E40" s="25">
-        <f>CEILING($D40*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F40" s="27" t="n">
+      <c r="C41" s="25">
+        <f>$B41+$Y41*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D41" s="26">
+        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E41" s="25">
+        <f>CEILING($D41*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="G40" s="27">
-        <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
-        <v/>
-      </c>
-      <c r="H40" s="28">
-        <f>IF($G40="","",$G40/$C40)</f>
-        <v/>
-      </c>
-      <c r="I40" s="29" t="n">
+      <c r="G41" s="27">
+        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="28">
+        <f>IF($G41="","",$G41/$C41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="J40" s="25">
-        <f>$C40/$I40</f>
-        <v/>
-      </c>
-      <c r="K40" s="25">
-        <f>IF($F40="","",$F40/$I40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="25">
-        <f>IF($G40="","",$G40/$I40)</f>
-        <v/>
-      </c>
-      <c r="M40" s="26">
-        <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N40" s="25" t="n">
+      <c r="J41" s="25">
+        <f>$C41/$I41</f>
+        <v/>
+      </c>
+      <c r="K41" s="25">
+        <f>IF($F41="","",$F41/$I41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="25">
+        <f>IF($G41="","",$G41/$I41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="26">
+        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N41" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="30" t="n">
+      <c r="O41" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="P40" s="30" t="n">
+      <c r="P41" s="30" t="n">
         <v>7.8</v>
       </c>
-      <c r="Q40" s="31" t="inlineStr">
+      <c r="Q41" s="31" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R40" s="31" t="inlineStr">
+      <c r="R41" s="31" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S40" s="31" t="inlineStr">
+      <c r="S41" s="31" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="T40" s="31" t="inlineStr">
+      <c r="T41" s="31" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="U40" s="23" t="inlineStr">
+      <c r="U41" s="23" t="inlineStr">
         <is>
           <t>Leboncoin + eBay, en lot</t>
         </is>
       </c>
-      <c r="V40" s="23" t="inlineStr"/>
-      <c r="W40" s="23" t="inlineStr">
+      <c r="V41" s="23" t="inlineStr"/>
+      <c r="W41" s="23" t="inlineStr">
         <is>
           <t>Marge faible</t>
         </is>
       </c>
-      <c r="X40" s="23" t="inlineStr"/>
-      <c r="Y40" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Boosters Pokémon MEGA Storm Emeralda M6 ×2 — 5 cartes chacun — prix à confirmer avant publication</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>12.74</v>
-      </c>
-      <c r="C41" s="6">
-        <f>$B41</f>
-        <v/>
-      </c>
-      <c r="D41" s="7">
-        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E41" s="6">
-        <f>CEILING($D41*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="G41" s="8">
-        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="9">
-        <f>IF($G41="","",$G41/$C41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="6">
-        <f>$C41/$I41</f>
-        <v/>
-      </c>
-      <c r="K41" s="6">
-        <f>IF($F41="","",$F41/$I41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="6">
-        <f>IF($G41="","",$G41/$I41)</f>
-        <v/>
-      </c>
-      <c r="M41" s="7">
-        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="13" t="n"/>
-      <c r="P41" s="13" t="n"/>
-      <c r="Q41" s="12" t="inlineStr">
-        <is>
-          <t>Meccha Japan</t>
-        </is>
-      </c>
-      <c r="R41" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S41" s="12" t="inlineStr">
-        <is>
-          <t>#FA429713</t>
-        </is>
-      </c>
-      <c r="T41" s="12" t="inlineStr">
-        <is>
-          <t>4521329462226</t>
-        </is>
-      </c>
-      <c r="U41" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin, lot de 2</t>
-        </is>
-      </c>
-      <c r="V41" s="4" t="inlineStr"/>
-      <c r="W41" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X41" s="4" t="inlineStr"/>
-      <c r="Y41" s="4" t="n">
+      <c r="X41" s="23" t="inlineStr"/>
+      <c r="Y41" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes — prix à confirmer avant publication</t>
+          <t>Boosters Pokémon MEGA Storm Emeralda M6 ×2 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>12.95</v>
+        <v>12.74</v>
       </c>
       <c r="C42" s="6">
         <f>$B42</f>
@@ -4254,7 +4254,7 @@
         <v/>
       </c>
       <c r="F42" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G42" s="8">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
@@ -4305,12 +4305,12 @@
       </c>
       <c r="T42" s="12" t="inlineStr">
         <is>
-          <t>4521329431925</t>
+          <t>4521329462226</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, à l'unité</t>
+          <t>Leboncoin, lot de 2</t>
         </is>
       </c>
       <c r="V42" s="4" t="inlineStr"/>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$Y$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$Y$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -156,7 +156,6 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +174,7 @@
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1618,18 +1618,18 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Lot de 3 pompes immergées ROBBY VP550W — 1 prélevée usage personnel, 2 à vendre</t>
+          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>45</v>
+        <v>37.8</v>
       </c>
       <c r="C15" s="6">
-        <f>$B15</f>
+        <f>$B15+$Y15*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E15" s="6">
@@ -1637,7 +1637,7 @@
         <v/>
       </c>
       <c r="F15" s="8" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G15" s="8">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
@@ -1648,7 +1648,7 @@
         <v/>
       </c>
       <c r="I15" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="6">
         <f>$C15/$I15</f>
@@ -1666,34 +1666,39 @@
         <f>IF($F15="","",$F15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="13" t="n"/>
-      <c r="P15" s="13" t="n"/>
+      <c r="N15" s="6">
+        <f>IF($F15="","",$F15*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>7.8</v>
+      </c>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>ADN (facture à retrouver)</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>434</t>
         </is>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
@@ -1704,214 +1709,214 @@
       </c>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="C16" s="15">
         <f>$B16+$Y16*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D16" s="7">
-        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="E16" s="6">
+      <c r="D16" s="16">
+        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
         <f>CEILING($D16*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="G16" s="8">
+      <c r="F16" s="17" t="n">
+        <v>168</v>
+      </c>
+      <c r="G16" s="17">
         <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
         <v/>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="18">
         <f>IF($G16="","",$G16/$C16)</f>
         <v/>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" s="15">
+        <f>$C16/$I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="15">
+        <f>IF($F16="","",$F16/$I16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="15">
+        <f>IF($G16="","",$G16/$I16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="16">
+        <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="P16" s="20" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R16" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S16" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-5844</t>
+        </is>
+      </c>
+      <c r="T16" s="21" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="U16" s="13" t="inlineStr">
+        <is>
+          <t>Leboncoin, à l'unité</t>
+        </is>
+      </c>
+      <c r="V16" s="13" t="inlineStr"/>
+      <c r="W16" s="13" t="inlineStr">
+        <is>
+          <t>URGENT — 2 sur 12 vendues</t>
+        </is>
+      </c>
+      <c r="X16" s="13" t="inlineStr">
+        <is>
+          <t>2 vendues</t>
+        </is>
+      </c>
+      <c r="Y16" s="13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C17" s="6">
+        <f>$B17+$Y17*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D17" s="7">
+        <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E17" s="6">
+        <f>CEILING($D17*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="G17" s="8">
+        <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>IF($G17="","",$G17/$C17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="6">
-        <f>$C16/$I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="6">
-        <f>IF($F16="","",$F16/$I16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="6">
-        <f>IF($G16="","",$G16/$I16)</f>
-        <v/>
-      </c>
-      <c r="M16" s="7">
-        <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N16" s="6">
-        <f>IF($F16="","",$F16*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O16" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P16" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q16" s="12" t="inlineStr">
+      <c r="J17" s="6">
+        <f>$C17/$I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="6">
+        <f>IF($F17="","",$F17/$I17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="6">
+        <f>IF($G17="","",$G17/$I17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="7">
+        <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N17" s="6">
+        <f>IF($F17="","",$F17*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q17" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R16" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S16" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T16" s="12" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
+      <c r="R17" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S17" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-44194</t>
+        </is>
+      </c>
+      <c r="T17" s="12" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
         <is>
           <t>Boutique</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="n">
+      <c r="X17" s="4" t="inlineStr"/>
+      <c r="Y17" s="4" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="C17" s="16">
-        <f>$B17+$Y17*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D17" s="17">
-        <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E17" s="16">
-        <f>CEILING($D17*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>168</v>
-      </c>
-      <c r="G17" s="18">
-        <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="19">
-        <f>IF($G17="","",$G17/$C17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" s="16">
-        <f>$C17/$I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="16">
-        <f>IF($F17="","",$F17/$I17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="16">
-        <f>IF($G17="","",$G17/$I17)</f>
-        <v/>
-      </c>
-      <c r="M17" s="17">
-        <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="P17" s="21" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q17" s="22" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R17" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S17" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-5844</t>
-        </is>
-      </c>
-      <c r="T17" s="22" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="U17" s="14" t="inlineStr">
-        <is>
-          <t>Leboncoin, à l'unité</t>
-        </is>
-      </c>
-      <c r="V17" s="14" t="inlineStr"/>
-      <c r="W17" s="14" t="inlineStr">
-        <is>
-          <t>URGENT — 2 sur 12 vendues</t>
-        </is>
-      </c>
-      <c r="X17" s="14" t="inlineStr">
-        <is>
-          <t>2 vendues</t>
-        </is>
-      </c>
-      <c r="Y17" s="14" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
+          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>50.4</v>
+        <v>31.95</v>
       </c>
       <c r="C18" s="6">
         <f>$B18+$Y18*Paramètres!$B$13</f>
@@ -1926,7 +1931,7 @@
         <v/>
       </c>
       <c r="F18" s="8" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G18" s="8">
         <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
@@ -1960,14 +1965,14 @@
         <v/>
       </c>
       <c r="O18" s="11" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="P18" s="11" t="n">
-        <v>10.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R18" s="12" t="inlineStr">
@@ -1977,17 +1982,17 @@
       </c>
       <c r="S18" s="12" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T18" s="12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr"/>
@@ -2004,18 +2009,18 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
+          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>31.95</v>
+        <v>25.2</v>
       </c>
       <c r="C19" s="6">
         <f>$B19+$Y19*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E19" s="6">
@@ -2023,7 +2028,7 @@
         <v/>
       </c>
       <c r="F19" s="8" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G19" s="8">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
@@ -2052,39 +2057,38 @@
         <f>IF($F19="","",$F19*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N19" s="6">
-        <f>IF($F19="","",$F19*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O19" s="11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P19" s="11" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>439</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
@@ -2101,18 +2105,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
+          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>25.2</v>
+        <v>25.56</v>
       </c>
       <c r="C20" s="6">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E20" s="6">
@@ -2149,8 +2153,9 @@
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>0</v>
+      <c r="N20" s="6">
+        <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O20" s="11" t="n">
         <v>20</v>
@@ -2160,27 +2165,27 @@
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
@@ -2197,18 +2202,18 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
+          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>25.56</v>
+        <v>57.51</v>
       </c>
       <c r="C21" s="6">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E21" s="6">
@@ -2216,7 +2221,7 @@
         <v/>
       </c>
       <c r="F21" s="8" t="n">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G21" s="8">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
@@ -2245,15 +2250,14 @@
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6">
-        <f>IF($F21="","",$F21*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>5.2</v>
+        <v>11.7</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
@@ -2267,17 +2271,17 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>159</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
@@ -2294,11 +2298,11 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
+          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>57.51</v>
+        <v>37.8</v>
       </c>
       <c r="C22" s="6">
         <f>$B22+$Y22*Paramètres!$B$13</f>
@@ -2313,7 +2317,7 @@
         <v/>
       </c>
       <c r="F22" s="8" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G22" s="8">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
@@ -2324,7 +2328,7 @@
         <v/>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" s="6">
         <f>$C22/$I22</f>
@@ -2346,254 +2350,254 @@
         <v>0</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R22" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-43717</t>
         </is>
       </c>
       <c r="T22" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="C23" s="24">
+        <f>$B23+$Y23*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D23" s="25">
+        <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>CEILING($D23*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="G23" s="26">
+        <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="27">
+        <f>IF($G23="","",$G23/$C23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="24">
+        <f>$C23/$I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="24">
+        <f>IF($F23="","",$F23/$I23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="24">
+        <f>IF($G23="","",$G23/$I23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="25">
+        <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N23" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="P23" s="29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q23" s="30" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R23" s="30" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S23" s="30" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T23" s="30" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="U23" s="22" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V23" s="22" t="inlineStr"/>
+      <c r="W23" s="22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X23" s="22" t="inlineStr"/>
+      <c r="Y23" s="22" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C23" s="6">
-        <f>$B23+$Y23*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D23" s="7">
-        <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E23" s="6">
-        <f>CEILING($D23*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="G23" s="8">
-        <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>IF($G23="","",$G23/$C23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="6">
-        <f>$C23/$I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="6">
-        <f>IF($F23="","",$F23/$I23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="6">
-        <f>IF($G23="","",$G23/$I23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="7">
-        <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N23" s="6" t="n">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>GEOX baskets P.35 — neuves</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="C24" s="6">
+        <f>$B24+$Y24*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D24" s="7">
+        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E24" s="6">
+        <f>CEILING($D24*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="G24" s="8">
+        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>IF($G24="","",$G24/$C24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="6">
+        <f>$C24/$I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="6">
+        <f>IF($F24="","",$F24/$I24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="6">
+        <f>IF($G24="","",$G24/$I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="7">
+        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P23" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q23" s="12" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R23" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S23" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T23" s="12" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr"/>
-      <c r="W23" s="4" t="inlineStr">
-        <is>
-          <t>URGENT — saisonnier</t>
-        </is>
-      </c>
-      <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="C24" s="25">
-        <f>$B24+$Y24*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D24" s="26">
-        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E24" s="25">
-        <f>CEILING($D24*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="G24" s="27">
-        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="28">
-        <f>IF($G24="","",$G24/$C24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="25">
-        <f>$C24/$I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="25">
-        <f>IF($F24="","",$F24/$I24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="25">
-        <f>IF($G24="","",$G24/$I24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="26">
-        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="P24" s="30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q24" s="31" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R24" s="31" t="inlineStr">
+      <c r="O24" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="Q24" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R24" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S24" s="31" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T24" s="31" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="U24" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay, en lot</t>
-        </is>
-      </c>
-      <c r="V24" s="23" t="inlineStr"/>
-      <c r="W24" s="23" t="inlineStr">
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T24" s="12" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X24" s="23" t="inlineStr"/>
-      <c r="Y24" s="23" t="n">
+      <c r="X24" s="4" t="inlineStr"/>
+      <c r="Y24" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>GEOX baskets P.35 — neuves</t>
+          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>21.73</v>
+        <v>50.4</v>
       </c>
       <c r="C25" s="6">
         <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E25" s="6">
@@ -2601,7 +2605,7 @@
         <v/>
       </c>
       <c r="F25" s="8" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="G25" s="8">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
@@ -2630,44 +2634,45 @@
         <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N25" s="6" t="n">
-        <v>0</v>
+      <c r="N25" s="6">
+        <f>IF($F25="","",$F25*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O25" s="11" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>4.42</v>
+        <v>10.4</v>
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R25" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>408</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X25" s="4" t="inlineStr"/>
@@ -2678,18 +2683,18 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
+          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>50.4</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="C26" s="6">
         <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E26" s="6">
@@ -2697,7 +2702,7 @@
         <v/>
       </c>
       <c r="F26" s="8" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="G26" s="8">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
@@ -2726,15 +2731,14 @@
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6">
-        <f>IF($F26="","",$F26*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N26" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O26" s="11" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P26" s="11" t="n">
-        <v>10.4</v>
+        <v>15.6</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
@@ -2753,18 +2757,18 @@
       </c>
       <c r="T26" s="12" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>199</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Liquider</t>
         </is>
       </c>
       <c r="X26" s="4" t="inlineStr"/>
@@ -2773,509 +2777,505 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="C27" s="15">
         <f>$B27+$Y27*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="16">
         <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="15">
         <f>CEILING($D27*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="G27" s="8">
+      <c r="F27" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G27" s="17">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
         <v/>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="18">
         <f>IF($G27="","",$G27/$C27)</f>
         <v/>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I27" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="15">
         <f>$C27/$I27</f>
         <v/>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="15">
         <f>IF($F27="","",$F27/$I27)</f>
         <v/>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="15">
         <f>IF($G27="","",$G27/$I27)</f>
         <v/>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="16">
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="11" t="n">
+      <c r="O27" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="P27" s="11" t="n">
+      <c r="P27" s="20" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q27" s="12" t="inlineStr">
+      <c r="Q27" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R27" s="12" t="inlineStr">
+      <c r="R27" s="21" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S27" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T27" s="21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U27" s="13" t="inlineStr">
+        <is>
+          <t>Vinted, Italie — non encaissé</t>
+        </is>
+      </c>
+      <c r="V27" s="13" t="inlineStr"/>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>VENDUE, en attente</t>
+        </is>
+      </c>
+      <c r="X27" s="13" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="Y27" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="C28" s="15">
+        <f>$B28+$Y28*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D28" s="16">
+        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
+        <f>CEILING($D28*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>135</v>
+      </c>
+      <c r="G28" s="17">
+        <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="18">
+        <f>IF($G28="","",$G28/$C28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="15">
+        <f>$C28/$I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="15">
+        <f>IF($F28="","",$F28/$I28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="15">
+        <f>IF($G28="","",$G28/$I28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="16">
+        <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="P28" s="20" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q28" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R28" s="21" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S28" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-44194</t>
+        </is>
+      </c>
+      <c r="T28" s="21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U28" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V28" s="13" t="inlineStr"/>
+      <c r="W28" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X28" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y28" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C29" s="15">
+        <f>$B29+$Y29*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D29" s="16">
+        <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E29" s="15">
+        <f>CEILING($D29*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G29" s="17">
+        <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="18">
+        <f>IF($G29="","",$G29/$C29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="15">
+        <f>$C29/$I29</f>
+        <v/>
+      </c>
+      <c r="K29" s="15">
+        <f>IF($F29="","",$F29/$I29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="15">
+        <f>IF($G29="","",$G29/$I29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="16">
+        <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="P29" s="20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q29" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R29" s="21" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S27" s="12" t="inlineStr">
+      <c r="S29" s="21" t="inlineStr">
         <is>
           <t>FB2026-43716</t>
         </is>
       </c>
-      <c r="T27" s="12" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr"/>
-      <c r="W27" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="4" t="n">
+      <c r="T29" s="21" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="U29" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V29" s="13" t="inlineStr"/>
+      <c r="W29" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X29" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y29" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>76.68000000000001</v>
-      </c>
-      <c r="C28" s="16">
-        <f>$B28+$Y28*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D28" s="17">
-        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E28" s="16">
-        <f>CEILING($D28*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="G28" s="18">
-        <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="19">
-        <f>IF($G28="","",$G28/$C28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="20" t="n">
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C30" s="15">
+        <f>$B30+$Y30*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D30" s="16">
+        <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E30" s="15">
+        <f>CEILING($D30*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G30" s="17">
+        <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="18">
+        <f>IF($G30="","",$G30/$C30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="16">
-        <f>$C28/$I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="16">
-        <f>IF($F28="","",$F28/$I28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="16">
-        <f>IF($G28="","",$G28/$I28)</f>
-        <v/>
-      </c>
-      <c r="M28" s="17">
-        <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N28" s="16" t="n">
+      <c r="J30" s="15">
+        <f>$C30/$I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="15">
+        <f>IF($F30="","",$F30/$I30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="15">
+        <f>IF($G30="","",$G30/$I30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="16">
+        <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="Q28" s="22" t="inlineStr">
+      <c r="O30" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="P30" s="20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q30" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R28" s="22" t="inlineStr">
+      <c r="R30" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S30" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T30" s="21" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="U30" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V30" s="13" t="inlineStr"/>
+      <c r="W30" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X30" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y30" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes — invendable seul : bundle avec 5 Nihil Zero à 30 €</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="C31" s="6">
+        <f>$B31</f>
+        <v/>
+      </c>
+      <c r="D31" s="7">
+        <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E31" s="6">
+        <f>CEILING($D31*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" s="8">
+        <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>IF($G31="","",$G31/$C31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="6">
+        <f>$C31/$I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="6">
+        <f>IF($F31="","",$F31/$I31)</f>
+        <v/>
+      </c>
+      <c r="L31" s="6">
+        <f>IF($G31="","",$G31/$I31)</f>
+        <v/>
+      </c>
+      <c r="M31" s="7">
+        <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="31" t="n"/>
+      <c r="P31" s="31" t="n"/>
+      <c r="Q31" s="12" t="inlineStr">
+        <is>
+          <t>Meccha Japan</t>
+        </is>
+      </c>
+      <c r="R31" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S28" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T28" s="22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="U28" s="14" t="inlineStr">
-        <is>
-          <t>Vinted, Italie — non encaissé</t>
-        </is>
-      </c>
-      <c r="V28" s="14" t="inlineStr"/>
-      <c r="W28" s="14" t="inlineStr">
-        <is>
-          <t>VENDUE, en attente</t>
-        </is>
-      </c>
-      <c r="X28" s="14" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="Y28" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>113.4</v>
-      </c>
-      <c r="C29" s="16">
-        <f>$B29+$Y29*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D29" s="17">
-        <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E29" s="16">
-        <f>CEILING($D29*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>135</v>
-      </c>
-      <c r="G29" s="18">
-        <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="19">
-        <f>IF($G29="","",$G29/$C29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="16">
-        <f>$C29/$I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="16">
-        <f>IF($F29="","",$F29/$I29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="16">
-        <f>IF($G29="","",$G29/$I29)</f>
-        <v/>
-      </c>
-      <c r="M29" s="17">
-        <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="P29" s="21" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Q29" s="22" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R29" s="22" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S29" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-44194</t>
-        </is>
-      </c>
-      <c r="T29" s="22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U29" s="14" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V29" s="14" t="inlineStr"/>
-      <c r="W29" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X29" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y29" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C30" s="16">
-        <f>$B30+$Y30*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D30" s="17">
-        <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E30" s="16">
-        <f>CEILING($D30*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="G30" s="18">
-        <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="19">
-        <f>IF($G30="","",$G30/$C30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="16">
-        <f>$C30/$I30</f>
-        <v/>
-      </c>
-      <c r="K30" s="16">
-        <f>IF($F30="","",$F30/$I30)</f>
-        <v/>
-      </c>
-      <c r="L30" s="16">
-        <f>IF($G30="","",$G30/$I30)</f>
-        <v/>
-      </c>
-      <c r="M30" s="17">
-        <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="P30" s="21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q30" s="22" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R30" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S30" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T30" s="22" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="U30" s="14" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V30" s="14" t="inlineStr"/>
-      <c r="W30" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X30" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y30" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C31" s="16">
-        <f>$B31+$Y31*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D31" s="17">
-        <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E31" s="16">
-        <f>CEILING($D31*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="G31" s="18">
-        <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="19">
-        <f>IF($G31="","",$G31/$C31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="16">
-        <f>$C31/$I31</f>
-        <v/>
-      </c>
-      <c r="K31" s="16">
-        <f>IF($F31="","",$F31/$I31)</f>
-        <v/>
-      </c>
-      <c r="L31" s="16">
-        <f>IF($G31="","",$G31/$I31)</f>
-        <v/>
-      </c>
-      <c r="M31" s="17">
-        <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="P31" s="21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q31" s="22" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R31" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S31" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T31" s="22" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="U31" s="14" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V31" s="14" t="inlineStr"/>
-      <c r="W31" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X31" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y31" s="14" t="n">
+      <c r="S31" s="12" t="inlineStr">
+        <is>
+          <t>#FA429713</t>
+        </is>
+      </c>
+      <c r="T31" s="12" t="inlineStr">
+        <is>
+          <t>4521329431925</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin, bundle</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X31" s="4" t="inlineStr"/>
+      <c r="Y31" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes — invendable seul : bundle avec 5 Nihil Zero à 30 €</t>
+          <t>Booster Box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters — 5 lots de 5 à 17 €, le 6e part en bundle</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>12.95</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="C32" s="6">
         <f>$B32</f>
@@ -3290,7 +3290,7 @@
         <v/>
       </c>
       <c r="F32" s="8" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="G32" s="8">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="I32" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J32" s="6">
         <f>$C32/$I32</f>
@@ -3322,8 +3322,8 @@
       <c r="N32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="13" t="n"/>
-      <c r="P32" s="13" t="n"/>
+      <c r="O32" s="31" t="n"/>
+      <c r="P32" s="31" t="n"/>
       <c r="Q32" s="12" t="inlineStr">
         <is>
           <t>Meccha Japan</t>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="T32" s="12" t="inlineStr">
         <is>
-          <t>4521329431925</t>
+          <t>4521329432274</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, bundle</t>
+          <t>Leboncoin, lots de 5</t>
         </is>
       </c>
       <c r="V32" s="4" t="inlineStr"/>
@@ -3357,20 +3357,20 @@
       </c>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Booster Box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters — 5 lots de 5 à 17 €, le 6e part en bundle</t>
+          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>51.12</v>
       </c>
       <c r="C33" s="6">
-        <f>$B33</f>
+        <f>$B33+$Y33*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D33" s="7">
@@ -3382,7 +3382,7 @@
         <v/>
       </c>
       <c r="F33" s="8" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G33" s="8">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="I33" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J33" s="6">
         <f>$C33/$I33</f>
@@ -3414,11 +3414,15 @@
       <c r="N33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="13" t="n"/>
-      <c r="P33" s="13" t="n"/>
+      <c r="O33" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P33" s="11" t="n">
+        <v>10.4</v>
+      </c>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R33" s="12" t="inlineStr">
@@ -3428,430 +3432,430 @@
       </c>
       <c r="S33" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>4521329432274</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U33" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lots de 5</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Liquider</t>
         </is>
       </c>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Baskets HOKA P.37 1/3 — neuves</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="C34" s="15">
+        <f>$B34+$Y34*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D34" s="16">
+        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E34" s="15">
+        <f>CEILING($D34*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="G34" s="17">
+        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f>IF($G34="","",$G34/$C34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="15">
+        <f>$C34/$I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="15">
+        <f>IF($F34="","",$F34/$I34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="15">
+        <f>IF($G34="","",$G34/$I34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="16">
+        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="P34" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q34" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R34" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S34" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T34" s="21" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="U34" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V34" s="13" t="inlineStr"/>
+      <c r="W34" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X34" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y34" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE sneakers P.38 — neuves</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C35" s="6">
+        <f>$B35+$Y35*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D35" s="7">
+        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E35" s="6">
+        <f>CEILING($D35*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="G35" s="8">
+        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="9">
+        <f>IF($G35="","",$G35/$C35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="6">
+        <f>$C35/$I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="6">
+        <f>IF($F35="","",$F35/$I35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="6">
+        <f>IF($G35="","",$G35/$I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="7">
+        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q35" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S35" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T35" s="12" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X35" s="4" t="inlineStr"/>
+      <c r="Y35" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C36" s="15">
+        <f>$B36+$Y36*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D36" s="16">
+        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
+        <f>CEILING($D36*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G36" s="17">
+        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="18">
+        <f>IF($G36="","",$G36/$C36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="15">
+        <f>$C36/$I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="15">
+        <f>IF($F36="","",$F36/$I36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="15">
+        <f>IF($G36="","",$G36/$I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="16">
+        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N36" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="P36" s="20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q36" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R36" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S36" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43717</t>
+        </is>
+      </c>
+      <c r="T36" s="21" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="U36" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V36" s="13" t="inlineStr"/>
+      <c r="W36" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X36" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y36" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
         <v>51.12</v>
       </c>
-      <c r="C34" s="6">
-        <f>$B34+$Y34*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D34" s="7">
-        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E34" s="6">
-        <f>CEILING($D34*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="G34" s="8">
-        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="9">
-        <f>IF($G34="","",$G34/$C34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="10" t="n">
+      <c r="C37" s="6">
+        <f>$B37+$Y37*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D37" s="7">
+        <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E37" s="6">
+        <f>CEILING($D37*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G37" s="8">
+        <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="9">
+        <f>IF($G37="","",$G37/$C37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="6">
-        <f>$C34/$I34</f>
-        <v/>
-      </c>
-      <c r="K34" s="6">
-        <f>IF($F34="","",$F34/$I34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="6">
-        <f>IF($G34="","",$G34/$I34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="7">
-        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N34" s="6" t="n">
+      <c r="J37" s="6">
+        <f>$C37/$I37</f>
+        <v/>
+      </c>
+      <c r="K37" s="6">
+        <f>IF($F37="","",$F37/$I37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="6">
+        <f>IF($G37="","",$G37/$I37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="7">
+        <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="11" t="n">
+      <c r="O37" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="P34" s="11" t="n">
+      <c r="P37" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q34" s="12" t="inlineStr">
+      <c r="Q37" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R34" s="12" t="inlineStr">
+      <c r="R37" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S34" s="12" t="inlineStr">
+      <c r="S37" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T34" s="12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="inlineStr">
+      <c r="T37" s="12" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="4" t="inlineStr">
+      <c r="V37" s="4" t="inlineStr"/>
+      <c r="W37" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="X34" s="4" t="inlineStr"/>
-      <c r="Y34" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Baskets HOKA P.37 1/3 — neuves</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n">
-        <v>63</v>
-      </c>
-      <c r="C35" s="16">
-        <f>$B35+$Y35*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D35" s="17">
-        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E35" s="16">
-        <f>CEILING($D35*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="G35" s="18">
-        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="19">
-        <f>IF($G35="","",$G35/$C35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="16">
-        <f>$C35/$I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="16">
-        <f>IF($F35="","",$F35/$I35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="16">
-        <f>IF($G35="","",$G35/$I35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="17">
-        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="21" t="n">
-        <v>50</v>
-      </c>
-      <c r="P35" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q35" s="22" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R35" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S35" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T35" s="22" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="U35" s="14" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V35" s="14" t="inlineStr"/>
-      <c r="W35" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X35" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y35" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>NEW BALANCE sneakers P.38 — neuves</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C36" s="6">
-        <f>$B36+$Y36*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D36" s="7">
-        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E36" s="6">
-        <f>CEILING($D36*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="G36" s="8">
-        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="9">
-        <f>IF($G36="","",$G36/$C36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="6">
-        <f>$C36/$I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="6">
-        <f>IF($F36="","",$F36/$I36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="6">
-        <f>IF($G36="","",$G36/$I36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="7">
-        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P36" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q36" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R36" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S36" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T36" s="12" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="inlineStr"/>
-      <c r="W36" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X36" s="4" t="inlineStr"/>
-      <c r="Y36" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="C37" s="16">
-        <f>$B37+$Y37*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D37" s="17">
-        <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E37" s="16">
-        <f>CEILING($D37*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="G37" s="18">
-        <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="19">
-        <f>IF($G37="","",$G37/$C37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="16">
-        <f>$C37/$I37</f>
-        <v/>
-      </c>
-      <c r="K37" s="16">
-        <f>IF($F37="","",$F37/$I37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="16">
-        <f>IF($G37="","",$G37/$I37)</f>
-        <v/>
-      </c>
-      <c r="M37" s="17">
-        <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N37" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="P37" s="21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q37" s="22" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R37" s="22" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S37" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T37" s="22" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="U37" s="14" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V37" s="14" t="inlineStr"/>
-      <c r="W37" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X37" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y37" s="14" t="n">
+      <c r="X37" s="4" t="inlineStr"/>
+      <c r="Y37" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
+          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>51.12</v>
+        <v>52.4</v>
       </c>
       <c r="C38" s="6">
         <f>$B38+$Y38*Paramètres!$B$13</f>
@@ -3899,10 +3903,10 @@
         <v>0</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P38" s="11" t="n">
-        <v>10.4</v>
+        <v>10.66</v>
       </c>
       <c r="Q38" s="12" t="inlineStr">
         <is>
@@ -3921,12 +3925,12 @@
       </c>
       <c r="T38" s="12" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>158</t>
         </is>
       </c>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V38" s="4" t="inlineStr"/>
@@ -3941,305 +3945,301 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="C39" s="6">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>LACOSTE sneakers P.42 — neuves</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="C39" s="15">
         <f>$B39+$Y39*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="16">
         <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="15">
         <f>CEILING($D39*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G39" s="8">
+      <c r="F39" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G39" s="17">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
         <v/>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="18">
         <f>IF($G39="","",$G39/$C39)</f>
         <v/>
       </c>
-      <c r="I39" s="10" t="n">
+      <c r="I39" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="15">
         <f>$C39/$I39</f>
         <v/>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="15">
         <f>IF($F39="","",$F39/$I39)</f>
         <v/>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="15">
         <f>IF($G39="","",$G39/$I39)</f>
         <v/>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="16">
         <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="P39" s="11" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="Q39" s="12" t="inlineStr">
+      <c r="O39" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="P39" s="20" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q39" s="21" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R39" s="12" t="inlineStr">
+      <c r="R39" s="21" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S39" s="12" t="inlineStr">
+      <c r="S39" s="21" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T39" s="12" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="U39" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V39" s="4" t="inlineStr"/>
-      <c r="W39" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X39" s="4" t="inlineStr"/>
-      <c r="Y39" s="4" t="n">
+      <c r="T39" s="21" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="U39" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V39" s="13" t="inlineStr"/>
+      <c r="W39" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X39" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y39" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>LACOSTE sneakers P.42 — neuves</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n">
-        <v>57.51</v>
-      </c>
-      <c r="C40" s="16">
-        <f>$B40+$Y40*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D40" s="17">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="C40" s="6">
+        <f>$B40</f>
+        <v/>
+      </c>
+      <c r="D40" s="7">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="6">
         <f>CEILING($D40*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F40" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="G40" s="18">
+      <c r="F40" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="G40" s="8">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
         <v/>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="9">
         <f>IF($G40="","",$G40/$C40)</f>
         <v/>
       </c>
-      <c r="I40" s="20" t="n">
+      <c r="I40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="6">
         <f>$C40/$I40</f>
         <v/>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="6">
         <f>IF($F40="","",$F40/$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="6">
         <f>IF($G40="","",$G40/$I40)</f>
         <v/>
       </c>
-      <c r="M40" s="17">
+      <c r="M40" s="7">
         <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N40" s="16" t="n">
+      <c r="N40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="21" t="n">
-        <v>45</v>
-      </c>
-      <c r="P40" s="21" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Q40" s="22" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R40" s="22" t="inlineStr">
+      <c r="O40" s="31" t="n"/>
+      <c r="P40" s="31" t="n"/>
+      <c r="Q40" s="12" t="inlineStr">
+        <is>
+          <t>ERA Enchères Rhône-Alpes</t>
+        </is>
+      </c>
+      <c r="R40" s="12" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="S40" s="12" t="inlineStr">
+        <is>
+          <t>507148</t>
+        </is>
+      </c>
+      <c r="T40" s="12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr"/>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X40" s="4" t="inlineStr"/>
+      <c r="Y40" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C41" s="24">
+        <f>$B41+$Y41*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D41" s="25">
+        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E41" s="24">
+        <f>CEILING($D41*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="G41" s="26">
+        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="27">
+        <f>IF($G41="","",$G41/$C41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" s="24">
+        <f>$C41/$I41</f>
+        <v/>
+      </c>
+      <c r="K41" s="24">
+        <f>IF($F41="","",$F41/$I41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="24">
+        <f>IF($G41="","",$G41/$I41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="25">
+        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N41" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="P41" s="29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q41" s="30" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R41" s="30" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S40" s="22" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T40" s="22" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="U40" s="14" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V40" s="14" t="inlineStr"/>
-      <c r="W40" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X40" s="14" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y40" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C41" s="25">
-        <f>$B41+$Y41*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D41" s="26">
-        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E41" s="25">
-        <f>CEILING($D41*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="G41" s="27">
-        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="28">
-        <f>IF($G41="","",$G41/$C41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" s="25">
-        <f>$C41/$I41</f>
-        <v/>
-      </c>
-      <c r="K41" s="25">
-        <f>IF($F41="","",$F41/$I41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="25">
-        <f>IF($G41="","",$G41/$I41)</f>
-        <v/>
-      </c>
-      <c r="M41" s="26">
-        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="P41" s="30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q41" s="31" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R41" s="31" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S41" s="31" t="inlineStr">
+      <c r="S41" s="30" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="T41" s="31" t="inlineStr">
+      <c r="T41" s="30" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="U41" s="23" t="inlineStr">
+      <c r="U41" s="22" t="inlineStr">
         <is>
           <t>Leboncoin + eBay, en lot</t>
         </is>
       </c>
-      <c r="V41" s="23" t="inlineStr"/>
-      <c r="W41" s="23" t="inlineStr">
+      <c r="V41" s="22" t="inlineStr"/>
+      <c r="W41" s="22" t="inlineStr">
         <is>
           <t>Marge faible</t>
         </is>
       </c>
-      <c r="X41" s="23" t="inlineStr"/>
-      <c r="Y41" s="23" t="n">
+      <c r="X41" s="22" t="inlineStr"/>
+      <c r="Y41" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Boosters Pokémon MEGA Storm Emeralda M6 ×2 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
+          <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>12.74</v>
+        <v>28.29</v>
       </c>
       <c r="C42" s="6">
         <f>$B42</f>
@@ -4254,7 +4254,7 @@
         <v/>
       </c>
       <c r="F42" s="8" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G42" s="8">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
@@ -4286,37 +4286,37 @@
       <c r="N42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="13" t="n"/>
-      <c r="P42" s="13" t="n"/>
+      <c r="O42" s="31" t="n"/>
+      <c r="P42" s="31" t="n"/>
       <c r="Q42" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ERA Enchères Rhône-Alpes</t>
         </is>
       </c>
       <c r="R42" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="S42" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>507148</t>
         </is>
       </c>
       <c r="T42" s="12" t="inlineStr">
         <is>
-          <t>4521329462226</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lot de 2</t>
+          <t>Leboncoin, main propre</t>
         </is>
       </c>
       <c r="V42" s="4" t="inlineStr"/>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Marge faible</t>
         </is>
       </c>
       <c r="X42" s="4" t="inlineStr"/>
@@ -4327,14 +4327,14 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
+          <t>Boosters Pokémon MEGA Storm Emeralda M6 ×2 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>63</v>
+        <v>12.74</v>
       </c>
       <c r="C43" s="6">
-        <f>$B43+$Y43*Paramètres!$B$13</f>
+        <f>$B43</f>
         <v/>
       </c>
       <c r="D43" s="7">
@@ -4345,7 +4345,9 @@
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F43" s="13" t="n"/>
+      <c r="F43" s="8" t="n">
+        <v>19</v>
+      </c>
       <c r="G43" s="8">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
@@ -4376,41 +4378,37 @@
       <c r="N43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="P43" s="11" t="n">
-        <v>13</v>
-      </c>
+      <c r="O43" s="31" t="n"/>
+      <c r="P43" s="31" t="n"/>
       <c r="Q43" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R43" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S43" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46056</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T43" s="12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4521329462226</t>
         </is>
       </c>
       <c r="U43" s="4" t="inlineStr">
         <is>
-          <t>Vinted, authentification</t>
+          <t>Leboncoin, lot de 2</t>
         </is>
       </c>
       <c r="V43" s="4" t="inlineStr"/>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>PRIX À ÉTABLIR</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X43" s="4" t="inlineStr"/>
@@ -4419,63 +4417,247 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="inlineStr">
-        <is>
-          <t>TOTAL — 38 lots</t>
-        </is>
-      </c>
-      <c r="B44" s="33">
-        <f>SUM(B6:B43)</f>
-        <v/>
-      </c>
-      <c r="C44" s="33">
-        <f>SUM(C6:C43)</f>
-        <v/>
-      </c>
-      <c r="D44" s="34" t="n"/>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="33">
-        <f>SUM(F6:F43)</f>
-        <v/>
-      </c>
-      <c r="G44" s="33">
-        <f>SUM(G6:G43)</f>
-        <v/>
-      </c>
-      <c r="H44" s="35">
-        <f>G44/C44</f>
-        <v/>
-      </c>
-      <c r="I44" s="36">
-        <f>SUM(I6:I43)</f>
-        <v/>
-      </c>
-      <c r="J44" s="34" t="n"/>
-      <c r="K44" s="34" t="n"/>
-      <c r="L44" s="34" t="n"/>
-      <c r="M44" s="33">
-        <f>SUM(M6:M43)</f>
-        <v/>
-      </c>
-      <c r="N44" s="33">
-        <f>SUM(N6:N43)</f>
-        <v/>
-      </c>
-      <c r="O44" s="34" t="n"/>
-      <c r="P44" s="34" t="n"/>
-      <c r="Q44" s="34" t="n"/>
-      <c r="R44" s="34" t="n"/>
-      <c r="S44" s="34" t="n"/>
-      <c r="T44" s="34" t="n"/>
-      <c r="U44" s="34" t="n"/>
-      <c r="V44" s="34" t="n"/>
-      <c r="W44" s="34" t="n"/>
-      <c r="X44" s="34" t="n"/>
-      <c r="Y44" s="34" t="n"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="C44" s="6">
+        <f>$B44</f>
+        <v/>
+      </c>
+      <c r="D44" s="7">
+        <f>$C44/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E44" s="6">
+        <f>CEILING($D44*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F44" s="31" t="n"/>
+      <c r="G44" s="8">
+        <f>IF($F44="","",$F44-$C44-$M44-$N44)</f>
+        <v/>
+      </c>
+      <c r="H44" s="9">
+        <f>IF($G44="","",$G44/$C44)</f>
+        <v/>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="6">
+        <f>$C44/$I44</f>
+        <v/>
+      </c>
+      <c r="K44" s="6">
+        <f>IF($F44="","",$F44/$I44)</f>
+        <v/>
+      </c>
+      <c r="L44" s="6">
+        <f>IF($G44="","",$G44/$I44)</f>
+        <v/>
+      </c>
+      <c r="M44" s="7">
+        <f>IF($F44="","",$F44*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="31" t="n"/>
+      <c r="P44" s="31" t="n"/>
+      <c r="Q44" s="12" t="inlineStr">
+        <is>
+          <t>ERA Enchères Rhône-Alpes</t>
+        </is>
+      </c>
+      <c r="R44" s="12" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="S44" s="12" t="inlineStr">
+        <is>
+          <t>507148</t>
+        </is>
+      </c>
+      <c r="T44" s="12" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>Prélevée — usage personnel</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr"/>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉE</t>
+        </is>
+      </c>
+      <c r="X44" s="4" t="inlineStr"/>
+      <c r="Y44" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C45" s="6">
+        <f>$B45+$Y45*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D45" s="7">
+        <f>$C45/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E45" s="6">
+        <f>CEILING($D45*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F45" s="31" t="n"/>
+      <c r="G45" s="8">
+        <f>IF($F45="","",$F45-$C45-$M45-$N45)</f>
+        <v/>
+      </c>
+      <c r="H45" s="9">
+        <f>IF($G45="","",$G45/$C45)</f>
+        <v/>
+      </c>
+      <c r="I45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="6">
+        <f>$C45/$I45</f>
+        <v/>
+      </c>
+      <c r="K45" s="6">
+        <f>IF($F45="","",$F45/$I45)</f>
+        <v/>
+      </c>
+      <c r="L45" s="6">
+        <f>IF($G45="","",$G45/$I45)</f>
+        <v/>
+      </c>
+      <c r="M45" s="7">
+        <f>IF($F45="","",$F45*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="P45" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q45" s="12" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R45" s="12" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="S45" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-46056</t>
+        </is>
+      </c>
+      <c r="T45" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="inlineStr">
+        <is>
+          <t>Vinted, authentification</t>
+        </is>
+      </c>
+      <c r="V45" s="4" t="inlineStr"/>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>PRIX À ÉTABLIR</t>
+        </is>
+      </c>
+      <c r="X45" s="4" t="inlineStr"/>
+      <c r="Y45" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL — 40 lots</t>
+        </is>
+      </c>
+      <c r="B46" s="33">
+        <f>SUM(B6:B45)</f>
+        <v/>
+      </c>
+      <c r="C46" s="33">
+        <f>SUM(C6:C45)</f>
+        <v/>
+      </c>
+      <c r="D46" s="34" t="n"/>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="33">
+        <f>SUM(F6:F45)</f>
+        <v/>
+      </c>
+      <c r="G46" s="33">
+        <f>SUM(G6:G45)</f>
+        <v/>
+      </c>
+      <c r="H46" s="35">
+        <f>G46/C46</f>
+        <v/>
+      </c>
+      <c r="I46" s="36">
+        <f>SUM(I6:I45)</f>
+        <v/>
+      </c>
+      <c r="J46" s="34" t="n"/>
+      <c r="K46" s="34" t="n"/>
+      <c r="L46" s="34" t="n"/>
+      <c r="M46" s="33">
+        <f>SUM(M6:M45)</f>
+        <v/>
+      </c>
+      <c r="N46" s="33">
+        <f>SUM(N6:N45)</f>
+        <v/>
+      </c>
+      <c r="O46" s="34" t="n"/>
+      <c r="P46" s="34" t="n"/>
+      <c r="Q46" s="34" t="n"/>
+      <c r="R46" s="34" t="n"/>
+      <c r="S46" s="34" t="n"/>
+      <c r="T46" s="34" t="n"/>
+      <c r="U46" s="34" t="n"/>
+      <c r="V46" s="34" t="n"/>
+      <c r="W46" s="34" t="n"/>
+      <c r="X46" s="34" t="n"/>
+      <c r="Y46" s="34" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Y43"/>
-  <conditionalFormatting sqref="G6:G43">
+  <autoFilter ref="A5:Y45"/>
+  <conditionalFormatting sqref="G6:G45">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -4540,7 +4722,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>139.93</v>
+        <v>178.53</v>
       </c>
     </row>
     <row r="7">
@@ -4550,7 +4732,7 @@
         </is>
       </c>
       <c r="B7" s="33">
-        <f>'Stock complet'!C44</f>
+        <f>'Stock complet'!C46</f>
         <v/>
       </c>
     </row>
@@ -4568,7 +4750,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>'Stock complet'!F44</f>
+        <f>'Stock complet'!F46</f>
         <v/>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4584,7 +4766,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>-'Stock complet'!M44</f>
+        <f>-'Stock complet'!M46</f>
         <v/>
       </c>
     </row>
@@ -4595,7 +4777,7 @@
         </is>
       </c>
       <c r="B12" s="6">
-        <f>-'Stock complet'!N44</f>
+        <f>-'Stock complet'!N46</f>
         <v/>
       </c>
     </row>
@@ -4605,7 +4787,7 @@
         <v/>
       </c>
       <c r="B13" s="33">
-        <f>'Stock complet'!G44</f>
+        <f>'Stock complet'!G46</f>
         <v/>
       </c>
     </row>
@@ -4698,7 +4880,7 @@
         </is>
       </c>
       <c r="B23" s="42">
-        <f>'Stock complet'!I44</f>
+        <f>'Stock complet'!I46</f>
         <v/>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -165,6 +165,7 @@
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,7 +175,6 @@
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2009,14 +2009,14 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
+          <t>Booster Box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters — 6 lots de 5 à 17 €</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>25.2</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="C19" s="6">
-        <f>$B19+$Y19*Paramètres!$B$13</f>
+        <f>$B19</f>
         <v/>
       </c>
       <c r="D19" s="7">
@@ -2028,7 +2028,7 @@
         <v/>
       </c>
       <c r="F19" s="8" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="G19" s="8">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
@@ -2039,7 +2039,7 @@
         <v/>
       </c>
       <c r="I19" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J19" s="6">
         <f>$C19/$I19</f>
@@ -2060,35 +2060,31 @@
       <c r="N19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="P19" s="11" t="n">
-        <v>5.2</v>
-      </c>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>4521329432274</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin, lots de 5</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
@@ -2099,24 +2095,24 @@
       </c>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
+          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>25.56</v>
+        <v>25.2</v>
       </c>
       <c r="C20" s="6">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E20" s="6">
@@ -2153,9 +2149,8 @@
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6">
-        <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O20" s="11" t="n">
         <v>20</v>
@@ -2165,27 +2160,27 @@
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>439</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
@@ -2202,18 +2197,18 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
+          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>57.51</v>
+        <v>25.56</v>
       </c>
       <c r="C21" s="6">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E21" s="6">
@@ -2221,7 +2216,7 @@
         <v/>
       </c>
       <c r="F21" s="8" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G21" s="8">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
@@ -2250,14 +2245,15 @@
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
+      <c r="N21" s="6">
+        <f>IF($F21="","",$F21*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O21" s="11" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>11.7</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
@@ -2271,17 +2267,17 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
@@ -2298,11 +2294,11 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
+          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>37.8</v>
+        <v>57.51</v>
       </c>
       <c r="C22" s="6">
         <f>$B22+$Y22*Paramètres!$B$13</f>
@@ -2317,7 +2313,7 @@
         <v/>
       </c>
       <c r="F22" s="8" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G22" s="8">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
@@ -2328,7 +2324,7 @@
         <v/>
       </c>
       <c r="I22" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J22" s="6">
         <f>$C22/$I22</f>
@@ -2350,254 +2346,254 @@
         <v>0</v>
       </c>
       <c r="O22" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>7.8</v>
+        <v>11.7</v>
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R22" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43717</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T22" s="12" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>159</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="C23" s="6">
+        <f>$B23+$Y23*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D23" s="7">
+        <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E23" s="6">
+        <f>CEILING($D23*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="G23" s="8">
+        <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>IF($G23="","",$G23/$C23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="10" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="J23" s="6">
+        <f>$C23/$I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="6">
+        <f>IF($F23="","",$F23/$I23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="6">
+        <f>IF($G23="","",$G23/$I23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="7">
+        <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q23" s="12" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R23" s="12" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43717</t>
+        </is>
+      </c>
+      <c r="T23" s="12" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>URGENT — saisonnier</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr"/>
+      <c r="Y23" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B24" s="24" t="n">
         <v>19.17</v>
       </c>
-      <c r="C23" s="24">
-        <f>$B23+$Y23*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
-        <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E23" s="24">
-        <f>CEILING($D23*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F23" s="26" t="n">
+      <c r="C24" s="25">
+        <f>$B24+$Y24*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D24" s="26">
+        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E24" s="25">
+        <f>CEILING($D24*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="G23" s="26">
-        <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="27">
-        <f>IF($G23="","",$G23/$C23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="28" t="n">
+      <c r="G24" s="27">
+        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="28">
+        <f>IF($G24="","",$G24/$C24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="24">
-        <f>$C23/$I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="24">
-        <f>IF($F23="","",$F23/$I23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="24">
-        <f>IF($G23="","",$G23/$I23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="25">
-        <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N23" s="24" t="n">
+      <c r="J24" s="25">
+        <f>$C24/$I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="25">
+        <f>IF($F24="","",$F24/$I24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="25">
+        <f>IF($G24="","",$G24/$I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="26">
+        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N24" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="29" t="n">
+      <c r="O24" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="P23" s="29" t="n">
+      <c r="P24" s="30" t="n">
         <v>3.9</v>
       </c>
-      <c r="Q23" s="30" t="inlineStr">
+      <c r="Q24" s="31" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R23" s="30" t="inlineStr">
+      <c r="R24" s="31" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S23" s="30" t="inlineStr">
+      <c r="S24" s="31" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="T23" s="30" t="inlineStr">
+      <c r="T24" s="31" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="U23" s="22" t="inlineStr">
+      <c r="U24" s="23" t="inlineStr">
         <is>
           <t>Leboncoin + eBay, en lot</t>
         </is>
       </c>
-      <c r="V23" s="22" t="inlineStr"/>
-      <c r="W23" s="22" t="inlineStr">
+      <c r="V24" s="23" t="inlineStr"/>
+      <c r="W24" s="23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X23" s="22" t="inlineStr"/>
-      <c r="Y23" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>GEOX baskets P.35 — neuves</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>21.73</v>
-      </c>
-      <c r="C24" s="6">
-        <f>$B24+$Y24*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D24" s="7">
-        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E24" s="6">
-        <f>CEILING($D24*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="G24" s="8">
-        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="9">
-        <f>IF($G24="","",$G24/$C24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="6">
-        <f>$C24/$I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="6">
-        <f>IF($F24="","",$F24/$I24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="6">
-        <f>IF($G24="","",$G24/$I24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="7">
-        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="P24" s="11" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="Q24" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R24" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S24" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T24" s="12" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="4" t="n">
+      <c r="X24" s="23" t="inlineStr"/>
+      <c r="Y24" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
+          <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>50.4</v>
+        <v>21.73</v>
       </c>
       <c r="C25" s="6">
         <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E25" s="6">
@@ -2605,7 +2601,7 @@
         <v/>
       </c>
       <c r="F25" s="8" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G25" s="8">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
@@ -2634,45 +2630,44 @@
         <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N25" s="6">
-        <f>IF($F25="","",$F25*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N25" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>10.4</v>
+        <v>4.42</v>
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R25" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X25" s="4" t="inlineStr"/>
@@ -2683,18 +2678,18 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>75.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="C26" s="6">
         <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E26" s="6">
@@ -2702,7 +2697,7 @@
         <v/>
       </c>
       <c r="F26" s="8" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G26" s="8">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
@@ -2731,14 +2726,15 @@
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="n">
-        <v>0</v>
+      <c r="N26" s="6">
+        <f>IF($F26="","",$F26*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O26" s="11" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P26" s="11" t="n">
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
@@ -2757,18 +2753,18 @@
       </c>
       <c r="T26" s="12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>408</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>Liquider</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X26" s="4" t="inlineStr"/>
@@ -2777,113 +2773,109 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="n">
-        <v>76.68000000000001</v>
-      </c>
-      <c r="C27" s="15">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="C27" s="6">
         <f>$B27+$Y27*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="7">
         <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="6">
         <f>CEILING($D27*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F27" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G27" s="17">
+      <c r="F27" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="G27" s="8">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
         <v/>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="9">
         <f>IF($G27="","",$G27/$C27)</f>
         <v/>
       </c>
-      <c r="I27" s="19" t="n">
+      <c r="I27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="6">
         <f>$C27/$I27</f>
         <v/>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="6">
         <f>IF($F27="","",$F27/$I27)</f>
         <v/>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="6">
         <f>IF($G27="","",$G27/$I27)</f>
         <v/>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="7">
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="15" t="n">
+      <c r="N27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="20" t="n">
+      <c r="O27" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="P27" s="20" t="n">
+      <c r="P27" s="11" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q27" s="21" t="inlineStr">
+      <c r="Q27" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R27" s="21" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S27" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T27" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="U27" s="13" t="inlineStr">
-        <is>
-          <t>Vinted, Italie — non encaissé</t>
-        </is>
-      </c>
-      <c r="V27" s="13" t="inlineStr"/>
-      <c r="W27" s="13" t="inlineStr">
-        <is>
-          <t>VENDUE, en attente</t>
-        </is>
-      </c>
-      <c r="X27" s="13" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="Y27" s="13" t="n">
+      <c r="R27" s="12" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S27" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T27" s="12" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X27" s="4" t="inlineStr"/>
+      <c r="Y27" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>113.4</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="C28" s="15">
         <f>$B28+$Y28*Paramètres!$B$13</f>
@@ -2898,7 +2890,7 @@
         <v/>
       </c>
       <c r="F28" s="17" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="G28" s="17">
         <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
@@ -2931,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="20" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="P28" s="20" t="n">
-        <v>23.4</v>
+        <v>15.6</v>
       </c>
       <c r="Q28" s="21" t="inlineStr">
         <is>
@@ -2948,28 +2940,28 @@
       </c>
       <c r="S28" s="21" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-44192</t>
         </is>
       </c>
       <c r="T28" s="21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U28" s="13" t="inlineStr">
         <is>
-          <t>vendu</t>
+          <t>Vinted, Italie — non encaissé</t>
         </is>
       </c>
       <c r="V28" s="13" t="inlineStr"/>
       <c r="W28" s="13" t="inlineStr">
         <is>
-          <t>VENDU</t>
+          <t>VENDUE, en attente</t>
         </is>
       </c>
       <c r="X28" s="13" t="inlineStr">
         <is>
-          <t>VENDU</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="Y28" s="13" t="n">
@@ -2979,11 +2971,11 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>50.4</v>
+        <v>113.4</v>
       </c>
       <c r="C29" s="15">
         <f>$B29+$Y29*Paramètres!$B$13</f>
@@ -2998,7 +2990,7 @@
         <v/>
       </c>
       <c r="F29" s="17" t="n">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="G29" s="17">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
@@ -3031,10 +3023,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="20" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="P29" s="20" t="n">
-        <v>10.4</v>
+        <v>23.4</v>
       </c>
       <c r="Q29" s="21" t="inlineStr">
         <is>
@@ -3043,17 +3035,17 @@
       </c>
       <c r="R29" s="21" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S29" s="21" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-44194</t>
         </is>
       </c>
       <c r="T29" s="21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U29" s="13" t="inlineStr">
@@ -3079,7 +3071,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
       <c r="B30" s="14" t="n">
@@ -3153,7 +3145,7 @@
       </c>
       <c r="T30" s="21" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>170</t>
         </is>
       </c>
       <c r="U30" s="13" t="inlineStr">
@@ -3177,108 +3169,116 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes — invendable seul : bundle avec 5 Nihil Zero à 30 €</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="C31" s="6">
-        <f>$B31</f>
-        <v/>
-      </c>
-      <c r="D31" s="7">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C31" s="15">
+        <f>$B31+$Y31*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D31" s="16">
         <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="15">
         <f>CEILING($D31*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F31" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="G31" s="8">
+      <c r="F31" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G31" s="17">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
         <v/>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="18">
         <f>IF($G31="","",$G31/$C31)</f>
         <v/>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="6">
+      <c r="J31" s="15">
         <f>$C31/$I31</f>
         <v/>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="15">
         <f>IF($F31="","",$F31/$I31)</f>
         <v/>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="15">
         <f>IF($G31="","",$G31/$I31)</f>
         <v/>
       </c>
-      <c r="M31" s="7">
+      <c r="M31" s="16">
         <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="31" t="n"/>
-      <c r="P31" s="31" t="n"/>
-      <c r="Q31" s="12" t="inlineStr">
-        <is>
-          <t>Meccha Japan</t>
-        </is>
-      </c>
-      <c r="R31" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S31" s="12" t="inlineStr">
-        <is>
-          <t>#FA429713</t>
-        </is>
-      </c>
-      <c r="T31" s="12" t="inlineStr">
-        <is>
-          <t>4521329431925</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin, bundle</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="inlineStr"/>
-      <c r="W31" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X31" s="4" t="inlineStr"/>
-      <c r="Y31" s="4" t="n">
+      <c r="O31" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="P31" s="20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q31" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R31" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S31" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T31" s="21" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="U31" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V31" s="13" t="inlineStr"/>
+      <c r="W31" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X31" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y31" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Booster Box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters — 5 lots de 5 à 17 €, le 6e part en bundle</t>
+          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>51.12</v>
       </c>
       <c r="C32" s="6">
-        <f>$B32</f>
+        <f>$B32+$Y32*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D32" s="7">
@@ -3290,7 +3290,7 @@
         <v/>
       </c>
       <c r="F32" s="8" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G32" s="8">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="I32" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J32" s="6">
         <f>$C32/$I32</f>
@@ -3322,11 +3322,15 @@
       <c r="N32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
+      <c r="O32" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P32" s="11" t="n">
+        <v>10.4</v>
+      </c>
       <c r="Q32" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R32" s="12" t="inlineStr">
@@ -3336,430 +3340,430 @@
       </c>
       <c r="S32" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T32" s="12" t="inlineStr">
         <is>
-          <t>4521329432274</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lots de 5</t>
+          <t>Leboncoin</t>
         </is>
       </c>
       <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Liquider</t>
         </is>
       </c>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Baskets HOKA P.37 1/3 — neuves</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="C33" s="15">
+        <f>$B33+$Y33*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D33" s="16">
+        <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E33" s="15">
+        <f>CEILING($D33*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="G33" s="17">
+        <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="18">
+        <f>IF($G33="","",$G33/$C33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="15">
+        <f>$C33/$I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="15">
+        <f>IF($F33="","",$F33/$I33)</f>
+        <v/>
+      </c>
+      <c r="L33" s="15">
+        <f>IF($G33="","",$G33/$I33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="16">
+        <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="P33" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q33" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R33" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S33" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T33" s="21" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="U33" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V33" s="13" t="inlineStr"/>
+      <c r="W33" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X33" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y33" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE sneakers P.38 — neuves</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C34" s="6">
+        <f>$B34+$Y34*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D34" s="7">
+        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E34" s="6">
+        <f>CEILING($D34*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="G34" s="8">
+        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="9">
+        <f>IF($G34="","",$G34/$C34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="6">
+        <f>$C34/$I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="6">
+        <f>IF($F34="","",$F34/$I34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="6">
+        <f>IF($G34="","",$G34/$I34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="7">
+        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P34" s="11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q34" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S34" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T34" s="12" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X34" s="4" t="inlineStr"/>
+      <c r="Y34" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C35" s="15">
+        <f>$B35+$Y35*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E35" s="15">
+        <f>CEILING($D35*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G35" s="17">
+        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="18">
+        <f>IF($G35="","",$G35/$C35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="15">
+        <f>$C35/$I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="15">
+        <f>IF($F35="","",$F35/$I35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="15">
+        <f>IF($G35="","",$G35/$I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="16">
+        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="P35" s="20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q35" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R35" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S35" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43717</t>
+        </is>
+      </c>
+      <c r="T35" s="21" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="U35" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V35" s="13" t="inlineStr"/>
+      <c r="W35" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X35" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y35" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
         <v>51.12</v>
       </c>
-      <c r="C33" s="6">
-        <f>$B33+$Y33*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D33" s="7">
-        <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E33" s="6">
-        <f>CEILING($D33*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="G33" s="8">
-        <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="9">
-        <f>IF($G33="","",$G33/$C33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="10" t="n">
+      <c r="C36" s="6">
+        <f>$B36+$Y36*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D36" s="7">
+        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E36" s="6">
+        <f>CEILING($D36*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G36" s="8">
+        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="9">
+        <f>IF($G36="","",$G36/$C36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6">
-        <f>$C33/$I33</f>
-        <v/>
-      </c>
-      <c r="K33" s="6">
-        <f>IF($F33="","",$F33/$I33)</f>
-        <v/>
-      </c>
-      <c r="L33" s="6">
-        <f>IF($G33="","",$G33/$I33)</f>
-        <v/>
-      </c>
-      <c r="M33" s="7">
-        <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N33" s="6" t="n">
+      <c r="J36" s="6">
+        <f>$C36/$I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="6">
+        <f>IF($F36="","",$F36/$I36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="6">
+        <f>IF($G36="","",$G36/$I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="7">
+        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="11" t="n">
+      <c r="O36" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="P33" s="11" t="n">
+      <c r="P36" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q33" s="12" t="inlineStr">
+      <c r="Q36" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R33" s="12" t="inlineStr">
+      <c r="R36" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S33" s="12" t="inlineStr">
+      <c r="S36" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T33" s="12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="U33" s="4" t="inlineStr">
+      <c r="T36" s="12" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="V33" s="4" t="inlineStr"/>
-      <c r="W33" s="4" t="inlineStr">
+      <c r="V36" s="4" t="inlineStr"/>
+      <c r="W36" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="X33" s="4" t="inlineStr"/>
-      <c r="Y33" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Baskets HOKA P.37 1/3 — neuves</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="n">
-        <v>63</v>
-      </c>
-      <c r="C34" s="15">
-        <f>$B34+$Y34*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D34" s="16">
-        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E34" s="15">
-        <f>CEILING($D34*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F34" s="17" t="n">
-        <v>80</v>
-      </c>
-      <c r="G34" s="17">
-        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="18">
-        <f>IF($G34="","",$G34/$C34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="15">
-        <f>$C34/$I34</f>
-        <v/>
-      </c>
-      <c r="K34" s="15">
-        <f>IF($F34="","",$F34/$I34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="15">
-        <f>IF($G34="","",$G34/$I34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="16">
-        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="P34" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q34" s="21" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R34" s="21" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S34" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T34" s="21" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="U34" s="13" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V34" s="13" t="inlineStr"/>
-      <c r="W34" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X34" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y34" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>NEW BALANCE sneakers P.38 — neuves</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C35" s="6">
-        <f>$B35+$Y35*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D35" s="7">
-        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E35" s="6">
-        <f>CEILING($D35*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="G35" s="8">
-        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="9">
-        <f>IF($G35="","",$G35/$C35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="6">
-        <f>$C35/$I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="6">
-        <f>IF($F35="","",$F35/$I35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="6">
-        <f>IF($G35="","",$G35/$I35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="7">
-        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P35" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q35" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R35" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S35" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T35" s="12" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="U35" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V35" s="4" t="inlineStr"/>
-      <c r="W35" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X35" s="4" t="inlineStr"/>
-      <c r="Y35" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="C36" s="15">
-        <f>$B36+$Y36*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D36" s="16">
-        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E36" s="15">
-        <f>CEILING($D36*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="G36" s="17">
-        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="18">
-        <f>IF($G36="","",$G36/$C36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="15">
-        <f>$C36/$I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="15">
-        <f>IF($F36="","",$F36/$I36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="15">
-        <f>IF($G36="","",$G36/$I36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="16">
-        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="P36" s="20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q36" s="21" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R36" s="21" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S36" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T36" s="21" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="U36" s="13" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V36" s="13" t="inlineStr"/>
-      <c r="W36" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X36" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y36" s="13" t="n">
+      <c r="X36" s="4" t="inlineStr"/>
+      <c r="Y36" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
+          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>51.12</v>
+        <v>52.4</v>
       </c>
       <c r="C37" s="6">
         <f>$B37+$Y37*Paramètres!$B$13</f>
@@ -3807,10 +3811,10 @@
         <v>0</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P37" s="11" t="n">
-        <v>10.4</v>
+        <v>10.66</v>
       </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
@@ -3829,12 +3833,12 @@
       </c>
       <c r="T37" s="12" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>158</t>
         </is>
       </c>
       <c r="U37" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V37" s="4" t="inlineStr"/>
@@ -3849,397 +3853,393 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="C38" s="6">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>LACOSTE sneakers P.42 — neuves</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="C38" s="15">
         <f>$B38+$Y38*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="16">
         <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="15">
         <f>CEILING($D38*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G38" s="8">
+      <c r="F38" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G38" s="17">
         <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
         <v/>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="18">
         <f>IF($G38="","",$G38/$C38)</f>
         <v/>
       </c>
-      <c r="I38" s="10" t="n">
+      <c r="I38" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="6">
+      <c r="J38" s="15">
         <f>$C38/$I38</f>
         <v/>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="15">
         <f>IF($F38="","",$F38/$I38)</f>
         <v/>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="15">
         <f>IF($G38="","",$G38/$I38)</f>
         <v/>
       </c>
-      <c r="M38" s="7">
+      <c r="M38" s="16">
         <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="N38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="P38" s="11" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="Q38" s="12" t="inlineStr">
+      <c r="O38" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="P38" s="20" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q38" s="21" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R38" s="12" t="inlineStr">
+      <c r="R38" s="21" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S38" s="12" t="inlineStr">
+      <c r="S38" s="21" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T38" s="12" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V38" s="4" t="inlineStr"/>
-      <c r="W38" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X38" s="4" t="inlineStr"/>
-      <c r="Y38" s="4" t="n">
+      <c r="T38" s="21" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="U38" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V38" s="13" t="inlineStr"/>
+      <c r="W38" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X38" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y38" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>LACOSTE sneakers P.42 — neuves</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="n">
-        <v>57.51</v>
-      </c>
-      <c r="C39" s="15">
-        <f>$B39+$Y39*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D39" s="16">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="C39" s="6">
+        <f>$B39</f>
+        <v/>
+      </c>
+      <c r="D39" s="7">
         <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="6">
         <f>CEILING($D39*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F39" s="17" t="n">
-        <v>70</v>
-      </c>
-      <c r="G39" s="17">
+      <c r="F39" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="G39" s="8">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="9">
         <f>IF($G39="","",$G39/$C39)</f>
         <v/>
       </c>
-      <c r="I39" s="19" t="n">
+      <c r="I39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="6">
         <f>$C39/$I39</f>
         <v/>
       </c>
-      <c r="K39" s="15">
+      <c r="K39" s="6">
         <f>IF($F39="","",$F39/$I39)</f>
         <v/>
       </c>
-      <c r="L39" s="15">
+      <c r="L39" s="6">
         <f>IF($G39="","",$G39/$I39)</f>
         <v/>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="7">
         <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N39" s="15" t="n">
+      <c r="N39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="P39" s="20" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Q39" s="21" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R39" s="21" t="inlineStr">
+      <c r="O39" s="22" t="n"/>
+      <c r="P39" s="22" t="n"/>
+      <c r="Q39" s="12" t="inlineStr">
+        <is>
+          <t>ERA Enchères Rhône-Alpes</t>
+        </is>
+      </c>
+      <c r="R39" s="12" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="S39" s="12" t="inlineStr">
+        <is>
+          <t>507148</t>
+        </is>
+      </c>
+      <c r="T39" s="12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin, main propre</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr"/>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X39" s="4" t="inlineStr"/>
+      <c r="Y39" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C40" s="25">
+        <f>$B40+$Y40*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E40" s="25">
+        <f>CEILING($D40*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="G40" s="27">
+        <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="28">
+        <f>IF($G40="","",$G40/$C40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" s="25">
+        <f>$C40/$I40</f>
+        <v/>
+      </c>
+      <c r="K40" s="25">
+        <f>IF($F40="","",$F40/$I40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="25">
+        <f>IF($G40="","",$G40/$I40)</f>
+        <v/>
+      </c>
+      <c r="M40" s="26">
+        <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="P40" s="30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q40" s="31" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R40" s="31" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S39" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T39" s="21" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="U39" s="13" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V39" s="13" t="inlineStr"/>
-      <c r="W39" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X39" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y39" s="13" t="n">
+      <c r="S40" s="31" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T40" s="31" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="U40" s="23" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V40" s="23" t="inlineStr"/>
+      <c r="W40" s="23" t="inlineStr">
+        <is>
+          <t>Marge faible</t>
+        </is>
+      </c>
+      <c r="X40" s="23" t="inlineStr"/>
+      <c r="Y40" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="C40" s="6">
-        <f>$B40</f>
-        <v/>
-      </c>
-      <c r="D40" s="7">
-        <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E40" s="6">
-        <f>CEILING($D40*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="G40" s="8">
-        <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
-        <v/>
-      </c>
-      <c r="H40" s="9">
-        <f>IF($G40="","",$G40/$C40)</f>
-        <v/>
-      </c>
-      <c r="I40" s="10" t="n">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="C41" s="6">
+        <f>$B41</f>
+        <v/>
+      </c>
+      <c r="D41" s="7">
+        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E41" s="6">
+        <f>CEILING($D41*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G41" s="8">
+        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="9">
+        <f>IF($G41="","",$G41/$C41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="6">
-        <f>$C40/$I40</f>
-        <v/>
-      </c>
-      <c r="K40" s="6">
-        <f>IF($F40="","",$F40/$I40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="6">
-        <f>IF($G40="","",$G40/$I40)</f>
-        <v/>
-      </c>
-      <c r="M40" s="7">
-        <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N40" s="6" t="n">
+      <c r="J41" s="6">
+        <f>$C41/$I41</f>
+        <v/>
+      </c>
+      <c r="K41" s="6">
+        <f>IF($F41="","",$F41/$I41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="6">
+        <f>IF($G41="","",$G41/$I41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="7">
+        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="31" t="n"/>
-      <c r="P40" s="31" t="n"/>
-      <c r="Q40" s="12" t="inlineStr">
+      <c r="O41" s="22" t="n"/>
+      <c r="P41" s="22" t="n"/>
+      <c r="Q41" s="12" t="inlineStr">
         <is>
           <t>ERA Enchères Rhône-Alpes</t>
         </is>
       </c>
-      <c r="R40" s="12" t="inlineStr">
+      <c r="R41" s="12" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="S40" s="12" t="inlineStr">
+      <c r="S41" s="12" t="inlineStr">
         <is>
           <t>507148</t>
         </is>
       </c>
-      <c r="T40" s="12" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="inlineStr">
+      <c r="T41" s="12" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
         <is>
           <t>Leboncoin, main propre</t>
         </is>
       </c>
-      <c r="V40" s="4" t="inlineStr"/>
-      <c r="W40" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X40" s="4" t="inlineStr"/>
-      <c r="Y40" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C41" s="24">
-        <f>$B41+$Y41*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D41" s="25">
-        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E41" s="24">
-        <f>CEILING($D41*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F41" s="26" t="n">
-        <v>49</v>
-      </c>
-      <c r="G41" s="26">
-        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="27">
-        <f>IF($G41="","",$G41/$C41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" s="24">
-        <f>$C41/$I41</f>
-        <v/>
-      </c>
-      <c r="K41" s="24">
-        <f>IF($F41="","",$F41/$I41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="24">
-        <f>IF($G41="","",$G41/$I41)</f>
-        <v/>
-      </c>
-      <c r="M41" s="25">
-        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N41" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="P41" s="29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q41" s="30" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R41" s="30" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S41" s="30" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T41" s="30" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="U41" s="22" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay, en lot</t>
-        </is>
-      </c>
-      <c r="V41" s="22" t="inlineStr"/>
-      <c r="W41" s="22" t="inlineStr">
+      <c r="V41" s="4" t="inlineStr"/>
+      <c r="W41" s="4" t="inlineStr">
         <is>
           <t>Marge faible</t>
         </is>
       </c>
-      <c r="X41" s="22" t="inlineStr"/>
-      <c r="Y41" s="22" t="n">
+      <c r="X41" s="4" t="inlineStr"/>
+      <c r="Y41" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
+          <t>Boosters Pokémon MEGA Storm Emeralda M6 ×2 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>28.29</v>
+        <v>12.74</v>
       </c>
       <c r="C42" s="6">
         <f>$B42</f>
@@ -4254,7 +4254,7 @@
         <v/>
       </c>
       <c r="F42" s="8" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G42" s="8">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
@@ -4286,37 +4286,37 @@
       <c r="N42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="31" t="n"/>
-      <c r="P42" s="31" t="n"/>
+      <c r="O42" s="22" t="n"/>
+      <c r="P42" s="22" t="n"/>
       <c r="Q42" s="12" t="inlineStr">
         <is>
-          <t>ERA Enchères Rhône-Alpes</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R42" s="12" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S42" s="12" t="inlineStr">
         <is>
-          <t>507148</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T42" s="12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>4521329462226</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Leboncoin, lot de 2</t>
         </is>
       </c>
       <c r="V42" s="4" t="inlineStr"/>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>Marge faible</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X42" s="4" t="inlineStr"/>
@@ -4327,11 +4327,11 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Boosters Pokémon MEGA Storm Emeralda M6 ×2 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
+          <t>Booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>12.74</v>
+        <v>12.95</v>
       </c>
       <c r="C43" s="6">
         <f>$B43</f>
@@ -4345,9 +4345,7 @@
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F43" s="8" t="n">
-        <v>19</v>
-      </c>
+      <c r="F43" s="22" t="n"/>
       <c r="G43" s="8">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
@@ -4378,8 +4376,8 @@
       <c r="N43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="31" t="n"/>
-      <c r="P43" s="31" t="n"/>
+      <c r="O43" s="22" t="n"/>
+      <c r="P43" s="22" t="n"/>
       <c r="Q43" s="12" t="inlineStr">
         <is>
           <t>Meccha Japan</t>
@@ -4397,18 +4395,18 @@
       </c>
       <c r="T43" s="12" t="inlineStr">
         <is>
-          <t>4521329462226</t>
+          <t>4521329431925</t>
         </is>
       </c>
       <c r="U43" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lot de 2</t>
+          <t>Prélevé — usage personnel</t>
         </is>
       </c>
       <c r="V43" s="4" t="inlineStr"/>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>PRÉLEVÉ</t>
         </is>
       </c>
       <c r="X43" s="4" t="inlineStr"/>
@@ -4437,7 +4435,7 @@
         <f>CEILING($D44*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F44" s="31" t="n"/>
+      <c r="F44" s="22" t="n"/>
       <c r="G44" s="8">
         <f>IF($F44="","",$F44-$C44-$M44-$N44)</f>
         <v/>
@@ -4468,8 +4466,8 @@
       <c r="N44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="31" t="n"/>
-      <c r="P44" s="31" t="n"/>
+      <c r="O44" s="22" t="n"/>
+      <c r="P44" s="22" t="n"/>
       <c r="Q44" s="12" t="inlineStr">
         <is>
           <t>ERA Enchères Rhône-Alpes</t>
@@ -4527,7 +4525,7 @@
         <f>CEILING($D45*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F45" s="31" t="n"/>
+      <c r="F45" s="22" t="n"/>
       <c r="G45" s="8">
         <f>IF($F45="","",$F45-$C45-$M45-$N45)</f>
         <v/>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2009,7 +2009,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Booster Box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters — 6 lots de 5 à 17 €</t>
+          <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 6 lots de 5 à 17 €</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -4235,7 +4235,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Boosters Pokémon MEGA Storm Emeralda M6 ×2 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
+          <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -4327,7 +4327,7 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes</t>
+          <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2009,14 +2009,14 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 6 lots de 5 à 17 €</t>
+          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>25.2</v>
       </c>
       <c r="C19" s="6">
-        <f>$B19</f>
+        <f>$B19+$Y19*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D19" s="7">
@@ -2028,7 +2028,7 @@
         <v/>
       </c>
       <c r="F19" s="8" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="G19" s="8">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
@@ -2039,7 +2039,7 @@
         <v/>
       </c>
       <c r="I19" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J19" s="6">
         <f>$C19/$I19</f>
@@ -2060,31 +2060,35 @@
       <c r="N19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
+      <c r="O19" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>5.2</v>
+      </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>4521329432274</t>
+          <t>439</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lots de 5</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
@@ -2095,24 +2099,24 @@
       </c>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
+          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>25.2</v>
+        <v>25.56</v>
       </c>
       <c r="C20" s="6">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E20" s="6">
@@ -2149,8 +2153,9 @@
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>0</v>
+      <c r="N20" s="6">
+        <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O20" s="11" t="n">
         <v>20</v>
@@ -2160,27 +2165,27 @@
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
@@ -2197,18 +2202,18 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
+          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>25.56</v>
+        <v>57.51</v>
       </c>
       <c r="C21" s="6">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E21" s="6">
@@ -2216,7 +2221,7 @@
         <v/>
       </c>
       <c r="F21" s="8" t="n">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G21" s="8">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
@@ -2245,15 +2250,14 @@
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6">
-        <f>IF($F21="","",$F21*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>5.2</v>
+        <v>11.7</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
@@ -2267,17 +2271,17 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>159</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
@@ -2294,14 +2298,14 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
+          <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>57.51</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="C22" s="6">
-        <f>$B22+$Y22*Paramètres!$B$13</f>
+        <f>$B22</f>
         <v/>
       </c>
       <c r="D22" s="7">
@@ -2313,7 +2317,7 @@
         <v/>
       </c>
       <c r="F22" s="8" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G22" s="8">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
@@ -2324,7 +2328,7 @@
         <v/>
       </c>
       <c r="I22" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="6">
         <f>$C22/$I22</f>
@@ -2345,15 +2349,11 @@
       <c r="N22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="P22" s="11" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="O22" s="22" t="n"/>
+      <c r="P22" s="22" t="n"/>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R22" s="12" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T22" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>4521329432274</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin, lots de 15</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +175,7 @@
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3071,7 +3072,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
       <c r="B30" s="14" t="n">
@@ -3145,7 +3146,7 @@
       </c>
       <c r="T30" s="21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>431</t>
         </is>
       </c>
       <c r="U30" s="13" t="inlineStr">
@@ -3169,113 +3170,109 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C31" s="15">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="C31" s="6">
         <f>$B31+$Y31*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="7">
         <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="6">
         <f>CEILING($D31*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F31" s="17" t="n">
-        <v>70</v>
-      </c>
-      <c r="G31" s="17">
+      <c r="F31" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="G31" s="8">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
         <v/>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="9">
         <f>IF($G31="","",$G31/$C31)</f>
         <v/>
       </c>
-      <c r="I31" s="19" t="n">
+      <c r="I31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="6">
         <f>$C31/$I31</f>
         <v/>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="6">
         <f>IF($F31="","",$F31/$I31)</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="6">
         <f>IF($G31="","",$G31/$I31)</f>
         <v/>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="7">
         <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N31" s="15" t="n">
+      <c r="N31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="20" t="n">
+      <c r="O31" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="P31" s="20" t="n">
+      <c r="P31" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q31" s="21" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R31" s="21" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S31" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T31" s="21" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="U31" s="13" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V31" s="13" t="inlineStr"/>
-      <c r="W31" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X31" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y31" s="13" t="n">
+      <c r="Q31" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R31" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S31" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T31" s="12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X31" s="4" t="inlineStr"/>
+      <c r="Y31" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
+          <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>51.12</v>
+        <v>38.34</v>
       </c>
       <c r="C32" s="6">
         <f>$B32+$Y32*Paramètres!$B$13</f>
@@ -3290,7 +3287,7 @@
         <v/>
       </c>
       <c r="F32" s="8" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="G32" s="8">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
@@ -3323,10 +3320,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="11" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P32" s="11" t="n">
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q32" s="12" t="inlineStr">
         <is>
@@ -3345,7 +3342,7 @@
       </c>
       <c r="T32" s="12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>114</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3367,11 +3364,11 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>Baskets HOKA P.37 1/3 — neuves</t>
+          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
       <c r="B33" s="14" t="n">
-        <v>63</v>
+        <v>25.2</v>
       </c>
       <c r="C33" s="15">
         <f>$B33+$Y33*Paramètres!$B$13</f>
@@ -3386,7 +3383,7 @@
         <v/>
       </c>
       <c r="F33" s="17" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G33" s="17">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
@@ -3419,10 +3416,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="20" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>13</v>
+        <v>5.2</v>
       </c>
       <c r="Q33" s="21" t="inlineStr">
         <is>
@@ -3436,12 +3433,12 @@
       </c>
       <c r="S33" s="21" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-43717</t>
         </is>
       </c>
       <c r="T33" s="21" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>168</t>
         </is>
       </c>
       <c r="U33" s="13" t="inlineStr">
@@ -3467,11 +3464,11 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE sneakers P.38 — neuves</t>
+          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>38.34</v>
+        <v>51.12</v>
       </c>
       <c r="C34" s="6">
         <f>$B34+$Y34*Paramètres!$B$13</f>
@@ -3486,7 +3483,7 @@
         <v/>
       </c>
       <c r="F34" s="8" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G34" s="8">
         <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
@@ -3519,10 +3516,10 @@
         <v>0</v>
       </c>
       <c r="O34" s="11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P34" s="11" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="Q34" s="12" t="inlineStr">
         <is>
@@ -3541,7 +3538,7 @@
       </c>
       <c r="T34" s="12" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>156</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3561,212 +3558,212 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="C35" s="15">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="C35" s="6">
         <f>$B35+$Y35*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="7">
         <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="6">
         <f>CEILING($D35*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F35" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="G35" s="17">
+      <c r="F35" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G35" s="8">
         <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
         <v/>
       </c>
-      <c r="H35" s="18">
+      <c r="H35" s="9">
         <f>IF($G35="","",$G35/$C35)</f>
         <v/>
       </c>
-      <c r="I35" s="19" t="n">
+      <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="6">
         <f>$C35/$I35</f>
         <v/>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="6">
         <f>IF($F35="","",$F35/$I35)</f>
         <v/>
       </c>
-      <c r="L35" s="15">
+      <c r="L35" s="6">
         <f>IF($G35="","",$G35/$I35)</f>
         <v/>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="7">
         <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N35" s="15" t="n">
+      <c r="N35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="P35" s="20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q35" s="21" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R35" s="21" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S35" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T35" s="21" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="U35" s="13" t="inlineStr">
+      <c r="O35" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="Q35" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R35" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S35" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T35" s="12" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X35" s="4" t="inlineStr"/>
+      <c r="Y35" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>LACOSTE sneakers P.42 — neuves</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="C36" s="15">
+        <f>$B36+$Y36*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D36" s="16">
+        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
+        <f>CEILING($D36*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G36" s="17">
+        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="18">
+        <f>IF($G36="","",$G36/$C36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="15">
+        <f>$C36/$I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="15">
+        <f>IF($F36="","",$F36/$I36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="15">
+        <f>IF($G36="","",$G36/$I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="16">
+        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N36" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="P36" s="20" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q36" s="21" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R36" s="21" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S36" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T36" s="21" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="U36" s="13" t="inlineStr">
         <is>
           <t>vendu</t>
         </is>
       </c>
-      <c r="V35" s="13" t="inlineStr"/>
-      <c r="W35" s="13" t="inlineStr">
+      <c r="V36" s="13" t="inlineStr"/>
+      <c r="W36" s="13" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X35" s="13" t="inlineStr">
+      <c r="X36" s="13" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="Y35" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="C36" s="6">
-        <f>$B36+$Y36*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D36" s="7">
-        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E36" s="6">
-        <f>CEILING($D36*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G36" s="8">
-        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="9">
-        <f>IF($G36="","",$G36/$C36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="6">
-        <f>$C36/$I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="6">
-        <f>IF($F36="","",$F36/$I36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="6">
-        <f>IF($G36="","",$G36/$I36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="7">
-        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="P36" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q36" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R36" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S36" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T36" s="12" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="inlineStr"/>
-      <c r="W36" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X36" s="4" t="inlineStr"/>
-      <c r="Y36" s="4" t="n">
+      <c r="Y36" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
+          <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>52.4</v>
+        <v>35.9</v>
       </c>
       <c r="C37" s="6">
-        <f>$B37+$Y37*Paramètres!$B$13</f>
+        <f>$B37</f>
         <v/>
       </c>
       <c r="D37" s="7">
@@ -3778,7 +3775,7 @@
         <v/>
       </c>
       <c r="F37" s="8" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="G37" s="8">
         <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
@@ -3810,41 +3807,37 @@
       <c r="N37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="P37" s="11" t="n">
-        <v>10.66</v>
-      </c>
+      <c r="O37" s="22" t="n"/>
+      <c r="P37" s="22" t="n"/>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ERA Enchères Rhône-Alpes</t>
         </is>
       </c>
       <c r="R37" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="S37" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>507148</t>
         </is>
       </c>
       <c r="T37" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U37" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin, main propre</t>
         </is>
       </c>
       <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>Liquider</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X37" s="4" t="inlineStr"/>
@@ -3853,113 +3846,109 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>LACOSTE sneakers P.42 — neuves</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="n">
-        <v>57.51</v>
-      </c>
-      <c r="C38" s="15">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C38" s="25">
         <f>$B38+$Y38*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="26">
         <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="25">
         <f>CEILING($D38*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F38" s="17" t="n">
-        <v>70</v>
-      </c>
-      <c r="G38" s="17">
+      <c r="F38" s="27" t="n">
+        <v>49</v>
+      </c>
+      <c r="G38" s="27">
         <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="28">
         <f>IF($G38="","",$G38/$C38)</f>
         <v/>
       </c>
-      <c r="I38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="15">
+      <c r="I38" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" s="25">
         <f>$C38/$I38</f>
         <v/>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="25">
         <f>IF($F38="","",$F38/$I38)</f>
         <v/>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="25">
         <f>IF($G38="","",$G38/$I38)</f>
         <v/>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="26">
         <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N38" s="15" t="n">
+      <c r="N38" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="P38" s="20" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Q38" s="21" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R38" s="21" t="inlineStr">
+      <c r="O38" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="P38" s="30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q38" s="31" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R38" s="31" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S38" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T38" s="21" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="U38" s="13" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V38" s="13" t="inlineStr"/>
-      <c r="W38" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X38" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y38" s="13" t="n">
+      <c r="S38" s="31" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T38" s="31" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="U38" s="23" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V38" s="23" t="inlineStr"/>
+      <c r="W38" s="23" t="inlineStr">
+        <is>
+          <t>Marge faible</t>
+        </is>
+      </c>
+      <c r="X38" s="23" t="inlineStr"/>
+      <c r="Y38" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
+          <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>35.9</v>
+        <v>28.29</v>
       </c>
       <c r="C39" s="6">
         <f>$B39</f>
@@ -3974,7 +3963,7 @@
         <v/>
       </c>
       <c r="F39" s="8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G39" s="8">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
@@ -4025,7 +4014,7 @@
       </c>
       <c r="T39" s="12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U39" s="4" t="inlineStr">
@@ -4036,7 +4025,7 @@
       <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Marge faible</t>
         </is>
       </c>
       <c r="X39" s="4" t="inlineStr"/>
@@ -4045,109 +4034,105 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C40" s="25">
-        <f>$B40+$Y40*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D40" s="26">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="C40" s="6">
+        <f>$B40</f>
+        <v/>
+      </c>
+      <c r="D40" s="7">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="6">
         <f>CEILING($D40*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F40" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="G40" s="27">
+      <c r="F40" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G40" s="8">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
         <v/>
       </c>
-      <c r="H40" s="28">
+      <c r="H40" s="9">
         <f>IF($G40="","",$G40/$C40)</f>
         <v/>
       </c>
-      <c r="I40" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="25">
+      <c r="I40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="6">
         <f>$C40/$I40</f>
         <v/>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="6">
         <f>IF($F40="","",$F40/$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="25">
+      <c r="L40" s="6">
         <f>IF($G40="","",$G40/$I40)</f>
         <v/>
       </c>
-      <c r="M40" s="26">
+      <c r="M40" s="7">
         <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N40" s="25" t="n">
+      <c r="N40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="P40" s="30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q40" s="31" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R40" s="31" t="inlineStr">
+      <c r="O40" s="22" t="n"/>
+      <c r="P40" s="22" t="n"/>
+      <c r="Q40" s="12" t="inlineStr">
+        <is>
+          <t>Meccha Japan</t>
+        </is>
+      </c>
+      <c r="R40" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S40" s="31" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T40" s="31" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="U40" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay, en lot</t>
-        </is>
-      </c>
-      <c r="V40" s="23" t="inlineStr"/>
-      <c r="W40" s="23" t="inlineStr">
-        <is>
-          <t>Marge faible</t>
-        </is>
-      </c>
-      <c r="X40" s="23" t="inlineStr"/>
-      <c r="Y40" s="23" t="n">
+      <c r="S40" s="12" t="inlineStr">
+        <is>
+          <t>#FA429713</t>
+        </is>
+      </c>
+      <c r="T40" s="12" t="inlineStr">
+        <is>
+          <t>4521329462226</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin, lot de 2</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr"/>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X40" s="4" t="inlineStr"/>
+      <c r="Y40" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
+          <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>28.29</v>
+        <v>12.95</v>
       </c>
       <c r="C41" s="6">
         <f>$B41</f>
@@ -4161,9 +4146,7 @@
         <f>CEILING($D41*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="F41" s="22" t="n"/>
       <c r="G41" s="8">
         <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
         <v/>
@@ -4198,33 +4181,33 @@
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="12" t="inlineStr">
         <is>
-          <t>ERA Enchères Rhône-Alpes</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R41" s="12" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S41" s="12" t="inlineStr">
         <is>
-          <t>507148</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T41" s="12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>4521329431925</t>
         </is>
       </c>
       <c r="U41" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Prélevé — usage personnel</t>
         </is>
       </c>
       <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>Marge faible</t>
+          <t>PRÉLEVÉ</t>
         </is>
       </c>
       <c r="X41" s="4" t="inlineStr"/>
@@ -4235,11 +4218,11 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
+          <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>12.74</v>
+        <v>19.41</v>
       </c>
       <c r="C42" s="6">
         <f>$B42</f>
@@ -4253,9 +4236,7 @@
         <f>CEILING($D42*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>19</v>
-      </c>
+      <c r="F42" s="22" t="n"/>
       <c r="G42" s="8">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
         <v/>
@@ -4290,33 +4271,33 @@
       <c r="P42" s="22" t="n"/>
       <c r="Q42" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ERA Enchères Rhône-Alpes</t>
         </is>
       </c>
       <c r="R42" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="S42" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>507148</t>
         </is>
       </c>
       <c r="T42" s="12" t="inlineStr">
         <is>
-          <t>4521329462226</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lot de 2</t>
+          <t>Prélevée — usage personnel</t>
         </is>
       </c>
       <c r="V42" s="4" t="inlineStr"/>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>PRÉLEVÉE</t>
         </is>
       </c>
       <c r="X42" s="4" t="inlineStr"/>
@@ -4325,182 +4306,198 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="C43" s="6">
-        <f>$B43</f>
-        <v/>
-      </c>
-      <c r="D43" s="7">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C43" s="15">
+        <f>$B43+$Y43*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D43" s="16">
         <f>$C43/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="15">
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F43" s="22" t="n"/>
-      <c r="G43" s="8">
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="17">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="18">
         <f>IF($G43="","",$G43/$C43)</f>
         <v/>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="6">
+      <c r="J43" s="15">
         <f>$C43/$I43</f>
         <v/>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="15">
         <f>IF($F43="","",$F43/$I43)</f>
         <v/>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="15">
         <f>IF($G43="","",$G43/$I43)</f>
         <v/>
       </c>
-      <c r="M43" s="7">
+      <c r="M43" s="16">
         <f>IF($F43="","",$F43*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="N43" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="22" t="n"/>
-      <c r="P43" s="22" t="n"/>
-      <c r="Q43" s="12" t="inlineStr">
-        <is>
-          <t>Meccha Japan</t>
-        </is>
-      </c>
-      <c r="R43" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S43" s="12" t="inlineStr">
-        <is>
-          <t>#FA429713</t>
-        </is>
-      </c>
-      <c r="T43" s="12" t="inlineStr">
-        <is>
-          <t>4521329431925</t>
-        </is>
-      </c>
-      <c r="U43" s="4" t="inlineStr">
-        <is>
-          <t>Prélevé — usage personnel</t>
-        </is>
-      </c>
-      <c r="V43" s="4" t="inlineStr"/>
-      <c r="W43" s="4" t="inlineStr">
-        <is>
-          <t>PRÉLEVÉ</t>
-        </is>
-      </c>
-      <c r="X43" s="4" t="inlineStr"/>
-      <c r="Y43" s="4" t="n">
+      <c r="O43" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="P43" s="20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q43" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R43" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S43" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T43" s="21" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="U43" s="13" t="inlineStr">
+        <is>
+          <t>Prélevées — usage personnel</t>
+        </is>
+      </c>
+      <c r="V43" s="13" t="inlineStr"/>
+      <c r="W43" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉES</t>
+        </is>
+      </c>
+      <c r="X43" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉES 09/08</t>
+        </is>
+      </c>
+      <c r="Y43" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>19.41</v>
-      </c>
-      <c r="C44" s="6">
-        <f>$B44</f>
-        <v/>
-      </c>
-      <c r="D44" s="7">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>Baskets HOKA P.37 1/3 — neuves</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="C44" s="15">
+        <f>$B44+$Y44*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D44" s="16">
         <f>$C44/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="15">
         <f>CEILING($D44*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F44" s="22" t="n"/>
-      <c r="G44" s="8">
+      <c r="F44" s="32" t="n"/>
+      <c r="G44" s="17">
         <f>IF($F44="","",$F44-$C44-$M44-$N44)</f>
         <v/>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="18">
         <f>IF($G44="","",$G44/$C44)</f>
         <v/>
       </c>
-      <c r="I44" s="10" t="n">
+      <c r="I44" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="6">
+      <c r="J44" s="15">
         <f>$C44/$I44</f>
         <v/>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="15">
         <f>IF($F44="","",$F44/$I44)</f>
         <v/>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="15">
         <f>IF($G44="","",$G44/$I44)</f>
         <v/>
       </c>
-      <c r="M44" s="7">
+      <c r="M44" s="16">
         <f>IF($F44="","",$F44*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="N44" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="22" t="n"/>
-      <c r="P44" s="22" t="n"/>
-      <c r="Q44" s="12" t="inlineStr">
-        <is>
-          <t>ERA Enchères Rhône-Alpes</t>
-        </is>
-      </c>
-      <c r="R44" s="12" t="inlineStr">
-        <is>
-          <t>26/07/2026</t>
-        </is>
-      </c>
-      <c r="S44" s="12" t="inlineStr">
-        <is>
-          <t>507148</t>
-        </is>
-      </c>
-      <c r="T44" s="12" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>Prélevée — usage personnel</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="inlineStr"/>
-      <c r="W44" s="4" t="inlineStr">
-        <is>
-          <t>PRÉLEVÉE</t>
-        </is>
-      </c>
-      <c r="X44" s="4" t="inlineStr"/>
-      <c r="Y44" s="4" t="n">
+      <c r="O44" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="P44" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q44" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R44" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S44" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T44" s="21" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="U44" s="13" t="inlineStr">
+        <is>
+          <t>Prélevées — usage personnel</t>
+        </is>
+      </c>
+      <c r="V44" s="13" t="inlineStr"/>
+      <c r="W44" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉES</t>
+        </is>
+      </c>
+      <c r="X44" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉES 09/08</t>
+        </is>
+      </c>
+      <c r="Y44" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4599,59 +4596,59 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="inlineStr">
+      <c r="A46" s="33" t="inlineStr">
         <is>
           <t>TOTAL — 40 lots</t>
         </is>
       </c>
-      <c r="B46" s="33">
+      <c r="B46" s="34">
         <f>SUM(B6:B45)</f>
         <v/>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="34">
         <f>SUM(C6:C45)</f>
         <v/>
       </c>
-      <c r="D46" s="34" t="n"/>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="33">
+      <c r="D46" s="35" t="n"/>
+      <c r="E46" s="35" t="n"/>
+      <c r="F46" s="34">
         <f>SUM(F6:F45)</f>
         <v/>
       </c>
-      <c r="G46" s="33">
+      <c r="G46" s="34">
         <f>SUM(G6:G45)</f>
         <v/>
       </c>
-      <c r="H46" s="35">
+      <c r="H46" s="36">
         <f>G46/C46</f>
         <v/>
       </c>
-      <c r="I46" s="36">
+      <c r="I46" s="37">
         <f>SUM(I6:I45)</f>
         <v/>
       </c>
-      <c r="J46" s="34" t="n"/>
-      <c r="K46" s="34" t="n"/>
-      <c r="L46" s="34" t="n"/>
-      <c r="M46" s="33">
+      <c r="J46" s="35" t="n"/>
+      <c r="K46" s="35" t="n"/>
+      <c r="L46" s="35" t="n"/>
+      <c r="M46" s="34">
         <f>SUM(M6:M45)</f>
         <v/>
       </c>
-      <c r="N46" s="33">
+      <c r="N46" s="34">
         <f>SUM(N6:N45)</f>
         <v/>
       </c>
-      <c r="O46" s="34" t="n"/>
-      <c r="P46" s="34" t="n"/>
-      <c r="Q46" s="34" t="n"/>
-      <c r="R46" s="34" t="n"/>
-      <c r="S46" s="34" t="n"/>
-      <c r="T46" s="34" t="n"/>
-      <c r="U46" s="34" t="n"/>
-      <c r="V46" s="34" t="n"/>
-      <c r="W46" s="34" t="n"/>
-      <c r="X46" s="34" t="n"/>
-      <c r="Y46" s="34" t="n"/>
+      <c r="O46" s="35" t="n"/>
+      <c r="P46" s="35" t="n"/>
+      <c r="Q46" s="35" t="n"/>
+      <c r="R46" s="35" t="n"/>
+      <c r="S46" s="35" t="n"/>
+      <c r="T46" s="35" t="n"/>
+      <c r="U46" s="35" t="n"/>
+      <c r="V46" s="35" t="n"/>
+      <c r="W46" s="35" t="n"/>
+      <c r="X46" s="35" t="n"/>
+      <c r="Y46" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:Y45"/>
@@ -4686,14 +4683,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>CAPITAL ENGAGÉ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Marchandise ADN</t>
         </is>
@@ -4703,7 +4700,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>Livraison ADN</t>
         </is>
@@ -4714,7 +4711,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>Achats hors ADN (pompes, Pokémon)</t>
         </is>
@@ -4724,25 +4721,25 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>TOTAL ENGAGÉ</t>
         </is>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="34">
         <f>'Stock complet'!C46</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>CHIFFRE D'AFFAIRES ET MARGE</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Chiffre d'affaires attendu</t>
         </is>
@@ -4758,7 +4755,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>− URSSAF + CFP</t>
         </is>
@@ -4769,7 +4766,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>− Commission carte</t>
         </is>
@@ -4780,17 +4777,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39">
+      <c r="A13" s="40">
         <f> Marge brute</f>
         <v/>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>'Stock complet'!G46</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>− Emballage</t>
         </is>
@@ -4801,7 +4798,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>− Frais fixe carte</t>
         </is>
@@ -4812,17 +4809,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39">
+      <c r="A16" s="40">
         <f> Marge avant impôt</f>
         <v/>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="34">
         <f>B13+B14+B15</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Base imposable</t>
         </is>
@@ -4833,7 +4830,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>− Impôt estimé</t>
         </is>
@@ -4844,81 +4841,81 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39">
+      <c r="A19" s="40">
         <f> CE QUI RESTE</f>
         <v/>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="41">
         <f>B16+B18</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>RENDEMENT</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>Marge nette / capital engagé</t>
         </is>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="42">
         <f>B19/B7</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>Articles physiques</t>
         </is>
       </c>
-      <c r="B23" s="42">
+      <c r="B23" s="43">
         <f>'Stock complet'!I46</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>À FAIRE</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>1 lot sans prix : Yeezy 700 V3, en attente d'authentification.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t>Ventes du 09/08 et du 10/08/2026 : espèces, main propre. Nom de l'acheteur à noter.</t>
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>CA encaissé : 343 €, pas 493 €. Les Hoka et les Nike sont des prélèvements, pas des ventes.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
-        <is>
-          <t>Factures annoncées : lot n°84 (3 pompes Robby) et boîte de 30 boosters Pokémon.</t>
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>Toutes les factures sont reçues. 150,50 € de stock prélevé pour usage personnel.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
+      <c r="A29" s="44" t="inlineStr">
         <is>
           <t>SEUIL D'ÉQUILIBRE : ne jamais vendre en dessous, la vente coûterait de l'argent.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>PRIX PLANCHER : 30 % au-dessus du seuil. Le plus bas acceptable, famille comprise.</t>
         </is>
@@ -4965,19 +4962,19 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>CHARGES SUR LE CHIFFRE D'AFFAIRES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>Cotisations URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="45" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4987,22 +4984,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>CFP — formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="45" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="45" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5012,24 +5009,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="46" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>LIVRAISON DES LOTS</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Total des factures de livraison ADN</t>
         </is>
@@ -5044,7 +5041,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Unités de vente reçues d'ADN</t>
         </is>
@@ -5059,7 +5056,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Livraison par unité de vente</t>
         </is>
@@ -5075,19 +5072,19 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>IMPÔT SUR LE REVENU — MICRO-BIC</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B16" s="44" t="n">
+      <c r="B16" s="45" t="n">
         <v>0.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5097,12 +5094,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Tranche marginale du foyer</t>
         </is>
       </c>
-      <c r="B17" s="44" t="n">
+      <c r="B17" s="45" t="n">
         <v>0.11</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5112,46 +5109,46 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>FRAIS DE VENTE</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>Emballage par colis</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n">
+      <c r="B20" s="46" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Nombre d'annonces prévues</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n">
+      <c r="B21" s="47" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>PLANCHER DE NÉGOCIATION</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>Coefficient sur le seuil d'équilibre</t>
         </is>
       </c>
-      <c r="B24" s="47" t="n">
+      <c r="B24" s="48" t="n">
         <v>1.3</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -6749,67 +6746,67 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="34" t="n"/>
-      <c r="B39" s="34" t="n"/>
-      <c r="C39" s="34" t="n"/>
-      <c r="D39" s="34" t="n"/>
-      <c r="E39" s="34" t="n"/>
-      <c r="F39" s="32" t="inlineStr">
+      <c r="A39" s="35" t="n"/>
+      <c r="B39" s="35" t="n"/>
+      <c r="C39" s="35" t="n"/>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="33" t="inlineStr">
         <is>
           <t>TOTAL MARCHANDISE</t>
         </is>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <f>SUM(G5:G38)</f>
         <v/>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <f>SUM(H5:H38)</f>
         <v/>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <f>SUM(I5:I38)</f>
         <v/>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <f>SUM(J5:J38)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>FACTURES DE LIVRAISON</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="48" t="inlineStr">
+      <c r="A42" s="49" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="B42" s="48" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C42" s="48" t="inlineStr">
+      <c r="C42" s="49" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="D42" s="48" t="inlineStr">
+      <c r="D42" s="49" t="inlineStr">
         <is>
           <t>Commande</t>
         </is>
       </c>
-      <c r="E42" s="48" t="inlineStr">
+      <c r="E42" s="49" t="inlineStr">
         <is>
           <t>Désignation</t>
         </is>
       </c>
-      <c r="F42" s="48" t="inlineStr">
+      <c r="F42" s="49" t="inlineStr">
         <is>
           <t>Total TTC</t>
         </is>
@@ -6966,16 +6963,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="34" t="n"/>
-      <c r="B48" s="34" t="n"/>
-      <c r="C48" s="34" t="n"/>
-      <c r="D48" s="34" t="n"/>
-      <c r="E48" s="32" t="inlineStr">
+      <c r="A48" s="35" t="n"/>
+      <c r="B48" s="35" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="33" t="inlineStr">
         <is>
           <t>TOTAL LIVRAISON</t>
         </is>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="34">
         <f>SUM(F43:F47)</f>
         <v/>
       </c>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -21,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00 &quot;€&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0 &quot;art.&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -140,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,11 +188,13 @@
     <xf numFmtId="165" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -4667,7 +4670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4879,50 +4882,159 @@
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t>À FAIRE</t>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>Taux de marge nette sur le CA</t>
+        </is>
+      </c>
+      <c r="B24" s="42">
+        <f>B19/B10</f>
+        <v/>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ce qui reste pour 1 € encaissé</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
-        <is>
-          <t>1 lot sans prix : Yeezy 700 V3, en attente d'authentification.</t>
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>CHARGES FIXES — CE QUE LA BOUTIQUE COÛTE AVANT DE VENDRE</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="44" t="inlineStr">
-        <is>
-          <t>CA encaissé : 343 €, pas 493 €. Les Hoka et les Nike sont des prélèvements, pas des ventes.</t>
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Shopify + Claude, aujourd'hui</t>
+        </is>
+      </c>
+      <c r="B27" s="6">
+        <f>Paramètres!B30</f>
+        <v/>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1 € + 22 €</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="39" t="inlineStr">
         <is>
+          <t>Shopify + Claude, à partir du 11/11/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="6">
+        <f>Paramètres!B31</f>
+        <v/>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>36 € + 22 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>Soit par an, à partir de novembre</t>
+        </is>
+      </c>
+      <c r="B29" s="34">
+        <f>Paramètres!B31*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>CA mensuel nécessaire pour les couvrir</t>
+        </is>
+      </c>
+      <c r="B30" s="41">
+        <f>Paramètres!B31/B24</f>
+        <v/>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>au taux de marge nette du stock actuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
+        <is>
+          <t>Marge du stock entier</t>
+        </is>
+      </c>
+      <c r="B31" s="6">
+        <f>B19</f>
+        <v/>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>de quoi couvrir combien de mois :</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>Mois de charges couverts par tout le stock</t>
+        </is>
+      </c>
+      <c r="B32" s="44">
+        <f>B19/Paramètres!B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>À FAIRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>1 lot sans prix : Yeezy 700 V3, en attente d'authentification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="45" t="inlineStr">
+        <is>
+          <t>CA encaissé : 343 €, pas 493 €. Les Hoka et les Nike sont des prélèvements, pas des ventes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
           <t>Toutes les factures sont reçues. 150,50 € de stock prélevé pour usage personnel.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="44" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="45" t="inlineStr">
         <is>
           <t>SEUIL D'ÉQUILIBRE : ne jamais vendre en dessous, la vente coûterait de l'argent.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>PRIX PLANCHER : 30 % au-dessus du seuil. Le plus bas acceptable, famille comprise.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Ne pas confondre avec le seuil de sourcing de 25 € : celui-là sert à decider d'ACHETER, pas de vendre.</t>
         </is>
@@ -4939,7 +5051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4974,7 +5086,7 @@
           <t>Cotisations URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="45" t="n">
+      <c r="B5" s="46" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4989,7 +5101,7 @@
           <t>CFP — formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="46" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -4999,7 +5111,7 @@
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="45" t="n">
+      <c r="B7" s="46" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5014,7 +5126,7 @@
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5084,7 +5196,7 @@
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B16" s="45" t="n">
+      <c r="B16" s="46" t="n">
         <v>0.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5099,7 +5211,7 @@
           <t>Tranche marginale du foyer</t>
         </is>
       </c>
-      <c r="B17" s="45" t="n">
+      <c r="B17" s="46" t="n">
         <v>0.11</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5121,7 +5233,7 @@
           <t>Emballage par colis</t>
         </is>
       </c>
-      <c r="B20" s="46" t="n">
+      <c r="B20" s="47" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5131,7 +5243,7 @@
           <t>Nombre d'annonces prévues</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n">
+      <c r="B21" s="48" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5148,12 +5260,113 @@
           <t>Coefficient sur le seuil d'équilibre</t>
         </is>
       </c>
-      <c r="B24" s="48" t="n">
+      <c r="B24" s="49" t="n">
         <v>1.3</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>plancher = seuil × ce coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>CHARGES FIXES MENSUELLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Abonnement Shopify — aujourd'hui</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1 €/mois jusqu'au 10/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>Abonnement Shopify — à partir du 11/11/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="47" t="n">
+        <v>36</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>432 €/an</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>Abonnement Claude</t>
+        </is>
+      </c>
+      <c r="B29" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>264 €/an</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>Total mensuel aujourd'hui</t>
+        </is>
+      </c>
+      <c r="B30" s="50">
+        <f>B27+B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
+        <is>
+          <t>Total mensuel à partir du 11/11/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="50">
+        <f>B28+B29</f>
+        <v/>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>696 €/an</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>CHARGES FIXES ANNUELLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="inlineStr">
+        <is>
+          <t>CFE — cotisation foncière des entreprises</t>
+        </is>
+      </c>
+      <c r="B34" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>exonérée en 2026, 200 à 600 €/an à partir de 2027</t>
         </is>
       </c>
     </row>
@@ -6781,32 +6994,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="49" t="inlineStr">
+      <c r="A42" s="51" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="B42" s="49" t="inlineStr">
+      <c r="B42" s="51" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C42" s="49" t="inlineStr">
+      <c r="C42" s="51" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="D42" s="49" t="inlineStr">
+      <c r="D42" s="51" t="inlineStr">
         <is>
           <t>Commande</t>
         </is>
       </c>
-      <c r="E42" s="49" t="inlineStr">
+      <c r="E42" s="51" t="inlineStr">
         <is>
           <t>Désignation</t>
         </is>
       </c>
-      <c r="F42" s="49" t="inlineStr">
+      <c r="F42" s="51" t="inlineStr">
         <is>
           <t>Total TTC</t>
         </is>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -1040,117 +1040,120 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="C9" s="15">
         <f>$B9+$Y9*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D9" s="7">
-        <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="16">
+        <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
         <f>CEILING($D9*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F9" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="F9" s="17" t="n">
+        <v>208</v>
+      </c>
+      <c r="G9" s="17">
         <f>IF($F9="","",$F9-$C9-$M9-$N9)</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="18">
         <f>IF($G9="","",$G9/$C9)</f>
         <v/>
       </c>
-      <c r="I9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="6">
+      <c r="I9" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" s="15">
         <f>$C9/$I9</f>
         <v/>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="15">
         <f>IF($F9="","",$F9/$I9)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="15">
         <f>IF($G9="","",$G9/$I9)</f>
         <v/>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="16">
         <f>IF($F9="","",$F9*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N9" s="6">
-        <f>IF($F9="","",$F9*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O9" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="P9" s="11" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q9" s="12" t="inlineStr">
+      <c r="N9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="P9" s="20" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R9" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S9" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-5996</t>
-        </is>
-      </c>
-      <c r="T9" s="12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="n">
-        <v>1</v>
+      <c r="R9" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S9" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-5844</t>
+        </is>
+      </c>
+      <c r="T9" s="21" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="U9" s="13" t="inlineStr">
+        <is>
+          <t>Vinted + Leboncoin, à l'unité</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="inlineStr"/>
+      <c r="W9" s="13" t="inlineStr">
+        <is>
+          <t>URGENT — 10 restent, monter à 18 €</t>
+        </is>
+      </c>
+      <c r="X9" s="13" t="inlineStr">
+        <is>
+          <t>2 vendues à 14 € le 10/08</t>
+        </is>
+      </c>
+      <c r="Y9" s="13" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
+          <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>68.56999999999999</v>
+        <v>20.45</v>
       </c>
       <c r="C10" s="6">
         <f>$B10+$Y10*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E10" s="6">
@@ -1158,7 +1161,7 @@
         <v/>
       </c>
       <c r="F10" s="8" t="n">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="G10" s="8">
         <f>IF($F10="","",$F10-$C10-$M10-$N10)</f>
@@ -1187,38 +1190,39 @@
         <f>IF($F10="","",$F10*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N10" s="6" t="n">
-        <v>0</v>
+      <c r="N10" s="6">
+        <f>IF($F10="","",$F10*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O10" s="11" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="P10" s="11" t="n">
-        <v>8.57</v>
+        <v>4.16</v>
       </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R10" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46060</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T10" s="12" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr"/>
@@ -1235,18 +1239,18 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Chaussures HOGAN P.36 — traces d'essayage</t>
+          <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>12.6</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="C11" s="6">
         <f>$B11+$Y11*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E11" s="6">
@@ -1254,7 +1258,7 @@
         <v/>
       </c>
       <c r="F11" s="8" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="G11" s="8">
         <f>IF($F11="","",$F11-$C11-$M11-$N11)</f>
@@ -1283,15 +1287,14 @@
         <f>IF($F11="","",$F11*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N11" s="6">
-        <f>IF($F11="","",$F11*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>2.6</v>
+        <v>8.57</v>
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
@@ -1300,22 +1303,22 @@
       </c>
       <c r="R11" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-46060</t>
         </is>
       </c>
       <c r="T11" s="12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
@@ -1332,11 +1335,11 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
+          <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>37.8</v>
+        <v>12.6</v>
       </c>
       <c r="C12" s="6">
         <f>$B12+$Y12*Paramètres!$B$13</f>
@@ -1351,7 +1354,7 @@
         <v/>
       </c>
       <c r="F12" s="8" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="G12" s="8">
         <f>IF($F12="","",$F12-$C12-$M12-$N12)</f>
@@ -1385,10 +1388,10 @@
         <v/>
       </c>
       <c r="O12" s="11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
@@ -1407,7 +1410,7 @@
       </c>
       <c r="T12" s="12" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
@@ -1429,7 +1432,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Robe SANDRO T.40 — neuve</t>
+          <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -1448,7 +1451,7 @@
         <v/>
       </c>
       <c r="F13" s="8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G13" s="8">
         <f>IF($F13="","",$F13-$C13-$M13-$N13)</f>
@@ -1504,7 +1507,7 @@
       </c>
       <c r="T13" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>417</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
@@ -1526,7 +1529,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
+          <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -1537,7 +1540,7 @@
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E14" s="6">
@@ -1545,7 +1548,7 @@
         <v/>
       </c>
       <c r="F14" s="8" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G14" s="8">
         <f>IF($F14="","",$F14-$C14-$M14-$N14)</f>
@@ -1556,7 +1559,7 @@
         <v/>
       </c>
       <c r="I14" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J14" s="6">
         <f>$C14/$I14</f>
@@ -1574,8 +1577,9 @@
         <f>IF($F14="","",$F14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N14" s="6" t="n">
-        <v>0</v>
+      <c r="N14" s="6">
+        <f>IF($F14="","",$F14*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O14" s="11" t="n">
         <v>30</v>
@@ -1590,22 +1594,22 @@
       </c>
       <c r="R14" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46056</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T14" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr"/>
@@ -1616,13 +1620,13 @@
       </c>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
+          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -1633,7 +1637,7 @@
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E15" s="6">
@@ -1641,7 +1645,7 @@
         <v/>
       </c>
       <c r="F15" s="8" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G15" s="8">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
@@ -1652,7 +1656,7 @@
         <v/>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J15" s="6">
         <f>$C15/$I15</f>
@@ -1670,9 +1674,8 @@
         <f>IF($F15="","",$F15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N15" s="6">
-        <f>IF($F15="","",$F15*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O15" s="11" t="n">
         <v>30</v>
@@ -1687,22 +1690,22 @@
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-46056</t>
         </is>
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>279</t>
         </is>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
@@ -1713,107 +1716,104 @@
       </c>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="C16" s="6">
+        <f>$B16+$Y16*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D16" s="7">
+        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E16" s="6">
+        <f>CEILING($D16*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="G16" s="8">
+        <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>IF($G16="","",$G16/$C16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="10" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="C16" s="15">
-        <f>$B16+$Y16*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D16" s="16">
-        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E16" s="15">
-        <f>CEILING($D16*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>168</v>
-      </c>
-      <c r="G16" s="17">
-        <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="18">
-        <f>IF($G16="","",$G16/$C16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" s="15">
+      <c r="J16" s="6">
         <f>$C16/$I16</f>
         <v/>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="6">
         <f>IF($F16="","",$F16/$I16)</f>
         <v/>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="6">
         <f>IF($G16="","",$G16/$I16)</f>
         <v/>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="7">
         <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="20" t="n">
-        <v>80</v>
-      </c>
-      <c r="P16" s="20" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q16" s="21" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R16" s="21" t="inlineStr">
+      <c r="N16" s="6">
+        <f>IF($F16="","",$F16*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q16" s="12" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R16" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S16" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-5844</t>
-        </is>
-      </c>
-      <c r="T16" s="21" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="U16" s="13" t="inlineStr">
-        <is>
-          <t>Leboncoin, à l'unité</t>
-        </is>
-      </c>
-      <c r="V16" s="13" t="inlineStr"/>
-      <c r="W16" s="13" t="inlineStr">
-        <is>
-          <t>URGENT — 2 sur 12 vendues</t>
-        </is>
-      </c>
-      <c r="X16" s="13" t="inlineStr">
-        <is>
-          <t>2 vendues</t>
-        </is>
-      </c>
-      <c r="Y16" s="13" t="n">
-        <v>12</v>
+      <c r="S16" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T16" s="12" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>Boutique</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr"/>
+      <c r="Y16" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -1645,7 +1645,7 @@
         <v/>
       </c>
       <c r="F15" s="8" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G15" s="8">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Leboncoin + eBay, à l'unité</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr"/>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Factures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$Y$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock complet'!$A$5:$AA$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -166,7 +166,6 @@
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +175,7 @@
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,11 +202,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FCE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E3F4E3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -572,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -600,6 +607,8 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -749,6 +758,16 @@
           <t>Unités de vente</t>
         </is>
       </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>MARGE PAR ANNONCE</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Objectif 25 €</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -845,6 +864,14 @@
       <c r="Y6" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z6" s="8">
+        <f>IF($G6="","",$G6/$Y6)</f>
+        <v/>
+      </c>
+      <c r="AA6" s="4">
+        <f>IF($Z6="","",IF($Z6&gt;=25,"atteint",TEXT(25-$Z6,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -941,6 +968,14 @@
       <c r="Y7" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="Z7" s="8">
+        <f>IF($G7="","",$G7/$Y7)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="4">
+        <f>IF($Z7="","",IF($Z7&gt;=25,"atteint",TEXT(25-$Z7,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1038,219 +1073,242 @@
       <c r="Y8" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z8" s="8">
+        <f>IF($G8="","",$G8/$Y8)</f>
+        <v/>
+      </c>
+      <c r="AA8" s="4">
+        <f>IF($Z8="","",IF($Z8&gt;=25,"atteint",TEXT(25-$Z8,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="C9" s="6">
+        <f>$B9+$Y9*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
+        <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E9" s="6">
+        <f>CEILING($D9*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="G9" s="8">
+        <f>IF($F9="","",$F9-$C9-$M9-$N9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>IF($G9="","",$G9/$C9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="6">
+        <f>$C9/$I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="6">
+        <f>IF($F9="","",$F9/$I9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="6">
+        <f>IF($G9="","",$G9/$I9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="7">
+        <f>IF($F9="","",$F9*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R9" s="12" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43717</t>
+        </is>
+      </c>
+      <c r="T9" s="12" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + Vinted, 34 €/gilet</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr"/>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>URGENT — saisonnier</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr"/>
+      <c r="Y9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="8">
+        <f>IF($G9="","",$G9/$Y9)</f>
+        <v/>
+      </c>
+      <c r="AA9" s="4">
+        <f>IF($Z9="","",IF($Z9&gt;=25,"atteint",TEXT(25-$Z9,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B10" s="14" t="n">
         <v>100.8</v>
       </c>
-      <c r="C9" s="15">
-        <f>$B9+$Y9*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D9" s="16">
-        <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E9" s="15">
-        <f>CEILING($D9*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F9" s="17" t="n">
+      <c r="C10" s="15">
+        <f>$B10+$Y10*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>CEILING($D10*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F10" s="17" t="n">
         <v>208</v>
       </c>
-      <c r="G9" s="17">
-        <f>IF($F9="","",$F9-$C9-$M9-$N9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="18">
-        <f>IF($G9="","",$G9/$C9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="19" t="n">
+      <c r="G10" s="17">
+        <f>IF($F10="","",$F10-$C10-$M10-$N10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="18">
+        <f>IF($G10="","",$G10/$C10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="J9" s="15">
-        <f>$C9/$I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="15">
-        <f>IF($F9="","",$F9/$I9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="15">
-        <f>IF($G9="","",$G9/$I9)</f>
-        <v/>
-      </c>
-      <c r="M9" s="16">
-        <f>IF($F9="","",$F9*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N9" s="15" t="n">
+      <c r="J10" s="15">
+        <f>$C10/$I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="15">
+        <f>IF($F10="","",$F10/$I10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="15">
+        <f>IF($G10="","",$G10/$I10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="16">
+        <f>IF($F10="","",$F10*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="20" t="n">
+      <c r="O10" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="P9" s="20" t="n">
+      <c r="P10" s="20" t="n">
         <v>20.8</v>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R9" s="21" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S9" s="21" t="inlineStr">
+      <c r="S10" s="21" t="inlineStr">
         <is>
           <t>FB2026-5844</t>
         </is>
       </c>
-      <c r="T9" s="21" t="inlineStr">
+      <c r="T10" s="21" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="U9" s="13" t="inlineStr">
+      <c r="U10" s="13" t="inlineStr">
         <is>
           <t>Vinted + Leboncoin, à l'unité</t>
         </is>
       </c>
-      <c r="V9" s="13" t="inlineStr"/>
-      <c r="W9" s="13" t="inlineStr">
+      <c r="V10" s="13" t="inlineStr"/>
+      <c r="W10" s="13" t="inlineStr">
         <is>
           <t>URGENT — 10 restent, monter à 18 €</t>
         </is>
       </c>
-      <c r="X9" s="13" t="inlineStr">
+      <c r="X10" s="13" t="inlineStr">
         <is>
           <t>2 vendues à 14 € le 10/08</t>
         </is>
       </c>
-      <c r="Y9" s="13" t="n">
+      <c r="Y10" s="13" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="C10" s="6">
-        <f>$B10+$Y10*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D10" s="7">
-        <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>CEILING($D10*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="G10" s="8">
-        <f>IF($F10="","",$F10-$C10-$M10-$N10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="9">
-        <f>IF($G10="","",$G10/$C10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="6">
-        <f>$C10/$I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="6">
-        <f>IF($F10="","",$F10/$I10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="6">
-        <f>IF($G10="","",$G10/$I10)</f>
-        <v/>
-      </c>
-      <c r="M10" s="7">
-        <f>IF($F10="","",$F10*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N10" s="6">
-        <f>IF($F10="","",$F10*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="P10" s="11" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q10" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R10" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S10" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-5996</t>
-        </is>
-      </c>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="n">
-        <v>1</v>
+      <c r="Z10" s="17">
+        <f>IF($G10="","",$G10/$Y10)</f>
+        <v/>
+      </c>
+      <c r="AA10" s="13">
+        <f>IF($Z10="","",IF($Z10&gt;=25,"atteint",TEXT(25-$Z10,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
+          <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>68.56999999999999</v>
+        <v>20.45</v>
       </c>
       <c r="C11" s="6">
         <f>$B11+$Y11*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E11" s="6">
@@ -1258,7 +1316,7 @@
         <v/>
       </c>
       <c r="F11" s="8" t="n">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="G11" s="8">
         <f>IF($F11="","",$F11-$C11-$M11-$N11)</f>
@@ -1287,38 +1345,39 @@
         <f>IF($F11="","",$F11*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N11" s="6" t="n">
-        <v>0</v>
+      <c r="N11" s="6">
+        <f>IF($F11="","",$F11*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O11" s="11" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>8.57</v>
+        <v>4.16</v>
       </c>
       <c r="Q11" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R11" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46060</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T11" s="12" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + Vinted</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr"/>
@@ -1331,22 +1390,30 @@
       <c r="Y11" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z11" s="8">
+        <f>IF($G11="","",$G11/$Y11)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="4">
+        <f>IF($Z11="","",IF($Z11&gt;=25,"atteint",TEXT(25-$Z11,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Chaussures HOGAN P.36 — traces d'essayage</t>
+          <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12.6</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="C12" s="6">
         <f>$B12+$Y12*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>$C12/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C12/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E12" s="6">
@@ -1354,7 +1421,7 @@
         <v/>
       </c>
       <c r="F12" s="8" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="G12" s="8">
         <f>IF($F12="","",$F12-$C12-$M12-$N12)</f>
@@ -1383,15 +1450,14 @@
         <f>IF($F12="","",$F12*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N12" s="6">
-        <f>IF($F12="","",$F12*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N12" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O12" s="11" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>2.6</v>
+        <v>8.57</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
         <is>
@@ -1400,22 +1466,22 @@
       </c>
       <c r="R12" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-46060</t>
         </is>
       </c>
       <c r="T12" s="12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + Vinted</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr"/>
@@ -1428,15 +1494,23 @@
       <c r="Y12" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z12" s="8">
+        <f>IF($G12="","",$G12/$Y12)</f>
+        <v/>
+      </c>
+      <c r="AA12" s="4">
+        <f>IF($Z12="","",IF($Z12&gt;=25,"atteint",TEXT(25-$Z12,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
+          <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>37.8</v>
+        <v>12.6</v>
       </c>
       <c r="C13" s="6">
         <f>$B13+$Y13*Paramètres!$B$13</f>
@@ -1451,7 +1525,7 @@
         <v/>
       </c>
       <c r="F13" s="8" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="G13" s="8">
         <f>IF($F13="","",$F13-$C13-$M13-$N13)</f>
@@ -1485,10 +1559,10 @@
         <v/>
       </c>
       <c r="O13" s="11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" s="12" t="inlineStr">
         <is>
@@ -1507,7 +1581,7 @@
       </c>
       <c r="T13" s="12" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
@@ -1525,11 +1599,19 @@
       <c r="Y13" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z13" s="8">
+        <f>IF($G13="","",$G13/$Y13)</f>
+        <v/>
+      </c>
+      <c r="AA13" s="4">
+        <f>IF($Z13="","",IF($Z13&gt;=25,"atteint",TEXT(25-$Z13,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Robe SANDRO T.40 — neuve</t>
+          <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -1548,7 +1630,7 @@
         <v/>
       </c>
       <c r="F14" s="8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G14" s="8">
         <f>IF($F14="","",$F14-$C14-$M14-$N14)</f>
@@ -1604,7 +1686,7 @@
       </c>
       <c r="T14" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>417</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
@@ -1622,11 +1704,19 @@
       <c r="Y14" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z14" s="8">
+        <f>IF($G14="","",$G14/$Y14)</f>
+        <v/>
+      </c>
+      <c r="AA14" s="4">
+        <f>IF($Z14="","",IF($Z14&gt;=25,"atteint",TEXT(25-$Z14,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
+          <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -1637,7 +1727,7 @@
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E15" s="6">
@@ -1645,7 +1735,7 @@
         <v/>
       </c>
       <c r="F15" s="8" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G15" s="8">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
@@ -1656,7 +1746,7 @@
         <v/>
       </c>
       <c r="I15" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J15" s="6">
         <f>$C15/$I15</f>
@@ -1674,8 +1764,9 @@
         <f>IF($F15="","",$F15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N15" s="6" t="n">
-        <v>0</v>
+      <c r="N15" s="6">
+        <f>IF($F15="","",$F15*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O15" s="11" t="n">
         <v>30</v>
@@ -1690,22 +1781,22 @@
       </c>
       <c r="R15" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>FB2026-46056</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay, à l'unité</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr"/>
@@ -1716,13 +1807,21 @@
       </c>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="Z15" s="8">
+        <f>IF($G15="","",$G15/$Y15)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="4">
+        <f>IF($Z15="","",IF($Z15&gt;=25,"atteint",TEXT(25-$Z15,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
+          <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1733,7 +1832,7 @@
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E16" s="6">
@@ -1741,7 +1840,7 @@
         <v/>
       </c>
       <c r="F16" s="8" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="G16" s="8">
         <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
@@ -1752,7 +1851,7 @@
         <v/>
       </c>
       <c r="I16" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J16" s="6">
         <f>$C16/$I16</f>
@@ -1770,9 +1869,8 @@
         <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N16" s="6">
-        <f>IF($F16="","",$F16*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N16" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O16" s="11" t="n">
         <v>30</v>
@@ -1787,22 +1885,22 @@
       </c>
       <c r="R16" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-46056</t>
         </is>
       </c>
       <c r="T16" s="12" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>279</t>
         </is>
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin + eBay, à l'unité</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr"/>
@@ -1813,24 +1911,32 @@
       </c>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="Z16" s="8">
+        <f>IF($G16="","",$G16/$Y16)</f>
+        <v/>
+      </c>
+      <c r="AA16" s="4">
+        <f>IF($Z16="","",IF($Z16&gt;=25,"atteint",TEXT(25-$Z16,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
+          <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>50.4</v>
+        <v>63</v>
       </c>
       <c r="C17" s="6">
         <f>$B17+$Y17*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E17" s="6">
@@ -1838,7 +1944,7 @@
         <v/>
       </c>
       <c r="F17" s="8" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G17" s="8">
         <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
@@ -1867,15 +1973,14 @@
         <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N17" s="6">
-        <f>IF($F17="","",$F17*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>10.4</v>
+        <v>13</v>
       </c>
       <c r="Q17" s="12" t="inlineStr">
         <is>
@@ -1884,43 +1989,51 @@
       </c>
       <c r="R17" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-46056</t>
         </is>
       </c>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Vinted, authentification</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Après authentification</t>
         </is>
       </c>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z17" s="8">
+        <f>IF($G17="","",$G17/$Y17)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="4">
+        <f>IF($Z17="","",IF($Z17&gt;=25,"atteint",TEXT(25-$Z17,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
+          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>31.95</v>
+        <v>37.8</v>
       </c>
       <c r="C18" s="6">
         <f>$B18+$Y18*Paramètres!$B$13</f>
@@ -1935,7 +2048,7 @@
         <v/>
       </c>
       <c r="F18" s="8" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G18" s="8">
         <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
@@ -1969,34 +2082,34 @@
         <v/>
       </c>
       <c r="O18" s="11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P18" s="11" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q18" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R18" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T18" s="12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>434</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr"/>
@@ -2009,22 +2122,30 @@
       <c r="Y18" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z18" s="8">
+        <f>IF($G18="","",$G18/$Y18)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="4">
+        <f>IF($Z18="","",IF($Z18&gt;=25,"atteint",TEXT(25-$Z18,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
+          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>25.2</v>
+        <v>50.4</v>
       </c>
       <c r="C19" s="6">
         <f>$B19+$Y19*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E19" s="6">
@@ -2032,7 +2153,7 @@
         <v/>
       </c>
       <c r="F19" s="8" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="G19" s="8">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
@@ -2061,14 +2182,15 @@
         <f>IF($F19="","",$F19*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N19" s="6" t="n">
-        <v>0</v>
+      <c r="N19" s="6">
+        <f>IF($F19="","",$F19*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O19" s="11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P19" s="11" t="n">
-        <v>5.2</v>
+        <v>10.4</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
@@ -2077,22 +2199,22 @@
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-44194</t>
         </is>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>229</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr"/>
@@ -2105,22 +2227,30 @@
       <c r="Y19" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z19" s="8">
+        <f>IF($G19="","",$G19/$Y19)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="4">
+        <f>IF($Z19="","",IF($Z19&gt;=25,"atteint",TEXT(25-$Z19,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
+          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>25.56</v>
+        <v>57.51</v>
       </c>
       <c r="C20" s="6">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E20" s="6">
@@ -2128,7 +2258,7 @@
         <v/>
       </c>
       <c r="F20" s="8" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="G20" s="8">
         <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
@@ -2157,15 +2287,14 @@
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6">
-        <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O20" s="11" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="P20" s="11" t="n">
-        <v>5.2</v>
+        <v>11.7</v>
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
@@ -2179,45 +2308,53 @@
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>159</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Plafonné par le marché</t>
         </is>
       </c>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z20" s="8">
+        <f>IF($G20="","",$G20/$Y20)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="4">
+        <f>IF($Z20="","",IF($Z20&gt;=25,"atteint",TEXT(25-$Z20,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
+          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>57.51</v>
+        <v>31.95</v>
       </c>
       <c r="C21" s="6">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E21" s="6">
@@ -2225,7 +2362,7 @@
         <v/>
       </c>
       <c r="F21" s="8" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="G21" s="8">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
@@ -2254,14 +2391,15 @@
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
+      <c r="N21" s="6">
+        <f>IF($F21="","",$F21*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O21" s="11" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>11.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
@@ -2275,17 +2413,17 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
@@ -2298,22 +2436,30 @@
       <c r="Y21" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z21" s="8">
+        <f>IF($G21="","",$G21/$Y21)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="4">
+        <f>IF($Z21="","",IF($Z21&gt;=25,"atteint",TEXT(25-$Z21,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
+          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>25.56</v>
       </c>
       <c r="C22" s="6">
-        <f>$B22</f>
+        <f>$B22+$Y22*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E22" s="6">
@@ -2321,7 +2467,7 @@
         <v/>
       </c>
       <c r="F22" s="8" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="G22" s="8">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
@@ -2332,7 +2478,7 @@
         <v/>
       </c>
       <c r="I22" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="6">
         <f>$C22/$I22</f>
@@ -2350,14 +2496,19 @@
         <f>IF($F22="","",$F22*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="22" t="n"/>
-      <c r="P22" s="22" t="n"/>
+      <c r="N22" s="6">
+        <f>IF($F22="","",$F22*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>5.2</v>
+      </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R22" s="12" t="inlineStr">
@@ -2367,17 +2518,17 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>FB2026-5996</t>
         </is>
       </c>
       <c r="T22" s="12" t="inlineStr">
         <is>
-          <t>4521329432274</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lots de 15</t>
+          <t>Boutique + Leboncoin</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr"/>
@@ -2388,199 +2539,223 @@
       </c>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Z22" s="8">
+        <f>IF($G22="","",$G22/$Y22)</f>
+        <v/>
+      </c>
+      <c r="AA22" s="4">
+        <f>IF($Z22="","",IF($Z22&gt;=25,"atteint",TEXT(25-$Z22,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="C23" s="24">
         <f>$B23+$Y23*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="25">
         <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="24">
         <f>CEILING($D23*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F23" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="G23" s="8">
+      <c r="F23" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="G23" s="26">
         <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
         <v/>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="27">
         <f>IF($G23="","",$G23/$C23)</f>
         <v/>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="I23" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="24">
         <f>$C23/$I23</f>
         <v/>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="24">
         <f>IF($F23="","",$F23/$I23)</f>
         <v/>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="24">
         <f>IF($G23="","",$G23/$I23)</f>
         <v/>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="25">
         <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P23" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q23" s="12" t="inlineStr">
+      <c r="O23" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="P23" s="29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q23" s="30" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R23" s="12" t="inlineStr">
+      <c r="R23" s="30" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S23" s="30" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T23" s="30" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="U23" s="22" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V23" s="22" t="inlineStr"/>
+      <c r="W23" s="22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X23" s="22" t="inlineStr"/>
+      <c r="Y23" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="26">
+        <f>IF($G23="","",$G23/$Y23)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="22">
+        <f>IF($Z23="","",IF($Z23&gt;=25,"atteint",TEXT(25-$Z23,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C24" s="6">
+        <f>$B24+$Y24*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D24" s="7">
+        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E24" s="6">
+        <f>CEILING($D24*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="G24" s="8">
+        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>IF($G24="","",$G24/$C24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="6">
+        <f>$C24/$I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="6">
+        <f>IF($F24="","",$F24/$I24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="6">
+        <f>IF($G24="","",$G24/$I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="7">
+        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q24" s="12" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R24" s="12" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S23" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T23" s="12" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + Vinted</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr"/>
-      <c r="W23" s="4" t="inlineStr">
-        <is>
-          <t>URGENT — saisonnier</t>
-        </is>
-      </c>
-      <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="C24" s="25">
-        <f>$B24+$Y24*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D24" s="26">
-        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E24" s="25">
-        <f>CEILING($D24*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="G24" s="27">
-        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="28">
-        <f>IF($G24="","",$G24/$C24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="25">
-        <f>$C24/$I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="25">
-        <f>IF($F24="","",$F24/$I24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="25">
-        <f>IF($G24="","",$G24/$I24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="26">
-        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="P24" s="30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q24" s="31" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R24" s="31" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S24" s="31" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T24" s="31" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="U24" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay, en lot</t>
-        </is>
-      </c>
-      <c r="V24" s="23" t="inlineStr"/>
-      <c r="W24" s="23" t="inlineStr">
+      <c r="S24" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T24" s="12" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X24" s="23" t="inlineStr"/>
-      <c r="Y24" s="23" t="n">
+      <c r="X24" s="4" t="inlineStr"/>
+      <c r="Y24" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="Z24" s="8">
+        <f>IF($G24="","",$G24/$Y24)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="4">
+        <f>IF($Z24="","",IF($Z24&gt;=25,"atteint",TEXT(25-$Z24,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -2605,7 +2780,7 @@
         <v/>
       </c>
       <c r="F25" s="8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G25" s="8">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
@@ -2671,29 +2846,37 @@
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Plafonné par le marché</t>
         </is>
       </c>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z25" s="8">
+        <f>IF($G25="","",$G25/$Y25)</f>
+        <v/>
+      </c>
+      <c r="AA25" s="4">
+        <f>IF($Z25="","",IF($Z25&gt;=25,"atteint",TEXT(25-$Z25,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
+          <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>50.4</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="C26" s="6">
-        <f>$B26+$Y26*Paramètres!$B$13</f>
+        <f>$B26</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E26" s="6">
@@ -2701,7 +2884,7 @@
         <v/>
       </c>
       <c r="F26" s="8" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="G26" s="8">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
@@ -2712,7 +2895,7 @@
         <v/>
       </c>
       <c r="I26" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="6">
         <f>$C26/$I26</f>
@@ -2730,67 +2913,70 @@
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6">
-        <f>IF($F26="","",$F26*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="P26" s="11" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="N26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="31" t="n"/>
+      <c r="P26" s="31" t="n"/>
       <c r="Q26" s="12" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R26" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T26" s="12" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>4521329432274</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>Boutique</t>
+          <t>Leboncoin, lots de 15</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>URGENT — saisonnier</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Z26" s="8">
+        <f>IF($G26="","",$G26/$Y26)</f>
+        <v/>
+      </c>
+      <c r="AA26" s="4">
+        <f>IF($Z26="","",IF($Z26&gt;=25,"atteint",TEXT(25-$Z26,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>75.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="C27" s="6">
         <f>$B27+$Y27*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E27" s="6">
@@ -2798,7 +2984,7 @@
         <v/>
       </c>
       <c r="F27" s="8" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G27" s="8">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
@@ -2827,14 +3013,15 @@
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="n">
-        <v>0</v>
+      <c r="N27" s="6">
+        <f>IF($F27="","",$F27*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O27" s="11" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P27" s="11" t="n">
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q27" s="12" t="inlineStr">
         <is>
@@ -2853,133 +3040,145 @@
       </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>408</t>
         </is>
       </c>
       <c r="U27" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>Liquider</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z27" s="8">
+        <f>IF($G27="","",$G27/$Y27)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="4">
+        <f>IF($Z27="","",IF($Z27&gt;=25,"atteint",TEXT(25-$Z27,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>76.68000000000001</v>
-      </c>
-      <c r="C28" s="15">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="C28" s="6">
         <f>$B28+$Y28*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="7">
         <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="6">
         <f>CEILING($D28*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F28" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G28" s="17">
+      <c r="F28" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="G28" s="8">
         <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
         <v/>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="9">
         <f>IF($G28="","",$G28/$C28)</f>
         <v/>
       </c>
-      <c r="I28" s="19" t="n">
+      <c r="I28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="6">
         <f>$C28/$I28</f>
         <v/>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="6">
         <f>IF($F28="","",$F28/$I28)</f>
         <v/>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="6">
         <f>IF($G28="","",$G28/$I28)</f>
         <v/>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="7">
         <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N28" s="15" t="n">
+      <c r="N28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="20" t="n">
+      <c r="O28" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="P28" s="20" t="n">
+      <c r="P28" s="11" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q28" s="21" t="inlineStr">
+      <c r="Q28" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R28" s="21" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S28" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T28" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="U28" s="13" t="inlineStr">
-        <is>
-          <t>Vinted, Italie — non encaissé</t>
-        </is>
-      </c>
-      <c r="V28" s="13" t="inlineStr"/>
-      <c r="W28" s="13" t="inlineStr">
-        <is>
-          <t>VENDUE, en attente</t>
-        </is>
-      </c>
-      <c r="X28" s="13" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="Y28" s="13" t="n">
+      <c r="R28" s="12" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S28" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T28" s="12" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X28" s="4" t="inlineStr"/>
+      <c r="Y28" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="Z28" s="8">
+        <f>IF($G28="","",$G28/$Y28)</f>
+        <v/>
+      </c>
+      <c r="AA28" s="4">
+        <f>IF($Z28="","",IF($Z28&gt;=25,"atteint",TEXT(25-$Z28,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>113.4</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="C29" s="15">
         <f>$B29+$Y29*Paramètres!$B$13</f>
@@ -2994,7 +3193,7 @@
         <v/>
       </c>
       <c r="F29" s="17" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="G29" s="17">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
@@ -3027,10 +3226,10 @@
         <v>0</v>
       </c>
       <c r="O29" s="20" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="P29" s="20" t="n">
-        <v>23.4</v>
+        <v>15.6</v>
       </c>
       <c r="Q29" s="21" t="inlineStr">
         <is>
@@ -3044,42 +3243,50 @@
       </c>
       <c r="S29" s="21" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-44192</t>
         </is>
       </c>
       <c r="T29" s="21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U29" s="13" t="inlineStr">
         <is>
-          <t>vendu</t>
+          <t>Vinted, Italie — non encaissé</t>
         </is>
       </c>
       <c r="V29" s="13" t="inlineStr"/>
       <c r="W29" s="13" t="inlineStr">
         <is>
-          <t>VENDU</t>
+          <t>VENDUE, en attente</t>
         </is>
       </c>
       <c r="X29" s="13" t="inlineStr">
         <is>
-          <t>VENDU</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="Y29" s="13" t="n">
         <v>1</v>
       </c>
+      <c r="Z29" s="17">
+        <f>IF($G29="","",$G29/$Y29)</f>
+        <v/>
+      </c>
+      <c r="AA29" s="13">
+        <f>IF($Z29="","",IF($Z29&gt;=25,"atteint",TEXT(25-$Z29,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>50.4</v>
+        <v>113.4</v>
       </c>
       <c r="C30" s="15">
         <f>$B30+$Y30*Paramètres!$B$13</f>
@@ -3094,7 +3301,7 @@
         <v/>
       </c>
       <c r="F30" s="17" t="n">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="G30" s="17">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
@@ -3127,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="O30" s="20" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="P30" s="20" t="n">
-        <v>10.4</v>
+        <v>23.4</v>
       </c>
       <c r="Q30" s="21" t="inlineStr">
         <is>
@@ -3139,17 +3346,17 @@
       </c>
       <c r="R30" s="21" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S30" s="21" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-44194</t>
         </is>
       </c>
       <c r="T30" s="21" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U30" s="13" t="inlineStr">
@@ -3171,111 +3378,131 @@
       <c r="Y30" s="13" t="n">
         <v>1</v>
       </c>
+      <c r="Z30" s="17">
+        <f>IF($G30="","",$G30/$Y30)</f>
+        <v/>
+      </c>
+      <c r="AA30" s="13">
+        <f>IF($Z30="","",IF($Z30&gt;=25,"atteint",TEXT(25-$Z30,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="C31" s="6">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C31" s="15">
         <f>$B31+$Y31*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="16">
         <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="15">
         <f>CEILING($D31*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F31" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="G31" s="8">
+      <c r="F31" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G31" s="17">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
         <v/>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="18">
         <f>IF($G31="","",$G31/$C31)</f>
         <v/>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="6">
+      <c r="J31" s="15">
         <f>$C31/$I31</f>
         <v/>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="15">
         <f>IF($F31="","",$F31/$I31)</f>
         <v/>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="15">
         <f>IF($G31="","",$G31/$I31)</f>
         <v/>
       </c>
-      <c r="M31" s="7">
+      <c r="M31" s="16">
         <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="11" t="n">
+      <c r="O31" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="P31" s="11" t="n">
+      <c r="P31" s="20" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q31" s="12" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R31" s="12" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S31" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T31" s="12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="inlineStr"/>
-      <c r="W31" s="4" t="inlineStr">
-        <is>
-          <t>Liquider</t>
-        </is>
-      </c>
-      <c r="X31" s="4" t="inlineStr"/>
-      <c r="Y31" s="4" t="n">
+      <c r="Q31" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R31" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S31" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T31" s="21" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="U31" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V31" s="13" t="inlineStr"/>
+      <c r="W31" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X31" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y31" s="13" t="n">
         <v>1</v>
+      </c>
+      <c r="Z31" s="17">
+        <f>IF($G31="","",$G31/$Y31)</f>
+        <v/>
+      </c>
+      <c r="AA31" s="13">
+        <f>IF($Z31="","",IF($Z31&gt;=25,"atteint",TEXT(25-$Z31,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE sneakers P.38 — neuves</t>
+          <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>38.34</v>
+        <v>51.12</v>
       </c>
       <c r="C32" s="6">
         <f>$B32+$Y32*Paramètres!$B$13</f>
@@ -3290,7 +3517,7 @@
         <v/>
       </c>
       <c r="F32" s="8" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G32" s="8">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
@@ -3323,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="11" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P32" s="11" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="Q32" s="12" t="inlineStr">
         <is>
@@ -3345,7 +3572,7 @@
       </c>
       <c r="T32" s="12" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U32" s="4" t="inlineStr">
@@ -3363,115 +3590,127 @@
       <c r="Y32" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z32" s="8">
+        <f>IF($G32="","",$G32/$Y32)</f>
+        <v/>
+      </c>
+      <c r="AA32" s="4">
+        <f>IF($Z32="","",IF($Z32&gt;=25,"atteint",TEXT(25-$Z32,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="C33" s="15">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="C33" s="24">
         <f>$B33+$Y33*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="25">
         <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="24">
         <f>CEILING($D33*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F33" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="G33" s="17">
+      <c r="F33" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="G33" s="26">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
         <v/>
       </c>
-      <c r="H33" s="18">
+      <c r="H33" s="27">
         <f>IF($G33="","",$G33/$C33)</f>
         <v/>
       </c>
-      <c r="I33" s="19" t="n">
+      <c r="I33" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="24">
+        <f>$C33/$I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="24">
+        <f>IF($F33="","",$F33/$I33)</f>
+        <v/>
+      </c>
+      <c r="L33" s="24">
+        <f>IF($G33="","",$G33/$I33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="25">
+        <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="P33" s="29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q33" s="30" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R33" s="30" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S33" s="30" t="inlineStr">
+        <is>
+          <t>FB2026-44192</t>
+        </is>
+      </c>
+      <c r="T33" s="30" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="U33" s="22" t="inlineStr">
+        <is>
+          <t>Leboncoin + eBay, en lot</t>
+        </is>
+      </c>
+      <c r="V33" s="22" t="inlineStr"/>
+      <c r="W33" s="22" t="inlineStr">
+        <is>
+          <t>Marge faible</t>
+        </is>
+      </c>
+      <c r="X33" s="22" t="inlineStr"/>
+      <c r="Y33" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="15">
-        <f>$C33/$I33</f>
-        <v/>
-      </c>
-      <c r="K33" s="15">
-        <f>IF($F33="","",$F33/$I33)</f>
-        <v/>
-      </c>
-      <c r="L33" s="15">
-        <f>IF($G33="","",$G33/$I33)</f>
-        <v/>
-      </c>
-      <c r="M33" s="16">
-        <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N33" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="P33" s="20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q33" s="21" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R33" s="21" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S33" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T33" s="21" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="U33" s="13" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V33" s="13" t="inlineStr"/>
-      <c r="W33" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X33" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y33" s="13" t="n">
-        <v>1</v>
+      <c r="Z33" s="26">
+        <f>IF($G33="","",$G33/$Y33)</f>
+        <v/>
+      </c>
+      <c r="AA33" s="22">
+        <f>IF($Z33="","",IF($Z33&gt;=25,"atteint",TEXT(25-$Z33,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
+          <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>51.12</v>
+        <v>38.34</v>
       </c>
       <c r="C34" s="6">
         <f>$B34+$Y34*Paramètres!$B$13</f>
@@ -3486,7 +3725,7 @@
         <v/>
       </c>
       <c r="F34" s="8" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G34" s="8">
         <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
@@ -3519,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="O34" s="11" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P34" s="11" t="n">
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q34" s="12" t="inlineStr">
         <is>
@@ -3541,7 +3780,7 @@
       </c>
       <c r="T34" s="12" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>114</t>
         </is>
       </c>
       <c r="U34" s="4" t="inlineStr">
@@ -3559,214 +3798,238 @@
       <c r="Y34" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z34" s="8">
+        <f>IF($G34="","",$G34/$Y34)</f>
+        <v/>
+      </c>
+      <c r="AA34" s="4">
+        <f>IF($Z34="","",IF($Z34&gt;=25,"atteint",TEXT(25-$Z34,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="C35" s="6">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C35" s="15">
         <f>$B35+$Y35*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="16">
         <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="15">
         <f>CEILING($D35*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="G35" s="17">
+        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="18">
+        <f>IF($G35="","",$G35/$C35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="15">
+        <f>$C35/$I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="15">
+        <f>IF($F35="","",$F35/$I35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="15">
+        <f>IF($G35="","",$G35/$I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="16">
+        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="P35" s="20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q35" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R35" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S35" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43717</t>
+        </is>
+      </c>
+      <c r="T35" s="21" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="U35" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V35" s="13" t="inlineStr"/>
+      <c r="W35" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X35" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="17">
+        <f>IF($G35="","",$G35/$Y35)</f>
+        <v/>
+      </c>
+      <c r="AA35" s="13">
+        <f>IF($Z35="","",IF($Z35&gt;=25,"atteint",TEXT(25-$Z35,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE baskets montantes P.44 — neuves</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="C36" s="6">
+        <f>$B36+$Y36*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D36" s="7">
+        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E36" s="6">
+        <f>CEILING($D36*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="G35" s="8">
-        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="9">
-        <f>IF($G35="","",$G35/$C35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="10" t="n">
+      <c r="G36" s="8">
+        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="9">
+        <f>IF($G36="","",$G36/$C36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="6">
-        <f>$C35/$I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="6">
-        <f>IF($F35="","",$F35/$I35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="6">
-        <f>IF($G35="","",$G35/$I35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="7">
-        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N35" s="6" t="n">
+      <c r="J36" s="6">
+        <f>$C36/$I36</f>
+        <v/>
+      </c>
+      <c r="K36" s="6">
+        <f>IF($F36="","",$F36/$I36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="6">
+        <f>IF($G36="","",$G36/$I36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="7">
+        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="P35" s="11" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="Q35" s="12" t="inlineStr">
+      <c r="O36" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q36" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R35" s="12" t="inlineStr">
+      <c r="R36" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S35" s="12" t="inlineStr">
+      <c r="S36" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T35" s="12" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="U35" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V35" s="4" t="inlineStr"/>
-      <c r="W35" s="4" t="inlineStr">
+      <c r="T36" s="12" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="inlineStr"/>
+      <c r="W36" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="X35" s="4" t="inlineStr"/>
-      <c r="Y35" s="4" t="n">
+      <c r="X36" s="4" t="inlineStr"/>
+      <c r="Y36" s="4" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>LACOSTE sneakers P.42 — neuves</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="n">
-        <v>57.51</v>
-      </c>
-      <c r="C36" s="15">
-        <f>$B36+$Y36*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D36" s="16">
-        <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E36" s="15">
-        <f>CEILING($D36*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>70</v>
-      </c>
-      <c r="G36" s="17">
-        <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="18">
-        <f>IF($G36="","",$G36/$C36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="15">
-        <f>$C36/$I36</f>
-        <v/>
-      </c>
-      <c r="K36" s="15">
-        <f>IF($F36="","",$F36/$I36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="15">
-        <f>IF($G36="","",$G36/$I36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="16">
-        <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="P36" s="20" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Q36" s="21" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="R36" s="21" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S36" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-6023</t>
-        </is>
-      </c>
-      <c r="T36" s="21" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="U36" s="13" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V36" s="13" t="inlineStr"/>
-      <c r="W36" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X36" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y36" s="13" t="n">
-        <v>1</v>
+      <c r="Z36" s="8">
+        <f>IF($G36="","",$G36/$Y36)</f>
+        <v/>
+      </c>
+      <c r="AA36" s="4">
+        <f>IF($Z36="","",IF($Z36&gt;=25,"atteint",TEXT(25-$Z36,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
+          <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>35.9</v>
+        <v>52.4</v>
       </c>
       <c r="C37" s="6">
-        <f>$B37</f>
+        <f>$B37+$Y37*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D37" s="7">
@@ -3778,7 +4041,7 @@
         <v/>
       </c>
       <c r="F37" s="8" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G37" s="8">
         <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
@@ -3810,148 +4073,172 @@
       <c r="N37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="22" t="n"/>
-      <c r="P37" s="22" t="n"/>
+      <c r="O37" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="P37" s="11" t="n">
+        <v>10.66</v>
+      </c>
       <c r="Q37" s="12" t="inlineStr">
         <is>
-          <t>ERA Enchères Rhône-Alpes</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R37" s="12" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S37" s="12" t="inlineStr">
         <is>
-          <t>507148</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T37" s="12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>158</t>
         </is>
       </c>
       <c r="U37" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, main propre</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Liquider</t>
         </is>
       </c>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z37" s="8">
+        <f>IF($G37="","",$G37/$Y37)</f>
+        <v/>
+      </c>
+      <c r="AA37" s="4">
+        <f>IF($Z37="","",IF($Z37&gt;=25,"atteint",TEXT(25-$Z37,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>Lot de 4 toupies BEYBLADE HASBRO</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="C38" s="25">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>LACOSTE sneakers P.42 — neuves</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="C38" s="15">
         <f>$B38+$Y38*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="16">
         <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="25">
+      <c r="E38" s="15">
         <f>CEILING($D38*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F38" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="G38" s="27">
+      <c r="F38" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G38" s="17">
         <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
         <v/>
       </c>
-      <c r="H38" s="28">
+      <c r="H38" s="18">
         <f>IF($G38="","",$G38/$C38)</f>
         <v/>
       </c>
-      <c r="I38" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="25">
+      <c r="I38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="15">
         <f>$C38/$I38</f>
         <v/>
       </c>
-      <c r="K38" s="25">
+      <c r="K38" s="15">
         <f>IF($F38="","",$F38/$I38)</f>
         <v/>
       </c>
-      <c r="L38" s="25">
+      <c r="L38" s="15">
         <f>IF($G38="","",$G38/$I38)</f>
         <v/>
       </c>
-      <c r="M38" s="26">
+      <c r="M38" s="16">
         <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N38" s="25" t="n">
+      <c r="N38" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="P38" s="30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q38" s="31" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R38" s="31" t="inlineStr">
+      <c r="O38" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="P38" s="20" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q38" s="21" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R38" s="21" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S38" s="31" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T38" s="31" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="U38" s="23" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay, en lot</t>
-        </is>
-      </c>
-      <c r="V38" s="23" t="inlineStr"/>
-      <c r="W38" s="23" t="inlineStr">
-        <is>
-          <t>Marge faible</t>
-        </is>
-      </c>
-      <c r="X38" s="23" t="inlineStr"/>
-      <c r="Y38" s="23" t="n">
+      <c r="S38" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-6023</t>
+        </is>
+      </c>
+      <c r="T38" s="21" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="U38" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V38" s="13" t="inlineStr"/>
+      <c r="W38" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X38" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y38" s="13" t="n">
         <v>1</v>
+      </c>
+      <c r="Z38" s="17">
+        <f>IF($G38="","",$G38/$Y38)</f>
+        <v/>
+      </c>
+      <c r="AA38" s="13">
+        <f>IF($Z38="","",IF($Z38&gt;=25,"atteint",TEXT(25-$Z38,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
+          <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>28.29</v>
+        <v>35.9</v>
       </c>
       <c r="C39" s="6">
         <f>$B39</f>
@@ -3966,7 +4253,7 @@
         <v/>
       </c>
       <c r="F39" s="8" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G39" s="8">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
@@ -3998,8 +4285,8 @@
       <c r="N39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="22" t="n"/>
-      <c r="P39" s="22" t="n"/>
+      <c r="O39" s="31" t="n"/>
+      <c r="P39" s="31" t="n"/>
       <c r="Q39" s="12" t="inlineStr">
         <is>
           <t>ERA Enchères Rhône-Alpes</t>
@@ -4017,7 +4304,7 @@
       </c>
       <c r="T39" s="12" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U39" s="4" t="inlineStr">
@@ -4028,22 +4315,30 @@
       <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>Marge faible</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z39" s="8">
+        <f>IF($G39="","",$G39/$Y39)</f>
+        <v/>
+      </c>
+      <c r="AA39" s="4">
+        <f>IF($Z39="","",IF($Z39&gt;=25,"atteint",TEXT(25-$Z39,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
+          <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>12.74</v>
+        <v>28.29</v>
       </c>
       <c r="C40" s="6">
         <f>$B40</f>
@@ -4058,7 +4353,7 @@
         <v/>
       </c>
       <c r="F40" s="8" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G40" s="8">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
@@ -4090,52 +4385,60 @@
       <c r="N40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="22" t="n"/>
-      <c r="P40" s="22" t="n"/>
+      <c r="O40" s="31" t="n"/>
+      <c r="P40" s="31" t="n"/>
       <c r="Q40" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ERA Enchères Rhône-Alpes</t>
         </is>
       </c>
       <c r="R40" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="S40" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>507148</t>
         </is>
       </c>
       <c r="T40" s="12" t="inlineStr">
         <is>
-          <t>4521329462226</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U40" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lot de 2</t>
+          <t>Leboncoin, main propre</t>
         </is>
       </c>
       <c r="V40" s="4" t="inlineStr"/>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Marge faible</t>
         </is>
       </c>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z40" s="8">
+        <f>IF($G40="","",$G40/$Y40)</f>
+        <v/>
+      </c>
+      <c r="AA40" s="4">
+        <f>IF($Z40="","",IF($Z40&gt;=25,"atteint",TEXT(25-$Z40,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
+          <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>12.95</v>
+        <v>12.74</v>
       </c>
       <c r="C41" s="6">
         <f>$B41</f>
@@ -4149,7 +4452,9 @@
         <f>CEILING($D41*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F41" s="22" t="n"/>
+      <c r="F41" s="8" t="n">
+        <v>19</v>
+      </c>
       <c r="G41" s="8">
         <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
         <v/>
@@ -4180,8 +4485,8 @@
       <c r="N41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="22" t="n"/>
-      <c r="P41" s="22" t="n"/>
+      <c r="O41" s="31" t="n"/>
+      <c r="P41" s="31" t="n"/>
       <c r="Q41" s="12" t="inlineStr">
         <is>
           <t>Meccha Japan</t>
@@ -4199,33 +4504,41 @@
       </c>
       <c r="T41" s="12" t="inlineStr">
         <is>
-          <t>4521329431925</t>
+          <t>4521329462226</t>
         </is>
       </c>
       <c r="U41" s="4" t="inlineStr">
         <is>
-          <t>Prélevé — usage personnel</t>
+          <t>Leboncoin, lot de 2</t>
         </is>
       </c>
       <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>PRÉLEVÉ</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X41" s="4" t="inlineStr"/>
       <c r="Y41" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z41" s="8">
+        <f>IF($G41="","",$G41/$Y41)</f>
+        <v/>
+      </c>
+      <c r="AA41" s="4">
+        <f>IF($Z41="","",IF($Z41&gt;=25,"atteint",TEXT(25-$Z41,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
+          <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>19.41</v>
+        <v>12.95</v>
       </c>
       <c r="C42" s="6">
         <f>$B42</f>
@@ -4239,7 +4552,7 @@
         <f>CEILING($D42*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F42" s="22" t="n"/>
+      <c r="F42" s="31" t="n"/>
       <c r="G42" s="8">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
         <v/>
@@ -4270,150 +4583,158 @@
       <c r="N42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="22" t="n"/>
-      <c r="P42" s="22" t="n"/>
+      <c r="O42" s="31" t="n"/>
+      <c r="P42" s="31" t="n"/>
       <c r="Q42" s="12" t="inlineStr">
         <is>
-          <t>ERA Enchères Rhône-Alpes</t>
+          <t>Meccha Japan</t>
         </is>
       </c>
       <c r="R42" s="12" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S42" s="12" t="inlineStr">
         <is>
-          <t>507148</t>
+          <t>#FA429713</t>
         </is>
       </c>
       <c r="T42" s="12" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>4521329431925</t>
         </is>
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>Prélevée — usage personnel</t>
+          <t>Prélevé — usage personnel</t>
         </is>
       </c>
       <c r="V42" s="4" t="inlineStr"/>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>PRÉLEVÉE</t>
+          <t>PRÉLEVÉ</t>
         </is>
       </c>
       <c r="X42" s="4" t="inlineStr"/>
       <c r="Y42" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="Z42" s="8">
+        <f>IF($G42="","",$G42/$Y42)</f>
+        <v/>
+      </c>
+      <c r="AA42" s="4">
+        <f>IF($Z42="","",IF($Z42&gt;=25,"atteint",TEXT(25-$Z42,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C43" s="15">
-        <f>$B43+$Y43*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D43" s="16">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="C43" s="6">
+        <f>$B43</f>
+        <v/>
+      </c>
+      <c r="D43" s="7">
         <f>$C43/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="6">
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="17">
+      <c r="F43" s="31" t="n"/>
+      <c r="G43" s="8">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="9">
         <f>IF($G43="","",$G43/$C43)</f>
         <v/>
       </c>
-      <c r="I43" s="19" t="n">
+      <c r="I43" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="6">
         <f>$C43/$I43</f>
         <v/>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="6">
         <f>IF($F43="","",$F43/$I43)</f>
         <v/>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="6">
         <f>IF($G43="","",$G43/$I43)</f>
         <v/>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="7">
         <f>IF($F43="","",$F43*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N43" s="15" t="n">
+      <c r="N43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="P43" s="20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q43" s="21" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R43" s="21" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S43" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T43" s="21" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="U43" s="13" t="inlineStr">
-        <is>
-          <t>Prélevées — usage personnel</t>
-        </is>
-      </c>
-      <c r="V43" s="13" t="inlineStr"/>
-      <c r="W43" s="13" t="inlineStr">
-        <is>
-          <t>PRÉLEVÉES</t>
-        </is>
-      </c>
-      <c r="X43" s="13" t="inlineStr">
-        <is>
-          <t>PRÉLEVÉES 09/08</t>
-        </is>
-      </c>
-      <c r="Y43" s="13" t="n">
+      <c r="O43" s="31" t="n"/>
+      <c r="P43" s="31" t="n"/>
+      <c r="Q43" s="12" t="inlineStr">
+        <is>
+          <t>ERA Enchères Rhône-Alpes</t>
+        </is>
+      </c>
+      <c r="R43" s="12" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="S43" s="12" t="inlineStr">
+        <is>
+          <t>507148</t>
+        </is>
+      </c>
+      <c r="T43" s="12" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>Prélevée — usage personnel</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr"/>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉE</t>
+        </is>
+      </c>
+      <c r="X43" s="4" t="inlineStr"/>
+      <c r="Y43" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="Z43" s="8">
+        <f>IF($G43="","",$G43/$Y43)</f>
+        <v/>
+      </c>
+      <c r="AA43" s="4">
+        <f>IF($Z43="","",IF($Z43&gt;=25,"atteint",TEXT(25-$Z43,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>Baskets HOKA P.37 1/3 — neuves</t>
+          <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
       <c r="B44" s="14" t="n">
-        <v>63</v>
+        <v>50.4</v>
       </c>
       <c r="C44" s="15">
         <f>$B44+$Y44*Paramètres!$B$13</f>
@@ -4459,10 +4780,10 @@
         <v>0</v>
       </c>
       <c r="O44" s="20" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P44" s="20" t="n">
-        <v>13</v>
+        <v>10.4</v>
       </c>
       <c r="Q44" s="21" t="inlineStr">
         <is>
@@ -4481,7 +4802,7 @@
       </c>
       <c r="T44" s="21" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>170</t>
         </is>
       </c>
       <c r="U44" s="13" t="inlineStr">
@@ -4503,99 +4824,119 @@
       <c r="Y44" s="13" t="n">
         <v>1</v>
       </c>
+      <c r="Z44" s="17">
+        <f>IF($G44="","",$G44/$Y44)</f>
+        <v/>
+      </c>
+      <c r="AA44" s="13">
+        <f>IF($Z44="","",IF($Z44&gt;=25,"atteint",TEXT(25-$Z44,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Baskets HOKA P.37 1/3 — neuves</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
         <v>63</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="15">
         <f>$B45+$Y45*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="16">
         <f>$C45/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="15">
         <f>CEILING($D45*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F45" s="22" t="n"/>
-      <c r="G45" s="8">
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="17">
         <f>IF($F45="","",$F45-$C45-$M45-$N45)</f>
         <v/>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="18">
         <f>IF($G45="","",$G45/$C45)</f>
         <v/>
       </c>
-      <c r="I45" s="10" t="n">
+      <c r="I45" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="6">
+      <c r="J45" s="15">
         <f>$C45/$I45</f>
         <v/>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="15">
         <f>IF($F45="","",$F45/$I45)</f>
         <v/>
       </c>
-      <c r="L45" s="6">
+      <c r="L45" s="15">
         <f>IF($G45="","",$G45/$I45)</f>
         <v/>
       </c>
-      <c r="M45" s="7">
+      <c r="M45" s="16">
         <f>IF($F45="","",$F45*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="N45" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="11" t="n">
+      <c r="O45" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="P45" s="11" t="n">
+      <c r="P45" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="Q45" s="12" t="inlineStr">
+      <c r="Q45" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R45" s="12" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="S45" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-46056</t>
-        </is>
-      </c>
-      <c r="T45" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U45" s="4" t="inlineStr">
-        <is>
-          <t>Vinted, authentification</t>
-        </is>
-      </c>
-      <c r="V45" s="4" t="inlineStr"/>
-      <c r="W45" s="4" t="inlineStr">
-        <is>
-          <t>PRIX À ÉTABLIR</t>
-        </is>
-      </c>
-      <c r="X45" s="4" t="inlineStr"/>
-      <c r="Y45" s="4" t="n">
+      <c r="R45" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S45" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T45" s="21" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="U45" s="13" t="inlineStr">
+        <is>
+          <t>Prélevées — usage personnel</t>
+        </is>
+      </c>
+      <c r="V45" s="13" t="inlineStr"/>
+      <c r="W45" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉES</t>
+        </is>
+      </c>
+      <c r="X45" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉES 09/08</t>
+        </is>
+      </c>
+      <c r="Y45" s="13" t="n">
         <v>1</v>
+      </c>
+      <c r="Z45" s="17">
+        <f>IF($G45="","",$G45/$Y45)</f>
+        <v/>
+      </c>
+      <c r="AA45" s="13">
+        <f>IF($Z45="","",IF($Z45&gt;=25,"atteint",TEXT(25-$Z45,"0.00")&amp;" € manquants"))</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -4652,12 +4993,25 @@
       <c r="W46" s="35" t="n"/>
       <c r="X46" s="35" t="n"/>
       <c r="Y46" s="35" t="n"/>
+      <c r="Z46" s="34">
+        <f>G46/SUM(Y6:Y45)</f>
+        <v/>
+      </c>
+      <c r="AA46" s="35" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:Y45"/>
+  <autoFilter ref="A5:AA45"/>
   <conditionalFormatting sqref="G6:G45">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z6:Z45">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
+      <formula>25</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>25</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4670,7 +5024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5001,7 +5355,7 @@
     <row r="35">
       <c r="A35" s="39" t="inlineStr">
         <is>
-          <t>1 lot sans prix : Yeezy 700 V3, en attente d'authentification.</t>
+          <t>Yeezy 700 V3 : 105 € sous réserve d'authentification. Neuve à 140 € (wehaveit.fr).</t>
         </is>
       </c>
     </row>
@@ -5037,6 +5391,34 @@
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Ne pas confondre avec le seuil de sourcing de 25 € : celui-là sert à decider d'ACHETER, pas de vendre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>OBJECTIF 25 € DE MARGE PAR VENTE : atteint sur 15 lots, impossible sur 13 — le prix de rue plafonne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="45" t="inlineStr">
+        <is>
+          <t>Règle d'achat qui en découle : coût maximum tout compris = prix marché × 0,876 − 25 €.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>Sous 121 € de prix marché, cette règle est plus stricte que celle des deux tiers. Au-dessus, c'est l'inverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="inlineStr">
+        <is>
+          <t>Sous 40 € de prix marché, 25 € de marge sont hors d'atteinte quelle que soit l'enchère. Ne pas miser.</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -21,11 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00 &quot;€&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0 &quot;art.&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0 &quot;art.&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -141,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,20 +182,22 @@
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -5433,7 +5436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5749,6 +5752,162 @@
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>exonérée en 2026, 200 à 600 €/an à partir de 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="38" t="inlineStr">
+        <is>
+          <t>COMMISSION D'ENCAISSEMENT PAR CANAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>Shopify Payments — taux</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>le moins cher : canal à privilégier</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>Shopify Payments — frais fixe</t>
+        </is>
+      </c>
+      <c r="B38" s="47" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>PayPal — taux</t>
+        </is>
+      </c>
+      <c r="B39" s="51" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>À RELEVER sur ton compte : Paramètres &gt; Frais marchands</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>PayPal — frais fixe</t>
+        </is>
+      </c>
+      <c r="B40" s="47" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>À RELEVER — les sources publiques donnent 0,25 à 0,49 €</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>PayPal — supplément hors zone euro</t>
+        </is>
+      </c>
+      <c r="B41" s="51" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>À RELEVER — s'ajoute au taux ci-dessus</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>Vinted et Leboncoin en main propre</t>
+        </is>
+      </c>
+      <c r="B42" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>aucune commission</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t>Coefficient de marge — Shopify Payments</t>
+        </is>
+      </c>
+      <c r="B44" s="52">
+        <f>1-B5-B6-B37</f>
+        <v/>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>marge = prix × ce coefficient − coût − frais fixe</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>Coefficient de marge — PayPal</t>
+        </is>
+      </c>
+      <c r="B45" s="52">
+        <f>1-B5-B6-B39</f>
+        <v/>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>chaque vente encaissée par PayPal coûte ce qui manque</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="inlineStr">
+        <is>
+          <t>Coefficient de marge — hors carte</t>
+        </is>
+      </c>
+      <c r="B46" s="52">
+        <f>1-B5-B6</f>
+        <v/>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Leboncoin, Vinted, espèces</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t>Écart PayPal / Shopify Payments sur une vente à 89 €</t>
+        </is>
+      </c>
+      <c r="B47" s="6">
+        <f>89*(B39-B37)+(B40-B38)</f>
+        <v/>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>multiplié par le nombre de ventes encaissées ainsi</t>
         </is>
       </c>
     </row>
@@ -7376,32 +7535,32 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="51" t="inlineStr">
+      <c r="A42" s="53" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="B42" s="51" t="inlineStr">
+      <c r="B42" s="53" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C42" s="51" t="inlineStr">
+      <c r="C42" s="53" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="D42" s="51" t="inlineStr">
+      <c r="D42" s="53" t="inlineStr">
         <is>
           <t>Commande</t>
         </is>
       </c>
-      <c r="E42" s="51" t="inlineStr">
+      <c r="E42" s="53" t="inlineStr">
         <is>
           <t>Désignation</t>
         </is>
       </c>
-      <c r="F42" s="51" t="inlineStr">
+      <c r="F42" s="53" t="inlineStr">
         <is>
           <t>Total TTC</t>
         </is>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -4535,197 +4535,205 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="14" t="n">
         <v>12.95</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="15">
         <f>$B42</f>
         <v/>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="16">
         <f>$C42/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="15">
         <f>CEILING($D42*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F42" s="31" t="n"/>
-      <c r="G42" s="8">
+      <c r="F42" s="32" t="n"/>
+      <c r="G42" s="17">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
         <v/>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="18">
         <f>IF($G42="","",$G42/$C42)</f>
         <v/>
       </c>
-      <c r="I42" s="10" t="n">
+      <c r="I42" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="6">
+      <c r="J42" s="15">
         <f>$C42/$I42</f>
         <v/>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="15">
         <f>IF($F42="","",$F42/$I42)</f>
         <v/>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="15">
         <f>IF($G42="","",$G42/$I42)</f>
         <v/>
       </c>
-      <c r="M42" s="7">
+      <c r="M42" s="16">
         <f>IF($F42="","",$F42*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="N42" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="31" t="n"/>
-      <c r="P42" s="31" t="n"/>
-      <c r="Q42" s="12" t="inlineStr">
+      <c r="O42" s="32" t="n"/>
+      <c r="P42" s="32" t="n"/>
+      <c r="Q42" s="21" t="inlineStr">
         <is>
           <t>Meccha Japan</t>
         </is>
       </c>
-      <c r="R42" s="12" t="inlineStr">
+      <c r="R42" s="21" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S42" s="12" t="inlineStr">
+      <c r="S42" s="21" t="inlineStr">
         <is>
           <t>#FA429713</t>
         </is>
       </c>
-      <c r="T42" s="12" t="inlineStr">
+      <c r="T42" s="21" t="inlineStr">
         <is>
           <t>4521329431925</t>
         </is>
       </c>
-      <c r="U42" s="4" t="inlineStr">
+      <c r="U42" s="13" t="inlineStr">
         <is>
           <t>Prélevé — usage personnel</t>
         </is>
       </c>
-      <c r="V42" s="4" t="inlineStr"/>
-      <c r="W42" s="4" t="inlineStr">
+      <c r="V42" s="13" t="inlineStr"/>
+      <c r="W42" s="13" t="inlineStr">
         <is>
           <t>PRÉLEVÉ</t>
         </is>
       </c>
-      <c r="X42" s="4" t="inlineStr"/>
-      <c r="Y42" s="4" t="n">
+      <c r="X42" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉ 13/08</t>
+        </is>
+      </c>
+      <c r="Y42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" s="8">
+      <c r="Z42" s="17">
         <f>IF($G42="","",$G42/$Y42)</f>
         <v/>
       </c>
-      <c r="AA42" s="4">
+      <c r="AA42" s="13">
         <f>IF($Z42="","",IF($Z42&gt;=25,"atteint",TEXT(25-$Z42,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="14" t="n">
         <v>19.41</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="15">
         <f>$B43</f>
         <v/>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="16">
         <f>$C43/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="15">
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F43" s="31" t="n"/>
-      <c r="G43" s="8">
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="17">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="18">
         <f>IF($G43="","",$G43/$C43)</f>
         <v/>
       </c>
-      <c r="I43" s="10" t="n">
+      <c r="I43" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="6">
+      <c r="J43" s="15">
         <f>$C43/$I43</f>
         <v/>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="15">
         <f>IF($F43="","",$F43/$I43)</f>
         <v/>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="15">
         <f>IF($G43="","",$G43/$I43)</f>
         <v/>
       </c>
-      <c r="M43" s="7">
+      <c r="M43" s="16">
         <f>IF($F43="","",$F43*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="N43" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="31" t="n"/>
-      <c r="P43" s="31" t="n"/>
-      <c r="Q43" s="12" t="inlineStr">
+      <c r="O43" s="32" t="n"/>
+      <c r="P43" s="32" t="n"/>
+      <c r="Q43" s="21" t="inlineStr">
         <is>
           <t>ERA Enchères Rhône-Alpes</t>
         </is>
       </c>
-      <c r="R43" s="12" t="inlineStr">
+      <c r="R43" s="21" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="S43" s="12" t="inlineStr">
+      <c r="S43" s="21" t="inlineStr">
         <is>
           <t>507148</t>
         </is>
       </c>
-      <c r="T43" s="12" t="inlineStr">
+      <c r="T43" s="21" t="inlineStr">
         <is>
           <t>131</t>
         </is>
       </c>
-      <c r="U43" s="4" t="inlineStr">
+      <c r="U43" s="13" t="inlineStr">
         <is>
           <t>Prélevée — usage personnel</t>
         </is>
       </c>
-      <c r="V43" s="4" t="inlineStr"/>
-      <c r="W43" s="4" t="inlineStr">
+      <c r="V43" s="13" t="inlineStr"/>
+      <c r="W43" s="13" t="inlineStr">
         <is>
           <t>PRÉLEVÉE</t>
         </is>
       </c>
-      <c r="X43" s="4" t="inlineStr"/>
-      <c r="Y43" s="4" t="n">
+      <c r="X43" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉE 13/08</t>
+        </is>
+      </c>
+      <c r="Y43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z43" s="8">
+      <c r="Z43" s="17">
         <f>IF($G43="","",$G43/$Y43)</f>
         <v/>
       </c>
-      <c r="AA43" s="4">
+      <c r="AA43" s="13">
         <f>IF($Z43="","",IF($Z43&gt;=25,"atteint",TEXT(25-$Z43,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2966,106 +2966,109 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C27" s="15">
         <f>$B27+$Y27*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D27" s="7">
-        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="E27" s="6">
+      <c r="D27" s="16">
+        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E27" s="15">
         <f>CEILING($D27*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G27" s="8">
+      <c r="F27" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="17">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
         <v/>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="18">
         <f>IF($G27="","",$G27/$C27)</f>
         <v/>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I27" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="15">
         <f>$C27/$I27</f>
         <v/>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="15">
         <f>IF($F27="","",$F27/$I27)</f>
         <v/>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="15">
         <f>IF($G27="","",$G27/$I27)</f>
         <v/>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="16">
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6">
-        <f>IF($F27="","",$F27*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O27" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="P27" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q27" s="12" t="inlineStr">
+      <c r="N27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="P27" s="20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q27" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R27" s="12" t="inlineStr">
+      <c r="R27" s="21" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S27" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T27" s="12" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr"/>
-      <c r="W27" s="4" t="inlineStr">
-        <is>
-          <t>URGENT — saisonnier</t>
-        </is>
-      </c>
-      <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="4" t="n">
+      <c r="S27" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43717</t>
+        </is>
+      </c>
+      <c r="T27" s="21" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="U27" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V27" s="13" t="inlineStr"/>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X27" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y27" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z27" s="8">
+      <c r="Z27" s="17">
         <f>IF($G27="","",$G27/$Y27)</f>
         <v/>
       </c>
-      <c r="AA27" s="4">
+      <c r="AA27" s="13">
         <f>IF($Z27="","",IF($Z27&gt;=25,"atteint",TEXT(25-$Z27,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -3073,18 +3076,18 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>75.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="C28" s="6">
         <f>$B28+$Y28*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E28" s="6">
@@ -3092,7 +3095,7 @@
         <v/>
       </c>
       <c r="F28" s="8" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G28" s="8">
         <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
@@ -3121,14 +3124,15 @@
         <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N28" s="6" t="n">
-        <v>0</v>
+      <c r="N28" s="6">
+        <f>IF($F28="","",$F28*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O28" s="11" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P28" s="11" t="n">
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q28" s="12" t="inlineStr">
         <is>
@@ -3147,18 +3151,18 @@
       </c>
       <c r="T28" s="12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>408</t>
         </is>
       </c>
       <c r="U28" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>Liquider</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X28" s="4" t="inlineStr"/>
@@ -3175,109 +3179,105 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="n">
-        <v>76.68000000000001</v>
-      </c>
-      <c r="C29" s="15">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="C29" s="6">
         <f>$B29+$Y29*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="7">
         <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="6">
         <f>CEILING($D29*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F29" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G29" s="17">
+      <c r="F29" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="G29" s="8">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
         <v/>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="9">
         <f>IF($G29="","",$G29/$C29)</f>
         <v/>
       </c>
-      <c r="I29" s="19" t="n">
+      <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="6">
         <f>$C29/$I29</f>
         <v/>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="6">
         <f>IF($F29="","",$F29/$I29)</f>
         <v/>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="6">
         <f>IF($G29="","",$G29/$I29)</f>
         <v/>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="7">
         <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N29" s="15" t="n">
+      <c r="N29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="20" t="n">
+      <c r="O29" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="P29" s="20" t="n">
+      <c r="P29" s="11" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q29" s="21" t="inlineStr">
+      <c r="Q29" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R29" s="21" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S29" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T29" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="U29" s="13" t="inlineStr">
-        <is>
-          <t>Vinted, Italie — non encaissé</t>
-        </is>
-      </c>
-      <c r="V29" s="13" t="inlineStr"/>
-      <c r="W29" s="13" t="inlineStr">
-        <is>
-          <t>VENDUE, en attente</t>
-        </is>
-      </c>
-      <c r="X29" s="13" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="Y29" s="13" t="n">
+      <c r="R29" s="12" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S29" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T29" s="12" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X29" s="4" t="inlineStr"/>
+      <c r="Y29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" s="17">
+      <c r="Z29" s="8">
         <f>IF($G29="","",$G29/$Y29)</f>
         <v/>
       </c>
-      <c r="AA29" s="13">
+      <c r="AA29" s="4">
         <f>IF($Z29="","",IF($Z29&gt;=25,"atteint",TEXT(25-$Z29,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -3285,11 +3285,11 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>113.4</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="C30" s="15">
         <f>$B30+$Y30*Paramètres!$B$13</f>
@@ -3304,7 +3304,7 @@
         <v/>
       </c>
       <c r="F30" s="17" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="G30" s="17">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
@@ -3337,10 +3337,10 @@
         <v>0</v>
       </c>
       <c r="O30" s="20" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="P30" s="20" t="n">
-        <v>23.4</v>
+        <v>15.6</v>
       </c>
       <c r="Q30" s="21" t="inlineStr">
         <is>
@@ -3354,28 +3354,28 @@
       </c>
       <c r="S30" s="21" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-44192</t>
         </is>
       </c>
       <c r="T30" s="21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U30" s="13" t="inlineStr">
         <is>
-          <t>vendu</t>
+          <t>Vinted, Italie — non encaissé</t>
         </is>
       </c>
       <c r="V30" s="13" t="inlineStr"/>
       <c r="W30" s="13" t="inlineStr">
         <is>
-          <t>VENDU</t>
+          <t>VENDUE, en attente</t>
         </is>
       </c>
       <c r="X30" s="13" t="inlineStr">
         <is>
-          <t>VENDU</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="Y30" s="13" t="n">
@@ -3393,11 +3393,11 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>50.4</v>
+        <v>113.4</v>
       </c>
       <c r="C31" s="15">
         <f>$B31+$Y31*Paramètres!$B$13</f>
@@ -3412,7 +3412,7 @@
         <v/>
       </c>
       <c r="F31" s="17" t="n">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="G31" s="17">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="20" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>10.4</v>
+        <v>23.4</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3457,17 +3457,17 @@
       </c>
       <c r="R31" s="21" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="S31" s="21" t="inlineStr">
         <is>
-          <t>FB2026-43716</t>
+          <t>FB2026-44194</t>
         </is>
       </c>
       <c r="T31" s="21" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U31" s="13" t="inlineStr">
@@ -3499,421 +3499,421 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C32" s="15">
+        <f>$B32+$Y32*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D32" s="16">
+        <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E32" s="15">
+        <f>CEILING($D32*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G32" s="17">
+        <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="18">
+        <f>IF($G32="","",$G32/$C32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="15">
+        <f>$C32/$I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="15">
+        <f>IF($F32="","",$F32/$I32)</f>
+        <v/>
+      </c>
+      <c r="L32" s="15">
+        <f>IF($G32="","",$G32/$I32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="16">
+        <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="P32" s="20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q32" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R32" s="21" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S32" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T32" s="21" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="U32" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V32" s="13" t="inlineStr"/>
+      <c r="W32" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X32" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="17">
+        <f>IF($G32="","",$G32/$Y32)</f>
+        <v/>
+      </c>
+      <c r="AA32" s="13">
+        <f>IF($Z32="","",IF($Z32&gt;=25,"atteint",TEXT(25-$Z32,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B33" s="5" t="n">
         <v>51.12</v>
       </c>
-      <c r="C32" s="6">
-        <f>$B32+$Y32*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D32" s="7">
-        <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E32" s="6">
-        <f>CEILING($D32*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F32" s="8" t="n">
+      <c r="C33" s="6">
+        <f>$B33+$Y33*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D33" s="7">
+        <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E33" s="6">
+        <f>CEILING($D33*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F33" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="G32" s="8">
-        <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="9">
-        <f>IF($G32="","",$G32/$C32)</f>
-        <v/>
-      </c>
-      <c r="I32" s="10" t="n">
+      <c r="G33" s="8">
+        <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="9">
+        <f>IF($G33="","",$G33/$C33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="6">
-        <f>$C32/$I32</f>
-        <v/>
-      </c>
-      <c r="K32" s="6">
-        <f>IF($F32="","",$F32/$I32)</f>
-        <v/>
-      </c>
-      <c r="L32" s="6">
-        <f>IF($G32="","",$G32/$I32)</f>
-        <v/>
-      </c>
-      <c r="M32" s="7">
-        <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N32" s="6" t="n">
+      <c r="J33" s="6">
+        <f>$C33/$I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="6">
+        <f>IF($F33="","",$F33/$I33)</f>
+        <v/>
+      </c>
+      <c r="L33" s="6">
+        <f>IF($G33="","",$G33/$I33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="7">
+        <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="11" t="n">
+      <c r="O33" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="P32" s="11" t="n">
+      <c r="P33" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="Q32" s="12" t="inlineStr">
+      <c r="Q33" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R32" s="12" t="inlineStr">
+      <c r="R33" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S32" s="12" t="inlineStr">
+      <c r="S33" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T32" s="12" t="inlineStr">
+      <c r="T33" s="12" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="U32" s="4" t="inlineStr">
+      <c r="U33" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="4" t="inlineStr">
+      <c r="V33" s="4" t="inlineStr"/>
+      <c r="W33" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="X32" s="4" t="inlineStr"/>
-      <c r="Y32" s="4" t="n">
+      <c r="X33" s="4" t="inlineStr"/>
+      <c r="Y33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z32" s="8">
-        <f>IF($G32="","",$G32/$Y32)</f>
-        <v/>
-      </c>
-      <c r="AA32" s="4">
-        <f>IF($Z32="","",IF($Z32&gt;=25,"atteint",TEXT(25-$Z32,"0.00")&amp;" € manquants"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="Z33" s="8">
+        <f>IF($G33="","",$G33/$Y33)</f>
+        <v/>
+      </c>
+      <c r="AA33" s="4">
+        <f>IF($Z33="","",IF($Z33&gt;=25,"atteint",TEXT(25-$Z33,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n">
+      <c r="B34" s="23" t="n">
         <v>38.34</v>
       </c>
-      <c r="C33" s="24">
-        <f>$B33+$Y33*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D33" s="25">
-        <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E33" s="24">
-        <f>CEILING($D33*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F33" s="26" t="n">
+      <c r="C34" s="24">
+        <f>$B34+$Y34*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D34" s="25">
+        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E34" s="24">
+        <f>CEILING($D34*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="26" t="n">
         <v>55</v>
       </c>
-      <c r="G33" s="26">
-        <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="27">
-        <f>IF($G33="","",$G33/$C33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="28" t="n">
+      <c r="G34" s="26">
+        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="27">
+        <f>IF($G34="","",$G34/$C34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J33" s="24">
-        <f>$C33/$I33</f>
-        <v/>
-      </c>
-      <c r="K33" s="24">
-        <f>IF($F33="","",$F33/$I33)</f>
-        <v/>
-      </c>
-      <c r="L33" s="24">
-        <f>IF($G33="","",$G33/$I33)</f>
-        <v/>
-      </c>
-      <c r="M33" s="25">
-        <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N33" s="24" t="n">
+      <c r="J34" s="24">
+        <f>$C34/$I34</f>
+        <v/>
+      </c>
+      <c r="K34" s="24">
+        <f>IF($F34="","",$F34/$I34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="24">
+        <f>IF($G34="","",$G34/$I34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="25">
+        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N34" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="29" t="n">
+      <c r="O34" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="P33" s="29" t="n">
+      <c r="P34" s="29" t="n">
         <v>7.8</v>
       </c>
-      <c r="Q33" s="30" t="inlineStr">
+      <c r="Q34" s="30" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R33" s="30" t="inlineStr">
+      <c r="R34" s="30" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S33" s="30" t="inlineStr">
+      <c r="S34" s="30" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="T33" s="30" t="inlineStr">
+      <c r="T34" s="30" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="U33" s="22" t="inlineStr">
+      <c r="U34" s="22" t="inlineStr">
         <is>
           <t>Leboncoin + eBay, en lot</t>
         </is>
       </c>
-      <c r="V33" s="22" t="inlineStr"/>
-      <c r="W33" s="22" t="inlineStr">
+      <c r="V34" s="22" t="inlineStr"/>
+      <c r="W34" s="22" t="inlineStr">
         <is>
           <t>Marge faible</t>
         </is>
       </c>
-      <c r="X33" s="22" t="inlineStr"/>
-      <c r="Y33" s="22" t="n">
+      <c r="X34" s="22" t="inlineStr"/>
+      <c r="Y34" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z33" s="26">
-        <f>IF($G33="","",$G33/$Y33)</f>
-        <v/>
-      </c>
-      <c r="AA33" s="22">
-        <f>IF($Z33="","",IF($Z33&gt;=25,"atteint",TEXT(25-$Z33,"0.00")&amp;" € manquants"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="Z34" s="26">
+        <f>IF($G34="","",$G34/$Y34)</f>
+        <v/>
+      </c>
+      <c r="AA34" s="22">
+        <f>IF($Z34="","",IF($Z34&gt;=25,"atteint",TEXT(25-$Z34,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B35" s="5" t="n">
         <v>38.34</v>
       </c>
-      <c r="C34" s="6">
-        <f>$B34+$Y34*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D34" s="7">
-        <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E34" s="6">
-        <f>CEILING($D34*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F34" s="8" t="n">
+      <c r="C35" s="6">
+        <f>$B35+$Y35*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D35" s="7">
+        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E35" s="6">
+        <f>CEILING($D35*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="G34" s="8">
-        <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="9">
-        <f>IF($G34="","",$G34/$C34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="10" t="n">
+      <c r="G35" s="8">
+        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="9">
+        <f>IF($G35="","",$G35/$C35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="6">
-        <f>$C34/$I34</f>
-        <v/>
-      </c>
-      <c r="K34" s="6">
-        <f>IF($F34="","",$F34/$I34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="6">
-        <f>IF($G34="","",$G34/$I34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="7">
-        <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N34" s="6" t="n">
+      <c r="J35" s="6">
+        <f>$C35/$I35</f>
+        <v/>
+      </c>
+      <c r="K35" s="6">
+        <f>IF($F35="","",$F35/$I35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="6">
+        <f>IF($G35="","",$G35/$I35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="7">
+        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="11" t="n">
+      <c r="O35" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="P34" s="11" t="n">
+      <c r="P35" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="Q34" s="12" t="inlineStr">
+      <c r="Q35" s="12" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="R34" s="12" t="inlineStr">
+      <c r="R35" s="12" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S34" s="12" t="inlineStr">
+      <c r="S35" s="12" t="inlineStr">
         <is>
           <t>FB2026-6023</t>
         </is>
       </c>
-      <c r="T34" s="12" t="inlineStr">
+      <c r="T35" s="12" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="U34" s="4" t="inlineStr">
+      <c r="U35" s="4" t="inlineStr">
         <is>
           <t>Leboncoin</t>
         </is>
       </c>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="4" t="inlineStr">
+      <c r="V35" s="4" t="inlineStr"/>
+      <c r="W35" s="4" t="inlineStr">
         <is>
           <t>Liquider</t>
         </is>
       </c>
-      <c r="X34" s="4" t="inlineStr"/>
-      <c r="Y34" s="4" t="n">
+      <c r="X35" s="4" t="inlineStr"/>
+      <c r="Y35" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z34" s="8">
-        <f>IF($G34="","",$G34/$Y34)</f>
-        <v/>
-      </c>
-      <c r="AA34" s="4">
-        <f>IF($Z34="","",IF($Z34&gt;=25,"atteint",TEXT(25-$Z34,"0.00")&amp;" € manquants"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="C35" s="15">
-        <f>$B35+$Y35*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D35" s="16">
-        <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E35" s="15">
-        <f>CEILING($D35*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="G35" s="17">
-        <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="18">
-        <f>IF($G35="","",$G35/$C35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="15">
-        <f>$C35/$I35</f>
-        <v/>
-      </c>
-      <c r="K35" s="15">
-        <f>IF($F35="","",$F35/$I35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="15">
-        <f>IF($G35="","",$G35/$I35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="16">
-        <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="P35" s="20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q35" s="21" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R35" s="21" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S35" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-43717</t>
-        </is>
-      </c>
-      <c r="T35" s="21" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="U35" s="13" t="inlineStr">
-        <is>
-          <t>vendu</t>
-        </is>
-      </c>
-      <c r="V35" s="13" t="inlineStr"/>
-      <c r="W35" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="X35" s="13" t="inlineStr">
-        <is>
-          <t>VENDU</t>
-        </is>
-      </c>
-      <c r="Y35" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="17">
+      <c r="Z35" s="8">
         <f>IF($G35="","",$G35/$Y35)</f>
         <v/>
       </c>
-      <c r="AA35" s="13">
+      <c r="AA35" s="4">
         <f>IF($Z35="","",IF($Z35&gt;=25,"atteint",TEXT(25-$Z35,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -5373,7 +5373,7 @@
     <row r="36">
       <c r="A36" s="45" t="inlineStr">
         <is>
-          <t>CA encaissé : 343 €, pas 493 €. Les Hoka et les Nike sont des prélèvements, pas des ventes.</t>
+          <t>CA encaissé : 353 €, pas 493 €. Les Hoka et les Nike sont des prélèvements, pas des ventes.</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2030,106 +2030,109 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="C18" s="15">
         <f>$B18+$Y18*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D18" s="7">
-        <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="E18" s="6">
+      <c r="D18" s="16">
+        <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
         <f>CEILING($D18*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="G18" s="8">
+      <c r="F18" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="G18" s="17">
         <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
         <v/>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="18">
         <f>IF($G18="","",$G18/$C18)</f>
         <v/>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="15">
         <f>$C18/$I18</f>
         <v/>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="15">
         <f>IF($F18="","",$F18/$I18)</f>
         <v/>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="15">
         <f>IF($G18="","",$G18/$I18)</f>
         <v/>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="16">
         <f>IF($F18="","",$F18*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N18" s="6">
-        <f>IF($F18="","",$F18*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O18" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="P18" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q18" s="12" t="inlineStr">
+      <c r="N18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="P18" s="20" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q18" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R18" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S18" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T18" s="12" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="4" t="n">
+      <c r="R18" s="21" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S18" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-44194</t>
+        </is>
+      </c>
+      <c r="T18" s="21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U18" s="13" t="inlineStr">
+        <is>
+          <t>vendu</t>
+        </is>
+      </c>
+      <c r="V18" s="13" t="inlineStr"/>
+      <c r="W18" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="X18" s="13" t="inlineStr">
+        <is>
+          <t>VENDU</t>
+        </is>
+      </c>
+      <c r="Y18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="8">
+      <c r="Z18" s="17">
         <f>IF($G18="","",$G18/$Y18)</f>
         <v/>
       </c>
-      <c r="AA18" s="4">
+      <c r="AA18" s="13">
         <f>IF($Z18="","",IF($Z18&gt;=25,"atteint",TEXT(25-$Z18,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -2137,11 +2140,11 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
+          <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>50.4</v>
+        <v>37.8</v>
       </c>
       <c r="C19" s="6">
         <f>$B19+$Y19*Paramètres!$B$13</f>
@@ -2156,7 +2159,7 @@
         <v/>
       </c>
       <c r="F19" s="8" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G19" s="8">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
@@ -2190,10 +2193,10 @@
         <v/>
       </c>
       <c r="O19" s="11" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P19" s="11" t="n">
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
         <is>
@@ -2202,17 +2205,17 @@
       </c>
       <c r="R19" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>434</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
@@ -2242,18 +2245,18 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
+          <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>57.51</v>
+        <v>50.4</v>
       </c>
       <c r="C20" s="6">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E20" s="6">
@@ -2261,7 +2264,7 @@
         <v/>
       </c>
       <c r="F20" s="8" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G20" s="8">
         <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
@@ -2290,18 +2293,19 @@
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>0</v>
+      <c r="N20" s="6">
+        <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O20" s="11" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="P20" s="11" t="n">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="Q20" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R20" s="12" t="inlineStr">
@@ -2311,23 +2315,23 @@
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-44194</t>
         </is>
       </c>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>229</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin + eBay</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>Plafonné par le marché</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X20" s="4" t="inlineStr"/>
@@ -2346,18 +2350,18 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
+          <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>31.95</v>
+        <v>57.51</v>
       </c>
       <c r="C21" s="6">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
       <c r="E21" s="6">
@@ -2365,7 +2369,7 @@
         <v/>
       </c>
       <c r="F21" s="8" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="G21" s="8">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
@@ -2394,15 +2398,14 @@
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6">
-        <f>IF($F21="","",$F21*Paramètres!$B$7)</f>
-        <v/>
+      <c r="N21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O21" s="11" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="P21" s="11" t="n">
-        <v>6.5</v>
+        <v>11.7</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
         <is>
@@ -2416,23 +2419,23 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>FB2026-5996</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>159</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>Boutique + Leboncoin</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Plafonné par le marché</t>
         </is>
       </c>
       <c r="X21" s="4" t="inlineStr"/>
@@ -2451,11 +2454,11 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
+          <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>25.56</v>
+        <v>31.95</v>
       </c>
       <c r="C22" s="6">
         <f>$B22+$Y22*Paramètres!$B$13</f>
@@ -2470,7 +2473,7 @@
         <v/>
       </c>
       <c r="F22" s="8" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G22" s="8">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
@@ -2504,10 +2507,10 @@
         <v/>
       </c>
       <c r="O22" s="11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P22" s="11" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
@@ -2526,7 +2529,7 @@
       </c>
       <c r="T22" s="12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
@@ -2554,209 +2557,210 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="C23" s="6">
+        <f>$B23+$Y23*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D23" s="7">
+        <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="E23" s="6">
+        <f>CEILING($D23*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="G23" s="8">
+        <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>IF($G23="","",$G23/$C23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="6">
+        <f>$C23/$I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="6">
+        <f>IF($F23="","",$F23/$I23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="6">
+        <f>IF($G23="","",$G23/$I23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="7">
+        <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N23" s="6">
+        <f>IF($F23="","",$F23*Paramètres!$B$7)</f>
+        <v/>
+      </c>
+      <c r="O23" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q23" s="12" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="R23" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S23" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-5996</t>
+        </is>
+      </c>
+      <c r="T23" s="12" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>Boutique + Leboncoin</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr"/>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr"/>
+      <c r="Y23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="8">
+        <f>IF($G23="","",$G23/$Y23)</f>
+        <v/>
+      </c>
+      <c r="AA23" s="4">
+        <f>IF($Z23="","",IF($Z23&gt;=25,"atteint",TEXT(25-$Z23,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B24" s="23" t="n">
         <v>19.17</v>
       </c>
-      <c r="C23" s="24">
-        <f>$B23+$Y23*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
-        <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E23" s="24">
-        <f>CEILING($D23*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F23" s="26" t="n">
+      <c r="C24" s="24">
+        <f>$B24+$Y24*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D24" s="25">
+        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>CEILING($D24*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="26" t="n">
         <v>55</v>
       </c>
-      <c r="G23" s="26">
-        <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="27">
-        <f>IF($G23="","",$G23/$C23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="28" t="n">
+      <c r="G24" s="26">
+        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="27">
+        <f>IF($G24="","",$G24/$C24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="24">
-        <f>$C23/$I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="24">
-        <f>IF($F23="","",$F23/$I23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="24">
-        <f>IF($G23="","",$G23/$I23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="25">
-        <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N23" s="24" t="n">
+      <c r="J24" s="24">
+        <f>$C24/$I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="24">
+        <f>IF($F24="","",$F24/$I24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="24">
+        <f>IF($G24="","",$G24/$I24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="25">
+        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N24" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="29" t="n">
+      <c r="O24" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="P23" s="29" t="n">
+      <c r="P24" s="29" t="n">
         <v>3.9</v>
       </c>
-      <c r="Q23" s="30" t="inlineStr">
+      <c r="Q24" s="30" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R23" s="30" t="inlineStr">
+      <c r="R24" s="30" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S23" s="30" t="inlineStr">
+      <c r="S24" s="30" t="inlineStr">
         <is>
           <t>FB2026-44192</t>
         </is>
       </c>
-      <c r="T23" s="30" t="inlineStr">
+      <c r="T24" s="30" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="U23" s="22" t="inlineStr">
+      <c r="U24" s="22" t="inlineStr">
         <is>
           <t>Leboncoin + eBay, en lot</t>
         </is>
       </c>
-      <c r="V23" s="22" t="inlineStr"/>
-      <c r="W23" s="22" t="inlineStr">
+      <c r="V24" s="22" t="inlineStr"/>
+      <c r="W24" s="22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="X23" s="22" t="inlineStr"/>
-      <c r="Y23" s="22" t="n">
+      <c r="X24" s="22" t="inlineStr"/>
+      <c r="Y24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z23" s="26">
-        <f>IF($G23="","",$G23/$Y23)</f>
-        <v/>
-      </c>
-      <c r="AA23" s="22">
-        <f>IF($Z23="","",IF($Z23&gt;=25,"atteint",TEXT(25-$Z23,"0.00")&amp;" € manquants"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="C24" s="6">
-        <f>$B24+$Y24*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D24" s="7">
-        <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E24" s="6">
-        <f>CEILING($D24*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="G24" s="8">
-        <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="9">
-        <f>IF($G24="","",$G24/$C24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="6">
-        <f>$C24/$I24</f>
-        <v/>
-      </c>
-      <c r="K24" s="6">
-        <f>IF($F24="","",$F24/$I24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="6">
-        <f>IF($G24="","",$G24/$I24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="7">
-        <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="P24" s="11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q24" s="12" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R24" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S24" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T24" s="12" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin + eBay</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X24" s="4" t="inlineStr"/>
-      <c r="Y24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="8">
+      <c r="Z24" s="26">
         <f>IF($G24="","",$G24/$Y24)</f>
         <v/>
       </c>
-      <c r="AA24" s="4">
+      <c r="AA24" s="22">
         <f>IF($Z24="","",IF($Z24&gt;=25,"atteint",TEXT(25-$Z24,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -2764,11 +2768,11 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>GEOX baskets P.35 — neuves</t>
+          <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>21.73</v>
+        <v>25.2</v>
       </c>
       <c r="C25" s="6">
         <f>$B25+$Y25*Paramètres!$B$13</f>
@@ -2783,7 +2787,7 @@
         <v/>
       </c>
       <c r="F25" s="8" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G25" s="8">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
@@ -2816,29 +2820,29 @@
         <v>0</v>
       </c>
       <c r="O25" s="11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P25" s="11" t="n">
-        <v>4.42</v>
+        <v>5.2</v>
       </c>
       <c r="Q25" s="12" t="inlineStr">
         <is>
-          <t>ADN Lyon</t>
+          <t>ADN Le Mans</t>
         </is>
       </c>
       <c r="R25" s="12" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="S25" s="12" t="inlineStr">
         <is>
-          <t>FB2026-6023</t>
+          <t>FB2026-43716</t>
         </is>
       </c>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>439</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr">
@@ -2849,7 +2853,7 @@
       <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>Plafonné par le marché</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="X25" s="4" t="inlineStr"/>
@@ -2868,14 +2872,14 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
+          <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>69.23999999999999</v>
+        <v>21.73</v>
       </c>
       <c r="C26" s="6">
-        <f>$B26</f>
+        <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D26" s="7">
@@ -2887,7 +2891,7 @@
         <v/>
       </c>
       <c r="F26" s="8" t="n">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="G26" s="8">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
@@ -2898,7 +2902,7 @@
         <v/>
       </c>
       <c r="I26" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="6">
         <f>$C26/$I26</f>
@@ -2919,11 +2923,15 @@
       <c r="N26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="31" t="n"/>
-      <c r="P26" s="31" t="n"/>
+      <c r="O26" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="P26" s="11" t="n">
+        <v>4.42</v>
+      </c>
       <c r="Q26" s="12" t="inlineStr">
         <is>
-          <t>Meccha Japan</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="R26" s="12" t="inlineStr">
@@ -2933,28 +2941,28 @@
       </c>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>#FA429713</t>
+          <t>FB2026-6023</t>
         </is>
       </c>
       <c r="T26" s="12" t="inlineStr">
         <is>
-          <t>4521329432274</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin, lots de 15</t>
+          <t>Leboncoin + eBay</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Plafonné par le marché</t>
         </is>
       </c>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="8">
         <f>IF($G26="","",$G26/$Y26)</f>
@@ -2966,214 +2974,209 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="C27" s="6">
+        <f>$B27</f>
+        <v/>
+      </c>
+      <c r="D27" s="7">
+        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E27" s="6">
+        <f>CEILING($D27*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="G27" s="8">
+        <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>IF($G27="","",$G27/$C27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="6">
+        <f>$C27/$I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="6">
+        <f>IF($F27="","",$F27/$I27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="6">
+        <f>IF($G27="","",$G27/$I27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="7">
+        <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="31" t="n"/>
+      <c r="P27" s="31" t="n"/>
+      <c r="Q27" s="12" t="inlineStr">
+        <is>
+          <t>Meccha Japan</t>
+        </is>
+      </c>
+      <c r="R27" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S27" s="12" t="inlineStr">
+        <is>
+          <t>#FA429713</t>
+        </is>
+      </c>
+      <c r="T27" s="12" t="inlineStr">
+        <is>
+          <t>4521329432274</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin, lots de 15</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X27" s="4" t="inlineStr"/>
+      <c r="Y27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z27" s="8">
+        <f>IF($G27="","",$G27/$Y27)</f>
+        <v/>
+      </c>
+      <c r="AA27" s="4">
+        <f>IF($Z27="","",IF($Z27&gt;=25,"atteint",TEXT(25-$Z27,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B28" s="14" t="n">
         <v>25.2</v>
       </c>
-      <c r="C27" s="15">
-        <f>$B27+$Y27*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D27" s="16">
-        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E27" s="15">
-        <f>CEILING($D27*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F27" s="17" t="n">
+      <c r="C28" s="15">
+        <f>$B28+$Y28*Paramètres!$B$13</f>
+        <v/>
+      </c>
+      <c r="D28" s="16">
+        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
+        <f>CEILING($D28*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F28" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="G27" s="17">
-        <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="18">
-        <f>IF($G27="","",$G27/$C27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="19" t="n">
+      <c r="G28" s="17">
+        <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="18">
+        <f>IF($G28="","",$G28/$C28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="15">
-        <f>$C27/$I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="15">
-        <f>IF($F27="","",$F27/$I27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="15">
-        <f>IF($G27="","",$G27/$I27)</f>
-        <v/>
-      </c>
-      <c r="M27" s="16">
-        <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N27" s="15" t="n">
+      <c r="J28" s="15">
+        <f>$C28/$I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="15">
+        <f>IF($F28="","",$F28/$I28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="15">
+        <f>IF($G28="","",$G28/$I28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="16">
+        <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="20" t="n">
+      <c r="O28" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="P27" s="20" t="n">
+      <c r="P28" s="20" t="n">
         <v>5.2</v>
       </c>
-      <c r="Q27" s="21" t="inlineStr">
+      <c r="Q28" s="21" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R27" s="21" t="inlineStr">
+      <c r="R28" s="21" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="S27" s="21" t="inlineStr">
+      <c r="S28" s="21" t="inlineStr">
         <is>
           <t>FB2026-43717</t>
         </is>
       </c>
-      <c r="T27" s="21" t="inlineStr">
+      <c r="T28" s="21" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="U27" s="13" t="inlineStr">
+      <c r="U28" s="13" t="inlineStr">
         <is>
           <t>vendu</t>
         </is>
       </c>
-      <c r="V27" s="13" t="inlineStr"/>
-      <c r="W27" s="13" t="inlineStr">
+      <c r="V28" s="13" t="inlineStr"/>
+      <c r="W28" s="13" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="X27" s="13" t="inlineStr">
+      <c r="X28" s="13" t="inlineStr">
         <is>
           <t>VENDU</t>
         </is>
       </c>
-      <c r="Y27" s="13" t="n">
+      <c r="Y28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z27" s="17">
-        <f>IF($G27="","",$G27/$Y27)</f>
-        <v/>
-      </c>
-      <c r="AA27" s="13">
-        <f>IF($Z27="","",IF($Z27&gt;=25,"atteint",TEXT(25-$Z27,"0.00")&amp;" € manquants"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C28" s="6">
-        <f>$B28+$Y28*Paramètres!$B$13</f>
-        <v/>
-      </c>
-      <c r="D28" s="7">
-        <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="E28" s="6">
-        <f>CEILING($D28*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="G28" s="8">
-        <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="9">
-        <f>IF($G28="","",$G28/$C28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="6">
-        <f>$C28/$I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="6">
-        <f>IF($F28="","",$F28/$I28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="6">
-        <f>IF($G28="","",$G28/$I28)</f>
-        <v/>
-      </c>
-      <c r="M28" s="7">
-        <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N28" s="6">
-        <f>IF($F28="","",$F28*Paramètres!$B$7)</f>
-        <v/>
-      </c>
-      <c r="O28" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="P28" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q28" s="12" t="inlineStr">
-        <is>
-          <t>ADN Le Mans</t>
-        </is>
-      </c>
-      <c r="R28" s="12" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="S28" s="12" t="inlineStr">
-        <is>
-          <t>FB2026-43716</t>
-        </is>
-      </c>
-      <c r="T28" s="12" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>Boutique</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr"/>
-      <c r="W28" s="4" t="inlineStr">
-        <is>
-          <t>URGENT — saisonnier</t>
-        </is>
-      </c>
-      <c r="X28" s="4" t="inlineStr"/>
-      <c r="Y28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="8">
+      <c r="Z28" s="17">
         <f>IF($G28="","",$G28/$Y28)</f>
         <v/>
       </c>
-      <c r="AA28" s="4">
+      <c r="AA28" s="13">
         <f>IF($Z28="","",IF($Z28&gt;=25,"atteint",TEXT(25-$Z28,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -3181,18 +3184,18 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+          <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>75.59999999999999</v>
+        <v>50.4</v>
       </c>
       <c r="C29" s="6">
         <f>$B29+$Y29*Paramètres!$B$13</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
       <c r="E29" s="6">
@@ -3200,7 +3203,7 @@
         <v/>
       </c>
       <c r="F29" s="8" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G29" s="8">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
@@ -3229,14 +3232,15 @@
         <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N29" s="6" t="n">
-        <v>0</v>
+      <c r="N29" s="6">
+        <f>IF($F29="","",$F29*Paramètres!$B$7)</f>
+        <v/>
       </c>
       <c r="O29" s="11" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P29" s="11" t="n">
-        <v>15.6</v>
+        <v>10.4</v>
       </c>
       <c r="Q29" s="12" t="inlineStr">
         <is>
@@ -3255,18 +3259,18 @@
       </c>
       <c r="T29" s="12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>408</t>
         </is>
       </c>
       <c r="U29" s="4" t="inlineStr">
         <is>
-          <t>Leboncoin</t>
+          <t>Boutique</t>
         </is>
       </c>
       <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>Liquider</t>
+          <t>URGENT — saisonnier</t>
         </is>
       </c>
       <c r="X29" s="4" t="inlineStr"/>
@@ -3283,109 +3287,105 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="n">
-        <v>76.68000000000001</v>
-      </c>
-      <c r="C30" s="15">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="C30" s="6">
         <f>$B30+$Y30*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="7">
         <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="6">
         <f>CEILING($D30*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F30" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G30" s="17">
+      <c r="F30" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="G30" s="8">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
         <v/>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="9">
         <f>IF($G30="","",$G30/$C30)</f>
         <v/>
       </c>
-      <c r="I30" s="19" t="n">
+      <c r="I30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="6">
         <f>$C30/$I30</f>
         <v/>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="6">
         <f>IF($F30="","",$F30/$I30)</f>
         <v/>
       </c>
-      <c r="L30" s="15">
+      <c r="L30" s="6">
         <f>IF($G30="","",$G30/$I30)</f>
         <v/>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="7">
         <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N30" s="15" t="n">
+      <c r="N30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="20" t="n">
+      <c r="O30" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="P30" s="20" t="n">
+      <c r="P30" s="11" t="n">
         <v>15.6</v>
       </c>
-      <c r="Q30" s="21" t="inlineStr">
+      <c r="Q30" s="12" t="inlineStr">
         <is>
           <t>ADN Le Mans</t>
         </is>
       </c>
-      <c r="R30" s="21" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S30" s="21" t="inlineStr">
-        <is>
-          <t>FB2026-44192</t>
-        </is>
-      </c>
-      <c r="T30" s="21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="U30" s="13" t="inlineStr">
-        <is>
-          <t>Vinted, Italie — non encaissé</t>
-        </is>
-      </c>
-      <c r="V30" s="13" t="inlineStr"/>
-      <c r="W30" s="13" t="inlineStr">
-        <is>
-          <t>VENDUE, en attente</t>
-        </is>
-      </c>
-      <c r="X30" s="13" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
-      <c r="Y30" s="13" t="n">
+      <c r="R30" s="12" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="S30" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-43716</t>
+        </is>
+      </c>
+      <c r="T30" s="12" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>Liquider</t>
+        </is>
+      </c>
+      <c r="X30" s="4" t="inlineStr"/>
+      <c r="Y30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z30" s="17">
+      <c r="Z30" s="8">
         <f>IF($G30="","",$G30/$Y30)</f>
         <v/>
       </c>
-      <c r="AA30" s="13">
+      <c r="AA30" s="4">
         <f>IF($Z30="","",IF($Z30&gt;=25,"atteint",TEXT(25-$Z30,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -3393,11 +3393,11 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>T-shirt BALENCIAGA T.2 — neuf</t>
+          <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>113.4</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="C31" s="15">
         <f>$B31+$Y31*Paramètres!$B$13</f>
@@ -3412,7 +3412,7 @@
         <v/>
       </c>
       <c r="F31" s="17" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="G31" s="17">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="20" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>23.4</v>
+        <v>15.6</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3462,28 +3462,28 @@
       </c>
       <c r="S31" s="21" t="inlineStr">
         <is>
-          <t>FB2026-44194</t>
+          <t>FB2026-44192</t>
         </is>
       </c>
       <c r="T31" s="21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U31" s="13" t="inlineStr">
         <is>
-          <t>vendu</t>
+          <t>Vinted, Italie — non encaissé</t>
         </is>
       </c>
       <c r="V31" s="13" t="inlineStr"/>
       <c r="W31" s="13" t="inlineStr">
         <is>
-          <t>VENDU</t>
+          <t>VENDUE, en attente</t>
         </is>
       </c>
       <c r="X31" s="13" t="inlineStr">
         <is>
-          <t>VENDU</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="Y31" s="13" t="n">
@@ -5373,7 +5373,7 @@
     <row r="36">
       <c r="A36" s="45" t="inlineStr">
         <is>
-          <t>CA encaissé : 353 €, pas 493 €. Les Hoka et les Nike sont des prélèvements, pas des ventes.</t>
+          <t>CA encaissé : 373 €, pas 493 €. Les Hoka et les Nike sont des prélèvements, pas des ventes.</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -22,11 +22,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;€&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="#,##0 &quot;art.&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0 &quot;art.&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,57 +150,81 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA46"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -778,25 +802,25 @@
           <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="54" t="n">
         <v>56.7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="55">
         <f>$B6+$Y6*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="56">
         <f>$C6/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="55">
         <f>CEILING($D6*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="57" t="n">
         <v>199</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="57">
         <f>IF($F6="","",$F6-$C6-$M6-$N6)</f>
         <v/>
       </c>
@@ -807,29 +831,29 @@
       <c r="I6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="55">
         <f>$C6/$I6</f>
         <v/>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="55">
         <f>IF($F6="","",$F6/$I6)</f>
         <v/>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="55">
         <f>IF($G6="","",$G6/$I6)</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="56">
         <f>IF($F6="","",$F6*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="58" t="n">
         <v>11.7</v>
       </c>
       <c r="Q6" s="12" t="inlineStr">
@@ -867,7 +891,7 @@
       <c r="Y6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" s="8">
+      <c r="Z6" s="57">
         <f>IF($G6="","",$G6/$Y6)</f>
         <v/>
       </c>
@@ -882,25 +906,25 @@
           <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="55">
         <f>$B7+$Y7*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="56">
         <f>$C7/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="55">
         <f>CEILING($D7*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="57" t="n">
         <v>178</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="57">
         <f>IF($F7="","",$F7-$C7-$M7-$N7)</f>
         <v/>
       </c>
@@ -911,29 +935,29 @@
       <c r="I7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="55">
         <f>$C7/$I7</f>
         <v/>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="55">
         <f>IF($F7="","",$F7/$I7)</f>
         <v/>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="55">
         <f>IF($G7="","",$G7/$I7)</f>
         <v/>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="56">
         <f>IF($F7="","",$F7*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="N7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q7" s="12" t="inlineStr">
@@ -971,7 +995,7 @@
       <c r="Y7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="Z7" s="57">
         <f>IF($G7="","",$G7/$Y7)</f>
         <v/>
       </c>
@@ -986,25 +1010,25 @@
           <t>Demi-bottes FORMA Legacy Waterproof T.45 noir — neuves</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="54" t="n">
         <v>63</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="55">
         <f>$B8+$Y8*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="56">
         <f>$C8/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="55">
         <f>CEILING($D8*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="57" t="n">
         <v>159</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="57">
         <f>IF($F8="","",$F8-$C8-$M8-$N8)</f>
         <v/>
       </c>
@@ -1015,30 +1039,30 @@
       <c r="I8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="55">
         <f>$C8/$I8</f>
         <v/>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="55">
         <f>IF($F8="","",$F8/$I8)</f>
         <v/>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="55">
         <f>IF($G8="","",$G8/$I8)</f>
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="56">
         <f>IF($F8="","",$F8*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="55">
         <f>IF($F8="","",$F8*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" s="58" t="n">
         <v>13</v>
       </c>
       <c r="Q8" s="12" t="inlineStr">
@@ -1076,7 +1100,7 @@
       <c r="Y8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z8" s="8">
+      <c r="Z8" s="57">
         <f>IF($G8="","",$G8/$Y8)</f>
         <v/>
       </c>
@@ -1091,25 +1115,25 @@
           <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="55">
         <f>$B9+$Y9*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="56">
         <f>$C9/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="55">
         <f>CEILING($D9*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="57" t="n">
         <v>136</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="57">
         <f>IF($F9="","",$F9-$C9-$M9-$N9)</f>
         <v/>
       </c>
@@ -1120,29 +1144,29 @@
       <c r="I9" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="55">
         <f>$C9/$I9</f>
         <v/>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="55">
         <f>IF($F9="","",$F9/$I9)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="55">
         <f>IF($G9="","",$G9/$I9)</f>
         <v/>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="56">
         <f>IF($F9="","",$F9*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="N9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q9" s="12" t="inlineStr">
@@ -1180,7 +1204,7 @@
       <c r="Y9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="Z9" s="8">
+      <c r="Z9" s="57">
         <f>IF($G9="","",$G9/$Y9)</f>
         <v/>
       </c>
@@ -1195,25 +1219,25 @@
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="59" t="n">
         <v>100.8</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="60">
         <f>$B10+$Y10*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="61">
         <f>$C10/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="60">
         <f>CEILING($D10*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="62" t="n">
         <v>208</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="62">
         <f>IF($F10="","",$F10-$C10-$M10-$N10)</f>
         <v/>
       </c>
@@ -1224,29 +1248,29 @@
       <c r="I10" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="60">
         <f>$C10/$I10</f>
         <v/>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="60">
         <f>IF($F10="","",$F10/$I10)</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="60">
         <f>IF($G10="","",$G10/$I10)</f>
         <v/>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="61">
         <f>IF($F10="","",$F10*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N10" s="15" t="n">
+      <c r="N10" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="20" t="n">
+      <c r="O10" s="63" t="n">
         <v>80</v>
       </c>
-      <c r="P10" s="20" t="n">
+      <c r="P10" s="63" t="n">
         <v>20.8</v>
       </c>
       <c r="Q10" s="21" t="inlineStr">
@@ -1288,7 +1312,7 @@
       <c r="Y10" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" s="17">
+      <c r="Z10" s="62">
         <f>IF($G10="","",$G10/$Y10)</f>
         <v/>
       </c>
@@ -1303,25 +1327,25 @@
           <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="54" t="n">
         <v>20.45</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="55">
         <f>$B11+$Y11*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="56">
         <f>$C11/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="55">
         <f>CEILING($D11*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="57">
         <f>IF($F11="","",$F11-$C11-$M11-$N11)</f>
         <v/>
       </c>
@@ -1332,30 +1356,30 @@
       <c r="I11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="55">
         <f>$C11/$I11</f>
         <v/>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="55">
         <f>IF($F11="","",$F11/$I11)</f>
         <v/>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="55">
         <f>IF($G11="","",$G11/$I11)</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="56">
         <f>IF($F11="","",$F11*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="55">
         <f>IF($F11="","",$F11*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O11" s="11" t="n">
+      <c r="O11" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="P11" s="11" t="n">
+      <c r="P11" s="58" t="n">
         <v>4.16</v>
       </c>
       <c r="Q11" s="12" t="inlineStr">
@@ -1393,7 +1417,7 @@
       <c r="Y11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z11" s="8">
+      <c r="Z11" s="57">
         <f>IF($G11="","",$G11/$Y11)</f>
         <v/>
       </c>
@@ -1408,25 +1432,25 @@
           <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="54" t="n">
         <v>68.56999999999999</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="55">
         <f>$B12+$Y12*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="56">
         <f>$C12/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="55">
         <f>CEILING($D12*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="57" t="n">
         <v>139</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="57">
         <f>IF($F12="","",$F12-$C12-$M12-$N12)</f>
         <v/>
       </c>
@@ -1437,29 +1461,29 @@
       <c r="I12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="55">
         <f>$C12/$I12</f>
         <v/>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="55">
         <f>IF($F12="","",$F12/$I12)</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="55">
         <f>IF($G12="","",$G12/$I12)</f>
         <v/>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="56">
         <f>IF($F12="","",$F12*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="11" t="n">
+      <c r="O12" s="58" t="n">
         <v>60</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="58" t="n">
         <v>8.57</v>
       </c>
       <c r="Q12" s="12" t="inlineStr">
@@ -1497,7 +1521,7 @@
       <c r="Y12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z12" s="8">
+      <c r="Z12" s="57">
         <f>IF($G12="","",$G12/$Y12)</f>
         <v/>
       </c>
@@ -1512,25 +1536,25 @@
           <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="54" t="n">
         <v>12.6</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="55">
         <f>$B13+$Y13*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="56">
         <f>$C13/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="55">
         <f>CEILING($D13*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="57">
         <f>IF($F13="","",$F13-$C13-$M13-$N13)</f>
         <v/>
       </c>
@@ -1541,30 +1565,30 @@
       <c r="I13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="55">
         <f>$C13/$I13</f>
         <v/>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="55">
         <f>IF($F13="","",$F13/$I13)</f>
         <v/>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="55">
         <f>IF($G13="","",$G13/$I13)</f>
         <v/>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="56">
         <f>IF($F13="","",$F13*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="55">
         <f>IF($F13="","",$F13*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O13" s="11" t="n">
+      <c r="O13" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="P13" s="11" t="n">
+      <c r="P13" s="58" t="n">
         <v>2.6</v>
       </c>
       <c r="Q13" s="12" t="inlineStr">
@@ -1602,7 +1626,7 @@
       <c r="Y13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z13" s="8">
+      <c r="Z13" s="57">
         <f>IF($G13="","",$G13/$Y13)</f>
         <v/>
       </c>
@@ -1617,25 +1641,25 @@
           <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="55">
         <f>$B14+$Y14*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="56">
         <f>$C14/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="55">
         <f>CEILING($D14*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="57">
         <f>IF($F14="","",$F14-$C14-$M14-$N14)</f>
         <v/>
       </c>
@@ -1646,30 +1670,30 @@
       <c r="I14" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="55">
         <f>$C14/$I14</f>
         <v/>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="55">
         <f>IF($F14="","",$F14/$I14)</f>
         <v/>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="55">
         <f>IF($G14="","",$G14/$I14)</f>
         <v/>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="56">
         <f>IF($F14="","",$F14*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="55">
         <f>IF($F14="","",$F14*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="11" t="n">
+      <c r="O14" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P14" s="11" t="n">
+      <c r="P14" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q14" s="12" t="inlineStr">
@@ -1707,7 +1731,7 @@
       <c r="Y14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z14" s="8">
+      <c r="Z14" s="57">
         <f>IF($G14="","",$G14/$Y14)</f>
         <v/>
       </c>
@@ -1722,25 +1746,25 @@
           <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="55">
         <f>$B15+$Y15*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="56">
         <f>$C15/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="55">
         <f>CEILING($D15*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="57" t="n">
         <v>89</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="57">
         <f>IF($F15="","",$F15-$C15-$M15-$N15)</f>
         <v/>
       </c>
@@ -1751,30 +1775,30 @@
       <c r="I15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="55">
         <f>$C15/$I15</f>
         <v/>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="55">
         <f>IF($F15="","",$F15/$I15)</f>
         <v/>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="55">
         <f>IF($G15="","",$G15/$I15)</f>
         <v/>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="56">
         <f>IF($F15="","",$F15*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="55">
         <f>IF($F15="","",$F15*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q15" s="12" t="inlineStr">
@@ -1812,7 +1836,7 @@
       <c r="Y15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z15" s="8">
+      <c r="Z15" s="57">
         <f>IF($G15="","",$G15/$Y15)</f>
         <v/>
       </c>
@@ -1827,25 +1851,25 @@
           <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="55">
         <f>$B16+$Y16*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="56">
         <f>$C16/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="55">
         <f>CEILING($D16*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="57" t="n">
         <v>98</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="57">
         <f>IF($F16="","",$F16-$C16-$M16-$N16)</f>
         <v/>
       </c>
@@ -1856,29 +1880,29 @@
       <c r="I16" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="55">
         <f>$C16/$I16</f>
         <v/>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="55">
         <f>IF($F16="","",$F16/$I16)</f>
         <v/>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="55">
         <f>IF($G16="","",$G16/$I16)</f>
         <v/>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="56">
         <f>IF($F16="","",$F16*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="11" t="n">
+      <c r="O16" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P16" s="11" t="n">
+      <c r="P16" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q16" s="12" t="inlineStr">
@@ -1916,7 +1940,7 @@
       <c r="Y16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Z16" s="8">
+      <c r="Z16" s="57">
         <f>IF($G16="","",$G16/$Y16)</f>
         <v/>
       </c>
@@ -1931,25 +1955,25 @@
           <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="54" t="n">
         <v>63</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="55">
         <f>$B17+$Y17*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="56">
         <f>$C17/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="55">
         <f>CEILING($D17*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="57" t="n">
         <v>105</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="57">
         <f>IF($F17="","",$F17-$C17-$M17-$N17)</f>
         <v/>
       </c>
@@ -1960,29 +1984,29 @@
       <c r="I17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="55">
         <f>$C17/$I17</f>
         <v/>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="55">
         <f>IF($F17="","",$F17/$I17)</f>
         <v/>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="55">
         <f>IF($G17="","",$G17/$I17)</f>
         <v/>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="56">
         <f>IF($F17="","",$F17*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" s="58" t="n">
         <v>13</v>
       </c>
       <c r="Q17" s="12" t="inlineStr">
@@ -2020,7 +2044,7 @@
       <c r="Y17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z17" s="8">
+      <c r="Z17" s="57">
         <f>IF($G17="","",$G17/$Y17)</f>
         <v/>
       </c>
@@ -2035,25 +2059,25 @@
           <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="59" t="n">
         <v>113.4</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="60">
         <f>$B18+$Y18*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="61">
         <f>$C18/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="60">
         <f>CEILING($D18*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="62" t="n">
         <v>155</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="62">
         <f>IF($F18="","",$F18-$C18-$M18-$N18)</f>
         <v/>
       </c>
@@ -2064,29 +2088,29 @@
       <c r="I18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="60">
         <f>$C18/$I18</f>
         <v/>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="60">
         <f>IF($F18="","",$F18/$I18)</f>
         <v/>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="60">
         <f>IF($G18="","",$G18/$I18)</f>
         <v/>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="61">
         <f>IF($F18="","",$F18*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N18" s="15" t="n">
+      <c r="N18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="20" t="n">
+      <c r="O18" s="63" t="n">
         <v>90</v>
       </c>
-      <c r="P18" s="20" t="n">
+      <c r="P18" s="63" t="n">
         <v>23.4</v>
       </c>
       <c r="Q18" s="21" t="inlineStr">
@@ -2128,7 +2152,7 @@
       <c r="Y18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="17">
+      <c r="Z18" s="62">
         <f>IF($G18="","",$G18/$Y18)</f>
         <v/>
       </c>
@@ -2143,25 +2167,25 @@
           <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="54" t="n">
         <v>37.8</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="55">
         <f>$B19+$Y19*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="56">
         <f>$C19/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="55">
         <f>CEILING($D19*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="57" t="n">
         <v>79</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="57">
         <f>IF($F19="","",$F19-$C19-$M19-$N19)</f>
         <v/>
       </c>
@@ -2172,30 +2196,30 @@
       <c r="I19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="55">
         <f>$C19/$I19</f>
         <v/>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="55">
         <f>IF($F19="","",$F19/$I19)</f>
         <v/>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="55">
         <f>IF($G19="","",$G19/$I19)</f>
         <v/>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="56">
         <f>IF($F19="","",$F19*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="55">
         <f>IF($F19="","",$F19*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q19" s="12" t="inlineStr">
@@ -2233,7 +2257,7 @@
       <c r="Y19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z19" s="8">
+      <c r="Z19" s="57">
         <f>IF($G19="","",$G19/$Y19)</f>
         <v/>
       </c>
@@ -2248,25 +2272,25 @@
           <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="54" t="n">
         <v>50.4</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="55">
         <f>$B20+$Y20*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="56">
         <f>$C20/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="55">
         <f>CEILING($D20*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="57" t="n">
         <v>91</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="57">
         <f>IF($F20="","",$F20-$C20-$M20-$N20)</f>
         <v/>
       </c>
@@ -2277,30 +2301,30 @@
       <c r="I20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="55">
         <f>$C20/$I20</f>
         <v/>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="55">
         <f>IF($F20="","",$F20/$I20)</f>
         <v/>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="55">
         <f>IF($G20="","",$G20/$I20)</f>
         <v/>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="56">
         <f>IF($F20="","",$F20*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="55">
         <f>IF($F20="","",$F20*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="O20" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P20" s="11" t="n">
+      <c r="P20" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q20" s="12" t="inlineStr">
@@ -2338,7 +2362,7 @@
       <c r="Y20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z20" s="8">
+      <c r="Z20" s="57">
         <f>IF($G20="","",$G20/$Y20)</f>
         <v/>
       </c>
@@ -2353,25 +2377,25 @@
           <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="54" t="n">
         <v>57.51</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="55">
         <f>$B21+$Y21*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="56">
         <f>$C21/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="55">
         <f>CEILING($D21*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="57" t="n">
         <v>95</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="57">
         <f>IF($F21="","",$F21-$C21-$M21-$N21)</f>
         <v/>
       </c>
@@ -2382,29 +2406,29 @@
       <c r="I21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="55">
         <f>$C21/$I21</f>
         <v/>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="55">
         <f>IF($F21="","",$F21/$I21)</f>
         <v/>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="55">
         <f>IF($G21="","",$G21/$I21)</f>
         <v/>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="56">
         <f>IF($F21="","",$F21*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="O21" s="58" t="n">
         <v>45</v>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" s="58" t="n">
         <v>11.7</v>
       </c>
       <c r="Q21" s="12" t="inlineStr">
@@ -2442,7 +2466,7 @@
       <c r="Y21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z21" s="8">
+      <c r="Z21" s="57">
         <f>IF($G21="","",$G21/$Y21)</f>
         <v/>
       </c>
@@ -2457,25 +2481,25 @@
           <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="54" t="n">
         <v>31.95</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="55">
         <f>$B22+$Y22*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="56">
         <f>$C22/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="55">
         <f>CEILING($D22*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="57">
         <f>IF($F22="","",$F22-$C22-$M22-$N22)</f>
         <v/>
       </c>
@@ -2486,30 +2510,30 @@
       <c r="I22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="55">
         <f>$C22/$I22</f>
         <v/>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="55">
         <f>IF($F22="","",$F22/$I22)</f>
         <v/>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="55">
         <f>IF($G22="","",$G22/$I22)</f>
         <v/>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="56">
         <f>IF($F22="","",$F22*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="55">
         <f>IF($F22="","",$F22*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="O22" s="58" t="n">
         <v>25</v>
       </c>
-      <c r="P22" s="11" t="n">
+      <c r="P22" s="58" t="n">
         <v>6.5</v>
       </c>
       <c r="Q22" s="12" t="inlineStr">
@@ -2547,7 +2571,7 @@
       <c r="Y22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z22" s="8">
+      <c r="Z22" s="57">
         <f>IF($G22="","",$G22/$Y22)</f>
         <v/>
       </c>
@@ -2562,25 +2586,25 @@
           <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="54" t="n">
         <v>25.56</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="55">
         <f>$B23+$Y23*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="56">
         <f>$C23/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="55">
         <f>CEILING($D23*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="57" t="n">
         <v>62</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="57">
         <f>IF($F23="","",$F23-$C23-$M23-$N23)</f>
         <v/>
       </c>
@@ -2591,30 +2615,30 @@
       <c r="I23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="55">
         <f>$C23/$I23</f>
         <v/>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="55">
         <f>IF($F23="","",$F23/$I23)</f>
         <v/>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="55">
         <f>IF($G23="","",$G23/$I23)</f>
         <v/>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="56">
         <f>IF($F23="","",$F23*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="55">
         <f>IF($F23="","",$F23*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="11" t="n">
+      <c r="O23" s="58" t="n">
         <v>20</v>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" s="58" t="n">
         <v>5.2</v>
       </c>
       <c r="Q23" s="12" t="inlineStr">
@@ -2652,7 +2676,7 @@
       <c r="Y23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z23" s="8">
+      <c r="Z23" s="57">
         <f>IF($G23="","",$G23/$Y23)</f>
         <v/>
       </c>
@@ -2667,25 +2691,25 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="64" t="n">
         <v>19.17</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="65">
         <f>$B24+$Y24*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="66">
         <f>$C24/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="65">
         <f>CEILING($D24*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="67" t="n">
         <v>55</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="67">
         <f>IF($F24="","",$F24-$C24-$M24-$N24)</f>
         <v/>
       </c>
@@ -2696,29 +2720,29 @@
       <c r="I24" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="65">
         <f>$C24/$I24</f>
         <v/>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="65">
         <f>IF($F24="","",$F24/$I24)</f>
         <v/>
       </c>
-      <c r="L24" s="24">
+      <c r="L24" s="65">
         <f>IF($G24="","",$G24/$I24)</f>
         <v/>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="66">
         <f>IF($F24="","",$F24*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N24" s="24" t="n">
+      <c r="N24" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="29" t="n">
+      <c r="O24" s="68" t="n">
         <v>15</v>
       </c>
-      <c r="P24" s="29" t="n">
+      <c r="P24" s="68" t="n">
         <v>3.9</v>
       </c>
       <c r="Q24" s="30" t="inlineStr">
@@ -2756,7 +2780,7 @@
       <c r="Y24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z24" s="26">
+      <c r="Z24" s="67">
         <f>IF($G24="","",$G24/$Y24)</f>
         <v/>
       </c>
@@ -2771,25 +2795,25 @@
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="54" t="n">
         <v>25.2</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="55">
         <f>$B25+$Y25*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="56">
         <f>$C25/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="55">
         <f>CEILING($D25*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="57" t="n">
         <v>61</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="57">
         <f>IF($F25="","",$F25-$C25-$M25-$N25)</f>
         <v/>
       </c>
@@ -2800,29 +2824,29 @@
       <c r="I25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="55">
         <f>$C25/$I25</f>
         <v/>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="55">
         <f>IF($F25="","",$F25/$I25)</f>
         <v/>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="55">
         <f>IF($G25="","",$G25/$I25)</f>
         <v/>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="56">
         <f>IF($F25="","",$F25*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="11" t="n">
+      <c r="O25" s="58" t="n">
         <v>20</v>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P25" s="58" t="n">
         <v>5.2</v>
       </c>
       <c r="Q25" s="12" t="inlineStr">
@@ -2860,7 +2884,7 @@
       <c r="Y25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" s="8">
+      <c r="Z25" s="57">
         <f>IF($G25="","",$G25/$Y25)</f>
         <v/>
       </c>
@@ -2875,25 +2899,25 @@
           <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="54" t="n">
         <v>21.73</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="55">
         <f>$B26+$Y26*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="56">
         <f>$C26/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="55">
         <f>CEILING($D26*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="57">
         <f>IF($F26="","",$F26-$C26-$M26-$N26)</f>
         <v/>
       </c>
@@ -2904,29 +2928,29 @@
       <c r="I26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="55">
         <f>$C26/$I26</f>
         <v/>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="55">
         <f>IF($F26="","",$F26/$I26)</f>
         <v/>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="55">
         <f>IF($G26="","",$G26/$I26)</f>
         <v/>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="56">
         <f>IF($F26="","",$F26*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="11" t="n">
+      <c r="O26" s="58" t="n">
         <v>17</v>
       </c>
-      <c r="P26" s="11" t="n">
+      <c r="P26" s="58" t="n">
         <v>4.42</v>
       </c>
       <c r="Q26" s="12" t="inlineStr">
@@ -2964,7 +2988,7 @@
       <c r="Y26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z26" s="8">
+      <c r="Z26" s="57">
         <f>IF($G26="","",$G26/$Y26)</f>
         <v/>
       </c>
@@ -2974,101 +2998,103 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>69.23999999999999</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="B27" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="60">
         <f>$B27</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="61">
         <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="60">
         <f>CEILING($D27*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="G27" s="8">
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="62">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
         <v/>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="18">
         <f>IF($G27="","",$G27/$C27)</f>
         <v/>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I27" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="60">
         <f>$C27/$I27</f>
         <v/>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="60">
         <f>IF($F27="","",$F27/$I27)</f>
         <v/>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="60">
         <f>IF($G27="","",$G27/$I27)</f>
         <v/>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="61">
         <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="31" t="n"/>
-      <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="12" t="inlineStr">
+      <c r="O27" s="63" t="n"/>
+      <c r="P27" s="63" t="n"/>
+      <c r="Q27" s="21" t="inlineStr">
         <is>
           <t>Meccha Japan</t>
         </is>
       </c>
-      <c r="R27" s="12" t="inlineStr">
+      <c r="R27" s="21" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S27" s="12" t="inlineStr">
+      <c r="S27" s="21" t="inlineStr">
         <is>
           <t>#FA429713</t>
         </is>
       </c>
-      <c r="T27" s="12" t="inlineStr">
+      <c r="T27" s="21" t="inlineStr">
         <is>
           <t>4521329432274</t>
         </is>
       </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin, lots de 15</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr"/>
-      <c r="W27" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X27" s="4" t="inlineStr"/>
-      <c r="Y27" s="4" t="n">
+      <c r="U27" s="13" t="inlineStr">
+        <is>
+          <t>Retiré — achat personnel (Pokémon), jamais dans l'activité</t>
+        </is>
+      </c>
+      <c r="V27" s="13" t="inlineStr"/>
+      <c r="W27" s="13" t="inlineStr">
+        <is>
+          <t>RETIRÉ — PERSONNEL</t>
+        </is>
+      </c>
+      <c r="X27" s="13" t="inlineStr">
+        <is>
+          <t>Retiré 17/08</t>
+        </is>
+      </c>
+      <c r="Y27" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="Z27" s="8">
+      <c r="Z27" s="62">
         <f>IF($G27="","",$G27/$Y27)</f>
         <v/>
       </c>
-      <c r="AA27" s="4">
+      <c r="AA27" s="13">
         <f>IF($Z27="","",IF($Z27&gt;=25,"atteint",TEXT(25-$Z27,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -3079,25 +3105,25 @@
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="59" t="n">
         <v>25.2</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="60">
         <f>$B28+$Y28*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="61">
         <f>$C28/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="60">
         <f>CEILING($D28*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="62" t="n">
         <v>50</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="62">
         <f>IF($F28="","",$F28-$C28-$M28-$N28)</f>
         <v/>
       </c>
@@ -3108,29 +3134,29 @@
       <c r="I28" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="60">
         <f>$C28/$I28</f>
         <v/>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="60">
         <f>IF($F28="","",$F28/$I28)</f>
         <v/>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="60">
         <f>IF($G28="","",$G28/$I28)</f>
         <v/>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="61">
         <f>IF($F28="","",$F28*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N28" s="15" t="n">
+      <c r="N28" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="20" t="n">
+      <c r="O28" s="63" t="n">
         <v>20</v>
       </c>
-      <c r="P28" s="20" t="n">
+      <c r="P28" s="63" t="n">
         <v>5.2</v>
       </c>
       <c r="Q28" s="21" t="inlineStr">
@@ -3172,7 +3198,7 @@
       <c r="Y28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z28" s="17">
+      <c r="Z28" s="62">
         <f>IF($G28="","",$G28/$Y28)</f>
         <v/>
       </c>
@@ -3187,25 +3213,25 @@
           <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="54" t="n">
         <v>50.4</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="55">
         <f>$B29+$Y29*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="56">
         <f>$C29/(1-Paramètres!$B$5-Paramètres!$B$6-Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="55">
         <f>CEILING($D29*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="57" t="n">
         <v>75</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="57">
         <f>IF($F29="","",$F29-$C29-$M29-$N29)</f>
         <v/>
       </c>
@@ -3216,30 +3242,30 @@
       <c r="I29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="55">
         <f>$C29/$I29</f>
         <v/>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="55">
         <f>IF($F29="","",$F29/$I29)</f>
         <v/>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="55">
         <f>IF($G29="","",$G29/$I29)</f>
         <v/>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="56">
         <f>IF($F29="","",$F29*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="55">
         <f>IF($F29="","",$F29*Paramètres!$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="11" t="n">
+      <c r="O29" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P29" s="11" t="n">
+      <c r="P29" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q29" s="12" t="inlineStr">
@@ -3277,7 +3303,7 @@
       <c r="Y29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" s="8">
+      <c r="Z29" s="57">
         <f>IF($G29="","",$G29/$Y29)</f>
         <v/>
       </c>
@@ -3292,25 +3318,25 @@
           <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="54" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="55">
         <f>$B30+$Y30*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="56">
         <f>$C30/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="55">
         <f>CEILING($D30*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="57" t="n">
         <v>99</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="57">
         <f>IF($F30="","",$F30-$C30-$M30-$N30)</f>
         <v/>
       </c>
@@ -3321,29 +3347,29 @@
       <c r="I30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="55">
         <f>$C30/$I30</f>
         <v/>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="55">
         <f>IF($F30="","",$F30/$I30)</f>
         <v/>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="55">
         <f>IF($G30="","",$G30/$I30)</f>
         <v/>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="56">
         <f>IF($F30="","",$F30*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="11" t="n">
+      <c r="O30" s="58" t="n">
         <v>60</v>
       </c>
-      <c r="P30" s="11" t="n">
+      <c r="P30" s="58" t="n">
         <v>15.6</v>
       </c>
       <c r="Q30" s="12" t="inlineStr">
@@ -3381,7 +3407,7 @@
       <c r="Y30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z30" s="8">
+      <c r="Z30" s="57">
         <f>IF($G30="","",$G30/$Y30)</f>
         <v/>
       </c>
@@ -3396,25 +3422,25 @@
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="59" t="n">
         <v>76.68000000000001</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="60">
         <f>$B31+$Y31*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="61">
         <f>$C31/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="60">
         <f>CEILING($D31*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="62" t="n">
         <v>100</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="62">
         <f>IF($F31="","",$F31-$C31-$M31-$N31)</f>
         <v/>
       </c>
@@ -3425,29 +3451,29 @@
       <c r="I31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="60">
         <f>$C31/$I31</f>
         <v/>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="60">
         <f>IF($F31="","",$F31/$I31)</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="60">
         <f>IF($G31="","",$G31/$I31)</f>
         <v/>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="61">
         <f>IF($F31="","",$F31*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N31" s="15" t="n">
+      <c r="N31" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="20" t="n">
+      <c r="O31" s="63" t="n">
         <v>60</v>
       </c>
-      <c r="P31" s="20" t="n">
+      <c r="P31" s="63" t="n">
         <v>15.6</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
@@ -3472,24 +3498,24 @@
       </c>
       <c r="U31" s="13" t="inlineStr">
         <is>
-          <t>Vinted, Italie — non encaissé</t>
+          <t>Vinted, Italie — encaissée 23/08</t>
         </is>
       </c>
       <c r="V31" s="13" t="inlineStr"/>
       <c r="W31" s="13" t="inlineStr">
         <is>
-          <t>VENDUE, en attente</t>
+          <t>VENDUE</t>
         </is>
       </c>
       <c r="X31" s="13" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>VENDUE 12/08, encaissée 23/08</t>
         </is>
       </c>
       <c r="Y31" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" s="17">
+      <c r="Z31" s="62">
         <f>IF($G31="","",$G31/$Y31)</f>
         <v/>
       </c>
@@ -3504,25 +3530,25 @@
           <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="59" t="n">
         <v>50.4</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="60">
         <f>$B32+$Y32*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="61">
         <f>$C32/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="60">
         <f>CEILING($D32*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="62" t="n">
         <v>70</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="62">
         <f>IF($F32="","",$F32-$C32-$M32-$N32)</f>
         <v/>
       </c>
@@ -3533,29 +3559,29 @@
       <c r="I32" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="60">
         <f>$C32/$I32</f>
         <v/>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="60">
         <f>IF($F32="","",$F32/$I32)</f>
         <v/>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="60">
         <f>IF($G32="","",$G32/$I32)</f>
         <v/>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="61">
         <f>IF($F32="","",$F32*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N32" s="15" t="n">
+      <c r="N32" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="20" t="n">
+      <c r="O32" s="63" t="n">
         <v>40</v>
       </c>
-      <c r="P32" s="20" t="n">
+      <c r="P32" s="63" t="n">
         <v>10.4</v>
       </c>
       <c r="Q32" s="21" t="inlineStr">
@@ -3597,7 +3623,7 @@
       <c r="Y32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z32" s="17">
+      <c r="Z32" s="62">
         <f>IF($G32="","",$G32/$Y32)</f>
         <v/>
       </c>
@@ -3612,25 +3638,25 @@
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="54" t="n">
         <v>51.12</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="55">
         <f>$B33+$Y33*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="56">
         <f>$C33/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="55">
         <f>CEILING($D33*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="57">
         <f>IF($F33="","",$F33-$C33-$M33-$N33)</f>
         <v/>
       </c>
@@ -3641,29 +3667,29 @@
       <c r="I33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="55">
         <f>$C33/$I33</f>
         <v/>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="55">
         <f>IF($F33="","",$F33/$I33)</f>
         <v/>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="55">
         <f>IF($G33="","",$G33/$I33)</f>
         <v/>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="56">
         <f>IF($F33="","",$F33*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="N33" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="11" t="n">
+      <c r="O33" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P33" s="11" t="n">
+      <c r="P33" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q33" s="12" t="inlineStr">
@@ -3701,7 +3727,7 @@
       <c r="Y33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z33" s="8">
+      <c r="Z33" s="57">
         <f>IF($G33="","",$G33/$Y33)</f>
         <v/>
       </c>
@@ -3716,25 +3742,25 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="64" t="n">
         <v>38.34</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="65">
         <f>$B34+$Y34*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="66">
         <f>$C34/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="65">
         <f>CEILING($D34*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="67" t="n">
         <v>55</v>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="67">
         <f>IF($F34="","",$F34-$C34-$M34-$N34)</f>
         <v/>
       </c>
@@ -3745,29 +3771,29 @@
       <c r="I34" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="J34" s="24">
+      <c r="J34" s="65">
         <f>$C34/$I34</f>
         <v/>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="65">
         <f>IF($F34="","",$F34/$I34)</f>
         <v/>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="65">
         <f>IF($G34="","",$G34/$I34)</f>
         <v/>
       </c>
-      <c r="M34" s="25">
+      <c r="M34" s="66">
         <f>IF($F34="","",$F34*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N34" s="24" t="n">
+      <c r="N34" s="65" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="29" t="n">
+      <c r="O34" s="68" t="n">
         <v>30</v>
       </c>
-      <c r="P34" s="29" t="n">
+      <c r="P34" s="68" t="n">
         <v>7.8</v>
       </c>
       <c r="Q34" s="30" t="inlineStr">
@@ -3805,7 +3831,7 @@
       <c r="Y34" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Z34" s="26">
+      <c r="Z34" s="67">
         <f>IF($G34="","",$G34/$Y34)</f>
         <v/>
       </c>
@@ -3820,25 +3846,25 @@
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="54" t="n">
         <v>38.34</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="55">
         <f>$B35+$Y35*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="56">
         <f>$C35/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="55">
         <f>CEILING($D35*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="57">
         <f>IF($F35="","",$F35-$C35-$M35-$N35)</f>
         <v/>
       </c>
@@ -3849,29 +3875,29 @@
       <c r="I35" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="55">
         <f>$C35/$I35</f>
         <v/>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="55">
         <f>IF($F35="","",$F35/$I35)</f>
         <v/>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="55">
         <f>IF($G35="","",$G35/$I35)</f>
         <v/>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="56">
         <f>IF($F35="","",$F35*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="11" t="n">
+      <c r="O35" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="P35" s="11" t="n">
+      <c r="P35" s="58" t="n">
         <v>7.8</v>
       </c>
       <c r="Q35" s="12" t="inlineStr">
@@ -3909,7 +3935,7 @@
       <c r="Y35" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z35" s="8">
+      <c r="Z35" s="57">
         <f>IF($G35="","",$G35/$Y35)</f>
         <v/>
       </c>
@@ -3924,25 +3950,25 @@
           <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="54" t="n">
         <v>51.12</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="55">
         <f>$B36+$Y36*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="56">
         <f>$C36/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="55">
         <f>CEILING($D36*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="57">
         <f>IF($F36="","",$F36-$C36-$M36-$N36)</f>
         <v/>
       </c>
@@ -3953,29 +3979,29 @@
       <c r="I36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="55">
         <f>$C36/$I36</f>
         <v/>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="55">
         <f>IF($F36="","",$F36/$I36)</f>
         <v/>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="55">
         <f>IF($G36="","",$G36/$I36)</f>
         <v/>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="56">
         <f>IF($F36="","",$F36*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="N36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="11" t="n">
+      <c r="O36" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="P36" s="11" t="n">
+      <c r="P36" s="58" t="n">
         <v>10.4</v>
       </c>
       <c r="Q36" s="12" t="inlineStr">
@@ -4013,7 +4039,7 @@
       <c r="Y36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z36" s="8">
+      <c r="Z36" s="57">
         <f>IF($G36="","",$G36/$Y36)</f>
         <v/>
       </c>
@@ -4028,25 +4054,25 @@
           <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="54" t="n">
         <v>52.4</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="55">
         <f>$B37+$Y37*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="56">
         <f>$C37/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="55">
         <f>CEILING($D37*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="57" t="n">
         <v>65</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="57">
         <f>IF($F37="","",$F37-$C37-$M37-$N37)</f>
         <v/>
       </c>
@@ -4057,29 +4083,29 @@
       <c r="I37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="55">
         <f>$C37/$I37</f>
         <v/>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="55">
         <f>IF($F37="","",$F37/$I37)</f>
         <v/>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="55">
         <f>IF($G37="","",$G37/$I37)</f>
         <v/>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="56">
         <f>IF($F37="","",$F37*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="N37" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="11" t="n">
+      <c r="O37" s="58" t="n">
         <v>41</v>
       </c>
-      <c r="P37" s="11" t="n">
+      <c r="P37" s="58" t="n">
         <v>10.66</v>
       </c>
       <c r="Q37" s="12" t="inlineStr">
@@ -4117,7 +4143,7 @@
       <c r="Y37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z37" s="8">
+      <c r="Z37" s="57">
         <f>IF($G37="","",$G37/$Y37)</f>
         <v/>
       </c>
@@ -4132,25 +4158,25 @@
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="59" t="n">
         <v>57.51</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="60">
         <f>$B38+$Y38*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="61">
         <f>$C38/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="60">
         <f>CEILING($D38*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F38" s="17" t="n">
+      <c r="F38" s="62" t="n">
         <v>70</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="62">
         <f>IF($F38="","",$F38-$C38-$M38-$N38)</f>
         <v/>
       </c>
@@ -4161,29 +4187,29 @@
       <c r="I38" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="60">
         <f>$C38/$I38</f>
         <v/>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="60">
         <f>IF($F38="","",$F38/$I38)</f>
         <v/>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="60">
         <f>IF($G38="","",$G38/$I38)</f>
         <v/>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="61">
         <f>IF($F38="","",$F38*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N38" s="15" t="n">
+      <c r="N38" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="20" t="n">
+      <c r="O38" s="63" t="n">
         <v>45</v>
       </c>
-      <c r="P38" s="20" t="n">
+      <c r="P38" s="63" t="n">
         <v>11.7</v>
       </c>
       <c r="Q38" s="21" t="inlineStr">
@@ -4225,7 +4251,7 @@
       <c r="Y38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z38" s="17">
+      <c r="Z38" s="62">
         <f>IF($G38="","",$G38/$Y38)</f>
         <v/>
       </c>
@@ -4240,25 +4266,25 @@
           <t>Pompe immergée ROBBY VP550W noir et bleu — produit d'occasion</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="54" t="n">
         <v>35.9</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="55">
         <f>$B39</f>
         <v/>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="56">
         <f>$C39/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="55">
         <f>CEILING($D39*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="57">
         <f>IF($F39="","",$F39-$C39-$M39-$N39)</f>
         <v/>
       </c>
@@ -4269,23 +4295,23 @@
       <c r="I39" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="55">
         <f>$C39/$I39</f>
         <v/>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="55">
         <f>IF($F39="","",$F39/$I39)</f>
         <v/>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="55">
         <f>IF($G39="","",$G39/$I39)</f>
         <v/>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="56">
         <f>IF($F39="","",$F39*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="N39" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="31" t="n"/>
@@ -4325,7 +4351,7 @@
       <c r="Y39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z39" s="8">
+      <c r="Z39" s="57">
         <f>IF($G39="","",$G39/$Y39)</f>
         <v/>
       </c>
@@ -4340,25 +4366,25 @@
           <t>Pompe immergée ROBBY VP550W noir/gris — comme neuf, SOCLE CASSÉ</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="54" t="n">
         <v>28.29</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="55">
         <f>$B40</f>
         <v/>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="56">
         <f>$C40/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="55">
         <f>CEILING($D40*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="57" t="n">
         <v>35</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="57">
         <f>IF($F40="","",$F40-$C40-$M40-$N40)</f>
         <v/>
       </c>
@@ -4369,23 +4395,23 @@
       <c r="I40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="55">
         <f>$C40/$I40</f>
         <v/>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="55">
         <f>IF($F40="","",$F40/$I40)</f>
         <v/>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="55">
         <f>IF($G40="","",$G40/$I40)</f>
         <v/>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="56">
         <f>IF($F40="","",$F40*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="N40" s="55" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="31" t="n"/>
@@ -4425,7 +4451,7 @@
       <c r="Y40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z40" s="8">
+      <c r="Z40" s="57">
         <f>IF($G40="","",$G40/$Y40)</f>
         <v/>
       </c>
@@ -4435,101 +4461,103 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
-        <v>12.74</v>
-      </c>
-      <c r="C41" s="6">
+      <c r="B41" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="60">
         <f>$B41</f>
         <v/>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="61">
         <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="60">
         <f>CEILING($D41*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="G41" s="8">
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="62">
         <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
         <v/>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="18">
         <f>IF($G41="","",$G41/$C41)</f>
         <v/>
       </c>
-      <c r="I41" s="10" t="n">
+      <c r="I41" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="60">
         <f>$C41/$I41</f>
         <v/>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="60">
         <f>IF($F41="","",$F41/$I41)</f>
         <v/>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="60">
         <f>IF($G41="","",$G41/$I41)</f>
         <v/>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="61">
         <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="N41" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="31" t="n"/>
-      <c r="P41" s="31" t="n"/>
-      <c r="Q41" s="12" t="inlineStr">
+      <c r="O41" s="63" t="n"/>
+      <c r="P41" s="63" t="n"/>
+      <c r="Q41" s="21" t="inlineStr">
         <is>
           <t>Meccha Japan</t>
         </is>
       </c>
-      <c r="R41" s="12" t="inlineStr">
+      <c r="R41" s="21" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="S41" s="12" t="inlineStr">
+      <c r="S41" s="21" t="inlineStr">
         <is>
           <t>#FA429713</t>
         </is>
       </c>
-      <c r="T41" s="12" t="inlineStr">
+      <c r="T41" s="21" t="inlineStr">
         <is>
           <t>4521329462226</t>
         </is>
       </c>
-      <c r="U41" s="4" t="inlineStr">
-        <is>
-          <t>Leboncoin, lot de 2</t>
-        </is>
-      </c>
-      <c r="V41" s="4" t="inlineStr"/>
-      <c r="W41" s="4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="X41" s="4" t="inlineStr"/>
-      <c r="Y41" s="4" t="n">
+      <c r="U41" s="13" t="inlineStr">
+        <is>
+          <t>Retiré — achat personnel (Pokémon), jamais dans l'activité</t>
+        </is>
+      </c>
+      <c r="V41" s="13" t="inlineStr"/>
+      <c r="W41" s="13" t="inlineStr">
+        <is>
+          <t>RETIRÉ — PERSONNEL</t>
+        </is>
+      </c>
+      <c r="X41" s="13" t="inlineStr">
+        <is>
+          <t>Retiré 17/08</t>
+        </is>
+      </c>
+      <c r="Y41" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z41" s="8">
+      <c r="Z41" s="62">
         <f>IF($G41="","",$G41/$Y41)</f>
         <v/>
       </c>
-      <c r="AA41" s="4">
+      <c r="AA41" s="13">
         <f>IF($Z41="","",IF($Z41&gt;=25,"atteint",TEXT(25-$Z41,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -4540,23 +4568,23 @@
           <t>1 booster Pokémon High Class Pack MEGA Dream ex M2a — 10 cartes dans le booster</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="C42" s="15">
+      <c r="B42" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="60">
         <f>$B42</f>
         <v/>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="61">
         <f>$C42/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="60">
         <f>CEILING($D42*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F42" s="32" t="n"/>
-      <c r="G42" s="17">
+      <c r="G42" s="62">
         <f>IF($F42="","",$F42-$C42-$M42-$N42)</f>
         <v/>
       </c>
@@ -4567,27 +4595,27 @@
       <c r="I42" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="60">
         <f>$C42/$I42</f>
         <v/>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="60">
         <f>IF($F42="","",$F42/$I42)</f>
         <v/>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="60">
         <f>IF($G42="","",$G42/$I42)</f>
         <v/>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="61">
         <f>IF($F42="","",$F42*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N42" s="15" t="n">
+      <c r="N42" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="32" t="n"/>
-      <c r="P42" s="32" t="n"/>
+      <c r="O42" s="63" t="n"/>
+      <c r="P42" s="63" t="n"/>
       <c r="Q42" s="21" t="inlineStr">
         <is>
           <t>Meccha Japan</t>
@@ -4610,24 +4638,24 @@
       </c>
       <c r="U42" s="13" t="inlineStr">
         <is>
-          <t>Prélevé — usage personnel</t>
+          <t>Retiré — achat personnel (Pokémon), jamais dans l'activité</t>
         </is>
       </c>
       <c r="V42" s="13" t="inlineStr"/>
       <c r="W42" s="13" t="inlineStr">
         <is>
-          <t>PRÉLEVÉ</t>
+          <t>RETIRÉ — PERSONNEL</t>
         </is>
       </c>
       <c r="X42" s="13" t="inlineStr">
         <is>
-          <t>PRÉLEVÉ 13/08</t>
+          <t>Retiré 17/08</t>
         </is>
       </c>
       <c r="Y42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z42" s="17">
+      <c r="Z42" s="62">
         <f>IF($G42="","",$G42/$Y42)</f>
         <v/>
       </c>
@@ -4642,23 +4670,23 @@
           <t>Pompe immergée ROBBY VP550W bleu et noir — occasion, NE MARCHE QU'EN MODE AUTO</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="59" t="n">
         <v>19.41</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="60">
         <f>$B43</f>
         <v/>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="61">
         <f>$C43/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="60">
         <f>CEILING($D43*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F43" s="32" t="n"/>
-      <c r="G43" s="17">
+      <c r="G43" s="62">
         <f>IF($F43="","",$F43-$C43-$M43-$N43)</f>
         <v/>
       </c>
@@ -4669,23 +4697,23 @@
       <c r="I43" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="60">
         <f>$C43/$I43</f>
         <v/>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="60">
         <f>IF($F43="","",$F43/$I43)</f>
         <v/>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="60">
         <f>IF($G43="","",$G43/$I43)</f>
         <v/>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="61">
         <f>IF($F43="","",$F43*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N43" s="15" t="n">
+      <c r="N43" s="60" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="32" t="n"/>
@@ -4729,7 +4757,7 @@
       <c r="Y43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z43" s="17">
+      <c r="Z43" s="62">
         <f>IF($G43="","",$G43/$Y43)</f>
         <v/>
       </c>
@@ -4744,23 +4772,23 @@
           <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="59" t="n">
         <v>50.4</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="60">
         <f>$B44+$Y44*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="61">
         <f>$C44/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="60">
         <f>CEILING($D44*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F44" s="32" t="n"/>
-      <c r="G44" s="17">
+      <c r="G44" s="62">
         <f>IF($F44="","",$F44-$C44-$M44-$N44)</f>
         <v/>
       </c>
@@ -4771,29 +4799,29 @@
       <c r="I44" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="60">
         <f>$C44/$I44</f>
         <v/>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="60">
         <f>IF($F44="","",$F44/$I44)</f>
         <v/>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="60">
         <f>IF($G44="","",$G44/$I44)</f>
         <v/>
       </c>
-      <c r="M44" s="16">
+      <c r="M44" s="61">
         <f>IF($F44="","",$F44*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N44" s="15" t="n">
+      <c r="N44" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="20" t="n">
+      <c r="O44" s="63" t="n">
         <v>40</v>
       </c>
-      <c r="P44" s="20" t="n">
+      <c r="P44" s="63" t="n">
         <v>10.4</v>
       </c>
       <c r="Q44" s="21" t="inlineStr">
@@ -4835,7 +4863,7 @@
       <c r="Y44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z44" s="17">
+      <c r="Z44" s="62">
         <f>IF($G44="","",$G44/$Y44)</f>
         <v/>
       </c>
@@ -4850,23 +4878,23 @@
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="59" t="n">
         <v>63</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="60">
         <f>$B45+$Y45*Paramètres!$B$13</f>
         <v/>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="61">
         <f>$C45/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
         <v/>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="60">
         <f>CEILING($D45*Paramètres!$B$24,1)</f>
         <v/>
       </c>
       <c r="F45" s="32" t="n"/>
-      <c r="G45" s="17">
+      <c r="G45" s="62">
         <f>IF($F45="","",$F45-$C45-$M45-$N45)</f>
         <v/>
       </c>
@@ -4877,29 +4905,29 @@
       <c r="I45" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="60">
         <f>$C45/$I45</f>
         <v/>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="60">
         <f>IF($F45="","",$F45/$I45)</f>
         <v/>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="60">
         <f>IF($G45="","",$G45/$I45)</f>
         <v/>
       </c>
-      <c r="M45" s="16">
+      <c r="M45" s="61">
         <f>IF($F45="","",$F45*(Paramètres!$B$5+Paramètres!$B$6))</f>
         <v/>
       </c>
-      <c r="N45" s="15" t="n">
+      <c r="N45" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="20" t="n">
+      <c r="O45" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="P45" s="20" t="n">
+      <c r="P45" s="63" t="n">
         <v>13</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
@@ -4941,7 +4969,7 @@
       <c r="Y45" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="Z45" s="17">
+      <c r="Z45" s="62">
         <f>IF($G45="","",$G45/$Y45)</f>
         <v/>
       </c>
@@ -4951,64 +4979,272 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL — 40 lots</t>
-        </is>
-      </c>
-      <c r="B46" s="34">
-        <f>SUM(B6:B45)</f>
-        <v/>
-      </c>
-      <c r="C46" s="34">
-        <f>SUM(C6:C45)</f>
-        <v/>
-      </c>
-      <c r="D46" s="35" t="n"/>
-      <c r="E46" s="35" t="n"/>
-      <c r="F46" s="34">
-        <f>SUM(F6:F45)</f>
-        <v/>
-      </c>
-      <c r="G46" s="34">
-        <f>SUM(G6:G45)</f>
-        <v/>
-      </c>
-      <c r="H46" s="36">
-        <f>G46/C46</f>
-        <v/>
-      </c>
-      <c r="I46" s="37">
-        <f>SUM(I6:I45)</f>
-        <v/>
-      </c>
-      <c r="J46" s="35" t="n"/>
-      <c r="K46" s="35" t="n"/>
-      <c r="L46" s="35" t="n"/>
-      <c r="M46" s="34">
-        <f>SUM(M6:M45)</f>
-        <v/>
-      </c>
-      <c r="N46" s="34">
-        <f>SUM(N6:N45)</f>
-        <v/>
-      </c>
-      <c r="O46" s="35" t="n"/>
-      <c r="P46" s="35" t="n"/>
-      <c r="Q46" s="35" t="n"/>
-      <c r="R46" s="35" t="n"/>
-      <c r="S46" s="35" t="n"/>
-      <c r="T46" s="35" t="n"/>
-      <c r="U46" s="35" t="n"/>
-      <c r="V46" s="35" t="n"/>
-      <c r="W46" s="35" t="n"/>
-      <c r="X46" s="35" t="n"/>
-      <c r="Y46" s="35" t="n"/>
-      <c r="Z46" s="34">
-        <f>G46/SUM(Y6:Y45)</f>
-        <v/>
-      </c>
-      <c r="AA46" s="35" t="n"/>
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Unité centrale gaming Acer Predator G3-605 — i7-4790, 16 Go RAM DDR3, GTX 980, 1 To HDD, Windows 10, état correct</t>
+        </is>
+      </c>
+      <c r="B46" s="54" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="C46" s="55">
+        <f>$B46</f>
+        <v/>
+      </c>
+      <c r="D46" s="56">
+        <f>$C46/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E46" s="55">
+        <f>CEILING($D46*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F46" s="57" t="n"/>
+      <c r="G46" s="57">
+        <f>IF($F46="","",$F46-$C46-$M46-$N46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="9">
+        <f>IF($G46="","",$G46/$C46)</f>
+        <v/>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="55">
+        <f>$C46/$I46</f>
+        <v/>
+      </c>
+      <c r="K46" s="55">
+        <f>IF($F46="","",$F46/$I46)</f>
+        <v/>
+      </c>
+      <c r="L46" s="55">
+        <f>IF($G46="","",$G46/$I46)</f>
+        <v/>
+      </c>
+      <c r="M46" s="56">
+        <f>IF($F46="","",$F46*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N46" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="58" t="n">
+        <v>70</v>
+      </c>
+      <c r="P46" s="58" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Q46" s="12" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R46" s="12" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="S46" s="12" t="inlineStr">
+        <is>
+          <t>FB2026-49549</t>
+        </is>
+      </c>
+      <c r="T46" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="inlineStr">
+        <is>
+          <t>Leboncoin informatique / eBay — pas la boutique</t>
+        </is>
+      </c>
+      <c r="V46" s="4" t="n"/>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>À TARIFER — livraison pas encore facturée</t>
+        </is>
+      </c>
+      <c r="X46" s="4" t="n"/>
+      <c r="Y46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="57">
+        <f>IF($G46="","",$G46/$Y46)</f>
+        <v/>
+      </c>
+      <c r="AA46" s="4">
+        <f>IF($Z46="","",IF($Z46&gt;=25,"atteint",TEXT(25-$Z46,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>Vidéoprojecteur PHILIPS NeoPix 110 noir — très bon état, testé, complet avec boîte</t>
+        </is>
+      </c>
+      <c r="B47" s="59" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C47" s="60">
+        <f>$B47</f>
+        <v/>
+      </c>
+      <c r="D47" s="61">
+        <f>$C47/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E47" s="60">
+        <f>CEILING($D47*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="62">
+        <f>IF($F47="","",$F47-$C47-$M47-$N47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="18">
+        <f>IF($G47="","",$G47/$C47)</f>
+        <v/>
+      </c>
+      <c r="I47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="60">
+        <f>$C47/$I47</f>
+        <v/>
+      </c>
+      <c r="K47" s="60">
+        <f>IF($F47="","",$F47/$I47)</f>
+        <v/>
+      </c>
+      <c r="L47" s="60">
+        <f>IF($G47="","",$G47/$I47)</f>
+        <v/>
+      </c>
+      <c r="M47" s="61">
+        <f>IF($F47="","",$F47*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N47" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="63" t="n">
+        <v>40</v>
+      </c>
+      <c r="P47" s="63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q47" s="21" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="R47" s="21" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="S47" s="21" t="inlineStr">
+        <is>
+          <t>FB2026-49549</t>
+        </is>
+      </c>
+      <c r="T47" s="21" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="U47" s="13" t="inlineStr">
+        <is>
+          <t>Prélevé — usage personnel</t>
+        </is>
+      </c>
+      <c r="V47" s="13" t="n"/>
+      <c r="W47" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉ</t>
+        </is>
+      </c>
+      <c r="X47" s="13" t="inlineStr">
+        <is>
+          <t>PRÉLEVÉ 23/08</t>
+        </is>
+      </c>
+      <c r="Y47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="62">
+        <f>IF($G47="","",$G47/$Y47)</f>
+        <v/>
+      </c>
+      <c r="AA47" s="13">
+        <f>IF($Z47="","",IF($Z47&gt;=25,"atteint",TEXT(25-$Z47,"0.00")&amp;" € manquants"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL — 42 lots</t>
+        </is>
+      </c>
+      <c r="B48" s="69">
+        <f>SUM(B6:B47)</f>
+        <v/>
+      </c>
+      <c r="C48" s="69">
+        <f>SUM(C6:C47)</f>
+        <v/>
+      </c>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="69">
+        <f>SUM(F6:F47)</f>
+        <v/>
+      </c>
+      <c r="G48" s="69">
+        <f>SUM(G6:G47)</f>
+        <v/>
+      </c>
+      <c r="H48" s="36">
+        <f>G48/C48</f>
+        <v/>
+      </c>
+      <c r="I48" s="70">
+        <f>SUM(I6:I47)</f>
+        <v/>
+      </c>
+      <c r="J48" s="35" t="n"/>
+      <c r="K48" s="35" t="n"/>
+      <c r="L48" s="35" t="n"/>
+      <c r="M48" s="69">
+        <f>SUM(M6:M47)</f>
+        <v/>
+      </c>
+      <c r="N48" s="69">
+        <f>SUM(N6:N47)</f>
+        <v/>
+      </c>
+      <c r="O48" s="35" t="n"/>
+      <c r="P48" s="35" t="n"/>
+      <c r="Q48" s="35" t="n"/>
+      <c r="R48" s="35" t="n"/>
+      <c r="S48" s="35" t="n"/>
+      <c r="T48" s="35" t="n"/>
+      <c r="U48" s="35" t="n"/>
+      <c r="V48" s="35" t="n"/>
+      <c r="W48" s="35" t="n"/>
+      <c r="X48" s="35" t="n"/>
+      <c r="Y48" s="35" t="n"/>
+      <c r="Z48" s="69">
+        <f>G48/SUM(Y6:Y47)</f>
+        <v/>
+      </c>
+      <c r="AA48" s="35" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:AA45"/>
@@ -5035,7 +5271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5063,8 +5299,8 @@
           <t>Marchandise ADN</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>1637.35</v>
+      <c r="B4" s="55" t="n">
+        <v>1775.95</v>
       </c>
     </row>
     <row r="5">
@@ -5073,7 +5309,7 @@
           <t>Livraison ADN</t>
         </is>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="55">
         <f>Paramètres!B11</f>
         <v/>
       </c>
@@ -5081,11 +5317,11 @@
     <row r="6">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>Achats hors ADN (pompes, Pokémon)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>178.53</v>
+          <t>Achats hors ADN (pompes)</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="n">
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -5094,8 +5330,8 @@
           <t>TOTAL ENGAGÉ</t>
         </is>
       </c>
-      <c r="B7" s="34">
-        <f>'Stock complet'!C46</f>
+      <c r="B7" s="69">
+        <f>'Stock complet'!C48</f>
         <v/>
       </c>
     </row>
@@ -5112,8 +5348,8 @@
           <t>Chiffre d'affaires attendu</t>
         </is>
       </c>
-      <c r="B10" s="8">
-        <f>'Stock complet'!F46</f>
+      <c r="B10" s="57">
+        <f>'Stock complet'!F48</f>
         <v/>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5128,8 +5364,8 @@
           <t>− URSSAF + CFP</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>-'Stock complet'!M46</f>
+      <c r="B11" s="56">
+        <f>-'Stock complet'!M48</f>
         <v/>
       </c>
     </row>
@@ -5139,8 +5375,8 @@
           <t>− Commission carte</t>
         </is>
       </c>
-      <c r="B12" s="6">
-        <f>-'Stock complet'!N46</f>
+      <c r="B12" s="55">
+        <f>-'Stock complet'!N48</f>
         <v/>
       </c>
     </row>
@@ -5149,8 +5385,8 @@
         <f> Marge brute</f>
         <v/>
       </c>
-      <c r="B13" s="34">
-        <f>'Stock complet'!G46</f>
+      <c r="B13" s="69">
+        <f>'Stock complet'!G48</f>
         <v/>
       </c>
     </row>
@@ -5160,7 +5396,7 @@
           <t>− Emballage</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="55">
         <f>-Paramètres!B20*Paramètres!B21</f>
         <v/>
       </c>
@@ -5171,7 +5407,7 @@
           <t>− Frais fixe carte</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="55">
         <f>-Paramètres!B8*Paramètres!B21</f>
         <v/>
       </c>
@@ -5181,7 +5417,7 @@
         <f> Marge avant impôt</f>
         <v/>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="69">
         <f>B13+B14+B15</f>
         <v/>
       </c>
@@ -5192,7 +5428,7 @@
           <t>Base imposable</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="55">
         <f>B10*(1-Paramètres!B16)</f>
         <v/>
       </c>
@@ -5203,7 +5439,7 @@
           <t>− Impôt estimé</t>
         </is>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="55">
         <f>-B17*Paramètres!B17</f>
         <v/>
       </c>
@@ -5213,7 +5449,7 @@
         <f> CE QUI RESTE</f>
         <v/>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="71">
         <f>B16+B18</f>
         <v/>
       </c>
@@ -5231,7 +5467,7 @@
           <t>Marge nette / capital engagé</t>
         </is>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="72">
         <f>B19/B7</f>
         <v/>
       </c>
@@ -5243,7 +5479,7 @@
         </is>
       </c>
       <c r="B23" s="43">
-        <f>'Stock complet'!I46</f>
+        <f>'Stock complet'!I48</f>
         <v/>
       </c>
     </row>
@@ -5253,7 +5489,7 @@
           <t>Taux de marge nette sur le CA</t>
         </is>
       </c>
-      <c r="B24" s="42">
+      <c r="B24" s="72">
         <f>B19/B10</f>
         <v/>
       </c>
@@ -5273,32 +5509,32 @@
     <row r="27">
       <c r="A27" s="39" t="inlineStr">
         <is>
-          <t>Shopify + Claude, aujourd'hui</t>
-        </is>
-      </c>
-      <c r="B27" s="6">
+          <t>Charges fixes, aujourd'hui</t>
+        </is>
+      </c>
+      <c r="B27" s="55">
         <f>Paramètres!B30</f>
         <v/>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1 € + 22 €</t>
+          <t>1 € + 22 € + médiateur 1,33 €</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="39" t="inlineStr">
         <is>
-          <t>Shopify + Claude, à partir du 11/11/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="6">
+          <t>Charges fixes, à partir du 11/11/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="55">
         <f>Paramètres!B31</f>
         <v/>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>36 € + 22 €</t>
+          <t>36 € + 22 € + médiateur 1,33 €</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5544,7 @@
           <t>Soit par an, à partir de novembre</t>
         </is>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="69">
         <f>Paramètres!B31*12</f>
         <v/>
       </c>
@@ -5319,7 +5555,7 @@
           <t>CA mensuel nécessaire pour les couvrir</t>
         </is>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="71">
         <f>Paramètres!B31/B24</f>
         <v/>
       </c>
@@ -5335,7 +5571,7 @@
           <t>Marge du stock entier</t>
         </is>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="55">
         <f>B19</f>
         <v/>
       </c>
@@ -5351,7 +5587,7 @@
           <t>Mois de charges couverts par tout le stock</t>
         </is>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="73">
         <f>B19/Paramètres!B31</f>
         <v/>
       </c>
@@ -5373,14 +5609,14 @@
     <row r="36">
       <c r="A36" s="45" t="inlineStr">
         <is>
-          <t>CA encaissé : 373 €, pas 493 €. Les Hoka et les Nike sont des prélèvements, pas des ventes.</t>
+          <t>CA encaissé : 473 €, Salomon comprise depuis le 23/08. Les Hoka et les Nike restent des prélèvements, pas des ventes.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="39" t="inlineStr">
         <is>
-          <t>Toutes les factures sont reçues. 150,50 € de stock prélevé pour usage personnel.</t>
+          <t>Frais de livraison de la facture FB2026-49549 encore en attente. 187,95 € de stock prélevé pour usage personnel (Hoka, Nike, pompe Robby, vidéoprojecteur).</t>
         </is>
       </c>
     </row>
@@ -5430,6 +5666,48 @@
       <c r="A44" s="45" t="inlineStr">
         <is>
           <t>Sous 40 € de prix marché, 25 € de marge sont hors d'atteinte quelle que soit l'enchère. Ne pas miser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="45" t="inlineStr">
+        <is>
+          <t>23/08 : achat FB2026-49549 — unité centrale Acer G3-605 (88,20 €, pas encore tarifée) + vidéoprojecteur Philips NeoPix 110 (50,40 €, prélevé, usage personnel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="45" t="inlineStr">
+        <is>
+          <t>Frais de livraison de la facture FB2026-49549 pas encore connus — à ajouter dans Factures et Paramètres &gt; Livraison ADN dès réception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="45" t="inlineStr">
+        <is>
+          <t>Cartes et boosters Pokémon retirés du stock professionnel le 17/08 — achetés à titre personnel dès l'origine, jamais dans l'activité (lignes 27, 41, 42 de Stock complet, coût à 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="45" t="inlineStr">
+        <is>
+          <t>Médiateur de la consommation : 48 € pour 3 ans intégrés aux charges fixes (Paramètres &gt; B50). CGV section 9 toujours à compléter tant que l'inscription n'est pas confirmée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="45" t="inlineStr">
+        <is>
+          <t>Salomon encaissée le 23/08 — 100 €, plus rien en attente sur les ventes déjà faites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="45" t="inlineStr">
+        <is>
+          <t>Sourcing en pause depuis le 23/08 : engagement total ~2 000 € atteint, plus d'achat avant que le stock déjà là se vende davantage.</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5479,7 +5757,7 @@
           <t>Cotisations URSSAF (achat-revente BIC)</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="74" t="n">
         <v>0.123</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5494,7 +5772,7 @@
           <t>CFP — formation professionnelle</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="74" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -5504,7 +5782,7 @@
           <t>Commission carte Shopify Payments</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="74" t="n">
         <v>0.015</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5519,7 +5797,7 @@
           <t>Frais fixe par transaction carte</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="75" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5536,7 +5814,7 @@
           <t>Total des factures de livraison ADN</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="54" t="n">
         <v>127.8</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5566,7 +5844,7 @@
           <t>Livraison par unité de vente</t>
         </is>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="55">
         <f>B11/B12</f>
         <v/>
       </c>
@@ -5589,7 +5867,7 @@
           <t>Abattement forfaitaire</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="74" t="n">
         <v>0.71</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5604,7 +5882,7 @@
           <t>Tranche marginale du foyer</t>
         </is>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="74" t="n">
         <v>0.11</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5626,7 +5904,7 @@
           <t>Emballage par colis</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n">
+      <c r="B20" s="75" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5675,7 +5953,7 @@
           <t>Abonnement Shopify — aujourd'hui</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n">
+      <c r="B27" s="75" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -5690,7 +5968,7 @@
           <t>Abonnement Shopify — à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n">
+      <c r="B28" s="75" t="n">
         <v>36</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5705,7 +5983,7 @@
           <t>Abonnement Claude</t>
         </is>
       </c>
-      <c r="B29" s="47" t="n">
+      <c r="B29" s="75" t="n">
         <v>22</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -5720,8 +5998,8 @@
           <t>Total mensuel aujourd'hui</t>
         </is>
       </c>
-      <c r="B30" s="50">
-        <f>B27+B29</f>
+      <c r="B30" s="76">
+        <f>B27+B29+B51</f>
         <v/>
       </c>
     </row>
@@ -5731,13 +6009,13 @@
           <t>Total mensuel à partir du 11/11/2026</t>
         </is>
       </c>
-      <c r="B31" s="50">
-        <f>B28+B29</f>
+      <c r="B31" s="76">
+        <f>B28+B29+B51</f>
         <v/>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>696 €/an</t>
+          <t>712 €/an</t>
         </is>
       </c>
     </row>
@@ -5754,7 +6032,7 @@
           <t>CFE — cotisation foncière des entreprises</t>
         </is>
       </c>
-      <c r="B34" s="47" t="n">
+      <c r="B34" s="75" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5791,7 +6069,7 @@
           <t>Shopify Payments — frais fixe</t>
         </is>
       </c>
-      <c r="B38" s="47" t="n">
+      <c r="B38" s="75" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5816,7 +6094,7 @@
           <t>PayPal — frais fixe</t>
         </is>
       </c>
-      <c r="B40" s="47" t="n">
+      <c r="B40" s="75" t="n">
         <v>0.35</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5861,7 +6139,7 @@
           <t>Coefficient de marge — Shopify Payments</t>
         </is>
       </c>
-      <c r="B44" s="52">
+      <c r="B44" s="77">
         <f>1-B5-B6-B37</f>
         <v/>
       </c>
@@ -5877,7 +6155,7 @@
           <t>Coefficient de marge — PayPal</t>
         </is>
       </c>
-      <c r="B45" s="52">
+      <c r="B45" s="77">
         <f>1-B5-B6-B39</f>
         <v/>
       </c>
@@ -5893,7 +6171,7 @@
           <t>Coefficient de marge — hors carte</t>
         </is>
       </c>
-      <c r="B46" s="52">
+      <c r="B46" s="77">
         <f>1-B5-B6</f>
         <v/>
       </c>
@@ -5909,13 +6187,51 @@
           <t>Écart PayPal / Shopify Payments sur une vente à 89 €</t>
         </is>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="55">
         <f>89*(B39-B37)+(B40-B38)</f>
         <v/>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>multiplié par le nombre de ventes encaissées ainsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="38" t="inlineStr">
+        <is>
+          <t>MÉDIATEUR DE LA CONSOMMATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>Coût du médiateur, pour 3 ans</t>
+        </is>
+      </c>
+      <c r="B50" s="75" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Payé le 23/08/2026 — CGV section 9 : inscription à confirmer avant d'être opposable</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>Coût médiateur, mensualisé</t>
+        </is>
+      </c>
+      <c r="B51" s="76">
+        <f>B50/36</f>
+        <v/>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>moyenne lissée sur 3 ans (36 mois), pour comparer avec les abonnements mensuels</t>
         </is>
       </c>
     </row>
@@ -5930,7 +6246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6042,16 +6358,16 @@
           <t>Lot de 12 paires de tongs HAVAIANAS fuchsia 35/36 — neuf</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="55" t="n">
         <v>80</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="55" t="n">
         <v>20.8</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="55" t="n">
         <v>100.8</v>
       </c>
     </row>
@@ -6086,16 +6402,16 @@
           <t>Veste en jean ARMANI EXCHANGE T.S — neuve</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="55" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -6130,16 +6446,16 @@
           <t>Lot de 4 gilets de flottaison MRS.ERTHA 3-6 ans — neuf</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6174,16 +6490,16 @@
           <t>Robe SANDRO T.40 — neuve</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6218,16 +6534,16 @@
           <t>Baskets HOKA P.37 1/3 — neuves</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -6262,16 +6578,16 @@
           <t>Baskets NIKE Air Max Moto 2K P.44.5 — neuves</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6306,16 +6622,16 @@
           <t>Chaussures HOGAN P.36 — traces d'essayage</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="55" t="n">
         <v>2.6</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="55" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -6350,16 +6666,16 @@
           <t>NEW BALANCE G19064IK Alkaline Green P.38½ — neuves avec boîte</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="55" t="n">
         <v>15.6</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="55" t="n">
         <v>75.59999999999999</v>
       </c>
     </row>
@@ -6394,16 +6710,16 @@
           <t>Lot de 2 paires ADIDAS Predator Edge P.48 2/3 — neuves</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6438,16 +6754,16 @@
           <t>Short BA&amp;SH Fegor T.34 — neuf</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6482,16 +6798,16 @@
           <t>Jupe midi SONIA RYKIEL T.34 — neuve</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6526,16 +6842,16 @@
           <t>Sac demi-lune nylon noir KARL LAGERFELD JEANS — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -6570,16 +6886,16 @@
           <t>ADIDAS x STELLA McCARTNEY ASMC Ultraboost 21 P.36 — modèle d'exposition</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -6614,16 +6930,16 @@
           <t>Ballerines MASSIMO DUTTI P.41 — traces d'essayage</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="55" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -6658,16 +6974,16 @@
           <t>NEW BALANCE sneakers P.38 — neuves</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="55" t="n">
         <v>38.34</v>
       </c>
     </row>
@@ -6702,16 +7018,16 @@
           <t>LACOSTE sneakers P.42 — neuves</t>
         </is>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="55" t="n">
         <v>57.51</v>
       </c>
     </row>
@@ -6746,16 +7062,16 @@
           <t>EMPORIO ARMANI baskets P.36 — neuves</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="55" t="n">
         <v>0.72</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="55" t="n">
         <v>51.12</v>
       </c>
     </row>
@@ -6790,16 +7106,16 @@
           <t>GEOX baskets P.35 — neuves</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="55" t="n">
         <v>4.42</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="55" t="n">
         <v>0.31</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="55" t="n">
         <v>21.73</v>
       </c>
     </row>
@@ -6834,16 +7150,16 @@
           <t>NEW BALANCE baskets montantes P.44 — neuves</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="55" t="n">
         <v>0.72</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="55" t="n">
         <v>51.12</v>
       </c>
     </row>
@@ -6878,16 +7194,16 @@
           <t>TOMMY JEANS baskets basses P.40 — neuves</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="55" t="n">
         <v>41</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="55" t="n">
         <v>10.66</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="55" t="n">
         <v>0.74</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="55" t="n">
         <v>52.4</v>
       </c>
     </row>
@@ -6922,16 +7238,16 @@
           <t>PHILIPP PLEIN SPORT baskets montantes P.40 — neuves</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="55" t="n">
         <v>57.51</v>
       </c>
     </row>
@@ -6966,16 +7282,16 @@
           <t>PIER ANTONIO GASPARI robe droite bleu marine T.42 — neuve</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="55" t="n">
         <v>5.2</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="55" t="n">
         <v>0.36</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="55" t="n">
         <v>25.56</v>
       </c>
     </row>
@@ -7010,16 +7326,16 @@
           <t>ELISABETTA FRANCHI robe asymétrique viscose T.46 IT — neuve</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="55" t="n">
         <v>4.16</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="55" t="n">
         <v>0.29</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="55" t="n">
         <v>20.45</v>
       </c>
     </row>
@@ -7054,16 +7370,16 @@
           <t>CHIARA FERRAGNI robe bustier courte T.M — neuve</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="55" t="n">
         <v>25</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="55" t="n">
         <v>6.5</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="55" t="n">
         <v>0.45</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="55" t="n">
         <v>31.95</v>
       </c>
     </row>
@@ -7098,16 +7414,16 @@
           <t>SALOMON X Ultra 5 Mid GTX P.44 — neuves</t>
         </is>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="55" t="n">
         <v>15.6</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="55" t="n">
         <v>1.08</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="55" t="n">
         <v>76.68000000000001</v>
       </c>
     </row>
@@ -7142,16 +7458,16 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="55" t="n">
         <v>3.9</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="55" t="n">
         <v>0.27</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="55" t="n">
         <v>19.17</v>
       </c>
     </row>
@@ -7186,16 +7502,16 @@
           <t>Lot de 4 toupies BEYBLADE HASBRO</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="55" t="n">
         <v>38.34</v>
       </c>
     </row>
@@ -7230,16 +7546,16 @@
           <t>T-shirt BALENCIAGA T.2 — neuf</t>
         </is>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="55" t="n">
         <v>90</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="55" t="n">
         <v>23.4</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="55" t="n">
         <v>113.4</v>
       </c>
     </row>
@@ -7274,16 +7590,16 @@
           <t>Blazer noir KARL LAGERFELD T.36 FR — neuf avec étiquette</t>
         </is>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="55" t="n">
         <v>10.4</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="55" t="n">
         <v>50.4</v>
       </c>
     </row>
@@ -7318,16 +7634,16 @@
           <t>ADIDAS Yeezy 700 V3 Mono Safflower T.38 — occasion</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7362,16 +7678,16 @@
           <t>Lot de 6 vêtements femme MORGAN T.40 et L — neuf</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="55" t="n">
         <v>7.8</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="55" t="n">
         <v>37.8</v>
       </c>
     </row>
@@ -7406,16 +7722,16 @@
           <t>Demi-bottes FORMA Legacy Waterproof T.45 noir — neuves</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="55" t="n">
         <v>63</v>
       </c>
     </row>
@@ -7450,16 +7766,16 @@
           <t>Combinaison de pluie BMW Overall ProRain unisexe XL — neuve</t>
         </is>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="55" t="n">
         <v>60</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="55" t="n">
         <v>8.57</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="55" t="n">
         <v>68.56999999999999</v>
       </c>
     </row>
@@ -7494,155 +7810,183 @@
           <t>Lot de 20 paires de sandales et tongs RELIFE / TOMMY JEANS — neuf</t>
         </is>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="55" t="n">
         <v>45</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="55" t="n">
         <v>11.7</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="55" t="n">
         <v>56.7</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="n"/>
-      <c r="B39" s="35" t="n"/>
-      <c r="C39" s="35" t="n"/>
-      <c r="D39" s="35" t="n"/>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="33" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FB2026-49549</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>ADN-1738-11</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Unité centrale gaming Acer Predator G3-605 — i7-4790, 16 Go RAM, GTX 980, 1 To HDD, Windows 10</t>
+        </is>
+      </c>
+      <c r="G39" s="55" t="n">
+        <v>70</v>
+      </c>
+      <c r="H39" s="55" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I39" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="55" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>FB2026-49549</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>ADN-1738-11</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Vidéoprojecteur PHILIPS NeoPix 110 noir — très bon état, testé, complet avec boîte</t>
+        </is>
+      </c>
+      <c r="G40" s="55" t="n">
+        <v>40</v>
+      </c>
+      <c r="H40" s="55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I40" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="55" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="n"/>
+      <c r="B41" s="35" t="n"/>
+      <c r="C41" s="35" t="n"/>
+      <c r="D41" s="35" t="n"/>
+      <c r="E41" s="35" t="n"/>
+      <c r="F41" s="33" t="inlineStr">
         <is>
           <t>TOTAL MARCHANDISE</t>
         </is>
       </c>
-      <c r="G39" s="34">
-        <f>SUM(G5:G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="34">
-        <f>SUM(H5:H38)</f>
-        <v/>
-      </c>
-      <c r="I39" s="34">
-        <f>SUM(I5:I38)</f>
-        <v/>
-      </c>
-      <c r="J39" s="34">
-        <f>SUM(J5:J38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="38" t="inlineStr">
+      <c r="G41" s="69">
+        <f>SUM(G5:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="69">
+        <f>SUM(H5:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="69">
+        <f>SUM(I5:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="69">
+        <f>SUM(J5:J40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>FACTURES DE LIVRAISON</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="53" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="53" t="inlineStr">
         <is>
           <t>Facture</t>
         </is>
       </c>
-      <c r="B42" s="53" t="inlineStr">
+      <c r="B44" s="53" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C42" s="53" t="inlineStr">
+      <c r="C44" s="53" t="inlineStr">
         <is>
           <t>Maison</t>
         </is>
       </c>
-      <c r="D42" s="53" t="inlineStr">
+      <c r="D44" s="53" t="inlineStr">
         <is>
           <t>Commande</t>
         </is>
       </c>
-      <c r="E42" s="53" t="inlineStr">
+      <c r="E44" s="53" t="inlineStr">
         <is>
           <t>Désignation</t>
         </is>
       </c>
-      <c r="F42" s="53" t="inlineStr">
+      <c r="F44" s="53" t="inlineStr">
         <is>
           <t>Total TTC</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>FF2026-4060</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>28/07/2026</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>TLE-C26638</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Colissimo Point Relais — assurance et signature</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>19.9</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>FF2026-4146</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>ADN Lyon</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>TLE-C26827</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Colissimo Point Relais — assurance et signature</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>18.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>FF2026-4160</t>
+          <t>FF2026-4060</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -7652,7 +7996,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>TLE-C26851</t>
+          <t>TLE-C26638</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -7660,83 +8004,150 @@
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n">
-        <v>29.94</v>
+      <c r="F45" s="55" t="n">
+        <v>19.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>FF2026-32305</t>
+          <t>FF2026-4146</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>ADN Le Mans</t>
+          <t>ADN Lyon</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>ADN-C208494</t>
+          <t>TLE-C26827</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Colissimo Point Relais</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>15.72</v>
+          <t>Colissimo Point Relais — assurance et signature</t>
+        </is>
+      </c>
+      <c r="F46" s="55" t="n">
+        <v>18.22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>FF2026-4160</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>ADN Lyon</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>TLE-C26851</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Colissimo Point Relais — assurance et signature</t>
+        </is>
+      </c>
+      <c r="F47" s="55" t="n">
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>FF2026-32305</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>ADN Le Mans</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>ADN-C208494</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Colissimo Point Relais</t>
+        </is>
+      </c>
+      <c r="F48" s="55" t="n">
+        <v>15.72</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
           <t>FF2026-4456</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>ADN Lyon</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>TLE-C27429</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Colissimo Point Relais — assurance et signature</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F49" s="55" t="n">
         <v>44.02</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="33" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="35" t="n"/>
+      <c r="B50" s="35" t="n"/>
+      <c r="C50" s="35" t="n"/>
+      <c r="D50" s="35" t="n"/>
+      <c r="E50" s="33" t="inlineStr">
         <is>
           <t>TOTAL LIVRAISON</t>
         </is>
       </c>
-      <c r="F48" s="34">
-        <f>SUM(F43:F47)</f>
-        <v/>
+      <c r="F50" s="69">
+        <f>SUM(F45:F49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Frais de livraison de la facture FB2026-49549 (unité centrale + vidéoprojecteur) pas encore reçus — à ajouter ici et dans Paramètres &gt; Livraison ADN dès réception.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -2998,103 +2998,101 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
         </is>
       </c>
-      <c r="B27" s="59" t="n">
+      <c r="B27" s="54" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="C27" s="55">
+        <f>$B27</f>
+        <v/>
+      </c>
+      <c r="D27" s="56">
+        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E27" s="55">
+        <f>CEILING($D27*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F27" s="57" t="n">
+        <v>98</v>
+      </c>
+      <c r="G27" s="57">
+        <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>IF($G27="","",$G27/$C27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="55">
+        <f>$C27/$I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="55">
+        <f>IF($F27="","",$F27/$I27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="55">
+        <f>IF($G27="","",$G27/$I27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="56">
+        <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N27" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="60">
-        <f>$B27</f>
-        <v/>
-      </c>
-      <c r="D27" s="61">
-        <f>$C27/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E27" s="60">
-        <f>CEILING($D27*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F27" s="32" t="n"/>
-      <c r="G27" s="62">
-        <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="18">
-        <f>IF($G27="","",$G27/$C27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="19" t="n">
+      <c r="O27" s="58" t="n"/>
+      <c r="P27" s="58" t="n"/>
+      <c r="Q27" s="12" t="inlineStr">
+        <is>
+          <t>Meccha Japan</t>
+        </is>
+      </c>
+      <c r="R27" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S27" s="12" t="inlineStr">
+        <is>
+          <t>#FA429713</t>
+        </is>
+      </c>
+      <c r="T27" s="12" t="inlineStr">
+        <is>
+          <t>4521329432274</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>Compte professionnel — Leboncoin, lots de 15</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X27" s="4" t="n"/>
+      <c r="Y27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="60">
-        <f>$C27/$I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="60">
-        <f>IF($F27="","",$F27/$I27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="60">
-        <f>IF($G27="","",$G27/$I27)</f>
-        <v/>
-      </c>
-      <c r="M27" s="61">
-        <f>IF($F27="","",$F27*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N27" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="63" t="n"/>
-      <c r="P27" s="63" t="n"/>
-      <c r="Q27" s="21" t="inlineStr">
-        <is>
-          <t>Meccha Japan</t>
-        </is>
-      </c>
-      <c r="R27" s="21" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S27" s="21" t="inlineStr">
-        <is>
-          <t>#FA429713</t>
-        </is>
-      </c>
-      <c r="T27" s="21" t="inlineStr">
-        <is>
-          <t>4521329432274</t>
-        </is>
-      </c>
-      <c r="U27" s="13" t="inlineStr">
-        <is>
-          <t>Retiré — achat personnel (Pokémon), jamais dans l'activité</t>
-        </is>
-      </c>
-      <c r="V27" s="13" t="inlineStr"/>
-      <c r="W27" s="13" t="inlineStr">
-        <is>
-          <t>RETIRÉ — PERSONNEL</t>
-        </is>
-      </c>
-      <c r="X27" s="13" t="inlineStr">
-        <is>
-          <t>Retiré 17/08</t>
-        </is>
-      </c>
-      <c r="Y27" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z27" s="62">
+      <c r="Z27" s="57">
         <f>IF($G27="","",$G27/$Y27)</f>
         <v/>
       </c>
-      <c r="AA27" s="13">
+      <c r="AA27" s="4">
         <f>IF($Z27="","",IF($Z27&gt;=25,"atteint",TEXT(25-$Z27,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -4461,103 +4459,101 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>2 boosters Pokémon MEGA Storm Emeralda M6 — 5 cartes chacun — set sorti le 31/07/2026, publier vite</t>
         </is>
       </c>
-      <c r="B41" s="59" t="n">
+      <c r="B41" s="54" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="C41" s="55">
+        <f>$B41</f>
+        <v/>
+      </c>
+      <c r="D41" s="56">
+        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
+        <v/>
+      </c>
+      <c r="E41" s="55">
+        <f>CEILING($D41*Paramètres!$B$24,1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="57" t="n">
+        <v>19</v>
+      </c>
+      <c r="G41" s="57">
+        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="9">
+        <f>IF($G41="","",$G41/$C41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="55">
+        <f>$C41/$I41</f>
+        <v/>
+      </c>
+      <c r="K41" s="55">
+        <f>IF($F41="","",$F41/$I41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="55">
+        <f>IF($G41="","",$G41/$I41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="56">
+        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
+        <v/>
+      </c>
+      <c r="N41" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="60">
-        <f>$B41</f>
-        <v/>
-      </c>
-      <c r="D41" s="61">
-        <f>$C41/(1-Paramètres!$B$5-Paramètres!$B$6)</f>
-        <v/>
-      </c>
-      <c r="E41" s="60">
-        <f>CEILING($D41*Paramètres!$B$24,1)</f>
-        <v/>
-      </c>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="62">
-        <f>IF($F41="","",$F41-$C41-$M41-$N41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="18">
-        <f>IF($G41="","",$G41/$C41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="19" t="n">
+      <c r="O41" s="58" t="n"/>
+      <c r="P41" s="58" t="n"/>
+      <c r="Q41" s="12" t="inlineStr">
+        <is>
+          <t>Meccha Japan</t>
+        </is>
+      </c>
+      <c r="R41" s="12" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="S41" s="12" t="inlineStr">
+        <is>
+          <t>#FA429713</t>
+        </is>
+      </c>
+      <c r="T41" s="12" t="inlineStr">
+        <is>
+          <t>4521329462226</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>Compte professionnel — Leboncoin, lot de 2</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr"/>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="X41" s="4" t="n"/>
+      <c r="Y41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="60">
-        <f>$C41/$I41</f>
-        <v/>
-      </c>
-      <c r="K41" s="60">
-        <f>IF($F41="","",$F41/$I41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="60">
-        <f>IF($G41="","",$G41/$I41)</f>
-        <v/>
-      </c>
-      <c r="M41" s="61">
-        <f>IF($F41="","",$F41*(Paramètres!$B$5+Paramètres!$B$6))</f>
-        <v/>
-      </c>
-      <c r="N41" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="63" t="n"/>
-      <c r="P41" s="63" t="n"/>
-      <c r="Q41" s="21" t="inlineStr">
-        <is>
-          <t>Meccha Japan</t>
-        </is>
-      </c>
-      <c r="R41" s="21" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="S41" s="21" t="inlineStr">
-        <is>
-          <t>#FA429713</t>
-        </is>
-      </c>
-      <c r="T41" s="21" t="inlineStr">
-        <is>
-          <t>4521329462226</t>
-        </is>
-      </c>
-      <c r="U41" s="13" t="inlineStr">
-        <is>
-          <t>Retiré — achat personnel (Pokémon), jamais dans l'activité</t>
-        </is>
-      </c>
-      <c r="V41" s="13" t="inlineStr"/>
-      <c r="W41" s="13" t="inlineStr">
-        <is>
-          <t>RETIRÉ — PERSONNEL</t>
-        </is>
-      </c>
-      <c r="X41" s="13" t="inlineStr">
-        <is>
-          <t>Retiré 17/08</t>
-        </is>
-      </c>
-      <c r="Y41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="62">
+      <c r="Z41" s="57">
         <f>IF($G41="","",$G41/$Y41)</f>
         <v/>
       </c>
-      <c r="AA41" s="13">
+      <c r="AA41" s="4">
         <f>IF($Z41="","",IF($Z41&gt;=25,"atteint",TEXT(25-$Z41,"0.00")&amp;" € manquants"))</f>
         <v/>
       </c>
@@ -5317,11 +5313,11 @@
     <row r="6">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>Achats hors ADN (pompes)</t>
+          <t>Achats hors ADN (pompes, Pokémon)</t>
         </is>
       </c>
       <c r="B6" s="55" t="n">
-        <v>83.59999999999999</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="7">
@@ -5686,7 +5682,7 @@
     <row r="47">
       <c r="A47" s="45" t="inlineStr">
         <is>
-          <t>Cartes et boosters Pokémon retirés du stock professionnel le 17/08 — achetés à titre personnel dès l'origine, jamais dans l'activité (lignes 27, 41, 42 de Stock complet, coût à 0).</t>
+          <t>Cartes et boosters Pokémon retirés du stock professionnel le 17/08, puis le display Nihil Zero et les boosters Storm Emeralda réintégrés le 23/08 — vendus via le compte professionnel (lignes 27 et 41 de Stock complet). Seul le booster High Class MEGA Dream ex (ligne 42) reste prélevé, usage personnel.</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5703,7 @@
     <row r="50">
       <c r="A50" s="45" t="inlineStr">
         <is>
-          <t>Sourcing en pause depuis le 23/08 : engagement total ~2 000 € atteint, plus d'achat avant que le stock déjà là se vende davantage.</t>
+          <t>Sourcing en pause depuis le 23/08 : engagement total à 2 069,33 €, au-dessus du repère des ~2 000 € — plus d'achat avant que le stock déjà là se vende davantage.</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -3000,7 +3000,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>1 booster box Pokémon MEGA Nihil Zero (Munikis Zero) M3 — 30 boosters de 5 cartes — 2 lots de 15 à 49 €, blister à photographier avant ouverture</t>
+          <t>Display Pokémon MEGA Nihil Zero (Munikis Zero) M3 — boîte scellée, 30 boosters de 5 cartes</t>
         </is>
       </c>
       <c r="B27" s="54" t="n">
@@ -3019,7 +3019,7 @@
         <v/>
       </c>
       <c r="F27" s="57" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G27" s="57">
         <f>IF($F27="","",$F27-$C27-$M27-$N27)</f>
@@ -3030,7 +3030,7 @@
         <v/>
       </c>
       <c r="I27" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="55">
         <f>$C27/$I27</f>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="U27" s="4" t="inlineStr">
         <is>
-          <t>Compte professionnel — Leboncoin, lots de 15</t>
+          <t>Compte professionnel — Leboncoin, box entière scellée</t>
         </is>
       </c>
       <c r="V27" s="4" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="X27" s="4" t="n"/>
       <c r="Y27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z27" s="57">
         <f>IF($G27="","",$G27/$Y27)</f>
@@ -5267,7 +5267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5704,6 +5704,13 @@
       <c r="A50" s="45" t="inlineStr">
         <is>
           <t>Sourcing en pause depuis le 23/08 : engagement total à 2 069,33 €, au-dessus du repère des ~2 000 € — plus d'achat avant que le stock déjà là se vende davantage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Display Nihil Zero revu le 23/08 : vendu en une seule box scellée à 89 € (marge 8,72 €) au lieu de deux lots de 15 boosters à 49 € (marge 16,61 €) — décision du porteur du projet, pas une correction de prix de marché.</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -4975,7 +4975,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Unité centrale gaming Acer Predator G3-605 — i7-4790, 16 Go RAM DDR3, GTX 980, 1 To HDD, Windows 10, état correct</t>
         </is>
@@ -4995,7 +4995,9 @@
         <f>CEILING($D46*Paramètres!$B$24,1)</f>
         <v/>
       </c>
-      <c r="F46" s="57" t="n"/>
+      <c r="F46" s="57" t="n">
+        <v>190</v>
+      </c>
       <c r="G46" s="57">
         <f>IF($F46="","",$F46-$C46-$M46-$N46)</f>
         <v/>
@@ -5024,7 +5026,7 @@
         <v/>
       </c>
       <c r="N46" s="55" t="n">
-        <v>0</v>
+        <v>23.15</v>
       </c>
       <c r="O46" s="58" t="n">
         <v>70</v>
@@ -5060,7 +5062,7 @@
       <c r="V46" s="4" t="n"/>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>À TARIFER — livraison pas encore facturée</t>
+          <t>Normal — vendue sur eBay, commission 12% + 0,35€ incluse dans la marge</t>
         </is>
       </c>
       <c r="X46" s="4" t="n"/>
@@ -5267,7 +5269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5711,6 +5713,13 @@
       <c r="A51" t="inlineStr">
         <is>
           <t>Display Nihil Zero revu le 23/08 : vendu en une seule box scellée à 89 € (marge 8,72 €) au lieu de deux lots de 15 boosters à 49 € (marge 16,61 €) — décision du porteur du projet, pas une correction de prix de marché.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unité centrale gaming tarifée le 23/08 à 190 € sur eBay. Marge réelle 55,09 € (colonne N réutilisée pour la commission eBay réelle de 23,15 €, 12 % + 0,35 € — contrairement aux autres lignes eBay du classeur qui ne déduisent aucune commission de plateforme).</t>
         </is>
       </c>
     </row>

--- a/exports/maison-nsaia-stock.xlsx
+++ b/exports/maison-nsaia-stock.xlsx
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="B47" s="59" t="n">
-        <v>50.4</v>
+        <v>0</v>
       </c>
       <c r="C47" s="60">
         <f>$B47</f>
@@ -5158,18 +5158,18 @@
       </c>
       <c r="U47" s="13" t="inlineStr">
         <is>
-          <t>Prélevé — usage personnel</t>
+          <t>Retiré — achat personnel, jamais dans l'activité</t>
         </is>
       </c>
       <c r="V47" s="13" t="n"/>
       <c r="W47" s="13" t="inlineStr">
         <is>
-          <t>PRÉLEVÉ</t>
+          <t>RETIRÉ — PERSONNEL</t>
         </is>
       </c>
       <c r="X47" s="13" t="inlineStr">
         <is>
-          <t>PRÉLEVÉ 23/08</t>
+          <t>RETIRÉ 23/08 — jamais un achat professionnel</t>
         </is>
       </c>
       <c r="Y47" s="13" t="n">
@@ -5269,7 +5269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="B4" s="55" t="n">
-        <v>1775.95</v>
+        <v>1725.55</v>
       </c>
     </row>
     <row r="5">
@@ -5614,7 +5614,7 @@
     <row r="37">
       <c r="A37" s="39" t="inlineStr">
         <is>
-          <t>Frais de livraison de la facture FB2026-49549 encore en attente. 187,95 € de stock prélevé pour usage personnel (Hoka, Nike, pompe Robby, vidéoprojecteur).</t>
+          <t>Frais de livraison de la facture FB2026-49549 encore en attente (part unité centrale uniquement). 137,55 € de stock prélevé pour usage personnel (Hoka, Nike, pompe Robby).</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
     <row r="45">
       <c r="A45" s="45" t="inlineStr">
         <is>
-          <t>23/08 : achat FB2026-49549 — unité centrale Acer G3-605 (88,20 €, pas encore tarifée) + vidéoprojecteur Philips NeoPix 110 (50,40 €, prélevé, usage personnel).</t>
+          <t>23/08 : achat FB2026-49549 — unité centrale Acer G3-605 (88,20 €, tarifée depuis à 190 € sur eBay). Le vidéoprojecteur Philips NeoPix 110 du même bordereau (50,40 €) n'est PAS un achat professionnel : réglé avec l'argent personnel du porteur du projet — voir A53.</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
     <row r="50">
       <c r="A50" s="45" t="inlineStr">
         <is>
-          <t>Sourcing en pause depuis le 23/08 : engagement total à 2 069,33 €, au-dessus du repère des ~2 000 € — plus d'achat avant que le stock déjà là se vende davantage.</t>
+          <t>Sourcing en pause depuis le 23/08 : engagement total à 2 018,93 €, tout juste au-dessus du repère des ~2 000 € — plus d'achat avant que le stock déjà là se vende davantage.</t>
         </is>
       </c>
     </row>
@@ -5720,6 +5720,13 @@
       <c r="A52" t="inlineStr">
         <is>
           <t>Unité centrale gaming tarifée le 23/08 à 190 € sur eBay. Marge réelle 55,09 € (colonne N réutilisée pour la commission eBay réelle de 23,15 €, 12 % + 0,35 € — contrairement aux autres lignes eBay du classeur qui ne déduisent aucune commission de plateforme).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Correction du 23/08 : le vidéoprojecteur Philips NeoPix 110 n'a jamais été un achat professionnel — payé avec l'argent personnel du porteur du projet, pas celui de la société, malgré le même bordereau que l'unité centrale. Ligne 47 de Stock complet neutralisée (coût à 0). Engagement total 2 069,33 € → 2 018,93 €, apport personnel à rembourser 187,95 € → 137,55 € (3 prélèvements au lieu de 4).</t>
         </is>
       </c>
     </row>
@@ -7907,7 +7914,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Vidéoprojecteur PHILIPS NeoPix 110 noir — très bon état, testé, complet avec boîte</t>
+          <t>Vidéoprojecteur PHILIPS NeoPix 110 — RÈGLEMENT PERSONNEL, hors comptabilité pro</t>
         </is>
       </c>
       <c r="G40" s="55" t="n">
@@ -7935,19 +7942,19 @@
         </is>
       </c>
       <c r="G41" s="69">
-        <f>SUM(G5:G40)</f>
+        <f>SUM(G5:G39)</f>
         <v/>
       </c>
       <c r="H41" s="69">
-        <f>SUM(H5:H40)</f>
+        <f>SUM(H5:H39)</f>
         <v/>
       </c>
       <c r="I41" s="69">
-        <f>SUM(I5:I40)</f>
+        <f>SUM(I5:I39)</f>
         <v/>
       </c>
       <c r="J41" s="69">
-        <f>SUM(J5:J40)</f>
+        <f>SUM(J5:J39)</f>
         <v/>
       </c>
     </row>
@@ -8158,7 +8165,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Frais de livraison de la facture FB2026-49549 (unité centrale + vidéoprojecteur) pas encore reçus — à ajouter ici et dans Paramètres &gt; Livraison ADN dès réception.</t>
+          <t>Frais de livraison de la facture FB2026-49549 pas encore reçus — à ajouter ici et dans Paramètres &gt; Livraison ADN dès réception, pour la seule part attribuable à l'unité centrale (ligne 39). Le vidéoprojecteur (ligne 40) est un règlement personnel, hors comptabilité professionnelle : sa part de livraison ne concerne pas la société.</t>
         </is>
       </c>
     </row>
